--- a/artfynd/A 32240-2025 artfynd.xlsx
+++ b/artfynd/A 32240-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY145"/>
+  <dimension ref="A1:AY168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -995,32 +995,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128087528</v>
+        <v>128087541</v>
       </c>
       <c r="B5" t="n">
-        <v>80160</v>
+        <v>78787</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544198</v>
+        <v>544267</v>
       </c>
       <c r="R5" t="n">
-        <v>6963228</v>
+        <v>6963196</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,32 +1092,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128087558</v>
+        <v>128087528</v>
       </c>
       <c r="B6" t="n">
-        <v>98467</v>
+        <v>80160</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1127,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544428</v>
+        <v>544198</v>
       </c>
       <c r="R6" t="n">
-        <v>6963233</v>
+        <v>6963228</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,11 +1163,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1194,32 +1189,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128087541</v>
+        <v>128087358</v>
       </c>
       <c r="B7" t="n">
-        <v>78787</v>
+        <v>80160</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6461</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1229,10 +1224,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544267</v>
+        <v>544278</v>
       </c>
       <c r="R7" t="n">
-        <v>6963196</v>
+        <v>6963265</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1388,32 +1383,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128087358</v>
+        <v>128087558</v>
       </c>
       <c r="B9" t="n">
-        <v>80160</v>
+        <v>98467</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1423,10 +1418,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544278</v>
+        <v>544428</v>
       </c>
       <c r="R9" t="n">
-        <v>6963265</v>
+        <v>6963233</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,6 +1454,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1485,32 +1485,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128078559</v>
+        <v>128087526</v>
       </c>
       <c r="B10" t="n">
-        <v>97344</v>
+        <v>92631</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544359</v>
+        <v>544728</v>
       </c>
       <c r="R10" t="n">
-        <v>6963083</v>
+        <v>6963223</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,6 +1556,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>10 exemplar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1582,10 +1587,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128087526</v>
+        <v>128087516</v>
       </c>
       <c r="B11" t="n">
-        <v>92631</v>
+        <v>57672</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1593,21 +1598,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4361</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1617,10 +1622,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544728</v>
+        <v>544388</v>
       </c>
       <c r="R11" t="n">
-        <v>6963223</v>
+        <v>6963226</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1657,7 +1662,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>10 exemplar</t>
+          <t>Ringhack av tretåig hackspett på Tall Äldre spår</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1684,32 +1689,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128087516</v>
+        <v>128078559</v>
       </c>
       <c r="B12" t="n">
-        <v>57672</v>
+        <v>97344</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1719,10 +1724,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544388</v>
+        <v>544359</v>
       </c>
       <c r="R12" t="n">
-        <v>6963226</v>
+        <v>6963083</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1755,11 +1760,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall Äldre spår</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1786,10 +1786,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128087324</v>
+        <v>128087520</v>
       </c>
       <c r="B13" t="n">
-        <v>57672</v>
+        <v>57832</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1797,21 +1797,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544792</v>
+        <v>544771</v>
       </c>
       <c r="R13" t="n">
-        <v>6963047</v>
+        <v>6963083</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>2 stycken.  Övriga läten</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1888,32 +1888,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128087323</v>
+        <v>128087347</v>
       </c>
       <c r="B14" t="n">
-        <v>57672</v>
+        <v>80161</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1923,10 +1923,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544646</v>
+        <v>544745</v>
       </c>
       <c r="R14" t="n">
-        <v>6963095</v>
+        <v>6963195</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1959,11 +1959,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2087,32 +2082,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128087347</v>
+        <v>128087323</v>
       </c>
       <c r="B16" t="n">
-        <v>80161</v>
+        <v>57672</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2122,10 +2117,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544745</v>
+        <v>544646</v>
       </c>
       <c r="R16" t="n">
-        <v>6963195</v>
+        <v>6963095</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2158,6 +2153,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2184,32 +2184,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128087550</v>
+        <v>128087324</v>
       </c>
       <c r="B17" t="n">
-        <v>98467</v>
+        <v>57672</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544490</v>
+        <v>544792</v>
       </c>
       <c r="R17" t="n">
-        <v>6963099</v>
+        <v>6963047</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2286,32 +2286,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128087520</v>
+        <v>128087550</v>
       </c>
       <c r="B18" t="n">
-        <v>57832</v>
+        <v>98467</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544771</v>
+        <v>544490</v>
       </c>
       <c r="R18" t="n">
-        <v>6963083</v>
+        <v>6963099</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2 stycken.  Övriga läten</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2485,32 +2485,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128087554</v>
+        <v>128087362</v>
       </c>
       <c r="B20" t="n">
-        <v>98467</v>
+        <v>80132</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544659</v>
+        <v>544799</v>
       </c>
       <c r="R20" t="n">
-        <v>6963253</v>
+        <v>6963263</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2556,11 +2556,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2587,32 +2582,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128087569</v>
+        <v>128087349</v>
       </c>
       <c r="B21" t="n">
-        <v>98467</v>
+        <v>80161</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2622,10 +2617,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544296</v>
+        <v>544475</v>
       </c>
       <c r="R21" t="n">
-        <v>6963084</v>
+        <v>6963205</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2658,11 +2653,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>100stycken</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2786,32 +2776,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128087349</v>
+        <v>128087359</v>
       </c>
       <c r="B23" t="n">
-        <v>80161</v>
+        <v>78788</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2821,10 +2811,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544475</v>
+        <v>544741</v>
       </c>
       <c r="R23" t="n">
-        <v>6963205</v>
+        <v>6963165</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2883,32 +2873,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128087362</v>
+        <v>128087569</v>
       </c>
       <c r="B24" t="n">
-        <v>80132</v>
+        <v>98467</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2918,10 +2908,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544799</v>
+        <v>544296</v>
       </c>
       <c r="R24" t="n">
-        <v>6963263</v>
+        <v>6963084</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2954,6 +2944,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>100stycken</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2980,32 +2975,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128087359</v>
+        <v>128087554</v>
       </c>
       <c r="B25" t="n">
-        <v>78788</v>
+        <v>98467</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3015,10 +3010,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544741</v>
+        <v>544659</v>
       </c>
       <c r="R25" t="n">
-        <v>6963165</v>
+        <v>6963253</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3051,6 +3046,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3077,49 +3077,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128078161</v>
+        <v>128087382</v>
       </c>
       <c r="B26" t="n">
-        <v>98467</v>
+        <v>92639</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>544362</v>
+        <v>544198</v>
       </c>
       <c r="R26" t="n">
-        <v>6963061</v>
+        <v>6963225</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3152,6 +3148,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3178,49 +3179,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128078740</v>
+        <v>128087532</v>
       </c>
       <c r="B27" t="n">
-        <v>98467</v>
+        <v>80132</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544307</v>
+        <v>544491</v>
       </c>
       <c r="R27" t="n">
-        <v>6963089</v>
+        <v>6963099</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3279,7 +3276,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128087333</v>
+        <v>128087331</v>
       </c>
       <c r="B28" t="n">
         <v>57672</v>
@@ -3314,10 +3311,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544355</v>
+        <v>544763</v>
       </c>
       <c r="R28" t="n">
-        <v>6963212</v>
+        <v>6963244</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3381,7 +3378,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128087331</v>
+        <v>128087333</v>
       </c>
       <c r="B29" t="n">
         <v>57672</v>
@@ -3416,10 +3413,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544763</v>
+        <v>544355</v>
       </c>
       <c r="R29" t="n">
-        <v>6963244</v>
+        <v>6963212</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3483,32 +3480,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128087382</v>
+        <v>128087562</v>
       </c>
       <c r="B30" t="n">
-        <v>92639</v>
+        <v>98467</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3518,10 +3515,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>544198</v>
+        <v>544367</v>
       </c>
       <c r="R30" t="n">
-        <v>6963225</v>
+        <v>6963253</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3558,7 +3555,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>5 ex</t>
+          <t>7. Kan möjlitvis finnas fler runt omkring.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3585,7 +3582,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128087562</v>
+        <v>128078161</v>
       </c>
       <c r="B31" t="n">
         <v>98467</v>
@@ -3613,17 +3610,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>544367</v>
+        <v>544362</v>
       </c>
       <c r="R31" t="n">
-        <v>6963253</v>
+        <v>6963061</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3656,11 +3657,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>7. Kan möjlitvis finnas fler runt omkring.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3687,7 +3683,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128087563</v>
+        <v>128078740</v>
       </c>
       <c r="B32" t="n">
         <v>98467</v>
@@ -3715,17 +3711,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544322</v>
+        <v>544307</v>
       </c>
       <c r="R32" t="n">
-        <v>6963250</v>
+        <v>6963089</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3758,11 +3758,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>12 stycken</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3789,32 +3784,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128087532</v>
+        <v>128087563</v>
       </c>
       <c r="B33" t="n">
-        <v>80132</v>
+        <v>98467</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3824,10 +3819,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>544491</v>
+        <v>544322</v>
       </c>
       <c r="R33" t="n">
-        <v>6963099</v>
+        <v>6963250</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3860,6 +3855,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>12 stycken</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3886,7 +3886,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128087365</v>
+        <v>128079621</v>
       </c>
       <c r="B34" t="n">
         <v>80132</v>
@@ -3921,10 +3921,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>544469</v>
+        <v>544274</v>
       </c>
       <c r="R34" t="n">
-        <v>6963145</v>
+        <v>6963119</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3983,32 +3983,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128087351</v>
+        <v>128087533</v>
       </c>
       <c r="B35" t="n">
-        <v>80161</v>
+        <v>80132</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4018,10 +4018,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>544299</v>
+        <v>544473</v>
       </c>
       <c r="R35" t="n">
-        <v>6963312</v>
+        <v>6963102</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4080,32 +4080,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128087336</v>
+        <v>128087351</v>
       </c>
       <c r="B36" t="n">
-        <v>57672</v>
+        <v>80161</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4115,10 +4115,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>544398</v>
+        <v>544299</v>
       </c>
       <c r="R36" t="n">
-        <v>6963202</v>
+        <v>6963312</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4151,11 +4151,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4182,7 +4177,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128087533</v>
+        <v>128087365</v>
       </c>
       <c r="B37" t="n">
         <v>80132</v>
@@ -4217,10 +4212,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>544473</v>
+        <v>544469</v>
       </c>
       <c r="R37" t="n">
-        <v>6963102</v>
+        <v>6963145</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4279,10 +4274,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128079621</v>
+        <v>128087336</v>
       </c>
       <c r="B38" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4290,21 +4285,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4314,10 +4309,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>544274</v>
+        <v>544398</v>
       </c>
       <c r="R38" t="n">
-        <v>6963119</v>
+        <v>6963202</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4350,6 +4345,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4575,32 +4575,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128087527</v>
+        <v>128087517</v>
       </c>
       <c r="B41" t="n">
-        <v>80160</v>
+        <v>57672</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4610,10 +4610,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>544246</v>
+        <v>544381</v>
       </c>
       <c r="R41" t="n">
-        <v>6963259</v>
+        <v>6963236</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4646,6 +4646,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall Äldre ringhack som återanvänds ( äldre och färska)</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4774,32 +4779,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128087517</v>
+        <v>128087527</v>
       </c>
       <c r="B43" t="n">
-        <v>57672</v>
+        <v>80160</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4809,10 +4814,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>544381</v>
+        <v>544246</v>
       </c>
       <c r="R43" t="n">
-        <v>6963236</v>
+        <v>6963259</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4845,11 +4850,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall Äldre ringhack som återanvänds ( äldre och färska)</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4876,32 +4876,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128079768</v>
+        <v>128087361</v>
       </c>
       <c r="B44" t="n">
-        <v>97350</v>
+        <v>80132</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221941</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4911,10 +4911,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>544287</v>
+        <v>544865</v>
       </c>
       <c r="R44" t="n">
-        <v>6963168</v>
+        <v>6963092</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4973,7 +4973,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128087361</v>
+        <v>128087360</v>
       </c>
       <c r="B45" t="n">
         <v>80132</v>
@@ -5008,10 +5008,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>544865</v>
+        <v>544615</v>
       </c>
       <c r="R45" t="n">
-        <v>6963092</v>
+        <v>6963093</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5070,10 +5070,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128087360</v>
+        <v>128087340</v>
       </c>
       <c r="B46" t="n">
-        <v>80132</v>
+        <v>57832</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5081,21 +5081,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5105,10 +5105,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>544615</v>
+        <v>544485</v>
       </c>
       <c r="R46" t="n">
-        <v>6963093</v>
+        <v>6963237</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5167,32 +5167,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128087340</v>
+        <v>128079768</v>
       </c>
       <c r="B47" t="n">
-        <v>57832</v>
+        <v>97350</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>221941</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5202,10 +5202,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>544485</v>
+        <v>544287</v>
       </c>
       <c r="R47" t="n">
-        <v>6963237</v>
+        <v>6963168</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5468,10 +5468,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128079839</v>
+        <v>128087342</v>
       </c>
       <c r="B50" t="n">
-        <v>105505</v>
+        <v>80161</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5479,21 +5479,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221144</v>
+        <v>6462</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5503,10 +5503,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>544288</v>
+        <v>544848</v>
       </c>
       <c r="R50" t="n">
-        <v>6963182</v>
+        <v>6963086</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5565,10 +5565,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128087339</v>
+        <v>128087367</v>
       </c>
       <c r="B51" t="n">
-        <v>57832</v>
+        <v>80132</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5576,21 +5576,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5600,10 +5600,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>544850</v>
+        <v>544298</v>
       </c>
       <c r="R51" t="n">
-        <v>6963099</v>
+        <v>6963312</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5636,11 +5636,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5667,7 +5662,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128087367</v>
+        <v>128087364</v>
       </c>
       <c r="B52" t="n">
         <v>80132</v>
@@ -5702,10 +5697,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>544298</v>
+        <v>544774</v>
       </c>
       <c r="R52" t="n">
-        <v>6963312</v>
+        <v>6963282</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5764,10 +5759,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128087342</v>
+        <v>128079839</v>
       </c>
       <c r="B53" t="n">
-        <v>80161</v>
+        <v>105505</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5775,21 +5770,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6462</v>
+        <v>221144</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5799,10 +5794,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>544848</v>
+        <v>544288</v>
       </c>
       <c r="R53" t="n">
-        <v>6963086</v>
+        <v>6963182</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5861,32 +5856,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128087364</v>
+        <v>128087553</v>
       </c>
       <c r="B54" t="n">
-        <v>80132</v>
+        <v>98467</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5896,10 +5891,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>544774</v>
+        <v>544677</v>
       </c>
       <c r="R54" t="n">
-        <v>6963282</v>
+        <v>6963260</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5932,6 +5927,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Mer än 70 stycken. Flera blommar</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5958,32 +5958,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128087555</v>
+        <v>128087339</v>
       </c>
       <c r="B55" t="n">
-        <v>98467</v>
+        <v>57832</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5993,10 +5993,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>544623</v>
+        <v>544850</v>
       </c>
       <c r="R55" t="n">
-        <v>6963241</v>
+        <v>6963099</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6033,7 +6033,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>60 stycken</t>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6060,7 +6060,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128087553</v>
+        <v>128087555</v>
       </c>
       <c r="B56" t="n">
         <v>98467</v>
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>544677</v>
+        <v>544623</v>
       </c>
       <c r="R56" t="n">
-        <v>6963260</v>
+        <v>6963241</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Mer än 70 stycken. Flera blommar</t>
+          <t>60 stycken</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6162,50 +6162,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128080012</v>
+        <v>128087585</v>
       </c>
       <c r="B57" t="n">
-        <v>57672</v>
+        <v>92639</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>544324</v>
+        <v>544536</v>
       </c>
       <c r="R57" t="n">
-        <v>6963220</v>
+        <v>6963255</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6242,7 +6237,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>8 äldre ex9 färska fruktkroppar</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6463,45 +6458,50 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128087585</v>
+        <v>128080012</v>
       </c>
       <c r="B60" t="n">
-        <v>92639</v>
+        <v>57672</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>544536</v>
+        <v>544324</v>
       </c>
       <c r="R60" t="n">
-        <v>6963255</v>
+        <v>6963220</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>8 äldre ex9 färska fruktkroppar</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6565,32 +6565,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128087386</v>
+        <v>128087375</v>
       </c>
       <c r="B61" t="n">
-        <v>92633</v>
+        <v>98467</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4362</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6600,10 +6600,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>544822</v>
+        <v>544478</v>
       </c>
       <c r="R61" t="n">
-        <v>6963295</v>
+        <v>6963117</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6636,6 +6636,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6662,32 +6667,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128087378</v>
+        <v>128087579</v>
       </c>
       <c r="B62" t="n">
-        <v>98467</v>
+        <v>79029</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6697,10 +6702,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>544218</v>
+        <v>544204</v>
       </c>
       <c r="R62" t="n">
-        <v>6963229</v>
+        <v>6963238</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6737,7 +6742,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>80 ex</t>
+          <t>Riklig förekomst av garnlav</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6764,32 +6769,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128087329</v>
+        <v>128087523</v>
       </c>
       <c r="B63" t="n">
-        <v>57672</v>
+        <v>80161</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6799,10 +6804,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>544757</v>
+        <v>544253</v>
       </c>
       <c r="R63" t="n">
-        <v>6963172</v>
+        <v>6963139</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6835,11 +6840,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6866,32 +6866,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128087377</v>
+        <v>128087386</v>
       </c>
       <c r="B64" t="n">
-        <v>98467</v>
+        <v>92633</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>4362</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6901,10 +6901,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>544403</v>
+        <v>544822</v>
       </c>
       <c r="R64" t="n">
-        <v>6963221</v>
+        <v>6963295</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6937,11 +6937,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>20 ex</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6968,32 +6963,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128087375</v>
+        <v>128078603</v>
       </c>
       <c r="B65" t="n">
-        <v>98467</v>
+        <v>80161</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7003,10 +6998,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>544478</v>
+        <v>544360</v>
       </c>
       <c r="R65" t="n">
-        <v>6963117</v>
+        <v>6963094</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7039,11 +7034,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>35 ex</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7070,32 +7060,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128078603</v>
+        <v>128087329</v>
       </c>
       <c r="B66" t="n">
-        <v>80161</v>
+        <v>57672</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7105,10 +7095,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>544360</v>
+        <v>544757</v>
       </c>
       <c r="R66" t="n">
-        <v>6963094</v>
+        <v>6963172</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7141,6 +7131,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7264,32 +7259,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128087523</v>
+        <v>128087566</v>
       </c>
       <c r="B68" t="n">
-        <v>80161</v>
+        <v>98467</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7299,10 +7294,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>544253</v>
+        <v>544261</v>
       </c>
       <c r="R68" t="n">
-        <v>6963139</v>
+        <v>6963170</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7335,6 +7330,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>4. Stycken. Finns möjligtvis fler i blåbärsriset.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7361,32 +7361,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128087579</v>
+        <v>128087377</v>
       </c>
       <c r="B69" t="n">
-        <v>79029</v>
+        <v>98467</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7396,10 +7396,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>544204</v>
+        <v>544403</v>
       </c>
       <c r="R69" t="n">
-        <v>6963238</v>
+        <v>6963221</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Riklig förekomst av garnlav</t>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7463,7 +7463,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128087566</v>
+        <v>128087378</v>
       </c>
       <c r="B70" t="n">
         <v>98467</v>
@@ -7498,10 +7498,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>544261</v>
+        <v>544218</v>
       </c>
       <c r="R70" t="n">
-        <v>6963170</v>
+        <v>6963229</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>4. Stycken. Finns möjligtvis fler i blåbärsriset.</t>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7565,10 +7565,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128080149</v>
+        <v>128087366</v>
       </c>
       <c r="B71" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7576,39 +7576,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>544295</v>
+        <v>544407</v>
       </c>
       <c r="R71" t="n">
-        <v>6963226</v>
+        <v>6963184</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7641,11 +7636,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7672,10 +7662,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128080054</v>
+        <v>128087537</v>
       </c>
       <c r="B72" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7683,39 +7673,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>544301</v>
+        <v>544205</v>
       </c>
       <c r="R72" t="n">
-        <v>6963231</v>
+        <v>6963241</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7748,11 +7733,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7779,7 +7759,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128080035</v>
+        <v>128087337</v>
       </c>
       <c r="B73" t="n">
         <v>57672</v>
@@ -7808,21 +7788,16 @@
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>544340</v>
+        <v>544197</v>
       </c>
       <c r="R73" t="n">
-        <v>6963223</v>
+        <v>6963237</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7859,7 +7834,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7886,7 +7861,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128087337</v>
+        <v>128080035</v>
       </c>
       <c r="B74" t="n">
         <v>57672</v>
@@ -7915,16 +7890,21 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>544197</v>
+        <v>544340</v>
       </c>
       <c r="R74" t="n">
-        <v>6963237</v>
+        <v>6963223</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7961,7 +7941,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7988,10 +7968,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128087366</v>
+        <v>128080054</v>
       </c>
       <c r="B75" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7999,34 +7979,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>544407</v>
+        <v>544301</v>
       </c>
       <c r="R75" t="n">
-        <v>6963184</v>
+        <v>6963231</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8059,6 +8044,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8085,10 +8075,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128087537</v>
+        <v>128080149</v>
       </c>
       <c r="B76" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8096,34 +8086,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>544205</v>
+        <v>544295</v>
       </c>
       <c r="R76" t="n">
-        <v>6963241</v>
+        <v>6963226</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8156,6 +8151,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8182,32 +8182,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128087346</v>
+        <v>128087330</v>
       </c>
       <c r="B77" t="n">
-        <v>80161</v>
+        <v>57672</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8217,10 +8217,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>544422</v>
+        <v>544750</v>
       </c>
       <c r="R77" t="n">
-        <v>6963240</v>
+        <v>6963177</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8253,6 +8253,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8279,7 +8284,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128087330</v>
+        <v>128087335</v>
       </c>
       <c r="B78" t="n">
         <v>57672</v>
@@ -8314,10 +8319,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>544750</v>
+        <v>544366</v>
       </c>
       <c r="R78" t="n">
-        <v>6963177</v>
+        <v>6963181</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8381,7 +8386,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128087343</v>
+        <v>128087346</v>
       </c>
       <c r="B79" t="n">
         <v>80161</v>
@@ -8416,10 +8421,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>544757</v>
+        <v>544422</v>
       </c>
       <c r="R79" t="n">
-        <v>6963156</v>
+        <v>6963240</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8478,7 +8483,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128078492</v>
+        <v>128087575</v>
       </c>
       <c r="B80" t="n">
         <v>92671</v>
@@ -8513,10 +8518,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>544362</v>
+        <v>544532</v>
       </c>
       <c r="R80" t="n">
-        <v>6963073</v>
+        <v>6963250</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8549,6 +8554,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Igen stor köttig svamp misstänker grantaggsvamp 2 ex</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8575,10 +8585,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128087335</v>
+        <v>128078492</v>
       </c>
       <c r="B81" t="n">
-        <v>57672</v>
+        <v>92671</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8586,21 +8596,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>1968</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8610,10 +8620,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>544366</v>
+        <v>544362</v>
       </c>
       <c r="R81" t="n">
-        <v>6963181</v>
+        <v>6963073</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8646,11 +8656,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8677,32 +8682,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128087380</v>
+        <v>128087536</v>
       </c>
       <c r="B82" t="n">
-        <v>105505</v>
+        <v>80132</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221144</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8712,10 +8717,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>544468</v>
+        <v>544215</v>
       </c>
       <c r="R82" t="n">
-        <v>6963173</v>
+        <v>6963245</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8774,32 +8779,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128087560</v>
+        <v>128087343</v>
       </c>
       <c r="B83" t="n">
-        <v>98467</v>
+        <v>80161</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8809,10 +8814,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>544383</v>
+        <v>544757</v>
       </c>
       <c r="R83" t="n">
-        <v>6963236</v>
+        <v>6963156</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8845,11 +8850,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8876,32 +8876,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128087542</v>
+        <v>128087570</v>
       </c>
       <c r="B84" t="n">
-        <v>98467</v>
+        <v>56855</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8911,10 +8911,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>544752</v>
+        <v>544287</v>
       </c>
       <c r="R84" t="n">
-        <v>6963192</v>
+        <v>6963082</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>40 stycken</t>
+          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8978,32 +8978,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128087547</v>
+        <v>128087380</v>
       </c>
       <c r="B85" t="n">
-        <v>98467</v>
+        <v>105505</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9013,10 +9013,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>544380</v>
+        <v>544468</v>
       </c>
       <c r="R85" t="n">
-        <v>6963236</v>
+        <v>6963173</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9049,11 +9049,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>33 stycken</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9080,45 +9075,49 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128087570</v>
+        <v>128079875</v>
       </c>
       <c r="B86" t="n">
-        <v>56855</v>
+        <v>98467</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>544287</v>
+        <v>544308</v>
       </c>
       <c r="R86" t="n">
-        <v>6963082</v>
+        <v>6963175</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9151,11 +9150,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9182,32 +9176,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128087536</v>
+        <v>128087542</v>
       </c>
       <c r="B87" t="n">
-        <v>80132</v>
+        <v>98467</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9217,10 +9211,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>544215</v>
+        <v>544752</v>
       </c>
       <c r="R87" t="n">
-        <v>6963245</v>
+        <v>6963192</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9253,6 +9247,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9279,45 +9278,49 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128087575</v>
+        <v>128080338</v>
       </c>
       <c r="B88" t="n">
-        <v>92671</v>
+        <v>98467</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1968</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>544532</v>
+        <v>544314</v>
       </c>
       <c r="R88" t="n">
-        <v>6963250</v>
+        <v>6963248</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9350,11 +9353,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Igen stor köttig svamp misstänker grantaggsvamp 2 ex</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9381,7 +9379,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128079875</v>
+        <v>128087547</v>
       </c>
       <c r="B89" t="n">
         <v>98467</v>
@@ -9409,21 +9407,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>544308</v>
+        <v>544380</v>
       </c>
       <c r="R89" t="n">
-        <v>6963175</v>
+        <v>6963236</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9456,6 +9450,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>33 stycken</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9482,7 +9481,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128080338</v>
+        <v>128087560</v>
       </c>
       <c r="B90" t="n">
         <v>98467</v>
@@ -9510,21 +9509,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>544314</v>
+        <v>544383</v>
       </c>
       <c r="R90" t="n">
-        <v>6963248</v>
+        <v>6963236</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9557,6 +9552,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9583,32 +9583,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128087376</v>
+        <v>128087587</v>
       </c>
       <c r="B91" t="n">
-        <v>98467</v>
+        <v>92639</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9618,10 +9618,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>544503</v>
+        <v>544245</v>
       </c>
       <c r="R91" t="n">
-        <v>6963182</v>
+        <v>6963255</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9658,7 +9658,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>60 ex</t>
+          <t>4stycken</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9685,32 +9685,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128087379</v>
+        <v>128087539</v>
       </c>
       <c r="B92" t="n">
-        <v>98467</v>
+        <v>80132</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9720,10 +9720,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>544263</v>
+        <v>544254</v>
       </c>
       <c r="R92" t="n">
-        <v>6963254</v>
+        <v>6963139</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9756,11 +9756,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>15 ex</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9884,32 +9879,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128087539</v>
+        <v>128087376</v>
       </c>
       <c r="B94" t="n">
-        <v>80132</v>
+        <v>98467</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9919,10 +9914,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>544254</v>
+        <v>544503</v>
       </c>
       <c r="R94" t="n">
-        <v>6963139</v>
+        <v>6963182</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9955,6 +9950,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>60 ex</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9981,32 +9981,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128087587</v>
+        <v>128087379</v>
       </c>
       <c r="B95" t="n">
-        <v>92639</v>
+        <v>98467</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10016,10 +10016,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>544245</v>
+        <v>544263</v>
       </c>
       <c r="R95" t="n">
-        <v>6963255</v>
+        <v>6963254</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10056,7 +10056,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>4stycken</t>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10083,10 +10083,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128087363</v>
+        <v>128087522</v>
       </c>
       <c r="B96" t="n">
-        <v>80132</v>
+        <v>57832</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10094,21 +10094,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10118,10 +10118,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>544818</v>
+        <v>544494</v>
       </c>
       <c r="R96" t="n">
-        <v>6963278</v>
+        <v>6963243</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10180,7 +10180,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128087384</v>
+        <v>128087383</v>
       </c>
       <c r="B97" t="n">
         <v>80167</v>
@@ -10215,10 +10215,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>544584</v>
+        <v>544566</v>
       </c>
       <c r="R97" t="n">
-        <v>6963261</v>
+        <v>6963076</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10277,10 +10277,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128087355</v>
+        <v>128087384</v>
       </c>
       <c r="B98" t="n">
-        <v>97350</v>
+        <v>80167</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10288,21 +10288,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>221941</v>
+        <v>6463</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10312,10 +10312,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>544500</v>
+        <v>544584</v>
       </c>
       <c r="R98" t="n">
-        <v>6963168</v>
+        <v>6963261</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10374,32 +10374,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128087373</v>
+        <v>128087576</v>
       </c>
       <c r="B99" t="n">
-        <v>98467</v>
+        <v>92671</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>1968</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10409,10 +10409,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>544469</v>
+        <v>544529</v>
       </c>
       <c r="R99" t="n">
-        <v>6963122</v>
+        <v>6963245</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10449,7 +10449,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>60 ex</t>
+          <t>Misstänkt grantaggsvamp men med mörk tydlig ring i mitten.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10476,32 +10476,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128087383</v>
+        <v>128087572</v>
       </c>
       <c r="B100" t="n">
-        <v>80167</v>
+        <v>92671</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6463</v>
+        <v>1968</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10511,10 +10511,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>544566</v>
+        <v>544632</v>
       </c>
       <c r="R100" t="n">
-        <v>6963076</v>
+        <v>6963245</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10547,6 +10547,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>1 ex</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10573,32 +10578,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128087556</v>
+        <v>128087363</v>
       </c>
       <c r="B101" t="n">
-        <v>98467</v>
+        <v>80132</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10608,10 +10613,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>544594</v>
+        <v>544818</v>
       </c>
       <c r="R101" t="n">
-        <v>6963215</v>
+        <v>6963278</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10644,11 +10649,6 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>6 stycken. Kan finnas mer i omgivningen</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10675,32 +10675,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128087572</v>
+        <v>128078864</v>
       </c>
       <c r="B102" t="n">
-        <v>92671</v>
+        <v>105505</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1968</v>
+        <v>221144</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10710,10 +10710,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>544632</v>
+        <v>544307</v>
       </c>
       <c r="R102" t="n">
-        <v>6963245</v>
+        <v>6963089</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10746,11 +10746,6 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>1 ex</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10777,32 +10772,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128087545</v>
+        <v>128087355</v>
       </c>
       <c r="B103" t="n">
-        <v>98467</v>
+        <v>97350</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10812,10 +10807,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>544633</v>
+        <v>544500</v>
       </c>
       <c r="R103" t="n">
-        <v>6963244</v>
+        <v>6963168</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10848,11 +10843,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10879,32 +10869,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128087576</v>
+        <v>128087545</v>
       </c>
       <c r="B104" t="n">
-        <v>92671</v>
+        <v>98467</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1968</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10914,10 +10904,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>544529</v>
+        <v>544633</v>
       </c>
       <c r="R104" t="n">
-        <v>6963245</v>
+        <v>6963244</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10954,7 +10944,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Misstänkt grantaggsvamp men med mörk tydlig ring i mitten.</t>
+          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11083,7 +11073,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128087559</v>
+        <v>128087556</v>
       </c>
       <c r="B106" t="n">
         <v>98467</v>
@@ -11118,10 +11108,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>544396</v>
+        <v>544594</v>
       </c>
       <c r="R106" t="n">
-        <v>6963233</v>
+        <v>6963215</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11158,7 +11148,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>18 stycken</t>
+          <t>6 stycken. Kan finnas mer i omgivningen</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11185,32 +11175,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128087522</v>
+        <v>128087373</v>
       </c>
       <c r="B107" t="n">
-        <v>57832</v>
+        <v>98467</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11220,10 +11210,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>544494</v>
+        <v>544469</v>
       </c>
       <c r="R107" t="n">
-        <v>6963243</v>
+        <v>6963122</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11256,6 +11246,11 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>60 ex</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11282,32 +11277,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128078864</v>
+        <v>128087559</v>
       </c>
       <c r="B108" t="n">
-        <v>105505</v>
+        <v>98467</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11317,10 +11312,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>544307</v>
+        <v>544396</v>
       </c>
       <c r="R108" t="n">
-        <v>6963089</v>
+        <v>6963233</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11353,6 +11348,11 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11379,7 +11379,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128087372</v>
+        <v>128079656</v>
       </c>
       <c r="B109" t="n">
         <v>98467</v>
@@ -11407,17 +11407,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>544472</v>
+        <v>544277</v>
       </c>
       <c r="R109" t="n">
-        <v>6963201</v>
+        <v>6963150</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11450,11 +11454,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>8 ex</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11481,7 +11480,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128079656</v>
+        <v>128087565</v>
       </c>
       <c r="B110" t="n">
         <v>98467</v>
@@ -11509,21 +11508,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>544277</v>
+        <v>544249</v>
       </c>
       <c r="R110" t="n">
-        <v>6963150</v>
+        <v>6963223</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11556,6 +11551,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>10. Kan möjlitvis finns mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11582,7 +11582,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128087551</v>
+        <v>128087372</v>
       </c>
       <c r="B111" t="n">
         <v>98467</v>
@@ -11617,10 +11617,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>544694</v>
+        <v>544472</v>
       </c>
       <c r="R111" t="n">
-        <v>6963258</v>
+        <v>6963201</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11657,7 +11657,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11684,7 +11684,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128087565</v>
+        <v>128087551</v>
       </c>
       <c r="B112" t="n">
         <v>98467</v>
@@ -11719,10 +11719,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>544249</v>
+        <v>544694</v>
       </c>
       <c r="R112" t="n">
-        <v>6963223</v>
+        <v>6963258</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11759,7 +11759,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>10. Kan möjlitvis finns mer i blåbärsriset</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11883,10 +11883,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128087586</v>
+        <v>128087531</v>
       </c>
       <c r="B114" t="n">
-        <v>92639</v>
+        <v>98501</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11894,21 +11894,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>4364</v>
+        <v>219874</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11918,10 +11918,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>544281</v>
+        <v>544755</v>
       </c>
       <c r="R114" t="n">
-        <v>6963257</v>
+        <v>6963130</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11958,7 +11958,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>2 nya exemplar 8 äldre ex</t>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11985,32 +11985,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128087577</v>
+        <v>128087586</v>
       </c>
       <c r="B115" t="n">
-        <v>92671</v>
+        <v>92639</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1968</v>
+        <v>4364</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12020,10 +12020,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>544494</v>
+        <v>544281</v>
       </c>
       <c r="R115" t="n">
-        <v>6963243</v>
+        <v>6963257</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12056,6 +12056,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>2 nya exemplar 8 äldre ex</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12082,32 +12087,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128087531</v>
+        <v>128087577</v>
       </c>
       <c r="B116" t="n">
-        <v>98501</v>
+        <v>92671</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>219874</v>
+        <v>1968</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12117,10 +12122,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>544755</v>
+        <v>544494</v>
       </c>
       <c r="R116" t="n">
-        <v>6963130</v>
+        <v>6963243</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12153,11 +12158,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12184,32 +12184,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128087571</v>
+        <v>128079848</v>
       </c>
       <c r="B117" t="n">
-        <v>92671</v>
+        <v>79053</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1968</v>
+        <v>6434</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12219,10 +12219,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>544679</v>
+        <v>544288</v>
       </c>
       <c r="R117" t="n">
-        <v>6963259</v>
+        <v>6963182</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12255,11 +12255,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Misstänker grantaggsvamp. 14 exemplar</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12286,10 +12281,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128087535</v>
+        <v>128078823</v>
       </c>
       <c r="B118" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12297,21 +12292,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12321,10 +12316,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>544312</v>
+        <v>544307</v>
       </c>
       <c r="R118" t="n">
-        <v>6963244</v>
+        <v>6963089</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12383,10 +12378,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128087538</v>
+        <v>128087571</v>
       </c>
       <c r="B119" t="n">
-        <v>80132</v>
+        <v>92671</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12394,21 +12389,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6458</v>
+        <v>1968</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12418,10 +12413,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>544262</v>
+        <v>544679</v>
       </c>
       <c r="R119" t="n">
-        <v>6963163</v>
+        <v>6963259</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12454,6 +12449,11 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Misstänker grantaggsvamp. 14 exemplar</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12480,32 +12480,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128087582</v>
+        <v>128087573</v>
       </c>
       <c r="B120" t="n">
-        <v>98384</v>
+        <v>92671</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>219790</v>
+        <v>1968</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12515,10 +12515,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>544489</v>
+        <v>544684</v>
       </c>
       <c r="R120" t="n">
-        <v>6963098</v>
+        <v>6963253</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12551,6 +12551,11 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Mörkt exemplar med vit yttre ring.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12577,10 +12582,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128087573</v>
+        <v>128087538</v>
       </c>
       <c r="B121" t="n">
-        <v>92671</v>
+        <v>80132</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12588,21 +12593,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1968</v>
+        <v>6458</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12612,10 +12617,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>544684</v>
+        <v>544262</v>
       </c>
       <c r="R121" t="n">
-        <v>6963253</v>
+        <v>6963163</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12648,11 +12653,6 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Mörkt exemplar med vit yttre ring.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12679,10 +12679,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128078823</v>
+        <v>128087535</v>
       </c>
       <c r="B122" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12690,21 +12690,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12714,10 +12714,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>544307</v>
+        <v>544312</v>
       </c>
       <c r="R122" t="n">
-        <v>6963089</v>
+        <v>6963244</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12776,49 +12776,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128079571</v>
+        <v>128087582</v>
       </c>
       <c r="B123" t="n">
-        <v>98467</v>
+        <v>98384</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>544274</v>
+        <v>544489</v>
       </c>
       <c r="R123" t="n">
-        <v>6963119</v>
+        <v>6963098</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12877,7 +12873,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128078138</v>
+        <v>128079571</v>
       </c>
       <c r="B124" t="n">
         <v>98467</v>
@@ -12907,7 +12903,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>400</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -12916,10 +12912,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>544374</v>
+        <v>544274</v>
       </c>
       <c r="R124" t="n">
-        <v>6963056</v>
+        <v>6963119</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12978,45 +12974,49 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128079848</v>
+        <v>128078138</v>
       </c>
       <c r="B125" t="n">
-        <v>79053</v>
+        <v>98467</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6434</v>
+        <v>220787</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>544288</v>
+        <v>544374</v>
       </c>
       <c r="R125" t="n">
-        <v>6963182</v>
+        <v>6963056</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13075,7 +13075,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128087583</v>
+        <v>128087584</v>
       </c>
       <c r="B126" t="n">
         <v>98384</v>
@@ -13110,10 +13110,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>544708</v>
+        <v>544718</v>
       </c>
       <c r="R126" t="n">
-        <v>6963086</v>
+        <v>6963053</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13150,7 +13150,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3 stycken</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13177,32 +13177,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128087574</v>
+        <v>128087583</v>
       </c>
       <c r="B127" t="n">
-        <v>92671</v>
+        <v>98384</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1968</v>
+        <v>219790</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13212,10 +13212,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>544552</v>
+        <v>544708</v>
       </c>
       <c r="R127" t="n">
-        <v>6963231</v>
+        <v>6963086</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13252,7 +13252,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>Misstänker grantaggsvamp 1 exemplar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13279,32 +13279,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128087584</v>
+        <v>128087370</v>
       </c>
       <c r="B128" t="n">
-        <v>98384</v>
+        <v>98467</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13314,10 +13314,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>544718</v>
+        <v>544751</v>
       </c>
       <c r="R128" t="n">
-        <v>6963053</v>
+        <v>6963146</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13354,7 +13354,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>3 stycken</t>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13381,7 +13381,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128087370</v>
+        <v>128087371</v>
       </c>
       <c r="B129" t="n">
         <v>98467</v>
@@ -13416,10 +13416,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>544751</v>
+        <v>544559</v>
       </c>
       <c r="R129" t="n">
-        <v>6963146</v>
+        <v>6963215</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13456,7 +13456,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>30 ex</t>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13483,32 +13483,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128087334</v>
+        <v>128079484</v>
       </c>
       <c r="B130" t="n">
-        <v>57672</v>
+        <v>80168</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13518,10 +13518,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>544348</v>
+        <v>544289</v>
       </c>
       <c r="R130" t="n">
-        <v>6963187</v>
+        <v>6963113</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13554,11 +13554,6 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13585,32 +13580,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128087371</v>
+        <v>128087574</v>
       </c>
       <c r="B131" t="n">
-        <v>98467</v>
+        <v>92671</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>220787</v>
+        <v>1968</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13620,10 +13615,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>544559</v>
+        <v>544552</v>
       </c>
       <c r="R131" t="n">
-        <v>6963215</v>
+        <v>6963231</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13660,7 +13655,7 @@
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>100 ex</t>
+          <t>Misstänker grantaggsvamp 1 exemplar</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13687,32 +13682,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128079484</v>
+        <v>128087334</v>
       </c>
       <c r="B132" t="n">
-        <v>80168</v>
+        <v>57672</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13722,10 +13717,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>544289</v>
+        <v>544348</v>
       </c>
       <c r="R132" t="n">
-        <v>6963113</v>
+        <v>6963187</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13758,6 +13753,11 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -13881,7 +13881,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128087345</v>
+        <v>128087344</v>
       </c>
       <c r="B134" t="n">
         <v>80161</v>
@@ -13916,10 +13916,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>544391</v>
+        <v>544581</v>
       </c>
       <c r="R134" t="n">
-        <v>6963205</v>
+        <v>6963278</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13978,32 +13978,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128087344</v>
+        <v>128087534</v>
       </c>
       <c r="B135" t="n">
-        <v>80161</v>
+        <v>80132</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14013,10 +14013,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>544581</v>
+        <v>544326</v>
       </c>
       <c r="R135" t="n">
-        <v>6963278</v>
+        <v>6963248</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14075,32 +14075,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128087381</v>
+        <v>128087540</v>
       </c>
       <c r="B136" t="n">
-        <v>98384</v>
+        <v>80132</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14110,10 +14110,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>544531</v>
+        <v>544282</v>
       </c>
       <c r="R136" t="n">
-        <v>6963190</v>
+        <v>6963082</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14274,32 +14274,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128087543</v>
+        <v>128087381</v>
       </c>
       <c r="B138" t="n">
-        <v>98467</v>
+        <v>98384</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14309,10 +14309,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>544674</v>
+        <v>544531</v>
       </c>
       <c r="R138" t="n">
-        <v>6963243</v>
+        <v>6963190</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14345,11 +14345,6 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14376,32 +14371,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128087534</v>
+        <v>128087530</v>
       </c>
       <c r="B139" t="n">
-        <v>80132</v>
+        <v>98501</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6458</v>
+        <v>219874</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14411,10 +14406,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>544326</v>
+        <v>544737</v>
       </c>
       <c r="R139" t="n">
-        <v>6963248</v>
+        <v>6963047</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14473,10 +14468,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128087530</v>
+        <v>128087345</v>
       </c>
       <c r="B140" t="n">
-        <v>98501</v>
+        <v>80161</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14484,21 +14479,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>219874</v>
+        <v>6462</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14508,10 +14503,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>544737</v>
+        <v>544391</v>
       </c>
       <c r="R140" t="n">
-        <v>6963047</v>
+        <v>6963205</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14570,32 +14565,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128087540</v>
+        <v>128087557</v>
       </c>
       <c r="B141" t="n">
-        <v>80132</v>
+        <v>98467</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14605,10 +14600,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>544282</v>
+        <v>544552</v>
       </c>
       <c r="R141" t="n">
-        <v>6963082</v>
+        <v>6963231</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14641,6 +14636,11 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14667,7 +14667,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128087557</v>
+        <v>128087543</v>
       </c>
       <c r="B142" t="n">
         <v>98467</v>
@@ -14702,10 +14702,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>544552</v>
+        <v>544674</v>
       </c>
       <c r="R142" t="n">
-        <v>6963231</v>
+        <v>6963243</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14742,7 +14742,7 @@
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>30 stycken</t>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15067,6 +15067,2332 @@
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>128094046</v>
+      </c>
+      <c r="B146" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Västermyrberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>544754</v>
+      </c>
+      <c r="R146" t="n">
+        <v>6963261</v>
+      </c>
+      <c r="S146" t="n">
+        <v>10</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>25 ex</t>
+        </is>
+      </c>
+      <c r="AD146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT146" t="inlineStr"/>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>128094035</v>
+      </c>
+      <c r="B147" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Västermyrberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>544736</v>
+      </c>
+      <c r="R147" t="n">
+        <v>6963232</v>
+      </c>
+      <c r="S147" t="n">
+        <v>10</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>128094050</v>
+      </c>
+      <c r="B148" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Västermyrberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>544428</v>
+      </c>
+      <c r="R148" t="n">
+        <v>6963142</v>
+      </c>
+      <c r="S148" t="n">
+        <v>10</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>70 ex</t>
+        </is>
+      </c>
+      <c r="AD148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>128094039</v>
+      </c>
+      <c r="B149" t="n">
+        <v>80133</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Västermyrberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>544445</v>
+      </c>
+      <c r="R149" t="n">
+        <v>6963135</v>
+      </c>
+      <c r="S149" t="n">
+        <v>10</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT149" t="inlineStr"/>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>128094032</v>
+      </c>
+      <c r="B150" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Västermyrberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>544279</v>
+      </c>
+      <c r="R150" t="n">
+        <v>6963296</v>
+      </c>
+      <c r="S150" t="n">
+        <v>10</v>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT150" t="inlineStr"/>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>128094042</v>
+      </c>
+      <c r="B151" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Västermyrberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>544528</v>
+      </c>
+      <c r="R151" t="n">
+        <v>6963294</v>
+      </c>
+      <c r="S151" t="n">
+        <v>10</v>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>75 ex</t>
+        </is>
+      </c>
+      <c r="AD151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT151" t="inlineStr"/>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>128094038</v>
+      </c>
+      <c r="B152" t="n">
+        <v>57669</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Västermyrberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>544469</v>
+      </c>
+      <c r="R152" t="n">
+        <v>6963307</v>
+      </c>
+      <c r="S152" t="n">
+        <v>10</v>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>Förbiflygande</t>
+        </is>
+      </c>
+      <c r="AD152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT152" t="inlineStr"/>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>128094044</v>
+      </c>
+      <c r="B153" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Västermyrberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q153" t="n">
+        <v>544703</v>
+      </c>
+      <c r="R153" t="n">
+        <v>6963330</v>
+      </c>
+      <c r="S153" t="n">
+        <v>10</v>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>100 ex</t>
+        </is>
+      </c>
+      <c r="AD153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT153" t="inlineStr"/>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>128094040</v>
+      </c>
+      <c r="B154" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Västermyrberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>544323</v>
+      </c>
+      <c r="R154" t="n">
+        <v>6963323</v>
+      </c>
+      <c r="S154" t="n">
+        <v>10</v>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>7 ex</t>
+        </is>
+      </c>
+      <c r="AD154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT154" t="inlineStr"/>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>128094043</v>
+      </c>
+      <c r="B155" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Västermyrberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>544546</v>
+      </c>
+      <c r="R155" t="n">
+        <v>6963293</v>
+      </c>
+      <c r="S155" t="n">
+        <v>10</v>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>25 ex</t>
+        </is>
+      </c>
+      <c r="AD155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT155" t="inlineStr"/>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>128094048</v>
+      </c>
+      <c r="B156" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Västermyrberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>544610</v>
+      </c>
+      <c r="R156" t="n">
+        <v>6963173</v>
+      </c>
+      <c r="S156" t="n">
+        <v>10</v>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>24 ex</t>
+        </is>
+      </c>
+      <c r="AD156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT156" t="inlineStr"/>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>128094041</v>
+      </c>
+      <c r="B157" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Västermyrberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>544411</v>
+      </c>
+      <c r="R157" t="n">
+        <v>6963326</v>
+      </c>
+      <c r="S157" t="n">
+        <v>10</v>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>34 ex</t>
+        </is>
+      </c>
+      <c r="AD157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT157" t="inlineStr"/>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>128094049</v>
+      </c>
+      <c r="B158" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Västermyrberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q158" t="n">
+        <v>544576</v>
+      </c>
+      <c r="R158" t="n">
+        <v>6963180</v>
+      </c>
+      <c r="S158" t="n">
+        <v>10</v>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>6 ex</t>
+        </is>
+      </c>
+      <c r="AD158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT158" t="inlineStr"/>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>128094053</v>
+      </c>
+      <c r="B159" t="n">
+        <v>105505</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Västermyrberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>544309</v>
+      </c>
+      <c r="R159" t="n">
+        <v>6963094</v>
+      </c>
+      <c r="S159" t="n">
+        <v>10</v>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT159" t="inlineStr"/>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>128094047</v>
+      </c>
+      <c r="B160" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Västermyrberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>544641</v>
+      </c>
+      <c r="R160" t="n">
+        <v>6963158</v>
+      </c>
+      <c r="S160" t="n">
+        <v>10</v>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>11 ex</t>
+        </is>
+      </c>
+      <c r="AD160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT160" t="inlineStr"/>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>128094052</v>
+      </c>
+      <c r="B161" t="n">
+        <v>56855</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>Västermyrberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q161" t="n">
+        <v>544577</v>
+      </c>
+      <c r="R161" t="n">
+        <v>6963169</v>
+      </c>
+      <c r="S161" t="n">
+        <v>10</v>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>Individ noterad genom sång</t>
+        </is>
+      </c>
+      <c r="AD161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT161" t="inlineStr"/>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>128094051</v>
+      </c>
+      <c r="B162" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>Västermyrberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q162" t="n">
+        <v>544310</v>
+      </c>
+      <c r="R162" t="n">
+        <v>6963314</v>
+      </c>
+      <c r="S162" t="n">
+        <v>10</v>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>80 ex</t>
+        </is>
+      </c>
+      <c r="AD162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT162" t="inlineStr"/>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>128094045</v>
+      </c>
+      <c r="B163" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>Västermyrberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q163" t="n">
+        <v>544760</v>
+      </c>
+      <c r="R163" t="n">
+        <v>6963251</v>
+      </c>
+      <c r="S163" t="n">
+        <v>10</v>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>35 ex</t>
+        </is>
+      </c>
+      <c r="AD163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT163" t="inlineStr"/>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>128094054</v>
+      </c>
+      <c r="B164" t="n">
+        <v>105505</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>Västermyrberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q164" t="n">
+        <v>544321</v>
+      </c>
+      <c r="R164" t="n">
+        <v>6963319</v>
+      </c>
+      <c r="S164" t="n">
+        <v>10</v>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT164" t="inlineStr"/>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>128094036</v>
+      </c>
+      <c r="B165" t="n">
+        <v>57832</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>Västermyrberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q165" t="n">
+        <v>544566</v>
+      </c>
+      <c r="R165" t="n">
+        <v>6963163</v>
+      </c>
+      <c r="S165" t="n">
+        <v>10</v>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>Lockläte övriga läten</t>
+        </is>
+      </c>
+      <c r="AD165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT165" t="inlineStr"/>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>128094033</v>
+      </c>
+      <c r="B166" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>Västermyrberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q166" t="n">
+        <v>544475</v>
+      </c>
+      <c r="R166" t="n">
+        <v>6963299</v>
+      </c>
+      <c r="S166" t="n">
+        <v>10</v>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT166" t="inlineStr"/>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>128094034</v>
+      </c>
+      <c r="B167" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>Västermyrberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q167" t="n">
+        <v>544903</v>
+      </c>
+      <c r="R167" t="n">
+        <v>6963331</v>
+      </c>
+      <c r="S167" t="n">
+        <v>10</v>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT167" t="inlineStr"/>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>128094055</v>
+      </c>
+      <c r="B168" t="n">
+        <v>105505</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>Västermyrberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q168" t="n">
+        <v>544667</v>
+      </c>
+      <c r="R168" t="n">
+        <v>6963168</v>
+      </c>
+      <c r="S168" t="n">
+        <v>10</v>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT168" t="inlineStr"/>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32240-2025 artfynd.xlsx
+++ b/artfynd/A 32240-2025 artfynd.xlsx
@@ -995,32 +995,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128087541</v>
+        <v>128087558</v>
       </c>
       <c r="B5" t="n">
-        <v>78787</v>
+        <v>98468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544267</v>
+        <v>544428</v>
       </c>
       <c r="R5" t="n">
-        <v>6963196</v>
+        <v>6963233</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,6 +1066,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1092,32 +1097,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128087528</v>
+        <v>128087541</v>
       </c>
       <c r="B6" t="n">
-        <v>80160</v>
+        <v>78787</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1127,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544198</v>
+        <v>544267</v>
       </c>
       <c r="R6" t="n">
-        <v>6963228</v>
+        <v>6963196</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,7 +1194,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128087358</v>
+        <v>128087528</v>
       </c>
       <c r="B7" t="n">
         <v>80160</v>
@@ -1224,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544278</v>
+        <v>544198</v>
       </c>
       <c r="R7" t="n">
-        <v>6963265</v>
+        <v>6963228</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128087524</v>
+        <v>128087358</v>
       </c>
       <c r="B8" t="n">
-        <v>80161</v>
+        <v>80160</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1297,21 +1302,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1321,10 +1326,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544281</v>
+        <v>544278</v>
       </c>
       <c r="R8" t="n">
-        <v>6963082</v>
+        <v>6963265</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,32 +1388,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128087558</v>
+        <v>128087524</v>
       </c>
       <c r="B9" t="n">
-        <v>98467</v>
+        <v>80161</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1418,10 +1423,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544428</v>
+        <v>544281</v>
       </c>
       <c r="R9" t="n">
-        <v>6963233</v>
+        <v>6963082</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1454,11 +1459,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1488,7 +1488,7 @@
         <v>128087526</v>
       </c>
       <c r="B10" t="n">
-        <v>92631</v>
+        <v>92632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>128078559</v>
       </c>
       <c r="B12" t="n">
-        <v>97344</v>
+        <v>97345</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128087520</v>
+        <v>128081639</v>
       </c>
       <c r="B13" t="n">
-        <v>57832</v>
+        <v>80133</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1797,21 +1797,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544771</v>
+        <v>544323</v>
       </c>
       <c r="R13" t="n">
-        <v>6963083</v>
+        <v>6963268</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1857,11 +1857,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>2 stycken.  Övriga läten</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1985,10 +1980,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128081639</v>
+        <v>128087323</v>
       </c>
       <c r="B15" t="n">
-        <v>80133</v>
+        <v>57672</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1996,21 +1991,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2020,10 +2015,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544323</v>
+        <v>544646</v>
       </c>
       <c r="R15" t="n">
-        <v>6963268</v>
+        <v>6963095</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2056,6 +2051,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2082,7 +2082,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128087323</v>
+        <v>128087324</v>
       </c>
       <c r="B16" t="n">
         <v>57672</v>
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544646</v>
+        <v>544792</v>
       </c>
       <c r="R16" t="n">
-        <v>6963095</v>
+        <v>6963047</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2184,10 +2184,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128087324</v>
+        <v>128087520</v>
       </c>
       <c r="B17" t="n">
-        <v>57672</v>
+        <v>57832</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2195,21 +2195,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544792</v>
+        <v>544771</v>
       </c>
       <c r="R17" t="n">
-        <v>6963047</v>
+        <v>6963083</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>2 stycken.  Övriga läten</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2289,7 +2289,7 @@
         <v>128087550</v>
       </c>
       <c r="B18" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2485,10 +2485,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128087362</v>
+        <v>128087354</v>
       </c>
       <c r="B20" t="n">
-        <v>80132</v>
+        <v>80133</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2496,21 +2496,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544799</v>
+        <v>544820</v>
       </c>
       <c r="R20" t="n">
-        <v>6963263</v>
+        <v>6963278</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2582,32 +2582,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128087349</v>
+        <v>128087569</v>
       </c>
       <c r="B21" t="n">
-        <v>80161</v>
+        <v>98468</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544475</v>
+        <v>544296</v>
       </c>
       <c r="R21" t="n">
-        <v>6963205</v>
+        <v>6963084</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2653,6 +2653,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>100stycken</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2679,32 +2684,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128087354</v>
+        <v>128087554</v>
       </c>
       <c r="B22" t="n">
-        <v>80133</v>
+        <v>98468</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2714,10 +2719,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544820</v>
+        <v>544659</v>
       </c>
       <c r="R22" t="n">
-        <v>6963278</v>
+        <v>6963253</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2750,6 +2755,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2776,10 +2786,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128087359</v>
+        <v>128087362</v>
       </c>
       <c r="B23" t="n">
-        <v>78788</v>
+        <v>80132</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2787,21 +2797,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2811,10 +2821,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544741</v>
+        <v>544799</v>
       </c>
       <c r="R23" t="n">
-        <v>6963165</v>
+        <v>6963263</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2873,32 +2883,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128087569</v>
+        <v>128087349</v>
       </c>
       <c r="B24" t="n">
-        <v>98467</v>
+        <v>80161</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2908,10 +2918,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544296</v>
+        <v>544475</v>
       </c>
       <c r="R24" t="n">
-        <v>6963084</v>
+        <v>6963205</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2944,11 +2954,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>100stycken</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2975,32 +2980,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128087554</v>
+        <v>128087359</v>
       </c>
       <c r="B25" t="n">
-        <v>98467</v>
+        <v>78788</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3010,10 +3015,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544659</v>
+        <v>544741</v>
       </c>
       <c r="R25" t="n">
-        <v>6963253</v>
+        <v>6963165</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3046,11 +3051,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3077,32 +3077,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128087382</v>
+        <v>128087562</v>
       </c>
       <c r="B26" t="n">
-        <v>92639</v>
+        <v>98468</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3112,10 +3112,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>544198</v>
+        <v>544367</v>
       </c>
       <c r="R26" t="n">
-        <v>6963225</v>
+        <v>6963253</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>5 ex</t>
+          <t>7. Kan möjlitvis finnas fler runt omkring.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3179,45 +3179,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128087532</v>
+        <v>128078161</v>
       </c>
       <c r="B27" t="n">
-        <v>80132</v>
+        <v>98468</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544491</v>
+        <v>544362</v>
       </c>
       <c r="R27" t="n">
-        <v>6963099</v>
+        <v>6963061</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3276,45 +3280,49 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128087331</v>
+        <v>128078740</v>
       </c>
       <c r="B28" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544763</v>
+        <v>544307</v>
       </c>
       <c r="R28" t="n">
-        <v>6963244</v>
+        <v>6963089</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3347,11 +3355,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3378,32 +3381,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128087333</v>
+        <v>128087563</v>
       </c>
       <c r="B29" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3413,10 +3416,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544355</v>
+        <v>544322</v>
       </c>
       <c r="R29" t="n">
-        <v>6963212</v>
+        <v>6963250</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3453,7 +3456,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>12 stycken</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3480,32 +3483,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128087562</v>
+        <v>128087382</v>
       </c>
       <c r="B30" t="n">
-        <v>98467</v>
+        <v>92640</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3515,10 +3518,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>544367</v>
+        <v>544198</v>
       </c>
       <c r="R30" t="n">
-        <v>6963253</v>
+        <v>6963225</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3555,7 +3558,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>7. Kan möjlitvis finnas fler runt omkring.</t>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3582,49 +3585,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128078161</v>
+        <v>128087532</v>
       </c>
       <c r="B31" t="n">
-        <v>98467</v>
+        <v>80132</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>544362</v>
+        <v>544491</v>
       </c>
       <c r="R31" t="n">
-        <v>6963061</v>
+        <v>6963099</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3683,49 +3682,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128078740</v>
+        <v>128087331</v>
       </c>
       <c r="B32" t="n">
-        <v>98467</v>
+        <v>57672</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544307</v>
+        <v>544763</v>
       </c>
       <c r="R32" t="n">
-        <v>6963089</v>
+        <v>6963244</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3758,6 +3753,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3784,32 +3784,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128087563</v>
+        <v>128087333</v>
       </c>
       <c r="B33" t="n">
-        <v>98467</v>
+        <v>57672</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>544322</v>
+        <v>544355</v>
       </c>
       <c r="R33" t="n">
-        <v>6963250</v>
+        <v>6963212</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3859,7 +3859,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>12 stycken</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3886,10 +3886,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128079621</v>
+        <v>128087336</v>
       </c>
       <c r="B34" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3897,21 +3897,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3921,10 +3921,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>544274</v>
+        <v>544398</v>
       </c>
       <c r="R34" t="n">
-        <v>6963119</v>
+        <v>6963202</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3957,6 +3957,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3983,7 +3988,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128087533</v>
+        <v>128079621</v>
       </c>
       <c r="B35" t="n">
         <v>80132</v>
@@ -4018,10 +4023,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>544473</v>
+        <v>544274</v>
       </c>
       <c r="R35" t="n">
-        <v>6963102</v>
+        <v>6963119</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4080,32 +4085,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128087351</v>
+        <v>128087533</v>
       </c>
       <c r="B36" t="n">
-        <v>80161</v>
+        <v>80132</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4115,10 +4120,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>544299</v>
+        <v>544473</v>
       </c>
       <c r="R36" t="n">
-        <v>6963312</v>
+        <v>6963102</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4177,32 +4182,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128087365</v>
+        <v>128087351</v>
       </c>
       <c r="B37" t="n">
-        <v>80132</v>
+        <v>80161</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4212,10 +4217,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>544469</v>
+        <v>544299</v>
       </c>
       <c r="R37" t="n">
-        <v>6963145</v>
+        <v>6963312</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4274,10 +4279,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128087336</v>
+        <v>128087365</v>
       </c>
       <c r="B38" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4285,21 +4290,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4309,10 +4314,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>544398</v>
+        <v>544469</v>
       </c>
       <c r="R38" t="n">
-        <v>6963202</v>
+        <v>6963145</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4345,11 +4350,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4376,10 +4376,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128087369</v>
+        <v>128087527</v>
       </c>
       <c r="B39" t="n">
-        <v>80168</v>
+        <v>80160</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4387,21 +4387,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6464</v>
+        <v>6461</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>544721</v>
+        <v>544246</v>
       </c>
       <c r="R39" t="n">
-        <v>6963277</v>
+        <v>6963259</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4473,32 +4473,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128087332</v>
+        <v>128087369</v>
       </c>
       <c r="B40" t="n">
-        <v>57672</v>
+        <v>80168</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>544431</v>
+        <v>544721</v>
       </c>
       <c r="R40" t="n">
-        <v>6963190</v>
+        <v>6963277</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4544,11 +4544,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4575,32 +4570,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128087517</v>
+        <v>128087588</v>
       </c>
       <c r="B41" t="n">
-        <v>57672</v>
+        <v>92640</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4610,10 +4605,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>544381</v>
+        <v>544183</v>
       </c>
       <c r="R41" t="n">
-        <v>6963236</v>
+        <v>6963214</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4650,7 +4645,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall Äldre ringhack som återanvänds ( äldre och färska)</t>
+          <t>9 ex äldre exemplar</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4677,32 +4672,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128087588</v>
+        <v>128087332</v>
       </c>
       <c r="B42" t="n">
-        <v>92639</v>
+        <v>57672</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4712,10 +4707,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>544183</v>
+        <v>544431</v>
       </c>
       <c r="R42" t="n">
-        <v>6963214</v>
+        <v>6963190</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4752,7 +4747,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>9 ex äldre exemplar</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4779,32 +4774,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128087527</v>
+        <v>128087517</v>
       </c>
       <c r="B43" t="n">
-        <v>80160</v>
+        <v>57672</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4814,10 +4809,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>544246</v>
+        <v>544381</v>
       </c>
       <c r="R43" t="n">
-        <v>6963259</v>
+        <v>6963236</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4850,6 +4845,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall Äldre ringhack som återanvänds ( äldre och färska)</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4876,32 +4876,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128087361</v>
+        <v>128087552</v>
       </c>
       <c r="B44" t="n">
-        <v>80132</v>
+        <v>98468</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4911,10 +4911,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>544865</v>
+        <v>544687</v>
       </c>
       <c r="R44" t="n">
-        <v>6963092</v>
+        <v>6963255</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4947,6 +4947,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>70</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4973,32 +4978,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128087360</v>
+        <v>128087548</v>
       </c>
       <c r="B45" t="n">
-        <v>80132</v>
+        <v>98468</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5008,10 +5013,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>544615</v>
+        <v>544213</v>
       </c>
       <c r="R45" t="n">
-        <v>6963093</v>
+        <v>6963197</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5044,6 +5049,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>100stycken.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5070,10 +5080,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128087340</v>
+        <v>128087361</v>
       </c>
       <c r="B46" t="n">
-        <v>57832</v>
+        <v>80132</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5081,21 +5091,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5105,10 +5115,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>544485</v>
+        <v>544865</v>
       </c>
       <c r="R46" t="n">
-        <v>6963237</v>
+        <v>6963092</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5167,32 +5177,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128079768</v>
+        <v>128087360</v>
       </c>
       <c r="B47" t="n">
-        <v>97350</v>
+        <v>80132</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221941</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5202,10 +5212,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>544287</v>
+        <v>544615</v>
       </c>
       <c r="R47" t="n">
-        <v>6963168</v>
+        <v>6963093</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5264,32 +5274,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128087552</v>
+        <v>128087340</v>
       </c>
       <c r="B48" t="n">
-        <v>98467</v>
+        <v>57832</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5299,10 +5309,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>544687</v>
+        <v>544485</v>
       </c>
       <c r="R48" t="n">
-        <v>6963255</v>
+        <v>6963237</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5335,11 +5345,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>70</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5366,32 +5371,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128087548</v>
+        <v>128079768</v>
       </c>
       <c r="B49" t="n">
-        <v>98467</v>
+        <v>97351</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5401,10 +5406,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>544213</v>
+        <v>544287</v>
       </c>
       <c r="R49" t="n">
-        <v>6963197</v>
+        <v>6963168</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5437,11 +5442,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>100stycken.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5662,10 +5662,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128087364</v>
+        <v>128087339</v>
       </c>
       <c r="B52" t="n">
-        <v>80132</v>
+        <v>57832</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5673,21 +5673,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5697,10 +5697,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>544774</v>
+        <v>544850</v>
       </c>
       <c r="R52" t="n">
-        <v>6963282</v>
+        <v>6963099</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5733,6 +5733,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5762,7 +5767,7 @@
         <v>128079839</v>
       </c>
       <c r="B53" t="n">
-        <v>105505</v>
+        <v>105506</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5859,7 +5864,7 @@
         <v>128087553</v>
       </c>
       <c r="B54" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5958,32 +5963,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128087339</v>
+        <v>128087555</v>
       </c>
       <c r="B55" t="n">
-        <v>57832</v>
+        <v>98468</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5993,10 +5998,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>544850</v>
+        <v>544623</v>
       </c>
       <c r="R55" t="n">
-        <v>6963099</v>
+        <v>6963241</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6033,7 +6038,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Lockläte/övriga läten</t>
+          <t>60 stycken</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6060,32 +6065,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128087555</v>
+        <v>128087364</v>
       </c>
       <c r="B56" t="n">
-        <v>98467</v>
+        <v>80132</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6095,10 +6100,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>544623</v>
+        <v>544774</v>
       </c>
       <c r="R56" t="n">
-        <v>6963241</v>
+        <v>6963282</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6131,11 +6136,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>60 stycken</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6162,10 +6162,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128087585</v>
+        <v>128087356</v>
       </c>
       <c r="B57" t="n">
-        <v>92639</v>
+        <v>80160</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6173,21 +6173,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>6461</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6197,10 +6197,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>544536</v>
+        <v>544772</v>
       </c>
       <c r="R57" t="n">
-        <v>6963255</v>
+        <v>6963323</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6233,11 +6233,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>8 äldre ex9 färska fruktkroppar</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6264,7 +6259,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128087356</v>
+        <v>128087357</v>
       </c>
       <c r="B58" t="n">
         <v>80160</v>
@@ -6299,10 +6294,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>544772</v>
+        <v>544466</v>
       </c>
       <c r="R58" t="n">
-        <v>6963323</v>
+        <v>6963277</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6361,45 +6356,50 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128087357</v>
+        <v>128080012</v>
       </c>
       <c r="B59" t="n">
-        <v>80160</v>
+        <v>57672</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>544466</v>
+        <v>544324</v>
       </c>
       <c r="R59" t="n">
-        <v>6963277</v>
+        <v>6963220</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6432,6 +6432,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6458,50 +6463,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128080012</v>
+        <v>128087585</v>
       </c>
       <c r="B60" t="n">
-        <v>57672</v>
+        <v>92640</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>544324</v>
+        <v>544536</v>
       </c>
       <c r="R60" t="n">
-        <v>6963220</v>
+        <v>6963255</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>8 äldre ex9 färska fruktkroppar</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6565,32 +6565,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128087375</v>
+        <v>128087579</v>
       </c>
       <c r="B61" t="n">
-        <v>98467</v>
+        <v>79029</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6600,10 +6600,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>544478</v>
+        <v>544204</v>
       </c>
       <c r="R61" t="n">
-        <v>6963117</v>
+        <v>6963238</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>35 ex</t>
+          <t>Riklig förekomst av garnlav</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6667,10 +6667,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128087579</v>
+        <v>128087386</v>
       </c>
       <c r="B62" t="n">
-        <v>79029</v>
+        <v>92634</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6678,21 +6678,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6702,10 +6702,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>544204</v>
+        <v>544822</v>
       </c>
       <c r="R62" t="n">
-        <v>6963238</v>
+        <v>6963295</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6738,11 +6738,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6769,7 +6764,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128087523</v>
+        <v>128078603</v>
       </c>
       <c r="B63" t="n">
         <v>80161</v>
@@ -6804,10 +6799,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>544253</v>
+        <v>544360</v>
       </c>
       <c r="R63" t="n">
-        <v>6963139</v>
+        <v>6963094</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6866,32 +6861,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128087386</v>
+        <v>128087523</v>
       </c>
       <c r="B64" t="n">
-        <v>92633</v>
+        <v>80161</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4362</v>
+        <v>6462</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6901,10 +6896,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>544822</v>
+        <v>544253</v>
       </c>
       <c r="R64" t="n">
-        <v>6963295</v>
+        <v>6963139</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6963,32 +6958,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128078603</v>
+        <v>128087525</v>
       </c>
       <c r="B65" t="n">
-        <v>80161</v>
+        <v>56248</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6462</v>
+        <v>206004</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6998,10 +6993,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>544360</v>
+        <v>544385</v>
       </c>
       <c r="R65" t="n">
-        <v>6963094</v>
+        <v>6963074</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7162,32 +7157,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128087525</v>
+        <v>128087566</v>
       </c>
       <c r="B67" t="n">
-        <v>56248</v>
+        <v>98468</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>206004</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7197,10 +7192,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>544385</v>
+        <v>544261</v>
       </c>
       <c r="R67" t="n">
-        <v>6963074</v>
+        <v>6963170</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7233,6 +7228,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>4. Stycken. Finns möjligtvis fler i blåbärsriset.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7259,10 +7259,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128087566</v>
+        <v>128087377</v>
       </c>
       <c r="B68" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7294,10 +7294,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>544261</v>
+        <v>544403</v>
       </c>
       <c r="R68" t="n">
-        <v>6963170</v>
+        <v>6963221</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>4. Stycken. Finns möjligtvis fler i blåbärsriset.</t>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7361,10 +7361,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128087377</v>
+        <v>128087378</v>
       </c>
       <c r="B69" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7396,10 +7396,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>544403</v>
+        <v>544218</v>
       </c>
       <c r="R69" t="n">
-        <v>6963221</v>
+        <v>6963229</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>20 ex</t>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7463,10 +7463,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128087378</v>
+        <v>128087375</v>
       </c>
       <c r="B70" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7498,10 +7498,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>544218</v>
+        <v>544478</v>
       </c>
       <c r="R70" t="n">
-        <v>6963229</v>
+        <v>6963117</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>80 ex</t>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8182,10 +8182,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128087330</v>
+        <v>128087575</v>
       </c>
       <c r="B77" t="n">
-        <v>57672</v>
+        <v>92672</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8193,21 +8193,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>1968</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8217,10 +8217,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>544750</v>
+        <v>544532</v>
       </c>
       <c r="R77" t="n">
-        <v>6963177</v>
+        <v>6963250</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8257,7 +8257,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Igen stor köttig svamp misstänker grantaggsvamp 2 ex</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8284,10 +8284,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128087335</v>
+        <v>128078492</v>
       </c>
       <c r="B78" t="n">
-        <v>57672</v>
+        <v>92672</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8295,21 +8295,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>1968</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8319,10 +8319,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>544366</v>
+        <v>544362</v>
       </c>
       <c r="R78" t="n">
-        <v>6963181</v>
+        <v>6963073</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8355,11 +8355,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8386,32 +8381,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128087346</v>
+        <v>128087536</v>
       </c>
       <c r="B79" t="n">
-        <v>80161</v>
+        <v>80132</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8421,10 +8416,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>544422</v>
+        <v>544215</v>
       </c>
       <c r="R79" t="n">
-        <v>6963240</v>
+        <v>6963245</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8483,32 +8478,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128087575</v>
+        <v>128087343</v>
       </c>
       <c r="B80" t="n">
-        <v>92671</v>
+        <v>80161</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1968</v>
+        <v>6462</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8518,10 +8513,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>544532</v>
+        <v>544757</v>
       </c>
       <c r="R80" t="n">
-        <v>6963250</v>
+        <v>6963156</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8554,11 +8549,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Igen stor köttig svamp misstänker grantaggsvamp 2 ex</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8585,32 +8575,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128078492</v>
+        <v>128087346</v>
       </c>
       <c r="B81" t="n">
-        <v>92671</v>
+        <v>80161</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1968</v>
+        <v>6462</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8620,10 +8610,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>544362</v>
+        <v>544422</v>
       </c>
       <c r="R81" t="n">
-        <v>6963073</v>
+        <v>6963240</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8682,10 +8672,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128087536</v>
+        <v>128087330</v>
       </c>
       <c r="B82" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8693,21 +8683,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8717,10 +8707,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>544215</v>
+        <v>544750</v>
       </c>
       <c r="R82" t="n">
-        <v>6963245</v>
+        <v>6963177</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8753,6 +8743,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8779,32 +8774,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128087343</v>
+        <v>128087335</v>
       </c>
       <c r="B83" t="n">
-        <v>80161</v>
+        <v>57672</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8814,10 +8809,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>544757</v>
+        <v>544366</v>
       </c>
       <c r="R83" t="n">
-        <v>6963156</v>
+        <v>6963181</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8850,6 +8845,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8981,7 +8981,7 @@
         <v>128087380</v>
       </c>
       <c r="B85" t="n">
-        <v>105505</v>
+        <v>105506</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>128079875</v>
       </c>
       <c r="B86" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>128087542</v>
       </c>
       <c r="B87" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9281,7 +9281,7 @@
         <v>128080338</v>
       </c>
       <c r="B88" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9382,7 +9382,7 @@
         <v>128087547</v>
       </c>
       <c r="B89" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9484,7 +9484,7 @@
         <v>128087560</v>
       </c>
       <c r="B90" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9583,32 +9583,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128087587</v>
+        <v>128087376</v>
       </c>
       <c r="B91" t="n">
-        <v>92639</v>
+        <v>98468</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9618,10 +9618,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>544245</v>
+        <v>544503</v>
       </c>
       <c r="R91" t="n">
-        <v>6963255</v>
+        <v>6963182</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9658,7 +9658,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>4stycken</t>
+          <t>60 ex</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9685,32 +9685,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128087539</v>
+        <v>128087379</v>
       </c>
       <c r="B92" t="n">
-        <v>80132</v>
+        <v>98468</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9720,10 +9720,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>544254</v>
+        <v>544263</v>
       </c>
       <c r="R92" t="n">
-        <v>6963139</v>
+        <v>6963254</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9756,6 +9756,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9782,10 +9787,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128087341</v>
+        <v>128087587</v>
       </c>
       <c r="B93" t="n">
-        <v>80161</v>
+        <v>92640</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9793,21 +9798,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9817,10 +9822,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>544615</v>
+        <v>544245</v>
       </c>
       <c r="R93" t="n">
-        <v>6963101</v>
+        <v>6963255</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9853,6 +9858,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>4stycken</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9879,32 +9889,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128087376</v>
+        <v>128087539</v>
       </c>
       <c r="B94" t="n">
-        <v>98467</v>
+        <v>80132</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9914,10 +9924,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>544503</v>
+        <v>544254</v>
       </c>
       <c r="R94" t="n">
-        <v>6963182</v>
+        <v>6963139</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9950,11 +9960,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>60 ex</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9981,32 +9986,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128087379</v>
+        <v>128087341</v>
       </c>
       <c r="B95" t="n">
-        <v>98467</v>
+        <v>80161</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10016,10 +10021,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>544263</v>
+        <v>544615</v>
       </c>
       <c r="R95" t="n">
-        <v>6963254</v>
+        <v>6963101</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10052,11 +10057,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>15 ex</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10083,10 +10083,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128087522</v>
+        <v>128087576</v>
       </c>
       <c r="B96" t="n">
-        <v>57832</v>
+        <v>92672</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10094,21 +10094,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>103021</v>
+        <v>1968</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10118,10 +10118,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>544494</v>
+        <v>544529</v>
       </c>
       <c r="R96" t="n">
-        <v>6963243</v>
+        <v>6963245</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10154,6 +10154,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Misstänkt grantaggsvamp men med mörk tydlig ring i mitten.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10180,32 +10185,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128087383</v>
+        <v>128087572</v>
       </c>
       <c r="B97" t="n">
-        <v>80167</v>
+        <v>92672</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6463</v>
+        <v>1968</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10215,10 +10220,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>544566</v>
+        <v>544632</v>
       </c>
       <c r="R97" t="n">
-        <v>6963076</v>
+        <v>6963245</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10251,6 +10256,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>1 ex</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10277,10 +10287,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128087384</v>
+        <v>128078864</v>
       </c>
       <c r="B98" t="n">
-        <v>80167</v>
+        <v>105506</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10288,21 +10298,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6463</v>
+        <v>221144</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10312,10 +10322,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>544584</v>
+        <v>544307</v>
       </c>
       <c r="R98" t="n">
-        <v>6963261</v>
+        <v>6963089</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10374,32 +10384,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128087576</v>
+        <v>128087545</v>
       </c>
       <c r="B99" t="n">
-        <v>92671</v>
+        <v>98468</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1968</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10409,10 +10419,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>544529</v>
+        <v>544633</v>
       </c>
       <c r="R99" t="n">
-        <v>6963245</v>
+        <v>6963244</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10449,7 +10459,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Misstänkt grantaggsvamp men med mörk tydlig ring i mitten.</t>
+          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10476,32 +10486,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128087572</v>
+        <v>128087567</v>
       </c>
       <c r="B100" t="n">
-        <v>92671</v>
+        <v>98468</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1968</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10511,10 +10521,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>544632</v>
+        <v>544274</v>
       </c>
       <c r="R100" t="n">
-        <v>6963245</v>
+        <v>6963090</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10551,7 +10561,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>1 ex</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10578,32 +10588,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128087363</v>
+        <v>128087556</v>
       </c>
       <c r="B101" t="n">
-        <v>80132</v>
+        <v>98468</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10613,10 +10623,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>544818</v>
+        <v>544594</v>
       </c>
       <c r="R101" t="n">
-        <v>6963278</v>
+        <v>6963215</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10649,6 +10659,11 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>6 stycken. Kan finnas mer i omgivningen</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10675,32 +10690,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128078864</v>
+        <v>128087373</v>
       </c>
       <c r="B102" t="n">
-        <v>105505</v>
+        <v>98468</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10710,10 +10725,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>544307</v>
+        <v>544469</v>
       </c>
       <c r="R102" t="n">
-        <v>6963089</v>
+        <v>6963122</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10746,6 +10761,11 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>60 ex</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10772,32 +10792,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128087355</v>
+        <v>128087559</v>
       </c>
       <c r="B103" t="n">
-        <v>97350</v>
+        <v>98468</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10807,10 +10827,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>544500</v>
+        <v>544396</v>
       </c>
       <c r="R103" t="n">
-        <v>6963168</v>
+        <v>6963233</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10843,6 +10863,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10869,32 +10894,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128087545</v>
+        <v>128087383</v>
       </c>
       <c r="B104" t="n">
-        <v>98467</v>
+        <v>80167</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10904,10 +10929,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>544633</v>
+        <v>544566</v>
       </c>
       <c r="R104" t="n">
-        <v>6963244</v>
+        <v>6963076</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10940,11 +10965,6 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10971,32 +10991,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128087567</v>
+        <v>128087384</v>
       </c>
       <c r="B105" t="n">
-        <v>98467</v>
+        <v>80167</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11006,10 +11026,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>544274</v>
+        <v>544584</v>
       </c>
       <c r="R105" t="n">
-        <v>6963090</v>
+        <v>6963261</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11042,11 +11062,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>110</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11073,32 +11088,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128087556</v>
+        <v>128087363</v>
       </c>
       <c r="B106" t="n">
-        <v>98467</v>
+        <v>80132</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11108,10 +11123,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>544594</v>
+        <v>544818</v>
       </c>
       <c r="R106" t="n">
-        <v>6963215</v>
+        <v>6963278</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11144,11 +11159,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>6 stycken. Kan finnas mer i omgivningen</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11175,32 +11185,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128087373</v>
+        <v>128087522</v>
       </c>
       <c r="B107" t="n">
-        <v>98467</v>
+        <v>57832</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11210,10 +11220,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>544469</v>
+        <v>544494</v>
       </c>
       <c r="R107" t="n">
-        <v>6963122</v>
+        <v>6963243</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11246,11 +11256,6 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>60 ex</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11277,32 +11282,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128087559</v>
+        <v>128087355</v>
       </c>
       <c r="B108" t="n">
-        <v>98467</v>
+        <v>97351</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11312,10 +11317,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>544396</v>
+        <v>544500</v>
       </c>
       <c r="R108" t="n">
-        <v>6963233</v>
+        <v>6963168</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11348,11 +11353,6 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11379,49 +11379,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128079656</v>
+        <v>128087578</v>
       </c>
       <c r="B109" t="n">
-        <v>98467</v>
+        <v>79029</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>544277</v>
+        <v>544246</v>
       </c>
       <c r="R109" t="n">
-        <v>6963150</v>
+        <v>6963257</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11480,32 +11476,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128087565</v>
+        <v>128087531</v>
       </c>
       <c r="B110" t="n">
-        <v>98467</v>
+        <v>98502</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11515,10 +11511,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>544249</v>
+        <v>544755</v>
       </c>
       <c r="R110" t="n">
-        <v>6963223</v>
+        <v>6963130</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11555,7 +11551,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>10. Kan möjlitvis finns mer i blåbärsriset</t>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11582,10 +11578,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128087372</v>
+        <v>128079656</v>
       </c>
       <c r="B111" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11610,17 +11606,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>544472</v>
+        <v>544277</v>
       </c>
       <c r="R111" t="n">
-        <v>6963201</v>
+        <v>6963150</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11653,11 +11653,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>8 ex</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11684,10 +11679,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128087551</v>
+        <v>128087565</v>
       </c>
       <c r="B112" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11719,10 +11714,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>544694</v>
+        <v>544249</v>
       </c>
       <c r="R112" t="n">
-        <v>6963258</v>
+        <v>6963223</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11759,7 +11754,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10. Kan möjlitvis finns mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11786,32 +11781,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128087578</v>
+        <v>128087372</v>
       </c>
       <c r="B113" t="n">
-        <v>79029</v>
+        <v>98468</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11821,10 +11816,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>544246</v>
+        <v>544472</v>
       </c>
       <c r="R113" t="n">
-        <v>6963257</v>
+        <v>6963201</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11857,6 +11852,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11883,32 +11883,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128087531</v>
+        <v>128087551</v>
       </c>
       <c r="B114" t="n">
-        <v>98501</v>
+        <v>98468</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11918,10 +11918,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>544755</v>
+        <v>544694</v>
       </c>
       <c r="R114" t="n">
-        <v>6963130</v>
+        <v>6963258</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11958,7 +11958,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>2 stycken</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11985,32 +11985,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128087586</v>
+        <v>128087577</v>
       </c>
       <c r="B115" t="n">
-        <v>92639</v>
+        <v>92672</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>4364</v>
+        <v>1968</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12020,10 +12020,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>544281</v>
+        <v>544494</v>
       </c>
       <c r="R115" t="n">
-        <v>6963257</v>
+        <v>6963243</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12056,11 +12056,6 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>2 nya exemplar 8 äldre ex</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12087,32 +12082,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128087577</v>
+        <v>128087586</v>
       </c>
       <c r="B116" t="n">
-        <v>92671</v>
+        <v>92640</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1968</v>
+        <v>4364</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12122,10 +12117,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>544494</v>
+        <v>544281</v>
       </c>
       <c r="R116" t="n">
-        <v>6963243</v>
+        <v>6963257</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12158,6 +12153,11 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>2 nya exemplar 8 äldre ex</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12184,32 +12184,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128079848</v>
+        <v>128087571</v>
       </c>
       <c r="B117" t="n">
-        <v>79053</v>
+        <v>92672</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6434</v>
+        <v>1968</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12219,10 +12219,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>544288</v>
+        <v>544679</v>
       </c>
       <c r="R117" t="n">
-        <v>6963182</v>
+        <v>6963259</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12255,6 +12255,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Misstänker grantaggsvamp. 14 exemplar</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12281,10 +12286,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128078823</v>
+        <v>128087573</v>
       </c>
       <c r="B118" t="n">
-        <v>79029</v>
+        <v>92672</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12292,21 +12297,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>1968</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12316,10 +12321,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>544307</v>
+        <v>544684</v>
       </c>
       <c r="R118" t="n">
-        <v>6963089</v>
+        <v>6963253</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12352,6 +12357,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Mörkt exemplar med vit yttre ring.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12378,32 +12388,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128087571</v>
+        <v>128079848</v>
       </c>
       <c r="B119" t="n">
-        <v>92671</v>
+        <v>79053</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1968</v>
+        <v>6434</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12413,10 +12423,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>544679</v>
+        <v>544288</v>
       </c>
       <c r="R119" t="n">
-        <v>6963259</v>
+        <v>6963182</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12449,11 +12459,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Misstänker grantaggsvamp. 14 exemplar</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12480,10 +12485,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128087573</v>
+        <v>128087538</v>
       </c>
       <c r="B120" t="n">
-        <v>92671</v>
+        <v>80132</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12491,21 +12496,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1968</v>
+        <v>6458</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12515,10 +12520,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>544684</v>
+        <v>544262</v>
       </c>
       <c r="R120" t="n">
-        <v>6963253</v>
+        <v>6963163</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12551,11 +12556,6 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Mörkt exemplar med vit yttre ring.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12582,7 +12582,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128087538</v>
+        <v>128087535</v>
       </c>
       <c r="B121" t="n">
         <v>80132</v>
@@ -12617,10 +12617,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>544262</v>
+        <v>544312</v>
       </c>
       <c r="R121" t="n">
-        <v>6963163</v>
+        <v>6963244</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12679,32 +12679,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128087535</v>
+        <v>128087582</v>
       </c>
       <c r="B122" t="n">
-        <v>80132</v>
+        <v>98385</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12714,10 +12714,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>544312</v>
+        <v>544489</v>
       </c>
       <c r="R122" t="n">
-        <v>6963244</v>
+        <v>6963098</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12776,32 +12776,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128087582</v>
+        <v>128078823</v>
       </c>
       <c r="B123" t="n">
-        <v>98384</v>
+        <v>79029</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12811,10 +12811,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>544489</v>
+        <v>544307</v>
       </c>
       <c r="R123" t="n">
-        <v>6963098</v>
+        <v>6963089</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12876,7 +12876,7 @@
         <v>128079571</v>
       </c>
       <c r="B124" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12977,7 +12977,7 @@
         <v>128078138</v>
       </c>
       <c r="B125" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13075,32 +13075,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128087584</v>
+        <v>128087574</v>
       </c>
       <c r="B126" t="n">
-        <v>98384</v>
+        <v>92672</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>219790</v>
+        <v>1968</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13110,10 +13110,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>544718</v>
+        <v>544552</v>
       </c>
       <c r="R126" t="n">
-        <v>6963053</v>
+        <v>6963231</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13150,7 +13150,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>3 stycken</t>
+          <t>Misstänker grantaggsvamp 1 exemplar</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13177,10 +13177,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128087583</v>
+        <v>128079484</v>
       </c>
       <c r="B127" t="n">
-        <v>98384</v>
+        <v>80168</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13188,21 +13188,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>219790</v>
+        <v>6464</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13212,10 +13212,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>544708</v>
+        <v>544289</v>
       </c>
       <c r="R127" t="n">
-        <v>6963086</v>
+        <v>6963113</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13248,11 +13248,6 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13279,32 +13274,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128087370</v>
+        <v>128087334</v>
       </c>
       <c r="B128" t="n">
-        <v>98467</v>
+        <v>57672</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13314,10 +13309,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>544751</v>
+        <v>544348</v>
       </c>
       <c r="R128" t="n">
-        <v>6963146</v>
+        <v>6963187</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13354,7 +13349,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>30 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13381,32 +13376,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128087371</v>
+        <v>128087583</v>
       </c>
       <c r="B129" t="n">
-        <v>98467</v>
+        <v>98385</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13416,10 +13411,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>544559</v>
+        <v>544708</v>
       </c>
       <c r="R129" t="n">
-        <v>6963215</v>
+        <v>6963086</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13456,7 +13451,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>100 ex</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13483,10 +13478,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128079484</v>
+        <v>128087584</v>
       </c>
       <c r="B130" t="n">
-        <v>80168</v>
+        <v>98385</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13494,21 +13489,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6464</v>
+        <v>219790</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13518,10 +13513,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>544289</v>
+        <v>544718</v>
       </c>
       <c r="R130" t="n">
-        <v>6963113</v>
+        <v>6963053</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13554,6 +13549,11 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>3 stycken</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13580,32 +13580,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128087574</v>
+        <v>128087370</v>
       </c>
       <c r="B131" t="n">
-        <v>92671</v>
+        <v>98468</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1968</v>
+        <v>220787</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13615,10 +13615,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>544552</v>
+        <v>544751</v>
       </c>
       <c r="R131" t="n">
-        <v>6963231</v>
+        <v>6963146</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13655,7 +13655,7 @@
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>Misstänker grantaggsvamp 1 exemplar</t>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13682,32 +13682,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128087334</v>
+        <v>128087371</v>
       </c>
       <c r="B132" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13717,10 +13717,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>544348</v>
+        <v>544559</v>
       </c>
       <c r="R132" t="n">
-        <v>6963187</v>
+        <v>6963215</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13757,7 +13757,7 @@
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -13784,32 +13784,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128078645</v>
+        <v>128087530</v>
       </c>
       <c r="B133" t="n">
-        <v>80132</v>
+        <v>98502</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6458</v>
+        <v>219874</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13819,10 +13819,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>544360</v>
+        <v>544737</v>
       </c>
       <c r="R133" t="n">
-        <v>6963094</v>
+        <v>6963047</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13881,10 +13881,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128087344</v>
+        <v>128087381</v>
       </c>
       <c r="B134" t="n">
-        <v>80161</v>
+        <v>98385</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13892,21 +13892,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6462</v>
+        <v>219790</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13916,10 +13916,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>544581</v>
+        <v>544531</v>
       </c>
       <c r="R134" t="n">
-        <v>6963278</v>
+        <v>6963190</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13978,7 +13978,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128087534</v>
+        <v>128078645</v>
       </c>
       <c r="B135" t="n">
         <v>80132</v>
@@ -14013,10 +14013,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>544326</v>
+        <v>544360</v>
       </c>
       <c r="R135" t="n">
-        <v>6963248</v>
+        <v>6963094</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14075,32 +14075,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128087540</v>
+        <v>128087344</v>
       </c>
       <c r="B136" t="n">
-        <v>80132</v>
+        <v>80161</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14110,10 +14110,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>544282</v>
+        <v>544581</v>
       </c>
       <c r="R136" t="n">
-        <v>6963082</v>
+        <v>6963278</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14172,10 +14172,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128087328</v>
+        <v>128087534</v>
       </c>
       <c r="B137" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14183,21 +14183,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14207,10 +14207,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>544736</v>
+        <v>544326</v>
       </c>
       <c r="R137" t="n">
-        <v>6963153</v>
+        <v>6963248</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14243,11 +14243,6 @@
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14274,10 +14269,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128087381</v>
+        <v>128087345</v>
       </c>
       <c r="B138" t="n">
-        <v>98384</v>
+        <v>80161</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14285,21 +14280,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>219790</v>
+        <v>6462</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14309,10 +14304,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>544531</v>
+        <v>544391</v>
       </c>
       <c r="R138" t="n">
-        <v>6963190</v>
+        <v>6963205</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14371,32 +14366,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128087530</v>
+        <v>128087540</v>
       </c>
       <c r="B139" t="n">
-        <v>98501</v>
+        <v>80132</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>219874</v>
+        <v>6458</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14406,10 +14401,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>544737</v>
+        <v>544282</v>
       </c>
       <c r="R139" t="n">
-        <v>6963047</v>
+        <v>6963082</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14468,32 +14463,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128087345</v>
+        <v>128087328</v>
       </c>
       <c r="B140" t="n">
-        <v>80161</v>
+        <v>57672</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14503,10 +14498,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>544391</v>
+        <v>544736</v>
       </c>
       <c r="R140" t="n">
-        <v>6963205</v>
+        <v>6963153</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14539,6 +14534,11 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14568,7 +14568,7 @@
         <v>128087557</v>
       </c>
       <c r="B141" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14670,7 +14670,7 @@
         <v>128087543</v>
       </c>
       <c r="B142" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14866,38 +14866,37 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128078685</v>
+        <v>128078529</v>
       </c>
       <c r="B144" t="n">
-        <v>56248</v>
+        <v>98468</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>206004</v>
+        <v>220787</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -14906,10 +14905,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>544307</v>
+        <v>544351</v>
       </c>
       <c r="R144" t="n">
-        <v>6963069</v>
+        <v>6963065</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14968,37 +14967,38 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128078529</v>
+        <v>128078685</v>
       </c>
       <c r="B145" t="n">
-        <v>98467</v>
+        <v>56248</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>220787</v>
+        <v>206004</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -15007,10 +15007,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>544351</v>
+        <v>544307</v>
       </c>
       <c r="R145" t="n">
-        <v>6963065</v>
+        <v>6963069</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15069,32 +15069,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128094046</v>
+        <v>128094035</v>
       </c>
       <c r="B146" t="n">
-        <v>98467</v>
+        <v>57672</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15104,10 +15104,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>544754</v>
+        <v>544736</v>
       </c>
       <c r="R146" t="n">
-        <v>6963261</v>
+        <v>6963232</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15144,7 +15144,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>25 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15171,32 +15171,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128094035</v>
+        <v>128094046</v>
       </c>
       <c r="B147" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15206,10 +15206,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>544736</v>
+        <v>544754</v>
       </c>
       <c r="R147" t="n">
-        <v>6963232</v>
+        <v>6963261</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15246,7 +15246,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15276,7 +15276,7 @@
         <v>128094050</v>
       </c>
       <c r="B148" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15472,32 +15472,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128094032</v>
+        <v>128094042</v>
       </c>
       <c r="B150" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15507,10 +15507,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>544279</v>
+        <v>544528</v>
       </c>
       <c r="R150" t="n">
-        <v>6963296</v>
+        <v>6963294</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15547,7 +15547,7 @@
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>75 ex</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15574,32 +15574,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128094042</v>
+        <v>128094032</v>
       </c>
       <c r="B151" t="n">
-        <v>98467</v>
+        <v>57672</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15609,10 +15609,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>544528</v>
+        <v>544279</v>
       </c>
       <c r="R151" t="n">
-        <v>6963294</v>
+        <v>6963296</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15649,7 +15649,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>75 ex</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15781,7 +15781,7 @@
         <v>128094044</v>
       </c>
       <c r="B153" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15883,7 +15883,7 @@
         <v>128094040</v>
       </c>
       <c r="B154" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15985,7 +15985,7 @@
         <v>128094043</v>
       </c>
       <c r="B155" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16087,7 +16087,7 @@
         <v>128094048</v>
       </c>
       <c r="B156" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>128094041</v>
       </c>
       <c r="B157" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16291,7 +16291,7 @@
         <v>128094049</v>
       </c>
       <c r="B158" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>128094053</v>
       </c>
       <c r="B159" t="n">
-        <v>105505</v>
+        <v>105506</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16487,32 +16487,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128094047</v>
+        <v>128094052</v>
       </c>
       <c r="B160" t="n">
-        <v>98467</v>
+        <v>56855</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16522,10 +16522,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>544641</v>
+        <v>544577</v>
       </c>
       <c r="R160" t="n">
-        <v>6963158</v>
+        <v>6963169</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16562,7 +16562,7 @@
       </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>11 ex</t>
+          <t>Individ noterad genom sång</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -16589,32 +16589,32 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128094052</v>
+        <v>128094054</v>
       </c>
       <c r="B161" t="n">
-        <v>56855</v>
+        <v>105506</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>102612</v>
+        <v>221144</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16624,10 +16624,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>544577</v>
+        <v>544321</v>
       </c>
       <c r="R161" t="n">
-        <v>6963169</v>
+        <v>6963319</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16660,11 +16660,6 @@
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>Individ noterad genom sång</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -16691,10 +16686,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128094051</v>
+        <v>128094047</v>
       </c>
       <c r="B162" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16726,10 +16721,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>544310</v>
+        <v>544641</v>
       </c>
       <c r="R162" t="n">
-        <v>6963314</v>
+        <v>6963158</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16766,7 +16761,7 @@
       </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>80 ex</t>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -16793,10 +16788,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128094045</v>
+        <v>128094051</v>
       </c>
       <c r="B163" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16828,10 +16823,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>544760</v>
+        <v>544310</v>
       </c>
       <c r="R163" t="n">
-        <v>6963251</v>
+        <v>6963314</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -16868,7 +16863,7 @@
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>35 ex</t>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -16895,32 +16890,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128094054</v>
+        <v>128094045</v>
       </c>
       <c r="B164" t="n">
-        <v>105505</v>
+        <v>98468</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -16930,10 +16925,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>544321</v>
+        <v>544760</v>
       </c>
       <c r="R164" t="n">
-        <v>6963319</v>
+        <v>6963251</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -16966,6 +16961,11 @@
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17301,7 +17301,7 @@
         <v>128094055</v>
       </c>
       <c r="B168" t="n">
-        <v>105505</v>
+        <v>105506</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>

--- a/artfynd/A 32240-2025 artfynd.xlsx
+++ b/artfynd/A 32240-2025 artfynd.xlsx
@@ -995,32 +995,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128087558</v>
+        <v>128087541</v>
       </c>
       <c r="B5" t="n">
-        <v>98468</v>
+        <v>78787</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544428</v>
+        <v>544267</v>
       </c>
       <c r="R5" t="n">
-        <v>6963233</v>
+        <v>6963196</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,11 +1066,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,32 +1092,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128087541</v>
+        <v>128087528</v>
       </c>
       <c r="B6" t="n">
-        <v>78787</v>
+        <v>80160</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6461</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544267</v>
+        <v>544198</v>
       </c>
       <c r="R6" t="n">
-        <v>6963196</v>
+        <v>6963228</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1189,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128087528</v>
+        <v>128087358</v>
       </c>
       <c r="B7" t="n">
         <v>80160</v>
@@ -1229,10 +1224,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544198</v>
+        <v>544278</v>
       </c>
       <c r="R7" t="n">
-        <v>6963228</v>
+        <v>6963265</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,10 +1286,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128087358</v>
+        <v>128087524</v>
       </c>
       <c r="B8" t="n">
-        <v>80160</v>
+        <v>80161</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,21 +1297,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1326,10 +1321,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544278</v>
+        <v>544281</v>
       </c>
       <c r="R8" t="n">
-        <v>6963265</v>
+        <v>6963082</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,32 +1383,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128087524</v>
+        <v>128087558</v>
       </c>
       <c r="B9" t="n">
-        <v>80161</v>
+        <v>98468</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1423,10 +1418,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544281</v>
+        <v>544428</v>
       </c>
       <c r="R9" t="n">
-        <v>6963082</v>
+        <v>6963233</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,6 +1454,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1485,32 +1485,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128087526</v>
+        <v>128078559</v>
       </c>
       <c r="B10" t="n">
-        <v>92632</v>
+        <v>97345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4361</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544728</v>
+        <v>544359</v>
       </c>
       <c r="R10" t="n">
-        <v>6963223</v>
+        <v>6963083</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,11 +1556,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>10 exemplar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1587,10 +1582,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128087516</v>
+        <v>128087526</v>
       </c>
       <c r="B11" t="n">
-        <v>57672</v>
+        <v>92632</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1598,21 +1593,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1622,10 +1617,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544388</v>
+        <v>544728</v>
       </c>
       <c r="R11" t="n">
-        <v>6963226</v>
+        <v>6963223</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1662,7 +1657,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall Äldre spår</t>
+          <t>10 exemplar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1689,32 +1684,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128078559</v>
+        <v>128087516</v>
       </c>
       <c r="B12" t="n">
-        <v>97345</v>
+        <v>57672</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1724,10 +1719,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544359</v>
+        <v>544388</v>
       </c>
       <c r="R12" t="n">
-        <v>6963083</v>
+        <v>6963226</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1760,6 +1755,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall Äldre spår</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2184,32 +2184,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128087520</v>
+        <v>128087550</v>
       </c>
       <c r="B17" t="n">
-        <v>57832</v>
+        <v>98468</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544771</v>
+        <v>544490</v>
       </c>
       <c r="R17" t="n">
-        <v>6963083</v>
+        <v>6963099</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2 stycken.  Övriga läten</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2286,32 +2286,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128087550</v>
+        <v>128087520</v>
       </c>
       <c r="B18" t="n">
-        <v>98468</v>
+        <v>57832</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544490</v>
+        <v>544771</v>
       </c>
       <c r="R18" t="n">
-        <v>6963099</v>
+        <v>6963083</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2 stycken.  Övriga läten</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2388,10 +2388,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128087581</v>
+        <v>128087354</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>80133</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2399,21 +2399,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2423,10 +2423,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544192</v>
+        <v>544820</v>
       </c>
       <c r="R19" t="n">
-        <v>6963197</v>
+        <v>6963278</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2485,10 +2485,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128087354</v>
+        <v>128087581</v>
       </c>
       <c r="B20" t="n">
-        <v>80133</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2496,21 +2496,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544820</v>
+        <v>544192</v>
       </c>
       <c r="R20" t="n">
-        <v>6963278</v>
+        <v>6963197</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2582,32 +2582,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128087569</v>
+        <v>128087362</v>
       </c>
       <c r="B21" t="n">
-        <v>98468</v>
+        <v>80132</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544296</v>
+        <v>544799</v>
       </c>
       <c r="R21" t="n">
-        <v>6963084</v>
+        <v>6963263</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2653,11 +2653,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>100stycken</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2684,32 +2679,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128087554</v>
+        <v>128087349</v>
       </c>
       <c r="B22" t="n">
-        <v>98468</v>
+        <v>80161</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2719,10 +2714,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544659</v>
+        <v>544475</v>
       </c>
       <c r="R22" t="n">
-        <v>6963253</v>
+        <v>6963205</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2755,11 +2750,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2786,32 +2776,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128087362</v>
+        <v>128087569</v>
       </c>
       <c r="B23" t="n">
-        <v>80132</v>
+        <v>98468</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2821,10 +2811,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544799</v>
+        <v>544296</v>
       </c>
       <c r="R23" t="n">
-        <v>6963263</v>
+        <v>6963084</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2857,6 +2847,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>100stycken</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2883,32 +2878,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128087349</v>
+        <v>128087554</v>
       </c>
       <c r="B24" t="n">
-        <v>80161</v>
+        <v>98468</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2918,10 +2913,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544475</v>
+        <v>544659</v>
       </c>
       <c r="R24" t="n">
-        <v>6963205</v>
+        <v>6963253</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2954,6 +2949,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3077,32 +3077,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128087562</v>
+        <v>128087331</v>
       </c>
       <c r="B26" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3112,10 +3112,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>544367</v>
+        <v>544763</v>
       </c>
       <c r="R26" t="n">
-        <v>6963253</v>
+        <v>6963244</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>7. Kan möjlitvis finnas fler runt omkring.</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3179,49 +3179,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128078161</v>
+        <v>128087333</v>
       </c>
       <c r="B27" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544362</v>
+        <v>544355</v>
       </c>
       <c r="R27" t="n">
-        <v>6963061</v>
+        <v>6963212</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3254,6 +3250,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3280,49 +3281,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128078740</v>
+        <v>128087382</v>
       </c>
       <c r="B28" t="n">
-        <v>98468</v>
+        <v>92640</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544307</v>
+        <v>544198</v>
       </c>
       <c r="R28" t="n">
-        <v>6963089</v>
+        <v>6963225</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3355,6 +3352,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3381,32 +3383,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128087563</v>
+        <v>128087532</v>
       </c>
       <c r="B29" t="n">
-        <v>98468</v>
+        <v>80132</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3416,10 +3418,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544322</v>
+        <v>544491</v>
       </c>
       <c r="R29" t="n">
-        <v>6963250</v>
+        <v>6963099</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3452,11 +3454,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>12 stycken</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3483,32 +3480,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128087382</v>
+        <v>128087562</v>
       </c>
       <c r="B30" t="n">
-        <v>92640</v>
+        <v>98468</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3518,10 +3515,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>544198</v>
+        <v>544367</v>
       </c>
       <c r="R30" t="n">
-        <v>6963225</v>
+        <v>6963253</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3558,7 +3555,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>5 ex</t>
+          <t>7. Kan möjlitvis finnas fler runt omkring.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3585,45 +3582,49 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128087532</v>
+        <v>128078161</v>
       </c>
       <c r="B31" t="n">
-        <v>80132</v>
+        <v>98468</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>544491</v>
+        <v>544362</v>
       </c>
       <c r="R31" t="n">
-        <v>6963099</v>
+        <v>6963061</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3682,45 +3683,49 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128087331</v>
+        <v>128078740</v>
       </c>
       <c r="B32" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544763</v>
+        <v>544307</v>
       </c>
       <c r="R32" t="n">
-        <v>6963244</v>
+        <v>6963089</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3753,11 +3758,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3784,32 +3784,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128087333</v>
+        <v>128087563</v>
       </c>
       <c r="B33" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>544355</v>
+        <v>544322</v>
       </c>
       <c r="R33" t="n">
-        <v>6963212</v>
+        <v>6963250</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3859,7 +3859,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>12 stycken</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3886,10 +3886,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128087336</v>
+        <v>128079621</v>
       </c>
       <c r="B34" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3897,21 +3897,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3921,10 +3921,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>544398</v>
+        <v>544274</v>
       </c>
       <c r="R34" t="n">
-        <v>6963202</v>
+        <v>6963119</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3957,11 +3957,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3988,7 +3983,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128079621</v>
+        <v>128087533</v>
       </c>
       <c r="B35" t="n">
         <v>80132</v>
@@ -4023,10 +4018,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>544274</v>
+        <v>544473</v>
       </c>
       <c r="R35" t="n">
-        <v>6963119</v>
+        <v>6963102</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4085,32 +4080,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128087533</v>
+        <v>128087351</v>
       </c>
       <c r="B36" t="n">
-        <v>80132</v>
+        <v>80161</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4120,10 +4115,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>544473</v>
+        <v>544299</v>
       </c>
       <c r="R36" t="n">
-        <v>6963102</v>
+        <v>6963312</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4182,32 +4177,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128087351</v>
+        <v>128087365</v>
       </c>
       <c r="B37" t="n">
-        <v>80161</v>
+        <v>80132</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4217,10 +4212,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>544299</v>
+        <v>544469</v>
       </c>
       <c r="R37" t="n">
-        <v>6963312</v>
+        <v>6963145</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4279,10 +4274,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128087365</v>
+        <v>128087336</v>
       </c>
       <c r="B38" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4290,21 +4285,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4314,10 +4309,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>544469</v>
+        <v>544398</v>
       </c>
       <c r="R38" t="n">
-        <v>6963145</v>
+        <v>6963202</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4350,6 +4345,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4376,32 +4376,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128087527</v>
+        <v>128087332</v>
       </c>
       <c r="B39" t="n">
-        <v>80160</v>
+        <v>57672</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>544246</v>
+        <v>544431</v>
       </c>
       <c r="R39" t="n">
-        <v>6963259</v>
+        <v>6963190</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4447,6 +4447,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4473,32 +4478,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128087369</v>
+        <v>128087517</v>
       </c>
       <c r="B40" t="n">
-        <v>80168</v>
+        <v>57672</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4508,10 +4513,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>544721</v>
+        <v>544381</v>
       </c>
       <c r="R40" t="n">
-        <v>6963277</v>
+        <v>6963236</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4544,6 +4549,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall Äldre ringhack som återanvänds ( äldre och färska)</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4672,32 +4682,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128087332</v>
+        <v>128087527</v>
       </c>
       <c r="B42" t="n">
-        <v>57672</v>
+        <v>80160</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4707,10 +4717,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>544431</v>
+        <v>544246</v>
       </c>
       <c r="R42" t="n">
-        <v>6963190</v>
+        <v>6963259</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4743,11 +4753,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4774,32 +4779,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128087517</v>
+        <v>128087369</v>
       </c>
       <c r="B43" t="n">
-        <v>57672</v>
+        <v>80168</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4809,10 +4814,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>544381</v>
+        <v>544721</v>
       </c>
       <c r="R43" t="n">
-        <v>6963236</v>
+        <v>6963277</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4845,11 +4850,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall Äldre ringhack som återanvänds ( äldre och färska)</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4876,32 +4876,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128087552</v>
+        <v>128087361</v>
       </c>
       <c r="B44" t="n">
-        <v>98468</v>
+        <v>80132</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4911,10 +4911,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>544687</v>
+        <v>544865</v>
       </c>
       <c r="R44" t="n">
-        <v>6963255</v>
+        <v>6963092</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4947,11 +4947,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>70</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4978,32 +4973,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128087548</v>
+        <v>128087360</v>
       </c>
       <c r="B45" t="n">
-        <v>98468</v>
+        <v>80132</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5013,10 +5008,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>544213</v>
+        <v>544615</v>
       </c>
       <c r="R45" t="n">
-        <v>6963197</v>
+        <v>6963093</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5049,11 +5044,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>100stycken.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5080,10 +5070,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128087361</v>
+        <v>128087340</v>
       </c>
       <c r="B46" t="n">
-        <v>80132</v>
+        <v>57832</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5091,21 +5081,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5115,10 +5105,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>544865</v>
+        <v>544485</v>
       </c>
       <c r="R46" t="n">
-        <v>6963092</v>
+        <v>6963237</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5177,32 +5167,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128087360</v>
+        <v>128079768</v>
       </c>
       <c r="B47" t="n">
-        <v>80132</v>
+        <v>97351</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>221941</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5212,10 +5202,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>544615</v>
+        <v>544287</v>
       </c>
       <c r="R47" t="n">
-        <v>6963093</v>
+        <v>6963168</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5274,32 +5264,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128087340</v>
+        <v>128087552</v>
       </c>
       <c r="B48" t="n">
-        <v>57832</v>
+        <v>98468</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5309,10 +5299,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>544485</v>
+        <v>544687</v>
       </c>
       <c r="R48" t="n">
-        <v>6963237</v>
+        <v>6963255</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5345,6 +5335,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>70</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5371,32 +5366,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128079768</v>
+        <v>128087548</v>
       </c>
       <c r="B49" t="n">
-        <v>97351</v>
+        <v>98468</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5406,10 +5401,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>544287</v>
+        <v>544213</v>
       </c>
       <c r="R49" t="n">
-        <v>6963168</v>
+        <v>6963197</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5442,6 +5437,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>100stycken.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5662,10 +5662,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128087339</v>
+        <v>128087364</v>
       </c>
       <c r="B52" t="n">
-        <v>57832</v>
+        <v>80132</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5673,21 +5673,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5697,10 +5697,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>544850</v>
+        <v>544774</v>
       </c>
       <c r="R52" t="n">
-        <v>6963099</v>
+        <v>6963282</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5733,11 +5733,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5764,32 +5759,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128079839</v>
+        <v>128087339</v>
       </c>
       <c r="B53" t="n">
-        <v>105506</v>
+        <v>57832</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5799,10 +5794,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>544288</v>
+        <v>544850</v>
       </c>
       <c r="R53" t="n">
-        <v>6963182</v>
+        <v>6963099</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5835,6 +5830,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5861,32 +5861,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128087553</v>
+        <v>128079839</v>
       </c>
       <c r="B54" t="n">
-        <v>98468</v>
+        <v>105506</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>544677</v>
+        <v>544288</v>
       </c>
       <c r="R54" t="n">
-        <v>6963260</v>
+        <v>6963182</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5932,11 +5932,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Mer än 70 stycken. Flera blommar</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5963,7 +5958,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128087555</v>
+        <v>128087553</v>
       </c>
       <c r="B55" t="n">
         <v>98468</v>
@@ -5998,10 +5993,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>544623</v>
+        <v>544677</v>
       </c>
       <c r="R55" t="n">
-        <v>6963241</v>
+        <v>6963260</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6038,7 +6033,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>60 stycken</t>
+          <t>Mer än 70 stycken. Flera blommar</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6065,32 +6060,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128087364</v>
+        <v>128087555</v>
       </c>
       <c r="B56" t="n">
-        <v>80132</v>
+        <v>98468</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6100,10 +6095,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>544774</v>
+        <v>544623</v>
       </c>
       <c r="R56" t="n">
-        <v>6963282</v>
+        <v>6963241</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6136,6 +6131,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>60 stycken</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6162,10 +6162,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128087356</v>
+        <v>128087585</v>
       </c>
       <c r="B57" t="n">
-        <v>80160</v>
+        <v>92640</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6173,21 +6173,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6461</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6197,10 +6197,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>544772</v>
+        <v>544536</v>
       </c>
       <c r="R57" t="n">
-        <v>6963323</v>
+        <v>6963255</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6233,6 +6233,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>8 äldre ex9 färska fruktkroppar</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6259,7 +6264,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128087357</v>
+        <v>128087356</v>
       </c>
       <c r="B58" t="n">
         <v>80160</v>
@@ -6294,10 +6299,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>544466</v>
+        <v>544772</v>
       </c>
       <c r="R58" t="n">
-        <v>6963277</v>
+        <v>6963323</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6356,50 +6361,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128080012</v>
+        <v>128087357</v>
       </c>
       <c r="B59" t="n">
-        <v>57672</v>
+        <v>80160</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>544324</v>
+        <v>544466</v>
       </c>
       <c r="R59" t="n">
-        <v>6963220</v>
+        <v>6963277</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6432,11 +6432,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6463,45 +6458,50 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128087585</v>
+        <v>128080012</v>
       </c>
       <c r="B60" t="n">
-        <v>92640</v>
+        <v>57672</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>544536</v>
+        <v>544324</v>
       </c>
       <c r="R60" t="n">
-        <v>6963255</v>
+        <v>6963220</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>8 äldre ex9 färska fruktkroppar</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6565,10 +6565,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128087579</v>
+        <v>128087386</v>
       </c>
       <c r="B61" t="n">
-        <v>79029</v>
+        <v>92634</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6576,21 +6576,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6600,10 +6600,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>544204</v>
+        <v>544822</v>
       </c>
       <c r="R61" t="n">
-        <v>6963238</v>
+        <v>6963295</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6636,11 +6636,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6667,32 +6662,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128087386</v>
+        <v>128087523</v>
       </c>
       <c r="B62" t="n">
-        <v>92634</v>
+        <v>80161</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4362</v>
+        <v>6462</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6702,10 +6697,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>544822</v>
+        <v>544253</v>
       </c>
       <c r="R62" t="n">
-        <v>6963295</v>
+        <v>6963139</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6764,32 +6759,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128078603</v>
+        <v>128087579</v>
       </c>
       <c r="B63" t="n">
-        <v>80161</v>
+        <v>79029</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6799,10 +6794,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>544360</v>
+        <v>544204</v>
       </c>
       <c r="R63" t="n">
-        <v>6963094</v>
+        <v>6963238</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6835,6 +6830,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6861,7 +6861,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128087523</v>
+        <v>128078603</v>
       </c>
       <c r="B64" t="n">
         <v>80161</v>
@@ -6896,10 +6896,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>544253</v>
+        <v>544360</v>
       </c>
       <c r="R64" t="n">
-        <v>6963139</v>
+        <v>6963094</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6958,10 +6958,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128087525</v>
+        <v>128087329</v>
       </c>
       <c r="B65" t="n">
-        <v>56248</v>
+        <v>57672</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6969,21 +6969,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6993,10 +6993,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>544385</v>
+        <v>544757</v>
       </c>
       <c r="R65" t="n">
-        <v>6963074</v>
+        <v>6963172</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7029,6 +7029,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7055,32 +7060,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128087329</v>
+        <v>128087566</v>
       </c>
       <c r="B66" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7090,10 +7095,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>544757</v>
+        <v>544261</v>
       </c>
       <c r="R66" t="n">
-        <v>6963172</v>
+        <v>6963170</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7130,7 +7135,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>4. Stycken. Finns möjligtvis fler i blåbärsriset.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7157,7 +7162,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128087566</v>
+        <v>128087377</v>
       </c>
       <c r="B67" t="n">
         <v>98468</v>
@@ -7192,10 +7197,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>544261</v>
+        <v>544403</v>
       </c>
       <c r="R67" t="n">
-        <v>6963170</v>
+        <v>6963221</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7232,7 +7237,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>4. Stycken. Finns möjligtvis fler i blåbärsriset.</t>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7259,7 +7264,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128087377</v>
+        <v>128087378</v>
       </c>
       <c r="B68" t="n">
         <v>98468</v>
@@ -7294,10 +7299,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>544403</v>
+        <v>544218</v>
       </c>
       <c r="R68" t="n">
-        <v>6963221</v>
+        <v>6963229</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7334,7 +7339,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>20 ex</t>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7361,7 +7366,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128087378</v>
+        <v>128087375</v>
       </c>
       <c r="B69" t="n">
         <v>98468</v>
@@ -7396,10 +7401,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>544218</v>
+        <v>544478</v>
       </c>
       <c r="R69" t="n">
-        <v>6963229</v>
+        <v>6963117</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7436,7 +7441,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>80 ex</t>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7463,32 +7468,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128087375</v>
+        <v>128087525</v>
       </c>
       <c r="B70" t="n">
-        <v>98468</v>
+        <v>56248</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>206004</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7498,10 +7503,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>544478</v>
+        <v>544385</v>
       </c>
       <c r="R70" t="n">
-        <v>6963117</v>
+        <v>6963074</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7534,11 +7539,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>35 ex</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8182,10 +8182,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128087575</v>
+        <v>128087570</v>
       </c>
       <c r="B77" t="n">
-        <v>92672</v>
+        <v>56855</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8193,21 +8193,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1968</v>
+        <v>102612</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8217,10 +8217,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>544532</v>
+        <v>544287</v>
       </c>
       <c r="R77" t="n">
-        <v>6963250</v>
+        <v>6963082</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8257,7 +8257,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Igen stor köttig svamp misstänker grantaggsvamp 2 ex</t>
+          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8284,45 +8284,49 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128078492</v>
+        <v>128079875</v>
       </c>
       <c r="B78" t="n">
-        <v>92672</v>
+        <v>98468</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1968</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>544362</v>
+        <v>544308</v>
       </c>
       <c r="R78" t="n">
-        <v>6963073</v>
+        <v>6963175</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8381,32 +8385,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128087536</v>
+        <v>128087542</v>
       </c>
       <c r="B79" t="n">
-        <v>80132</v>
+        <v>98468</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8416,10 +8420,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>544215</v>
+        <v>544752</v>
       </c>
       <c r="R79" t="n">
-        <v>6963245</v>
+        <v>6963192</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8452,6 +8456,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8478,45 +8487,49 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128087343</v>
+        <v>128080338</v>
       </c>
       <c r="B80" t="n">
-        <v>80161</v>
+        <v>98468</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>544757</v>
+        <v>544314</v>
       </c>
       <c r="R80" t="n">
-        <v>6963156</v>
+        <v>6963248</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8575,32 +8588,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128087346</v>
+        <v>128087547</v>
       </c>
       <c r="B81" t="n">
-        <v>80161</v>
+        <v>98468</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8610,10 +8623,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>544422</v>
+        <v>544380</v>
       </c>
       <c r="R81" t="n">
-        <v>6963240</v>
+        <v>6963236</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8646,6 +8659,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>33 stycken</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8672,32 +8690,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128087330</v>
+        <v>128087380</v>
       </c>
       <c r="B82" t="n">
-        <v>57672</v>
+        <v>105506</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8707,10 +8725,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>544750</v>
+        <v>544468</v>
       </c>
       <c r="R82" t="n">
-        <v>6963177</v>
+        <v>6963173</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8743,11 +8761,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8774,32 +8787,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128087335</v>
+        <v>128087560</v>
       </c>
       <c r="B83" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8809,10 +8822,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>544366</v>
+        <v>544383</v>
       </c>
       <c r="R83" t="n">
-        <v>6963181</v>
+        <v>6963236</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8849,7 +8862,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8876,10 +8889,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128087570</v>
+        <v>128087575</v>
       </c>
       <c r="B84" t="n">
-        <v>56855</v>
+        <v>92672</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8887,21 +8900,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>102612</v>
+        <v>1968</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8911,10 +8924,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>544287</v>
+        <v>544532</v>
       </c>
       <c r="R84" t="n">
-        <v>6963082</v>
+        <v>6963250</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8951,7 +8964,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Fjäder</t>
+          <t>Igen stor köttig svamp misstänker grantaggsvamp 2 ex</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8978,32 +8991,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128087380</v>
+        <v>128078492</v>
       </c>
       <c r="B85" t="n">
-        <v>105506</v>
+        <v>92672</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>221144</v>
+        <v>1968</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9013,10 +9026,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>544468</v>
+        <v>544362</v>
       </c>
       <c r="R85" t="n">
-        <v>6963173</v>
+        <v>6963073</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9075,49 +9088,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128079875</v>
+        <v>128087536</v>
       </c>
       <c r="B86" t="n">
-        <v>98468</v>
+        <v>80132</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>544308</v>
+        <v>544215</v>
       </c>
       <c r="R86" t="n">
-        <v>6963175</v>
+        <v>6963245</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9176,32 +9185,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128087542</v>
+        <v>128087343</v>
       </c>
       <c r="B87" t="n">
-        <v>98468</v>
+        <v>80161</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9211,10 +9220,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>544752</v>
+        <v>544757</v>
       </c>
       <c r="R87" t="n">
-        <v>6963192</v>
+        <v>6963156</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9247,11 +9256,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9278,49 +9282,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128080338</v>
+        <v>128087346</v>
       </c>
       <c r="B88" t="n">
-        <v>98468</v>
+        <v>80161</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>544314</v>
+        <v>544422</v>
       </c>
       <c r="R88" t="n">
-        <v>6963248</v>
+        <v>6963240</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9379,32 +9379,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128087547</v>
+        <v>128087330</v>
       </c>
       <c r="B89" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9414,10 +9414,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>544380</v>
+        <v>544750</v>
       </c>
       <c r="R89" t="n">
-        <v>6963236</v>
+        <v>6963177</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9454,7 +9454,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>33 stycken</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9481,32 +9481,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128087560</v>
+        <v>128087335</v>
       </c>
       <c r="B90" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9516,10 +9516,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>544383</v>
+        <v>544366</v>
       </c>
       <c r="R90" t="n">
-        <v>6963236</v>
+        <v>6963181</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9556,7 +9556,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>40 stycken</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9583,32 +9583,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128087376</v>
+        <v>128087587</v>
       </c>
       <c r="B91" t="n">
-        <v>98468</v>
+        <v>92640</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9618,10 +9618,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>544503</v>
+        <v>544245</v>
       </c>
       <c r="R91" t="n">
-        <v>6963182</v>
+        <v>6963255</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9658,7 +9658,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>60 ex</t>
+          <t>4stycken</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9685,32 +9685,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128087379</v>
+        <v>128087539</v>
       </c>
       <c r="B92" t="n">
-        <v>98468</v>
+        <v>80132</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9720,10 +9720,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>544263</v>
+        <v>544254</v>
       </c>
       <c r="R92" t="n">
-        <v>6963254</v>
+        <v>6963139</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9756,11 +9756,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>15 ex</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9787,10 +9782,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128087587</v>
+        <v>128087341</v>
       </c>
       <c r="B93" t="n">
-        <v>92640</v>
+        <v>80161</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9798,21 +9793,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9822,10 +9817,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>544245</v>
+        <v>544615</v>
       </c>
       <c r="R93" t="n">
-        <v>6963255</v>
+        <v>6963101</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9858,11 +9853,6 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>4stycken</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9889,32 +9879,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128087539</v>
+        <v>128087376</v>
       </c>
       <c r="B94" t="n">
-        <v>80132</v>
+        <v>98468</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9924,10 +9914,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>544254</v>
+        <v>544503</v>
       </c>
       <c r="R94" t="n">
-        <v>6963139</v>
+        <v>6963182</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9960,6 +9950,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>60 ex</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9986,32 +9981,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128087341</v>
+        <v>128087379</v>
       </c>
       <c r="B95" t="n">
-        <v>80161</v>
+        <v>98468</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10021,10 +10016,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>544615</v>
+        <v>544263</v>
       </c>
       <c r="R95" t="n">
-        <v>6963101</v>
+        <v>6963254</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10057,6 +10052,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10083,32 +10083,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128087576</v>
+        <v>128087383</v>
       </c>
       <c r="B96" t="n">
-        <v>92672</v>
+        <v>80167</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1968</v>
+        <v>6463</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10118,10 +10118,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>544529</v>
+        <v>544566</v>
       </c>
       <c r="R96" t="n">
-        <v>6963245</v>
+        <v>6963076</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10154,11 +10154,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Misstänkt grantaggsvamp men med mörk tydlig ring i mitten.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10185,32 +10180,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128087572</v>
+        <v>128087384</v>
       </c>
       <c r="B97" t="n">
-        <v>92672</v>
+        <v>80167</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1968</v>
+        <v>6463</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10220,10 +10215,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>544632</v>
+        <v>544584</v>
       </c>
       <c r="R97" t="n">
-        <v>6963245</v>
+        <v>6963261</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10256,11 +10251,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>1 ex</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10287,32 +10277,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128078864</v>
+        <v>128087522</v>
       </c>
       <c r="B98" t="n">
-        <v>105506</v>
+        <v>57832</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10322,10 +10312,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>544307</v>
+        <v>544494</v>
       </c>
       <c r="R98" t="n">
-        <v>6963089</v>
+        <v>6963243</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10384,32 +10374,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128087545</v>
+        <v>128087355</v>
       </c>
       <c r="B99" t="n">
-        <v>98468</v>
+        <v>97351</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10419,10 +10409,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>544633</v>
+        <v>544500</v>
       </c>
       <c r="R99" t="n">
-        <v>6963244</v>
+        <v>6963168</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10455,11 +10445,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10486,7 +10471,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128087567</v>
+        <v>128087545</v>
       </c>
       <c r="B100" t="n">
         <v>98468</v>
@@ -10521,10 +10506,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>544274</v>
+        <v>544633</v>
       </c>
       <c r="R100" t="n">
-        <v>6963090</v>
+        <v>6963244</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10561,7 +10546,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10588,7 +10573,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128087556</v>
+        <v>128087567</v>
       </c>
       <c r="B101" t="n">
         <v>98468</v>
@@ -10623,10 +10608,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>544594</v>
+        <v>544274</v>
       </c>
       <c r="R101" t="n">
-        <v>6963215</v>
+        <v>6963090</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10663,7 +10648,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>6 stycken. Kan finnas mer i omgivningen</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10690,7 +10675,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128087373</v>
+        <v>128087556</v>
       </c>
       <c r="B102" t="n">
         <v>98468</v>
@@ -10725,10 +10710,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>544469</v>
+        <v>544594</v>
       </c>
       <c r="R102" t="n">
-        <v>6963122</v>
+        <v>6963215</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10765,7 +10750,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>60 ex</t>
+          <t>6 stycken. Kan finnas mer i omgivningen</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10792,7 +10777,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128087559</v>
+        <v>128087373</v>
       </c>
       <c r="B103" t="n">
         <v>98468</v>
@@ -10827,10 +10812,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>544396</v>
+        <v>544469</v>
       </c>
       <c r="R103" t="n">
-        <v>6963233</v>
+        <v>6963122</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10867,7 +10852,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>18 stycken</t>
+          <t>60 ex</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10894,10 +10879,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128087383</v>
+        <v>128078864</v>
       </c>
       <c r="B104" t="n">
-        <v>80167</v>
+        <v>105506</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10905,21 +10890,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6463</v>
+        <v>221144</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10929,10 +10914,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>544566</v>
+        <v>544307</v>
       </c>
       <c r="R104" t="n">
-        <v>6963076</v>
+        <v>6963089</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10991,32 +10976,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128087384</v>
+        <v>128087559</v>
       </c>
       <c r="B105" t="n">
-        <v>80167</v>
+        <v>98468</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11026,10 +11011,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>544584</v>
+        <v>544396</v>
       </c>
       <c r="R105" t="n">
-        <v>6963261</v>
+        <v>6963233</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11062,6 +11047,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11088,10 +11078,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128087363</v>
+        <v>128087576</v>
       </c>
       <c r="B106" t="n">
-        <v>80132</v>
+        <v>92672</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11099,21 +11089,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6458</v>
+        <v>1968</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11123,10 +11113,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>544818</v>
+        <v>544529</v>
       </c>
       <c r="R106" t="n">
-        <v>6963278</v>
+        <v>6963245</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11159,6 +11149,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Misstänkt grantaggsvamp men med mörk tydlig ring i mitten.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11185,10 +11180,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128087522</v>
+        <v>128087572</v>
       </c>
       <c r="B107" t="n">
-        <v>57832</v>
+        <v>92672</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11196,21 +11191,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>103021</v>
+        <v>1968</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11220,10 +11215,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>544494</v>
+        <v>544632</v>
       </c>
       <c r="R107" t="n">
-        <v>6963243</v>
+        <v>6963245</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11256,6 +11251,11 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>1 ex</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11282,32 +11282,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128087355</v>
+        <v>128087363</v>
       </c>
       <c r="B108" t="n">
-        <v>97351</v>
+        <v>80132</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>221941</v>
+        <v>6458</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11317,10 +11317,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>544500</v>
+        <v>544818</v>
       </c>
       <c r="R108" t="n">
-        <v>6963168</v>
+        <v>6963278</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11379,10 +11379,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128087578</v>
+        <v>128087577</v>
       </c>
       <c r="B109" t="n">
-        <v>79029</v>
+        <v>92672</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11390,21 +11390,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>1968</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11414,10 +11414,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>544246</v>
+        <v>544494</v>
       </c>
       <c r="R109" t="n">
-        <v>6963257</v>
+        <v>6963243</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11476,10 +11476,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128087531</v>
+        <v>128087586</v>
       </c>
       <c r="B110" t="n">
-        <v>98502</v>
+        <v>92640</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11487,21 +11487,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>219874</v>
+        <v>4364</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11511,10 +11511,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>544755</v>
+        <v>544281</v>
       </c>
       <c r="R110" t="n">
-        <v>6963130</v>
+        <v>6963257</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11551,7 +11551,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>2 stycken</t>
+          <t>2 nya exemplar 8 äldre ex</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11578,49 +11578,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128079656</v>
+        <v>128087578</v>
       </c>
       <c r="B111" t="n">
-        <v>98468</v>
+        <v>79029</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>544277</v>
+        <v>544246</v>
       </c>
       <c r="R111" t="n">
-        <v>6963150</v>
+        <v>6963257</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11679,7 +11675,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128087565</v>
+        <v>128079656</v>
       </c>
       <c r="B112" t="n">
         <v>98468</v>
@@ -11707,17 +11703,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>544249</v>
+        <v>544277</v>
       </c>
       <c r="R112" t="n">
-        <v>6963223</v>
+        <v>6963150</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11750,11 +11750,6 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>10. Kan möjlitvis finns mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11781,7 +11776,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128087372</v>
+        <v>128087565</v>
       </c>
       <c r="B113" t="n">
         <v>98468</v>
@@ -11816,10 +11811,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>544472</v>
+        <v>544249</v>
       </c>
       <c r="R113" t="n">
-        <v>6963201</v>
+        <v>6963223</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11856,7 +11851,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>8 ex</t>
+          <t>10. Kan möjlitvis finns mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11883,7 +11878,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128087551</v>
+        <v>128087372</v>
       </c>
       <c r="B114" t="n">
         <v>98468</v>
@@ -11918,10 +11913,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>544694</v>
+        <v>544472</v>
       </c>
       <c r="R114" t="n">
-        <v>6963258</v>
+        <v>6963201</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11958,7 +11953,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11985,32 +11980,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128087577</v>
+        <v>128087551</v>
       </c>
       <c r="B115" t="n">
-        <v>92672</v>
+        <v>98468</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1968</v>
+        <v>220787</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12020,10 +12015,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>544494</v>
+        <v>544694</v>
       </c>
       <c r="R115" t="n">
-        <v>6963243</v>
+        <v>6963258</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12056,6 +12051,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12082,10 +12082,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128087586</v>
+        <v>128087531</v>
       </c>
       <c r="B116" t="n">
-        <v>92640</v>
+        <v>98502</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12093,21 +12093,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>4364</v>
+        <v>219874</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12117,10 +12117,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>544281</v>
+        <v>544755</v>
       </c>
       <c r="R116" t="n">
-        <v>6963257</v>
+        <v>6963130</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12157,7 +12157,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>2 nya exemplar 8 äldre ex</t>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12388,45 +12388,49 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128079848</v>
+        <v>128079571</v>
       </c>
       <c r="B119" t="n">
-        <v>79053</v>
+        <v>98468</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6434</v>
+        <v>220787</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>544288</v>
+        <v>544274</v>
       </c>
       <c r="R119" t="n">
-        <v>6963182</v>
+        <v>6963119</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12485,45 +12489,49 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128087538</v>
+        <v>128078138</v>
       </c>
       <c r="B120" t="n">
-        <v>80132</v>
+        <v>98468</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>544262</v>
+        <v>544374</v>
       </c>
       <c r="R120" t="n">
-        <v>6963163</v>
+        <v>6963056</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12582,32 +12590,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128087535</v>
+        <v>128079848</v>
       </c>
       <c r="B121" t="n">
-        <v>80132</v>
+        <v>79053</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6458</v>
+        <v>6434</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12617,10 +12625,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>544312</v>
+        <v>544288</v>
       </c>
       <c r="R121" t="n">
-        <v>6963244</v>
+        <v>6963182</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12679,32 +12687,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128087582</v>
+        <v>128087538</v>
       </c>
       <c r="B122" t="n">
-        <v>98385</v>
+        <v>80132</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12714,10 +12722,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>544489</v>
+        <v>544262</v>
       </c>
       <c r="R122" t="n">
-        <v>6963098</v>
+        <v>6963163</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12776,10 +12784,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128078823</v>
+        <v>128087535</v>
       </c>
       <c r="B123" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12787,21 +12795,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12811,10 +12819,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>544307</v>
+        <v>544312</v>
       </c>
       <c r="R123" t="n">
-        <v>6963089</v>
+        <v>6963244</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12873,49 +12881,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128079571</v>
+        <v>128078823</v>
       </c>
       <c r="B124" t="n">
-        <v>98468</v>
+        <v>79029</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>544274</v>
+        <v>544307</v>
       </c>
       <c r="R124" t="n">
-        <v>6963119</v>
+        <v>6963089</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12974,49 +12978,45 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128078138</v>
+        <v>128087582</v>
       </c>
       <c r="B125" t="n">
-        <v>98468</v>
+        <v>98385</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>544374</v>
+        <v>544489</v>
       </c>
       <c r="R125" t="n">
-        <v>6963056</v>
+        <v>6963098</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13376,32 +13376,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128087583</v>
+        <v>128087370</v>
       </c>
       <c r="B129" t="n">
-        <v>98385</v>
+        <v>98468</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13411,10 +13411,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>544708</v>
+        <v>544751</v>
       </c>
       <c r="R129" t="n">
-        <v>6963086</v>
+        <v>6963146</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13451,7 +13451,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13478,32 +13478,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128087584</v>
+        <v>128087371</v>
       </c>
       <c r="B130" t="n">
-        <v>98385</v>
+        <v>98468</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13513,10 +13513,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>544718</v>
+        <v>544559</v>
       </c>
       <c r="R130" t="n">
-        <v>6963053</v>
+        <v>6963215</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13553,7 +13553,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>3 stycken</t>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13580,32 +13580,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128087370</v>
+        <v>128087584</v>
       </c>
       <c r="B131" t="n">
-        <v>98468</v>
+        <v>98385</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13615,10 +13615,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>544751</v>
+        <v>544718</v>
       </c>
       <c r="R131" t="n">
-        <v>6963146</v>
+        <v>6963053</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13655,7 +13655,7 @@
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>30 ex</t>
+          <t>3 stycken</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13682,32 +13682,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128087371</v>
+        <v>128087583</v>
       </c>
       <c r="B132" t="n">
-        <v>98468</v>
+        <v>98385</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13717,10 +13717,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>544559</v>
+        <v>544708</v>
       </c>
       <c r="R132" t="n">
-        <v>6963215</v>
+        <v>6963086</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13757,7 +13757,7 @@
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>100 ex</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -13881,32 +13881,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128087381</v>
+        <v>128078645</v>
       </c>
       <c r="B134" t="n">
-        <v>98385</v>
+        <v>80132</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13916,10 +13916,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>544531</v>
+        <v>544360</v>
       </c>
       <c r="R134" t="n">
-        <v>6963190</v>
+        <v>6963094</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13978,32 +13978,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128078645</v>
+        <v>128087344</v>
       </c>
       <c r="B135" t="n">
-        <v>80132</v>
+        <v>80161</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14013,10 +14013,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>544360</v>
+        <v>544581</v>
       </c>
       <c r="R135" t="n">
-        <v>6963094</v>
+        <v>6963278</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14075,32 +14075,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128087344</v>
+        <v>128087534</v>
       </c>
       <c r="B136" t="n">
-        <v>80161</v>
+        <v>80132</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14110,10 +14110,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>544581</v>
+        <v>544326</v>
       </c>
       <c r="R136" t="n">
-        <v>6963278</v>
+        <v>6963248</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14172,7 +14172,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128087534</v>
+        <v>128087540</v>
       </c>
       <c r="B137" t="n">
         <v>80132</v>
@@ -14207,10 +14207,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>544326</v>
+        <v>544282</v>
       </c>
       <c r="R137" t="n">
-        <v>6963248</v>
+        <v>6963082</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14366,10 +14366,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128087540</v>
+        <v>128087328</v>
       </c>
       <c r="B139" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14377,21 +14377,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14401,10 +14401,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>544282</v>
+        <v>544736</v>
       </c>
       <c r="R139" t="n">
-        <v>6963082</v>
+        <v>6963153</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14437,6 +14437,11 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14463,32 +14468,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128087328</v>
+        <v>128087557</v>
       </c>
       <c r="B140" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14498,10 +14503,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>544736</v>
+        <v>544552</v>
       </c>
       <c r="R140" t="n">
-        <v>6963153</v>
+        <v>6963231</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14538,7 +14543,7 @@
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14565,7 +14570,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128087557</v>
+        <v>128087543</v>
       </c>
       <c r="B141" t="n">
         <v>98468</v>
@@ -14600,10 +14605,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>544552</v>
+        <v>544674</v>
       </c>
       <c r="R141" t="n">
-        <v>6963231</v>
+        <v>6963243</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14640,7 +14645,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>30 stycken</t>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14667,32 +14672,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128087543</v>
+        <v>128087381</v>
       </c>
       <c r="B142" t="n">
-        <v>98468</v>
+        <v>98385</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14702,10 +14707,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>544674</v>
+        <v>544531</v>
       </c>
       <c r="R142" t="n">
-        <v>6963243</v>
+        <v>6963190</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14738,11 +14743,6 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15472,32 +15472,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128094042</v>
+        <v>128094032</v>
       </c>
       <c r="B150" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15507,10 +15507,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>544528</v>
+        <v>544279</v>
       </c>
       <c r="R150" t="n">
-        <v>6963294</v>
+        <v>6963296</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15547,7 +15547,7 @@
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>75 ex</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15574,32 +15574,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128094032</v>
+        <v>128094042</v>
       </c>
       <c r="B151" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15609,10 +15609,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>544279</v>
+        <v>544528</v>
       </c>
       <c r="R151" t="n">
-        <v>6963296</v>
+        <v>6963294</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15649,7 +15649,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>75 ex</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16589,32 +16589,32 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128094054</v>
+        <v>128094047</v>
       </c>
       <c r="B161" t="n">
-        <v>105506</v>
+        <v>98468</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16624,10 +16624,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>544321</v>
+        <v>544641</v>
       </c>
       <c r="R161" t="n">
-        <v>6963319</v>
+        <v>6963158</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16660,6 +16660,11 @@
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -16686,7 +16691,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128094047</v>
+        <v>128094051</v>
       </c>
       <c r="B162" t="n">
         <v>98468</v>
@@ -16721,10 +16726,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>544641</v>
+        <v>544310</v>
       </c>
       <c r="R162" t="n">
-        <v>6963158</v>
+        <v>6963314</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16761,7 +16766,7 @@
       </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>11 ex</t>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -16788,7 +16793,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128094051</v>
+        <v>128094045</v>
       </c>
       <c r="B163" t="n">
         <v>98468</v>
@@ -16823,10 +16828,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>544310</v>
+        <v>544760</v>
       </c>
       <c r="R163" t="n">
-        <v>6963314</v>
+        <v>6963251</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -16863,7 +16868,7 @@
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>80 ex</t>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -16890,32 +16895,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128094045</v>
+        <v>128094054</v>
       </c>
       <c r="B164" t="n">
-        <v>98468</v>
+        <v>105506</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -16925,10 +16930,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>544760</v>
+        <v>544321</v>
       </c>
       <c r="R164" t="n">
-        <v>6963251</v>
+        <v>6963319</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -16961,11 +16966,6 @@
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>35 ex</t>
         </is>
       </c>
       <c r="AD164" t="b">

--- a/artfynd/A 32240-2025 artfynd.xlsx
+++ b/artfynd/A 32240-2025 artfynd.xlsx
@@ -995,32 +995,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128087541</v>
+        <v>128087528</v>
       </c>
       <c r="B5" t="n">
-        <v>78787</v>
+        <v>80160</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6461</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544267</v>
+        <v>544198</v>
       </c>
       <c r="R5" t="n">
-        <v>6963196</v>
+        <v>6963228</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,7 +1092,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128087528</v>
+        <v>128087358</v>
       </c>
       <c r="B6" t="n">
         <v>80160</v>
@@ -1127,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544198</v>
+        <v>544278</v>
       </c>
       <c r="R6" t="n">
-        <v>6963228</v>
+        <v>6963265</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128087358</v>
+        <v>128087524</v>
       </c>
       <c r="B7" t="n">
-        <v>80160</v>
+        <v>80161</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1200,21 +1200,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544278</v>
+        <v>544281</v>
       </c>
       <c r="R7" t="n">
-        <v>6963265</v>
+        <v>6963082</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,32 +1286,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128087524</v>
+        <v>128087541</v>
       </c>
       <c r="B8" t="n">
-        <v>80161</v>
+        <v>78787</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1321,10 +1321,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544281</v>
+        <v>544267</v>
       </c>
       <c r="R8" t="n">
-        <v>6963082</v>
+        <v>6963196</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,7 +1386,7 @@
         <v>128087558</v>
       </c>
       <c r="B9" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>128078559</v>
       </c>
       <c r="B10" t="n">
-        <v>97345</v>
+        <v>97346</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>128087526</v>
       </c>
       <c r="B11" t="n">
-        <v>92632</v>
+        <v>92633</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1980,32 +1980,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128087323</v>
+        <v>128087550</v>
       </c>
       <c r="B15" t="n">
-        <v>57672</v>
+        <v>98469</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2015,10 +2015,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544646</v>
+        <v>544490</v>
       </c>
       <c r="R15" t="n">
-        <v>6963095</v>
+        <v>6963099</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2184,32 +2184,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128087550</v>
+        <v>128087323</v>
       </c>
       <c r="B17" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544490</v>
+        <v>544646</v>
       </c>
       <c r="R17" t="n">
-        <v>6963099</v>
+        <v>6963095</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2388,10 +2388,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128087354</v>
+        <v>128087581</v>
       </c>
       <c r="B19" t="n">
-        <v>80133</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2399,21 +2399,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2423,10 +2423,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544820</v>
+        <v>544192</v>
       </c>
       <c r="R19" t="n">
-        <v>6963278</v>
+        <v>6963197</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2485,32 +2485,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128087581</v>
+        <v>128087569</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>98469</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544192</v>
+        <v>544296</v>
       </c>
       <c r="R20" t="n">
-        <v>6963197</v>
+        <v>6963084</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2556,6 +2556,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>100stycken</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2582,32 +2587,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128087362</v>
+        <v>128087554</v>
       </c>
       <c r="B21" t="n">
-        <v>80132</v>
+        <v>98469</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2617,10 +2622,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544799</v>
+        <v>544659</v>
       </c>
       <c r="R21" t="n">
-        <v>6963263</v>
+        <v>6963253</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2653,6 +2658,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2679,32 +2689,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128087349</v>
+        <v>128087359</v>
       </c>
       <c r="B22" t="n">
-        <v>80161</v>
+        <v>78788</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2714,10 +2724,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544475</v>
+        <v>544741</v>
       </c>
       <c r="R22" t="n">
-        <v>6963205</v>
+        <v>6963165</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2776,32 +2786,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128087569</v>
+        <v>128087354</v>
       </c>
       <c r="B23" t="n">
-        <v>98468</v>
+        <v>80133</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2811,10 +2821,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544296</v>
+        <v>544820</v>
       </c>
       <c r="R23" t="n">
-        <v>6963084</v>
+        <v>6963278</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2847,11 +2857,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>100stycken</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2878,32 +2883,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128087554</v>
+        <v>128087362</v>
       </c>
       <c r="B24" t="n">
-        <v>98468</v>
+        <v>80132</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2913,10 +2918,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544659</v>
+        <v>544799</v>
       </c>
       <c r="R24" t="n">
-        <v>6963253</v>
+        <v>6963263</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2949,11 +2954,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2980,32 +2980,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128087359</v>
+        <v>128087349</v>
       </c>
       <c r="B25" t="n">
-        <v>78788</v>
+        <v>80161</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544741</v>
+        <v>544475</v>
       </c>
       <c r="R25" t="n">
-        <v>6963165</v>
+        <v>6963205</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3077,32 +3077,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128087331</v>
+        <v>128087382</v>
       </c>
       <c r="B26" t="n">
-        <v>57672</v>
+        <v>92641</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3112,10 +3112,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>544763</v>
+        <v>544198</v>
       </c>
       <c r="R26" t="n">
-        <v>6963244</v>
+        <v>6963225</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3179,10 +3179,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128087333</v>
+        <v>128087532</v>
       </c>
       <c r="B27" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3190,21 +3190,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3214,10 +3214,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544355</v>
+        <v>544491</v>
       </c>
       <c r="R27" t="n">
-        <v>6963212</v>
+        <v>6963099</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3250,11 +3250,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3281,32 +3276,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128087382</v>
+        <v>128087562</v>
       </c>
       <c r="B28" t="n">
-        <v>92640</v>
+        <v>98469</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3316,10 +3311,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544198</v>
+        <v>544367</v>
       </c>
       <c r="R28" t="n">
-        <v>6963225</v>
+        <v>6963253</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3356,7 +3351,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>5 ex</t>
+          <t>7. Kan möjlitvis finnas fler runt omkring.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3383,45 +3378,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128087532</v>
+        <v>128078161</v>
       </c>
       <c r="B29" t="n">
-        <v>80132</v>
+        <v>98469</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544491</v>
+        <v>544362</v>
       </c>
       <c r="R29" t="n">
-        <v>6963099</v>
+        <v>6963061</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3480,10 +3479,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128087562</v>
+        <v>128078740</v>
       </c>
       <c r="B30" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3508,17 +3507,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>544367</v>
+        <v>544307</v>
       </c>
       <c r="R30" t="n">
-        <v>6963253</v>
+        <v>6963089</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3551,11 +3554,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>7. Kan möjlitvis finnas fler runt omkring.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3582,10 +3580,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128078161</v>
+        <v>128087563</v>
       </c>
       <c r="B31" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3610,21 +3608,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>544362</v>
+        <v>544322</v>
       </c>
       <c r="R31" t="n">
-        <v>6963061</v>
+        <v>6963250</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3657,6 +3651,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>12 stycken</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3683,49 +3682,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128078740</v>
+        <v>128087333</v>
       </c>
       <c r="B32" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544307</v>
+        <v>544355</v>
       </c>
       <c r="R32" t="n">
-        <v>6963089</v>
+        <v>6963212</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3758,6 +3753,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3784,32 +3784,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128087563</v>
+        <v>128087331</v>
       </c>
       <c r="B33" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>544322</v>
+        <v>544763</v>
       </c>
       <c r="R33" t="n">
-        <v>6963250</v>
+        <v>6963244</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3859,7 +3859,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>12 stycken</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4376,32 +4376,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128087332</v>
+        <v>128087588</v>
       </c>
       <c r="B39" t="n">
-        <v>57672</v>
+        <v>92641</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>544431</v>
+        <v>544183</v>
       </c>
       <c r="R39" t="n">
-        <v>6963190</v>
+        <v>6963214</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>9 ex äldre exemplar</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4478,32 +4478,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128087517</v>
+        <v>128087527</v>
       </c>
       <c r="B40" t="n">
-        <v>57672</v>
+        <v>80160</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4513,10 +4513,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>544381</v>
+        <v>544246</v>
       </c>
       <c r="R40" t="n">
-        <v>6963236</v>
+        <v>6963259</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4549,11 +4549,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall Äldre ringhack som återanvänds ( äldre och färska)</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4580,10 +4575,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128087588</v>
+        <v>128087369</v>
       </c>
       <c r="B41" t="n">
-        <v>92640</v>
+        <v>80168</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4591,21 +4586,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4615,10 +4610,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>544183</v>
+        <v>544721</v>
       </c>
       <c r="R41" t="n">
-        <v>6963214</v>
+        <v>6963277</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4651,11 +4646,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>9 ex äldre exemplar</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4682,32 +4672,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128087527</v>
+        <v>128087332</v>
       </c>
       <c r="B42" t="n">
-        <v>80160</v>
+        <v>57672</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4717,10 +4707,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>544246</v>
+        <v>544431</v>
       </c>
       <c r="R42" t="n">
-        <v>6963259</v>
+        <v>6963190</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4753,6 +4743,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4779,32 +4774,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128087369</v>
+        <v>128087517</v>
       </c>
       <c r="B43" t="n">
-        <v>80168</v>
+        <v>57672</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4814,10 +4809,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>544721</v>
+        <v>544381</v>
       </c>
       <c r="R43" t="n">
-        <v>6963277</v>
+        <v>6963236</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4850,6 +4845,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall Äldre ringhack som återanvänds ( äldre och färska)</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4876,7 +4876,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128087361</v>
+        <v>128087360</v>
       </c>
       <c r="B44" t="n">
         <v>80132</v>
@@ -4911,10 +4911,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>544865</v>
+        <v>544615</v>
       </c>
       <c r="R44" t="n">
-        <v>6963092</v>
+        <v>6963093</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4973,7 +4973,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128087360</v>
+        <v>128087361</v>
       </c>
       <c r="B45" t="n">
         <v>80132</v>
@@ -5008,10 +5008,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>544615</v>
+        <v>544865</v>
       </c>
       <c r="R45" t="n">
-        <v>6963093</v>
+        <v>6963092</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5167,32 +5167,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128079768</v>
+        <v>128087552</v>
       </c>
       <c r="B47" t="n">
-        <v>97351</v>
+        <v>98469</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5202,10 +5202,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>544287</v>
+        <v>544687</v>
       </c>
       <c r="R47" t="n">
-        <v>6963168</v>
+        <v>6963255</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5238,6 +5238,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>70</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5264,10 +5269,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128087552</v>
+        <v>128087548</v>
       </c>
       <c r="B48" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5299,10 +5304,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>544687</v>
+        <v>544213</v>
       </c>
       <c r="R48" t="n">
-        <v>6963255</v>
+        <v>6963197</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5339,7 +5344,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>100stycken.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5366,32 +5371,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128087548</v>
+        <v>128079768</v>
       </c>
       <c r="B49" t="n">
-        <v>98468</v>
+        <v>97352</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5401,10 +5406,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>544213</v>
+        <v>544287</v>
       </c>
       <c r="R49" t="n">
-        <v>6963197</v>
+        <v>6963168</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5437,11 +5442,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>100stycken.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5468,32 +5468,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128087342</v>
+        <v>128087339</v>
       </c>
       <c r="B50" t="n">
-        <v>80161</v>
+        <v>57832</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5503,10 +5503,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>544848</v>
+        <v>544850</v>
       </c>
       <c r="R50" t="n">
-        <v>6963086</v>
+        <v>6963099</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5539,6 +5539,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5565,32 +5570,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128087367</v>
+        <v>128079839</v>
       </c>
       <c r="B51" t="n">
-        <v>80132</v>
+        <v>105507</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>221144</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5600,10 +5605,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>544298</v>
+        <v>544288</v>
       </c>
       <c r="R51" t="n">
-        <v>6963312</v>
+        <v>6963182</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5662,32 +5667,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128087364</v>
+        <v>128087342</v>
       </c>
       <c r="B52" t="n">
-        <v>80132</v>
+        <v>80161</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5697,10 +5702,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>544774</v>
+        <v>544848</v>
       </c>
       <c r="R52" t="n">
-        <v>6963282</v>
+        <v>6963086</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5759,10 +5764,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128087339</v>
+        <v>128087367</v>
       </c>
       <c r="B53" t="n">
-        <v>57832</v>
+        <v>80132</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5770,21 +5775,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5794,10 +5799,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>544850</v>
+        <v>544298</v>
       </c>
       <c r="R53" t="n">
-        <v>6963099</v>
+        <v>6963312</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5830,11 +5835,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5861,32 +5861,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128079839</v>
+        <v>128087364</v>
       </c>
       <c r="B54" t="n">
-        <v>105506</v>
+        <v>80132</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221144</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>544288</v>
+        <v>544774</v>
       </c>
       <c r="R54" t="n">
-        <v>6963182</v>
+        <v>6963282</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5961,7 +5961,7 @@
         <v>128087553</v>
       </c>
       <c r="B55" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>128087555</v>
       </c>
       <c r="B56" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>128087585</v>
       </c>
       <c r="B57" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6565,10 +6565,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128087386</v>
+        <v>128087525</v>
       </c>
       <c r="B61" t="n">
-        <v>92634</v>
+        <v>56248</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6576,21 +6576,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4362</v>
+        <v>206004</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6600,10 +6600,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>544822</v>
+        <v>544385</v>
       </c>
       <c r="R61" t="n">
-        <v>6963295</v>
+        <v>6963074</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6662,32 +6662,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128087523</v>
+        <v>128087377</v>
       </c>
       <c r="B62" t="n">
-        <v>80161</v>
+        <v>98469</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6697,10 +6697,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>544253</v>
+        <v>544403</v>
       </c>
       <c r="R62" t="n">
-        <v>6963139</v>
+        <v>6963221</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6733,6 +6733,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6759,32 +6764,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128087579</v>
+        <v>128087566</v>
       </c>
       <c r="B63" t="n">
-        <v>79029</v>
+        <v>98469</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6794,10 +6799,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>544204</v>
+        <v>544261</v>
       </c>
       <c r="R63" t="n">
-        <v>6963238</v>
+        <v>6963170</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6834,7 +6839,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Riklig förekomst av garnlav</t>
+          <t>4. Stycken. Finns möjligtvis fler i blåbärsriset.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6861,32 +6866,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128078603</v>
+        <v>128087378</v>
       </c>
       <c r="B64" t="n">
-        <v>80161</v>
+        <v>98469</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6896,10 +6901,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>544360</v>
+        <v>544218</v>
       </c>
       <c r="R64" t="n">
-        <v>6963094</v>
+        <v>6963229</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6932,6 +6937,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6958,32 +6968,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128087329</v>
+        <v>128087375</v>
       </c>
       <c r="B65" t="n">
-        <v>57672</v>
+        <v>98469</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6993,10 +7003,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>544757</v>
+        <v>544478</v>
       </c>
       <c r="R65" t="n">
-        <v>6963172</v>
+        <v>6963117</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7033,7 +7043,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7060,32 +7070,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128087566</v>
+        <v>128087386</v>
       </c>
       <c r="B66" t="n">
-        <v>98468</v>
+        <v>92635</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>4362</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7095,10 +7105,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>544261</v>
+        <v>544822</v>
       </c>
       <c r="R66" t="n">
-        <v>6963170</v>
+        <v>6963295</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7131,11 +7141,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>4. Stycken. Finns möjligtvis fler i blåbärsriset.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7162,32 +7167,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128087377</v>
+        <v>128078603</v>
       </c>
       <c r="B67" t="n">
-        <v>98468</v>
+        <v>80161</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7197,10 +7202,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>544403</v>
+        <v>544360</v>
       </c>
       <c r="R67" t="n">
-        <v>6963221</v>
+        <v>6963094</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7233,11 +7238,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>20 ex</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7264,32 +7264,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128087378</v>
+        <v>128087523</v>
       </c>
       <c r="B68" t="n">
-        <v>98468</v>
+        <v>80161</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7299,10 +7299,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>544218</v>
+        <v>544253</v>
       </c>
       <c r="R68" t="n">
-        <v>6963229</v>
+        <v>6963139</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7335,11 +7335,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>80 ex</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7366,32 +7361,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128087375</v>
+        <v>128087579</v>
       </c>
       <c r="B69" t="n">
-        <v>98468</v>
+        <v>79029</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7401,10 +7396,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>544478</v>
+        <v>544204</v>
       </c>
       <c r="R69" t="n">
-        <v>6963117</v>
+        <v>6963238</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7441,7 +7436,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>35 ex</t>
+          <t>Riklig förekomst av garnlav</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7468,10 +7463,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128087525</v>
+        <v>128087329</v>
       </c>
       <c r="B70" t="n">
-        <v>56248</v>
+        <v>57672</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7479,21 +7474,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7503,10 +7498,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>544385</v>
+        <v>544757</v>
       </c>
       <c r="R70" t="n">
-        <v>6963074</v>
+        <v>6963172</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7539,6 +7534,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7759,7 +7759,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128087337</v>
+        <v>128080054</v>
       </c>
       <c r="B73" t="n">
         <v>57672</v>
@@ -7788,16 +7788,21 @@
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>544197</v>
+        <v>544301</v>
       </c>
       <c r="R73" t="n">
-        <v>6963237</v>
+        <v>6963231</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7834,7 +7839,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7968,7 +7973,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128080054</v>
+        <v>128080149</v>
       </c>
       <c r="B75" t="n">
         <v>57672</v>
@@ -8008,10 +8013,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>544301</v>
+        <v>544295</v>
       </c>
       <c r="R75" t="n">
-        <v>6963231</v>
+        <v>6963226</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8075,7 +8080,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128080149</v>
+        <v>128087337</v>
       </c>
       <c r="B76" t="n">
         <v>57672</v>
@@ -8104,21 +8109,16 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>544295</v>
+        <v>544197</v>
       </c>
       <c r="R76" t="n">
-        <v>6963226</v>
+        <v>6963237</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8155,7 +8155,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8182,10 +8182,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128087570</v>
+        <v>128087575</v>
       </c>
       <c r="B77" t="n">
-        <v>56855</v>
+        <v>92673</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8193,21 +8193,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>102612</v>
+        <v>1968</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8217,10 +8217,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>544287</v>
+        <v>544532</v>
       </c>
       <c r="R77" t="n">
-        <v>6963082</v>
+        <v>6963250</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8257,7 +8257,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Fjäder</t>
+          <t>Igen stor köttig svamp misstänker grantaggsvamp 2 ex</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8284,49 +8284,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128079875</v>
+        <v>128078492</v>
       </c>
       <c r="B78" t="n">
-        <v>98468</v>
+        <v>92673</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>1968</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>544308</v>
+        <v>544362</v>
       </c>
       <c r="R78" t="n">
-        <v>6963175</v>
+        <v>6963073</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8385,32 +8381,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128087542</v>
+        <v>128087536</v>
       </c>
       <c r="B79" t="n">
-        <v>98468</v>
+        <v>80132</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8420,10 +8416,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>544752</v>
+        <v>544215</v>
       </c>
       <c r="R79" t="n">
-        <v>6963192</v>
+        <v>6963245</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8456,11 +8452,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8487,49 +8478,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128080338</v>
+        <v>128087343</v>
       </c>
       <c r="B80" t="n">
-        <v>98468</v>
+        <v>80161</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>544314</v>
+        <v>544757</v>
       </c>
       <c r="R80" t="n">
-        <v>6963248</v>
+        <v>6963156</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8588,32 +8575,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128087547</v>
+        <v>128087346</v>
       </c>
       <c r="B81" t="n">
-        <v>98468</v>
+        <v>80161</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8623,10 +8610,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>544380</v>
+        <v>544422</v>
       </c>
       <c r="R81" t="n">
-        <v>6963236</v>
+        <v>6963240</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8659,11 +8646,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>33 stycken</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8690,32 +8672,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128087380</v>
+        <v>128087335</v>
       </c>
       <c r="B82" t="n">
-        <v>105506</v>
+        <v>57672</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221144</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8725,10 +8707,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>544468</v>
+        <v>544366</v>
       </c>
       <c r="R82" t="n">
-        <v>6963173</v>
+        <v>6963181</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8761,6 +8743,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8787,32 +8774,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128087560</v>
+        <v>128087330</v>
       </c>
       <c r="B83" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8822,10 +8809,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>544383</v>
+        <v>544750</v>
       </c>
       <c r="R83" t="n">
-        <v>6963236</v>
+        <v>6963177</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8862,7 +8849,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>40 stycken</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8889,10 +8876,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128087575</v>
+        <v>128087570</v>
       </c>
       <c r="B84" t="n">
-        <v>92672</v>
+        <v>56855</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8900,21 +8887,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1968</v>
+        <v>102612</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8924,10 +8911,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>544532</v>
+        <v>544287</v>
       </c>
       <c r="R84" t="n">
-        <v>6963250</v>
+        <v>6963082</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8964,7 +8951,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Igen stor köttig svamp misstänker grantaggsvamp 2 ex</t>
+          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8991,45 +8978,49 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128078492</v>
+        <v>128079875</v>
       </c>
       <c r="B85" t="n">
-        <v>92672</v>
+        <v>98469</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1968</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>544362</v>
+        <v>544308</v>
       </c>
       <c r="R85" t="n">
-        <v>6963073</v>
+        <v>6963175</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9088,32 +9079,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128087536</v>
+        <v>128087542</v>
       </c>
       <c r="B86" t="n">
-        <v>80132</v>
+        <v>98469</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9123,10 +9114,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>544215</v>
+        <v>544752</v>
       </c>
       <c r="R86" t="n">
-        <v>6963245</v>
+        <v>6963192</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9159,6 +9150,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9185,45 +9181,49 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128087343</v>
+        <v>128080338</v>
       </c>
       <c r="B87" t="n">
-        <v>80161</v>
+        <v>98469</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>544757</v>
+        <v>544314</v>
       </c>
       <c r="R87" t="n">
-        <v>6963156</v>
+        <v>6963248</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9282,32 +9282,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128087346</v>
+        <v>128087547</v>
       </c>
       <c r="B88" t="n">
-        <v>80161</v>
+        <v>98469</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9317,10 +9317,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>544422</v>
+        <v>544380</v>
       </c>
       <c r="R88" t="n">
-        <v>6963240</v>
+        <v>6963236</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9353,6 +9353,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>33 stycken</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9379,32 +9384,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128087330</v>
+        <v>128087560</v>
       </c>
       <c r="B89" t="n">
-        <v>57672</v>
+        <v>98469</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9414,10 +9419,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>544750</v>
+        <v>544383</v>
       </c>
       <c r="R89" t="n">
-        <v>6963177</v>
+        <v>6963236</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9454,7 +9459,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9481,32 +9486,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128087335</v>
+        <v>128087380</v>
       </c>
       <c r="B90" t="n">
-        <v>57672</v>
+        <v>105507</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9516,10 +9521,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>544366</v>
+        <v>544468</v>
       </c>
       <c r="R90" t="n">
-        <v>6963181</v>
+        <v>6963173</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9552,11 +9557,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9586,7 +9586,7 @@
         <v>128087587</v>
       </c>
       <c r="B91" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         <v>128087376</v>
       </c>
       <c r="B94" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>128087379</v>
       </c>
       <c r="B95" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10277,10 +10277,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128087522</v>
+        <v>128087363</v>
       </c>
       <c r="B98" t="n">
-        <v>57832</v>
+        <v>80132</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10288,21 +10288,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10312,10 +10312,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>544494</v>
+        <v>544818</v>
       </c>
       <c r="R98" t="n">
-        <v>6963243</v>
+        <v>6963278</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10374,32 +10374,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128087355</v>
+        <v>128087522</v>
       </c>
       <c r="B99" t="n">
-        <v>97351</v>
+        <v>57832</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10409,10 +10409,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>544500</v>
+        <v>544494</v>
       </c>
       <c r="R99" t="n">
-        <v>6963168</v>
+        <v>6963243</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10474,7 +10474,7 @@
         <v>128087545</v>
       </c>
       <c r="B100" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10576,7 +10576,7 @@
         <v>128087567</v>
       </c>
       <c r="B101" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
         <v>128087556</v>
       </c>
       <c r="B102" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>128087373</v>
       </c>
       <c r="B103" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10879,10 +10879,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128078864</v>
+        <v>128087355</v>
       </c>
       <c r="B104" t="n">
-        <v>105506</v>
+        <v>97352</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10890,21 +10890,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>221144</v>
+        <v>221941</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10914,10 +10914,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>544307</v>
+        <v>544500</v>
       </c>
       <c r="R104" t="n">
-        <v>6963089</v>
+        <v>6963168</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10979,7 +10979,7 @@
         <v>128087559</v>
       </c>
       <c r="B105" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11078,32 +11078,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128087576</v>
+        <v>128078864</v>
       </c>
       <c r="B106" t="n">
-        <v>92672</v>
+        <v>105507</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1968</v>
+        <v>221144</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11113,10 +11113,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>544529</v>
+        <v>544307</v>
       </c>
       <c r="R106" t="n">
-        <v>6963245</v>
+        <v>6963089</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11149,11 +11149,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Misstänkt grantaggsvamp men med mörk tydlig ring i mitten.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11180,10 +11175,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128087572</v>
+        <v>128087576</v>
       </c>
       <c r="B107" t="n">
-        <v>92672</v>
+        <v>92673</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11215,7 +11210,7 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>544632</v>
+        <v>544529</v>
       </c>
       <c r="R107" t="n">
         <v>6963245</v>
@@ -11255,7 +11250,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>1 ex</t>
+          <t>Misstänkt grantaggsvamp men med mörk tydlig ring i mitten.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11282,10 +11277,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128087363</v>
+        <v>128087572</v>
       </c>
       <c r="B108" t="n">
-        <v>80132</v>
+        <v>92673</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11293,21 +11288,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6458</v>
+        <v>1968</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11317,10 +11312,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>544818</v>
+        <v>544632</v>
       </c>
       <c r="R108" t="n">
-        <v>6963278</v>
+        <v>6963245</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11353,6 +11348,11 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>1 ex</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11382,7 +11382,7 @@
         <v>128087577</v>
       </c>
       <c r="B109" t="n">
-        <v>92672</v>
+        <v>92673</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11476,45 +11476,49 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128087586</v>
+        <v>128079656</v>
       </c>
       <c r="B110" t="n">
-        <v>92640</v>
+        <v>98469</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>544281</v>
+        <v>544277</v>
       </c>
       <c r="R110" t="n">
-        <v>6963257</v>
+        <v>6963150</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11547,11 +11551,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>2 nya exemplar 8 äldre ex</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11578,32 +11577,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128087578</v>
+        <v>128087565</v>
       </c>
       <c r="B111" t="n">
-        <v>79029</v>
+        <v>98469</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11613,10 +11612,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>544246</v>
+        <v>544249</v>
       </c>
       <c r="R111" t="n">
-        <v>6963257</v>
+        <v>6963223</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11649,6 +11648,11 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>10. Kan möjlitvis finns mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11675,10 +11679,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128079656</v>
+        <v>128087372</v>
       </c>
       <c r="B112" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11703,21 +11707,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>544277</v>
+        <v>544472</v>
       </c>
       <c r="R112" t="n">
-        <v>6963150</v>
+        <v>6963201</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11750,6 +11750,11 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11776,10 +11781,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128087565</v>
+        <v>128087551</v>
       </c>
       <c r="B113" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11811,10 +11816,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>544249</v>
+        <v>544694</v>
       </c>
       <c r="R113" t="n">
-        <v>6963223</v>
+        <v>6963258</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11851,7 +11856,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>10. Kan möjlitvis finns mer i blåbärsriset</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11878,32 +11883,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128087372</v>
+        <v>128087531</v>
       </c>
       <c r="B114" t="n">
-        <v>98468</v>
+        <v>98503</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11913,10 +11918,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>544472</v>
+        <v>544755</v>
       </c>
       <c r="R114" t="n">
-        <v>6963201</v>
+        <v>6963130</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11953,7 +11958,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>8 ex</t>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11980,32 +11985,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128087551</v>
+        <v>128087586</v>
       </c>
       <c r="B115" t="n">
-        <v>98468</v>
+        <v>92641</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12015,10 +12020,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>544694</v>
+        <v>544281</v>
       </c>
       <c r="R115" t="n">
-        <v>6963258</v>
+        <v>6963257</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12055,7 +12060,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2 nya exemplar 8 äldre ex</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12082,32 +12087,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128087531</v>
+        <v>128087578</v>
       </c>
       <c r="B116" t="n">
-        <v>98502</v>
+        <v>79029</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>219874</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12117,10 +12122,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>544755</v>
+        <v>544246</v>
       </c>
       <c r="R116" t="n">
-        <v>6963130</v>
+        <v>6963257</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12153,11 +12158,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12187,7 +12187,7 @@
         <v>128087571</v>
       </c>
       <c r="B117" t="n">
-        <v>92672</v>
+        <v>92673</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>128087573</v>
       </c>
       <c r="B118" t="n">
-        <v>92672</v>
+        <v>92673</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12388,49 +12388,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128079571</v>
+        <v>128087538</v>
       </c>
       <c r="B119" t="n">
-        <v>98468</v>
+        <v>80132</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>544274</v>
+        <v>544262</v>
       </c>
       <c r="R119" t="n">
-        <v>6963119</v>
+        <v>6963163</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12489,49 +12485,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128078138</v>
+        <v>128087535</v>
       </c>
       <c r="B120" t="n">
-        <v>98468</v>
+        <v>80132</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>544374</v>
+        <v>544312</v>
       </c>
       <c r="R120" t="n">
-        <v>6963056</v>
+        <v>6963244</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12687,10 +12679,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128087538</v>
+        <v>128078823</v>
       </c>
       <c r="B122" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12698,21 +12690,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12722,10 +12714,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>544262</v>
+        <v>544307</v>
       </c>
       <c r="R122" t="n">
-        <v>6963163</v>
+        <v>6963089</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12784,32 +12776,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128087535</v>
+        <v>128087582</v>
       </c>
       <c r="B123" t="n">
-        <v>80132</v>
+        <v>98386</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12819,10 +12811,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>544312</v>
+        <v>544489</v>
       </c>
       <c r="R123" t="n">
-        <v>6963244</v>
+        <v>6963098</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12881,45 +12873,49 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128078823</v>
+        <v>128079571</v>
       </c>
       <c r="B124" t="n">
-        <v>79029</v>
+        <v>98469</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>544307</v>
+        <v>544274</v>
       </c>
       <c r="R124" t="n">
-        <v>6963089</v>
+        <v>6963119</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12978,45 +12974,49 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128087582</v>
+        <v>128078138</v>
       </c>
       <c r="B125" t="n">
-        <v>98385</v>
+        <v>98469</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>544489</v>
+        <v>544374</v>
       </c>
       <c r="R125" t="n">
-        <v>6963098</v>
+        <v>6963056</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13075,32 +13075,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128087574</v>
+        <v>128079484</v>
       </c>
       <c r="B126" t="n">
-        <v>92672</v>
+        <v>80168</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1968</v>
+        <v>6464</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13110,10 +13110,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>544552</v>
+        <v>544289</v>
       </c>
       <c r="R126" t="n">
-        <v>6963231</v>
+        <v>6963113</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13146,11 +13146,6 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Misstänker grantaggsvamp 1 exemplar</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13177,32 +13172,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128079484</v>
+        <v>128087334</v>
       </c>
       <c r="B127" t="n">
-        <v>80168</v>
+        <v>57672</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13212,10 +13207,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>544289</v>
+        <v>544348</v>
       </c>
       <c r="R127" t="n">
-        <v>6963113</v>
+        <v>6963187</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13248,6 +13243,11 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13274,32 +13274,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128087334</v>
+        <v>128087583</v>
       </c>
       <c r="B128" t="n">
-        <v>57672</v>
+        <v>98386</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13309,10 +13309,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>544348</v>
+        <v>544708</v>
       </c>
       <c r="R128" t="n">
-        <v>6963187</v>
+        <v>6963086</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13349,7 +13349,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13376,32 +13376,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128087370</v>
+        <v>128087584</v>
       </c>
       <c r="B129" t="n">
-        <v>98468</v>
+        <v>98386</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13411,10 +13411,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>544751</v>
+        <v>544718</v>
       </c>
       <c r="R129" t="n">
-        <v>6963146</v>
+        <v>6963053</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13451,7 +13451,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>30 ex</t>
+          <t>3 stycken</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13478,10 +13478,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128087371</v>
+        <v>128087370</v>
       </c>
       <c r="B130" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13513,10 +13513,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>544559</v>
+        <v>544751</v>
       </c>
       <c r="R130" t="n">
-        <v>6963215</v>
+        <v>6963146</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13553,7 +13553,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>100 ex</t>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13580,32 +13580,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128087584</v>
+        <v>128087371</v>
       </c>
       <c r="B131" t="n">
-        <v>98385</v>
+        <v>98469</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13615,10 +13615,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>544718</v>
+        <v>544559</v>
       </c>
       <c r="R131" t="n">
-        <v>6963053</v>
+        <v>6963215</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13655,7 +13655,7 @@
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>3 stycken</t>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13682,32 +13682,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128087583</v>
+        <v>128087574</v>
       </c>
       <c r="B132" t="n">
-        <v>98385</v>
+        <v>92673</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>219790</v>
+        <v>1968</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13717,10 +13717,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>544708</v>
+        <v>544552</v>
       </c>
       <c r="R132" t="n">
-        <v>6963086</v>
+        <v>6963231</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13757,7 +13757,7 @@
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Misstänker grantaggsvamp 1 exemplar</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -13784,32 +13784,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128087530</v>
+        <v>128087543</v>
       </c>
       <c r="B133" t="n">
-        <v>98502</v>
+        <v>98469</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13819,10 +13819,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>544737</v>
+        <v>544674</v>
       </c>
       <c r="R133" t="n">
-        <v>6963047</v>
+        <v>6963243</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13855,6 +13855,11 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -13881,32 +13886,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128078645</v>
+        <v>128087381</v>
       </c>
       <c r="B134" t="n">
-        <v>80132</v>
+        <v>98386</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13916,10 +13921,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>544360</v>
+        <v>544531</v>
       </c>
       <c r="R134" t="n">
-        <v>6963094</v>
+        <v>6963190</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13978,10 +13983,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128087344</v>
+        <v>128087530</v>
       </c>
       <c r="B135" t="n">
-        <v>80161</v>
+        <v>98503</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13989,21 +13994,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6462</v>
+        <v>219874</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14013,10 +14018,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>544581</v>
+        <v>544737</v>
       </c>
       <c r="R135" t="n">
-        <v>6963278</v>
+        <v>6963047</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14075,10 +14080,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128087534</v>
+        <v>128087328</v>
       </c>
       <c r="B136" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14086,21 +14091,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14110,10 +14115,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>544326</v>
+        <v>544736</v>
       </c>
       <c r="R136" t="n">
-        <v>6963248</v>
+        <v>6963153</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14146,6 +14151,11 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14172,7 +14182,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128087540</v>
+        <v>128078645</v>
       </c>
       <c r="B137" t="n">
         <v>80132</v>
@@ -14207,10 +14217,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>544282</v>
+        <v>544360</v>
       </c>
       <c r="R137" t="n">
-        <v>6963082</v>
+        <v>6963094</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14269,7 +14279,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128087345</v>
+        <v>128087344</v>
       </c>
       <c r="B138" t="n">
         <v>80161</v>
@@ -14304,10 +14314,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>544391</v>
+        <v>544581</v>
       </c>
       <c r="R138" t="n">
-        <v>6963205</v>
+        <v>6963278</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14366,10 +14376,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128087328</v>
+        <v>128087534</v>
       </c>
       <c r="B139" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14377,21 +14387,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14401,10 +14411,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>544736</v>
+        <v>544326</v>
       </c>
       <c r="R139" t="n">
-        <v>6963153</v>
+        <v>6963248</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14437,11 +14447,6 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14468,32 +14473,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128087557</v>
+        <v>128087345</v>
       </c>
       <c r="B140" t="n">
-        <v>98468</v>
+        <v>80161</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14503,10 +14508,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>544552</v>
+        <v>544391</v>
       </c>
       <c r="R140" t="n">
-        <v>6963231</v>
+        <v>6963205</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14539,11 +14544,6 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14570,32 +14570,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128087543</v>
+        <v>128087540</v>
       </c>
       <c r="B141" t="n">
-        <v>98468</v>
+        <v>80132</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14605,10 +14605,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>544674</v>
+        <v>544282</v>
       </c>
       <c r="R141" t="n">
-        <v>6963243</v>
+        <v>6963082</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14641,11 +14641,6 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14672,32 +14667,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128087381</v>
+        <v>128087557</v>
       </c>
       <c r="B142" t="n">
-        <v>98385</v>
+        <v>98469</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14707,10 +14702,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>544531</v>
+        <v>544552</v>
       </c>
       <c r="R142" t="n">
-        <v>6963190</v>
+        <v>6963231</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14743,6 +14738,11 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -14769,10 +14769,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128087368</v>
+        <v>128078685</v>
       </c>
       <c r="B143" t="n">
-        <v>80132</v>
+        <v>56248</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14780,34 +14780,39 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>544314</v>
+        <v>544307</v>
       </c>
       <c r="R143" t="n">
-        <v>6963248</v>
+        <v>6963069</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14869,7 +14874,7 @@
         <v>128078529</v>
       </c>
       <c r="B144" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14967,10 +14972,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128078685</v>
+        <v>128087368</v>
       </c>
       <c r="B145" t="n">
-        <v>56248</v>
+        <v>80132</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14978,39 +14983,34 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>206004</v>
+        <v>6458</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>544307</v>
+        <v>544314</v>
       </c>
       <c r="R145" t="n">
-        <v>6963069</v>
+        <v>6963248</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15174,7 +15174,7 @@
         <v>128094046</v>
       </c>
       <c r="B147" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15276,7 +15276,7 @@
         <v>128094050</v>
       </c>
       <c r="B148" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15577,7 +15577,7 @@
         <v>128094042</v>
       </c>
       <c r="B151" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>128094044</v>
       </c>
       <c r="B153" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15883,7 +15883,7 @@
         <v>128094040</v>
       </c>
       <c r="B154" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15985,7 +15985,7 @@
         <v>128094043</v>
       </c>
       <c r="B155" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16084,10 +16084,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128094048</v>
+        <v>128094041</v>
       </c>
       <c r="B156" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16119,10 +16119,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>544610</v>
+        <v>544411</v>
       </c>
       <c r="R156" t="n">
-        <v>6963173</v>
+        <v>6963326</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16159,7 +16159,7 @@
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>24 ex</t>
+          <t>34 ex</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16186,10 +16186,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128094041</v>
+        <v>128094048</v>
       </c>
       <c r="B157" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16221,10 +16221,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>544411</v>
+        <v>544610</v>
       </c>
       <c r="R157" t="n">
-        <v>6963326</v>
+        <v>6963173</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16261,7 +16261,7 @@
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>34 ex</t>
+          <t>24 ex</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16291,7 +16291,7 @@
         <v>128094049</v>
       </c>
       <c r="B158" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>128094053</v>
       </c>
       <c r="B159" t="n">
-        <v>105506</v>
+        <v>105507</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>128094047</v>
       </c>
       <c r="B161" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>128094051</v>
       </c>
       <c r="B162" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>128094045</v>
       </c>
       <c r="B163" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16898,7 +16898,7 @@
         <v>128094054</v>
       </c>
       <c r="B164" t="n">
-        <v>105506</v>
+        <v>105507</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16992,10 +16992,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128094036</v>
+        <v>128094033</v>
       </c>
       <c r="B165" t="n">
-        <v>57832</v>
+        <v>57672</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17003,21 +17003,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17027,10 +17027,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>544566</v>
+        <v>544475</v>
       </c>
       <c r="R165" t="n">
-        <v>6963163</v>
+        <v>6963299</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17067,7 +17067,7 @@
       </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>Lockläte övriga läten</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17094,10 +17094,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128094033</v>
+        <v>128094036</v>
       </c>
       <c r="B166" t="n">
-        <v>57672</v>
+        <v>57832</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17105,21 +17105,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17129,10 +17129,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>544475</v>
+        <v>544566</v>
       </c>
       <c r="R166" t="n">
-        <v>6963299</v>
+        <v>6963163</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17169,7 +17169,7 @@
       </c>
       <c r="AC166" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Lockläte övriga läten</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17301,7 +17301,7 @@
         <v>128094055</v>
       </c>
       <c r="B168" t="n">
-        <v>105506</v>
+        <v>105507</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>

--- a/artfynd/A 32240-2025 artfynd.xlsx
+++ b/artfynd/A 32240-2025 artfynd.xlsx
@@ -995,32 +995,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128087528</v>
+        <v>128087541</v>
       </c>
       <c r="B5" t="n">
-        <v>80160</v>
+        <v>78787</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544198</v>
+        <v>544267</v>
       </c>
       <c r="R5" t="n">
-        <v>6963228</v>
+        <v>6963196</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,7 +1092,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128087358</v>
+        <v>128087528</v>
       </c>
       <c r="B6" t="n">
         <v>80160</v>
@@ -1127,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544278</v>
+        <v>544198</v>
       </c>
       <c r="R6" t="n">
-        <v>6963265</v>
+        <v>6963228</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128087524</v>
+        <v>128087358</v>
       </c>
       <c r="B7" t="n">
-        <v>80161</v>
+        <v>80160</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1200,21 +1200,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544281</v>
+        <v>544278</v>
       </c>
       <c r="R7" t="n">
-        <v>6963082</v>
+        <v>6963265</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,32 +1286,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128087541</v>
+        <v>128087524</v>
       </c>
       <c r="B8" t="n">
-        <v>78787</v>
+        <v>80161</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1321,10 +1321,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544267</v>
+        <v>544281</v>
       </c>
       <c r="R8" t="n">
-        <v>6963196</v>
+        <v>6963082</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,7 +1386,7 @@
         <v>128087558</v>
       </c>
       <c r="B9" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1485,32 +1485,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128078559</v>
+        <v>128087516</v>
       </c>
       <c r="B10" t="n">
-        <v>97346</v>
+        <v>57672</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544359</v>
+        <v>544388</v>
       </c>
       <c r="R10" t="n">
-        <v>6963083</v>
+        <v>6963226</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,6 +1556,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall Äldre spår</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1585,7 +1590,7 @@
         <v>128087526</v>
       </c>
       <c r="B11" t="n">
-        <v>92633</v>
+        <v>92634</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1684,32 +1689,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128087516</v>
+        <v>128078559</v>
       </c>
       <c r="B12" t="n">
-        <v>57672</v>
+        <v>97347</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1719,10 +1724,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544388</v>
+        <v>544359</v>
       </c>
       <c r="R12" t="n">
-        <v>6963226</v>
+        <v>6963083</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1755,11 +1760,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall Äldre spår</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1980,32 +1980,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128087550</v>
+        <v>128087323</v>
       </c>
       <c r="B15" t="n">
-        <v>98469</v>
+        <v>57672</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2015,10 +2015,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544490</v>
+        <v>544646</v>
       </c>
       <c r="R15" t="n">
-        <v>6963099</v>
+        <v>6963095</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2184,10 +2184,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128087323</v>
+        <v>128087520</v>
       </c>
       <c r="B17" t="n">
-        <v>57672</v>
+        <v>57832</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2195,21 +2195,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544646</v>
+        <v>544771</v>
       </c>
       <c r="R17" t="n">
-        <v>6963095</v>
+        <v>6963083</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>2 stycken.  Övriga läten</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2286,32 +2286,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128087520</v>
+        <v>128087550</v>
       </c>
       <c r="B18" t="n">
-        <v>57832</v>
+        <v>98470</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544771</v>
+        <v>544490</v>
       </c>
       <c r="R18" t="n">
-        <v>6963083</v>
+        <v>6963099</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2 stycken.  Övriga läten</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2388,10 +2388,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128087581</v>
+        <v>128087359</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2399,21 +2399,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2423,10 +2423,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544192</v>
+        <v>544741</v>
       </c>
       <c r="R19" t="n">
-        <v>6963197</v>
+        <v>6963165</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2485,32 +2485,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128087569</v>
+        <v>128087354</v>
       </c>
       <c r="B20" t="n">
-        <v>98469</v>
+        <v>80133</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544296</v>
+        <v>544820</v>
       </c>
       <c r="R20" t="n">
-        <v>6963084</v>
+        <v>6963278</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2556,11 +2556,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>100stycken</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2587,32 +2582,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128087554</v>
+        <v>128087581</v>
       </c>
       <c r="B21" t="n">
-        <v>98469</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2622,10 +2617,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544659</v>
+        <v>544192</v>
       </c>
       <c r="R21" t="n">
-        <v>6963253</v>
+        <v>6963197</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2658,11 +2653,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2689,10 +2679,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128087359</v>
+        <v>128087362</v>
       </c>
       <c r="B22" t="n">
-        <v>78788</v>
+        <v>80132</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2700,21 +2690,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2724,10 +2714,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544741</v>
+        <v>544799</v>
       </c>
       <c r="R22" t="n">
-        <v>6963165</v>
+        <v>6963263</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2786,32 +2776,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128087354</v>
+        <v>128087349</v>
       </c>
       <c r="B23" t="n">
-        <v>80133</v>
+        <v>80161</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2821,10 +2811,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544820</v>
+        <v>544475</v>
       </c>
       <c r="R23" t="n">
-        <v>6963278</v>
+        <v>6963205</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2883,32 +2873,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128087362</v>
+        <v>128087569</v>
       </c>
       <c r="B24" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2918,10 +2908,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544799</v>
+        <v>544296</v>
       </c>
       <c r="R24" t="n">
-        <v>6963263</v>
+        <v>6963084</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2954,6 +2944,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>100stycken</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2980,32 +2975,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128087349</v>
+        <v>128087554</v>
       </c>
       <c r="B25" t="n">
-        <v>80161</v>
+        <v>98470</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3015,10 +3010,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544475</v>
+        <v>544659</v>
       </c>
       <c r="R25" t="n">
-        <v>6963205</v>
+        <v>6963253</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3051,6 +3046,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3077,32 +3077,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128087382</v>
+        <v>128087562</v>
       </c>
       <c r="B26" t="n">
-        <v>92641</v>
+        <v>98470</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3112,10 +3112,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>544198</v>
+        <v>544367</v>
       </c>
       <c r="R26" t="n">
-        <v>6963225</v>
+        <v>6963253</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>5 ex</t>
+          <t>7. Kan möjlitvis finnas fler runt omkring.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3179,45 +3179,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128087532</v>
+        <v>128078161</v>
       </c>
       <c r="B27" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544491</v>
+        <v>544362</v>
       </c>
       <c r="R27" t="n">
-        <v>6963099</v>
+        <v>6963061</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3276,10 +3280,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128087562</v>
+        <v>128078740</v>
       </c>
       <c r="B28" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3304,17 +3308,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544367</v>
+        <v>544307</v>
       </c>
       <c r="R28" t="n">
-        <v>6963253</v>
+        <v>6963089</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3347,11 +3355,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>7. Kan möjlitvis finnas fler runt omkring.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3378,10 +3381,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128078161</v>
+        <v>128087563</v>
       </c>
       <c r="B29" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3406,21 +3409,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544362</v>
+        <v>544322</v>
       </c>
       <c r="R29" t="n">
-        <v>6963061</v>
+        <v>6963250</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3453,6 +3452,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>12 stycken</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3479,49 +3483,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128078740</v>
+        <v>128087331</v>
       </c>
       <c r="B30" t="n">
-        <v>98469</v>
+        <v>57672</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>544307</v>
+        <v>544763</v>
       </c>
       <c r="R30" t="n">
-        <v>6963089</v>
+        <v>6963244</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3554,6 +3554,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3580,32 +3585,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128087563</v>
+        <v>128087333</v>
       </c>
       <c r="B31" t="n">
-        <v>98469</v>
+        <v>57672</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3615,10 +3620,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>544322</v>
+        <v>544355</v>
       </c>
       <c r="R31" t="n">
-        <v>6963250</v>
+        <v>6963212</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3655,7 +3660,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>12 stycken</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3682,10 +3687,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128087333</v>
+        <v>128087532</v>
       </c>
       <c r="B32" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3693,21 +3698,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3717,10 +3722,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544355</v>
+        <v>544491</v>
       </c>
       <c r="R32" t="n">
-        <v>6963212</v>
+        <v>6963099</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3753,11 +3758,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3784,32 +3784,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128087331</v>
+        <v>128087382</v>
       </c>
       <c r="B33" t="n">
-        <v>57672</v>
+        <v>92642</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>544763</v>
+        <v>544198</v>
       </c>
       <c r="R33" t="n">
-        <v>6963244</v>
+        <v>6963225</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3859,7 +3859,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3886,10 +3886,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128079621</v>
+        <v>128087336</v>
       </c>
       <c r="B34" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3897,21 +3897,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3921,10 +3921,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>544274</v>
+        <v>544398</v>
       </c>
       <c r="R34" t="n">
-        <v>6963119</v>
+        <v>6963202</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3957,6 +3957,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3983,7 +3988,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128087533</v>
+        <v>128079621</v>
       </c>
       <c r="B35" t="n">
         <v>80132</v>
@@ -4018,10 +4023,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>544473</v>
+        <v>544274</v>
       </c>
       <c r="R35" t="n">
-        <v>6963102</v>
+        <v>6963119</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4080,32 +4085,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128087351</v>
+        <v>128087533</v>
       </c>
       <c r="B36" t="n">
-        <v>80161</v>
+        <v>80132</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4115,10 +4120,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>544299</v>
+        <v>544473</v>
       </c>
       <c r="R36" t="n">
-        <v>6963312</v>
+        <v>6963102</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4177,32 +4182,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128087365</v>
+        <v>128087351</v>
       </c>
       <c r="B37" t="n">
-        <v>80132</v>
+        <v>80161</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4212,10 +4217,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>544469</v>
+        <v>544299</v>
       </c>
       <c r="R37" t="n">
-        <v>6963145</v>
+        <v>6963312</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4274,10 +4279,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128087336</v>
+        <v>128087365</v>
       </c>
       <c r="B38" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4285,21 +4290,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4309,10 +4314,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>544398</v>
+        <v>544469</v>
       </c>
       <c r="R38" t="n">
-        <v>6963202</v>
+        <v>6963145</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4345,11 +4350,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4379,7 +4379,7 @@
         <v>128087588</v>
       </c>
       <c r="B39" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4973,32 +4973,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128087361</v>
+        <v>128087552</v>
       </c>
       <c r="B45" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5008,10 +5008,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>544865</v>
+        <v>544687</v>
       </c>
       <c r="R45" t="n">
-        <v>6963092</v>
+        <v>6963255</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5044,6 +5044,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>70</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5070,32 +5075,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128087340</v>
+        <v>128087548</v>
       </c>
       <c r="B46" t="n">
-        <v>57832</v>
+        <v>98470</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5105,10 +5110,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>544485</v>
+        <v>544213</v>
       </c>
       <c r="R46" t="n">
-        <v>6963237</v>
+        <v>6963197</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5141,6 +5146,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>100stycken.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5167,32 +5177,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128087552</v>
+        <v>128079768</v>
       </c>
       <c r="B47" t="n">
-        <v>98469</v>
+        <v>97353</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5202,10 +5212,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>544687</v>
+        <v>544287</v>
       </c>
       <c r="R47" t="n">
-        <v>6963255</v>
+        <v>6963168</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5238,11 +5248,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>70</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5269,32 +5274,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128087548</v>
+        <v>128087361</v>
       </c>
       <c r="B48" t="n">
-        <v>98469</v>
+        <v>80132</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5304,10 +5309,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>544213</v>
+        <v>544865</v>
       </c>
       <c r="R48" t="n">
-        <v>6963197</v>
+        <v>6963092</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5340,11 +5345,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>100stycken.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5371,32 +5371,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128079768</v>
+        <v>128087340</v>
       </c>
       <c r="B49" t="n">
-        <v>97352</v>
+        <v>57832</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>544287</v>
+        <v>544485</v>
       </c>
       <c r="R49" t="n">
-        <v>6963168</v>
+        <v>6963237</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5468,32 +5468,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128087339</v>
+        <v>128087342</v>
       </c>
       <c r="B50" t="n">
-        <v>57832</v>
+        <v>80161</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5503,10 +5503,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>544850</v>
+        <v>544848</v>
       </c>
       <c r="R50" t="n">
-        <v>6963099</v>
+        <v>6963086</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5539,11 +5539,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5570,32 +5565,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128079839</v>
+        <v>128087367</v>
       </c>
       <c r="B51" t="n">
-        <v>105507</v>
+        <v>80132</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221144</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5605,10 +5600,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>544288</v>
+        <v>544298</v>
       </c>
       <c r="R51" t="n">
-        <v>6963182</v>
+        <v>6963312</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5667,32 +5662,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128087342</v>
+        <v>128087364</v>
       </c>
       <c r="B52" t="n">
-        <v>80161</v>
+        <v>80132</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5702,10 +5697,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>544848</v>
+        <v>544774</v>
       </c>
       <c r="R52" t="n">
-        <v>6963086</v>
+        <v>6963282</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5764,32 +5759,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128087367</v>
+        <v>128087553</v>
       </c>
       <c r="B53" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5799,10 +5794,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>544298</v>
+        <v>544677</v>
       </c>
       <c r="R53" t="n">
-        <v>6963312</v>
+        <v>6963260</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5835,6 +5830,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Mer än 70 stycken. Flera blommar</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5861,32 +5861,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128087364</v>
+        <v>128087555</v>
       </c>
       <c r="B54" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>544774</v>
+        <v>544623</v>
       </c>
       <c r="R54" t="n">
-        <v>6963282</v>
+        <v>6963241</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5932,6 +5932,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>60 stycken</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5958,32 +5963,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128087553</v>
+        <v>128079839</v>
       </c>
       <c r="B55" t="n">
-        <v>98469</v>
+        <v>105508</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5993,10 +5998,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>544677</v>
+        <v>544288</v>
       </c>
       <c r="R55" t="n">
-        <v>6963260</v>
+        <v>6963182</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6029,11 +6034,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Mer än 70 stycken. Flera blommar</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6060,32 +6060,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128087555</v>
+        <v>128087339</v>
       </c>
       <c r="B56" t="n">
-        <v>98469</v>
+        <v>57832</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>544623</v>
+        <v>544850</v>
       </c>
       <c r="R56" t="n">
-        <v>6963241</v>
+        <v>6963099</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>60 stycken</t>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6162,10 +6162,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128087585</v>
+        <v>128087356</v>
       </c>
       <c r="B57" t="n">
-        <v>92641</v>
+        <v>80160</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6173,21 +6173,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>6461</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6197,10 +6197,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>544536</v>
+        <v>544772</v>
       </c>
       <c r="R57" t="n">
-        <v>6963255</v>
+        <v>6963323</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6233,11 +6233,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>8 äldre ex9 färska fruktkroppar</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6264,7 +6259,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128087356</v>
+        <v>128087357</v>
       </c>
       <c r="B58" t="n">
         <v>80160</v>
@@ -6299,10 +6294,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>544772</v>
+        <v>544466</v>
       </c>
       <c r="R58" t="n">
-        <v>6963323</v>
+        <v>6963277</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6361,10 +6356,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128087357</v>
+        <v>128087585</v>
       </c>
       <c r="B59" t="n">
-        <v>80160</v>
+        <v>92642</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6372,21 +6367,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6461</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6396,10 +6391,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>544466</v>
+        <v>544536</v>
       </c>
       <c r="R59" t="n">
-        <v>6963277</v>
+        <v>6963255</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6432,6 +6427,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>8 äldre ex9 färska fruktkroppar</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6565,10 +6565,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128087525</v>
+        <v>128087386</v>
       </c>
       <c r="B61" t="n">
-        <v>56248</v>
+        <v>92636</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6576,21 +6576,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>206004</v>
+        <v>4362</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6600,10 +6600,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>544385</v>
+        <v>544822</v>
       </c>
       <c r="R61" t="n">
-        <v>6963074</v>
+        <v>6963295</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6662,32 +6662,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128087377</v>
+        <v>128078603</v>
       </c>
       <c r="B62" t="n">
-        <v>98469</v>
+        <v>80161</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6697,10 +6697,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>544403</v>
+        <v>544360</v>
       </c>
       <c r="R62" t="n">
-        <v>6963221</v>
+        <v>6963094</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6733,11 +6733,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>20 ex</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6764,32 +6759,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128087566</v>
+        <v>128087523</v>
       </c>
       <c r="B63" t="n">
-        <v>98469</v>
+        <v>80161</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6799,10 +6794,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>544261</v>
+        <v>544253</v>
       </c>
       <c r="R63" t="n">
-        <v>6963170</v>
+        <v>6963139</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6835,11 +6830,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>4. Stycken. Finns möjligtvis fler i blåbärsriset.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6866,32 +6856,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128087378</v>
+        <v>128087579</v>
       </c>
       <c r="B64" t="n">
-        <v>98469</v>
+        <v>79029</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6901,10 +6891,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>544218</v>
+        <v>544204</v>
       </c>
       <c r="R64" t="n">
-        <v>6963229</v>
+        <v>6963238</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6941,7 +6931,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>80 ex</t>
+          <t>Riklig förekomst av garnlav</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6968,32 +6958,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128087375</v>
+        <v>128087329</v>
       </c>
       <c r="B65" t="n">
-        <v>98469</v>
+        <v>57672</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7003,10 +6993,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>544478</v>
+        <v>544757</v>
       </c>
       <c r="R65" t="n">
-        <v>6963117</v>
+        <v>6963172</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7043,7 +7033,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>35 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7070,32 +7060,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128087386</v>
+        <v>128087566</v>
       </c>
       <c r="B66" t="n">
-        <v>92635</v>
+        <v>98470</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4362</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7105,10 +7095,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>544822</v>
+        <v>544261</v>
       </c>
       <c r="R66" t="n">
-        <v>6963295</v>
+        <v>6963170</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7141,6 +7131,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>4. Stycken. Finns möjligtvis fler i blåbärsriset.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7167,32 +7162,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128078603</v>
+        <v>128087377</v>
       </c>
       <c r="B67" t="n">
-        <v>80161</v>
+        <v>98470</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7202,10 +7197,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>544360</v>
+        <v>544403</v>
       </c>
       <c r="R67" t="n">
-        <v>6963094</v>
+        <v>6963221</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7238,6 +7233,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7264,32 +7264,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128087523</v>
+        <v>128087378</v>
       </c>
       <c r="B68" t="n">
-        <v>80161</v>
+        <v>98470</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7299,10 +7299,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>544253</v>
+        <v>544218</v>
       </c>
       <c r="R68" t="n">
-        <v>6963139</v>
+        <v>6963229</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7335,6 +7335,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7361,32 +7366,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128087579</v>
+        <v>128087375</v>
       </c>
       <c r="B69" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7396,10 +7401,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>544204</v>
+        <v>544478</v>
       </c>
       <c r="R69" t="n">
-        <v>6963238</v>
+        <v>6963117</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7436,7 +7441,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Riklig förekomst av garnlav</t>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7463,10 +7468,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128087329</v>
+        <v>128087525</v>
       </c>
       <c r="B70" t="n">
-        <v>57672</v>
+        <v>56248</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7474,21 +7479,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7498,10 +7503,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>544757</v>
+        <v>544385</v>
       </c>
       <c r="R70" t="n">
-        <v>6963172</v>
+        <v>6963074</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7534,11 +7539,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7759,7 +7759,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128080054</v>
+        <v>128087337</v>
       </c>
       <c r="B73" t="n">
         <v>57672</v>
@@ -7788,21 +7788,16 @@
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>544301</v>
+        <v>544197</v>
       </c>
       <c r="R73" t="n">
-        <v>6963231</v>
+        <v>6963237</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7839,7 +7834,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7973,7 +7968,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128080149</v>
+        <v>128080054</v>
       </c>
       <c r="B75" t="n">
         <v>57672</v>
@@ -8013,10 +8008,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>544295</v>
+        <v>544301</v>
       </c>
       <c r="R75" t="n">
-        <v>6963226</v>
+        <v>6963231</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8080,7 +8075,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128087337</v>
+        <v>128080149</v>
       </c>
       <c r="B76" t="n">
         <v>57672</v>
@@ -8109,16 +8104,21 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>544197</v>
+        <v>544295</v>
       </c>
       <c r="R76" t="n">
-        <v>6963237</v>
+        <v>6963226</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8155,7 +8155,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8182,10 +8182,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128087575</v>
+        <v>128087536</v>
       </c>
       <c r="B77" t="n">
-        <v>92673</v>
+        <v>80132</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8193,21 +8193,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1968</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8217,10 +8217,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>544532</v>
+        <v>544215</v>
       </c>
       <c r="R77" t="n">
-        <v>6963250</v>
+        <v>6963245</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8253,11 +8253,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Igen stor köttig svamp misstänker grantaggsvamp 2 ex</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8284,32 +8279,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128078492</v>
+        <v>128087343</v>
       </c>
       <c r="B78" t="n">
-        <v>92673</v>
+        <v>80161</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1968</v>
+        <v>6462</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8319,10 +8314,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>544362</v>
+        <v>544757</v>
       </c>
       <c r="R78" t="n">
-        <v>6963073</v>
+        <v>6963156</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8381,32 +8376,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128087536</v>
+        <v>128087346</v>
       </c>
       <c r="B79" t="n">
-        <v>80132</v>
+        <v>80161</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8416,10 +8411,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>544215</v>
+        <v>544422</v>
       </c>
       <c r="R79" t="n">
-        <v>6963245</v>
+        <v>6963240</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8478,45 +8473,49 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128087343</v>
+        <v>128079875</v>
       </c>
       <c r="B80" t="n">
-        <v>80161</v>
+        <v>98470</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>544757</v>
+        <v>544308</v>
       </c>
       <c r="R80" t="n">
-        <v>6963156</v>
+        <v>6963175</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8575,32 +8574,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128087346</v>
+        <v>128087542</v>
       </c>
       <c r="B81" t="n">
-        <v>80161</v>
+        <v>98470</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8610,10 +8609,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>544422</v>
+        <v>544752</v>
       </c>
       <c r="R81" t="n">
-        <v>6963240</v>
+        <v>6963192</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8646,6 +8645,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8672,45 +8676,49 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128087335</v>
+        <v>128080338</v>
       </c>
       <c r="B82" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>544366</v>
+        <v>544314</v>
       </c>
       <c r="R82" t="n">
-        <v>6963181</v>
+        <v>6963248</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8743,11 +8751,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8774,32 +8777,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128087330</v>
+        <v>128087547</v>
       </c>
       <c r="B83" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8809,10 +8812,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>544750</v>
+        <v>544380</v>
       </c>
       <c r="R83" t="n">
-        <v>6963177</v>
+        <v>6963236</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8849,7 +8852,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>33 stycken</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8876,32 +8879,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128087570</v>
+        <v>128087560</v>
       </c>
       <c r="B84" t="n">
-        <v>56855</v>
+        <v>98470</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8911,10 +8914,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>544287</v>
+        <v>544383</v>
       </c>
       <c r="R84" t="n">
-        <v>6963082</v>
+        <v>6963236</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8951,7 +8954,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Fjäder</t>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8978,49 +8981,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128079875</v>
+        <v>128087575</v>
       </c>
       <c r="B85" t="n">
-        <v>98469</v>
+        <v>92674</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>1968</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>544308</v>
+        <v>544532</v>
       </c>
       <c r="R85" t="n">
-        <v>6963175</v>
+        <v>6963250</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9053,6 +9052,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Igen stor köttig svamp misstänker grantaggsvamp 2 ex</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9079,32 +9083,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128087542</v>
+        <v>128078492</v>
       </c>
       <c r="B86" t="n">
-        <v>98469</v>
+        <v>92674</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>1968</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9114,10 +9118,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>544752</v>
+        <v>544362</v>
       </c>
       <c r="R86" t="n">
-        <v>6963192</v>
+        <v>6963073</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9150,11 +9154,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9181,49 +9180,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128080338</v>
+        <v>128087570</v>
       </c>
       <c r="B87" t="n">
-        <v>98469</v>
+        <v>56855</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>544314</v>
+        <v>544287</v>
       </c>
       <c r="R87" t="n">
-        <v>6963248</v>
+        <v>6963082</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9256,6 +9251,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9282,32 +9282,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128087547</v>
+        <v>128087330</v>
       </c>
       <c r="B88" t="n">
-        <v>98469</v>
+        <v>57672</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9317,10 +9317,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>544380</v>
+        <v>544750</v>
       </c>
       <c r="R88" t="n">
-        <v>6963236</v>
+        <v>6963177</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9357,7 +9357,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>33 stycken</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9384,32 +9384,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128087560</v>
+        <v>128087335</v>
       </c>
       <c r="B89" t="n">
-        <v>98469</v>
+        <v>57672</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9419,10 +9419,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>544383</v>
+        <v>544366</v>
       </c>
       <c r="R89" t="n">
-        <v>6963236</v>
+        <v>6963181</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9459,7 +9459,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>40 stycken</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9489,7 +9489,7 @@
         <v>128087380</v>
       </c>
       <c r="B90" t="n">
-        <v>105507</v>
+        <v>105508</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9583,32 +9583,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128087587</v>
+        <v>128087539</v>
       </c>
       <c r="B91" t="n">
-        <v>92641</v>
+        <v>80132</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9618,10 +9618,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>544245</v>
+        <v>544254</v>
       </c>
       <c r="R91" t="n">
-        <v>6963255</v>
+        <v>6963139</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9654,11 +9654,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>4stycken</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9685,32 +9680,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128087539</v>
+        <v>128087341</v>
       </c>
       <c r="B92" t="n">
-        <v>80132</v>
+        <v>80161</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9720,10 +9715,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>544254</v>
+        <v>544615</v>
       </c>
       <c r="R92" t="n">
-        <v>6963139</v>
+        <v>6963101</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9782,10 +9777,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128087341</v>
+        <v>128087587</v>
       </c>
       <c r="B93" t="n">
-        <v>80161</v>
+        <v>92642</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9793,21 +9788,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9817,10 +9812,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>544615</v>
+        <v>544245</v>
       </c>
       <c r="R93" t="n">
-        <v>6963101</v>
+        <v>6963255</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9853,6 +9848,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>4stycken</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9882,7 +9882,7 @@
         <v>128087376</v>
       </c>
       <c r="B94" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>128087379</v>
       </c>
       <c r="B95" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10083,32 +10083,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128087383</v>
+        <v>128087545</v>
       </c>
       <c r="B96" t="n">
-        <v>80167</v>
+        <v>98470</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10118,10 +10118,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>544566</v>
+        <v>544633</v>
       </c>
       <c r="R96" t="n">
-        <v>6963076</v>
+        <v>6963244</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10154,6 +10154,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10180,32 +10185,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128087384</v>
+        <v>128087567</v>
       </c>
       <c r="B97" t="n">
-        <v>80167</v>
+        <v>98470</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10215,10 +10220,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>544584</v>
+        <v>544274</v>
       </c>
       <c r="R97" t="n">
-        <v>6963261</v>
+        <v>6963090</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10251,6 +10256,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>110</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10277,32 +10287,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128087363</v>
+        <v>128087556</v>
       </c>
       <c r="B98" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10312,10 +10322,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>544818</v>
+        <v>544594</v>
       </c>
       <c r="R98" t="n">
-        <v>6963278</v>
+        <v>6963215</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10348,6 +10358,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>6 stycken. Kan finnas mer i omgivningen</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10374,32 +10389,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128087522</v>
+        <v>128087373</v>
       </c>
       <c r="B99" t="n">
-        <v>57832</v>
+        <v>98470</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10409,10 +10424,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>544494</v>
+        <v>544469</v>
       </c>
       <c r="R99" t="n">
-        <v>6963243</v>
+        <v>6963122</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10445,6 +10460,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>60 ex</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10471,10 +10491,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128087545</v>
+        <v>128087559</v>
       </c>
       <c r="B100" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10506,10 +10526,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>544633</v>
+        <v>544396</v>
       </c>
       <c r="R100" t="n">
-        <v>6963244</v>
+        <v>6963233</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10546,7 +10566,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>30 stycken</t>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10573,32 +10593,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128087567</v>
+        <v>128087355</v>
       </c>
       <c r="B101" t="n">
-        <v>98469</v>
+        <v>97353</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10608,10 +10628,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>544274</v>
+        <v>544500</v>
       </c>
       <c r="R101" t="n">
-        <v>6963090</v>
+        <v>6963168</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10644,11 +10664,6 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>110</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10675,32 +10690,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128087556</v>
+        <v>128087383</v>
       </c>
       <c r="B102" t="n">
-        <v>98469</v>
+        <v>80167</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10710,10 +10725,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>544594</v>
+        <v>544566</v>
       </c>
       <c r="R102" t="n">
-        <v>6963215</v>
+        <v>6963076</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10746,11 +10761,6 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>6 stycken. Kan finnas mer i omgivningen</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10777,32 +10787,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128087373</v>
+        <v>128087384</v>
       </c>
       <c r="B103" t="n">
-        <v>98469</v>
+        <v>80167</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10812,10 +10822,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>544469</v>
+        <v>544584</v>
       </c>
       <c r="R103" t="n">
-        <v>6963122</v>
+        <v>6963261</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10848,11 +10858,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>60 ex</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10879,32 +10884,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128087355</v>
+        <v>128087363</v>
       </c>
       <c r="B104" t="n">
-        <v>97352</v>
+        <v>80132</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>221941</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10914,10 +10919,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>544500</v>
+        <v>544818</v>
       </c>
       <c r="R104" t="n">
-        <v>6963168</v>
+        <v>6963278</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10976,32 +10981,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128087559</v>
+        <v>128087576</v>
       </c>
       <c r="B105" t="n">
-        <v>98469</v>
+        <v>92674</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>1968</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11011,10 +11016,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>544396</v>
+        <v>544529</v>
       </c>
       <c r="R105" t="n">
-        <v>6963233</v>
+        <v>6963245</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11051,7 +11056,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>18 stycken</t>
+          <t>Misstänkt grantaggsvamp men med mörk tydlig ring i mitten.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11078,32 +11083,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128078864</v>
+        <v>128087572</v>
       </c>
       <c r="B106" t="n">
-        <v>105507</v>
+        <v>92674</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>221144</v>
+        <v>1968</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11113,10 +11118,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>544307</v>
+        <v>544632</v>
       </c>
       <c r="R106" t="n">
-        <v>6963089</v>
+        <v>6963245</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11149,6 +11154,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>1 ex</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11175,10 +11185,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128087576</v>
+        <v>128087522</v>
       </c>
       <c r="B107" t="n">
-        <v>92673</v>
+        <v>57832</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11186,21 +11196,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1968</v>
+        <v>103021</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11210,10 +11220,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>544529</v>
+        <v>544494</v>
       </c>
       <c r="R107" t="n">
-        <v>6963245</v>
+        <v>6963243</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11246,11 +11256,6 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Misstänkt grantaggsvamp men med mörk tydlig ring i mitten.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11277,32 +11282,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128087572</v>
+        <v>128078864</v>
       </c>
       <c r="B108" t="n">
-        <v>92673</v>
+        <v>105508</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1968</v>
+        <v>221144</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11312,10 +11317,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>544632</v>
+        <v>544307</v>
       </c>
       <c r="R108" t="n">
-        <v>6963245</v>
+        <v>6963089</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11348,11 +11353,6 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>1 ex</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11382,7 +11382,7 @@
         <v>128087577</v>
       </c>
       <c r="B109" t="n">
-        <v>92673</v>
+        <v>92674</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11476,49 +11476,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128079656</v>
+        <v>128087531</v>
       </c>
       <c r="B110" t="n">
-        <v>98469</v>
+        <v>98504</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>544277</v>
+        <v>544755</v>
       </c>
       <c r="R110" t="n">
-        <v>6963150</v>
+        <v>6963130</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11551,6 +11547,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11577,32 +11578,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128087565</v>
+        <v>128087578</v>
       </c>
       <c r="B111" t="n">
-        <v>98469</v>
+        <v>79029</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11612,10 +11613,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>544249</v>
+        <v>544246</v>
       </c>
       <c r="R111" t="n">
-        <v>6963223</v>
+        <v>6963257</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11648,11 +11649,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>10. Kan möjlitvis finns mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11679,32 +11675,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128087372</v>
+        <v>128087586</v>
       </c>
       <c r="B112" t="n">
-        <v>98469</v>
+        <v>92642</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11714,10 +11710,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>544472</v>
+        <v>544281</v>
       </c>
       <c r="R112" t="n">
-        <v>6963201</v>
+        <v>6963257</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11754,7 +11750,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>8 ex</t>
+          <t>2 nya exemplar 8 äldre ex</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11781,10 +11777,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128087551</v>
+        <v>128079656</v>
       </c>
       <c r="B113" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11809,17 +11805,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>544694</v>
+        <v>544277</v>
       </c>
       <c r="R113" t="n">
-        <v>6963258</v>
+        <v>6963150</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11852,11 +11852,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11883,32 +11878,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128087531</v>
+        <v>128087565</v>
       </c>
       <c r="B114" t="n">
-        <v>98503</v>
+        <v>98470</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11918,10 +11913,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>544755</v>
+        <v>544249</v>
       </c>
       <c r="R114" t="n">
-        <v>6963130</v>
+        <v>6963223</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11958,7 +11953,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>2 stycken</t>
+          <t>10. Kan möjlitvis finns mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11985,32 +11980,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128087586</v>
+        <v>128087372</v>
       </c>
       <c r="B115" t="n">
-        <v>92641</v>
+        <v>98470</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12020,10 +12015,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>544281</v>
+        <v>544472</v>
       </c>
       <c r="R115" t="n">
-        <v>6963257</v>
+        <v>6963201</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12060,7 +12055,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>2 nya exemplar 8 äldre ex</t>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12087,32 +12082,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128087578</v>
+        <v>128087551</v>
       </c>
       <c r="B116" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12122,10 +12117,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>544246</v>
+        <v>544694</v>
       </c>
       <c r="R116" t="n">
-        <v>6963257</v>
+        <v>6963258</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12158,6 +12153,11 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12187,7 +12187,7 @@
         <v>128087571</v>
       </c>
       <c r="B117" t="n">
-        <v>92673</v>
+        <v>92674</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>128087573</v>
       </c>
       <c r="B118" t="n">
-        <v>92673</v>
+        <v>92674</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12388,32 +12388,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128087538</v>
+        <v>128079848</v>
       </c>
       <c r="B119" t="n">
-        <v>80132</v>
+        <v>79053</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6458</v>
+        <v>6434</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12423,10 +12423,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>544262</v>
+        <v>544288</v>
       </c>
       <c r="R119" t="n">
-        <v>6963163</v>
+        <v>6963182</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12485,7 +12485,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128087535</v>
+        <v>128087538</v>
       </c>
       <c r="B120" t="n">
         <v>80132</v>
@@ -12520,10 +12520,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>544312</v>
+        <v>544262</v>
       </c>
       <c r="R120" t="n">
-        <v>6963244</v>
+        <v>6963163</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12582,32 +12582,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128079848</v>
+        <v>128087535</v>
       </c>
       <c r="B121" t="n">
-        <v>79053</v>
+        <v>80132</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6434</v>
+        <v>6458</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12617,10 +12617,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>544288</v>
+        <v>544312</v>
       </c>
       <c r="R121" t="n">
-        <v>6963182</v>
+        <v>6963244</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12779,7 +12779,7 @@
         <v>128087582</v>
       </c>
       <c r="B123" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12876,7 +12876,7 @@
         <v>128079571</v>
       </c>
       <c r="B124" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12977,7 +12977,7 @@
         <v>128078138</v>
       </c>
       <c r="B125" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13075,32 +13075,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128079484</v>
+        <v>128087574</v>
       </c>
       <c r="B126" t="n">
-        <v>80168</v>
+        <v>92674</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6464</v>
+        <v>1968</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13110,10 +13110,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>544289</v>
+        <v>544552</v>
       </c>
       <c r="R126" t="n">
-        <v>6963113</v>
+        <v>6963231</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13146,6 +13146,11 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Misstänker grantaggsvamp 1 exemplar</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13172,32 +13177,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128087334</v>
+        <v>128079484</v>
       </c>
       <c r="B127" t="n">
-        <v>57672</v>
+        <v>80168</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13207,10 +13212,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>544348</v>
+        <v>544289</v>
       </c>
       <c r="R127" t="n">
-        <v>6963187</v>
+        <v>6963113</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13243,11 +13248,6 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13274,32 +13274,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128087583</v>
+        <v>128087334</v>
       </c>
       <c r="B128" t="n">
-        <v>98386</v>
+        <v>57672</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13309,10 +13309,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>544708</v>
+        <v>544348</v>
       </c>
       <c r="R128" t="n">
-        <v>6963086</v>
+        <v>6963187</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13349,7 +13349,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13376,10 +13376,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128087584</v>
+        <v>128087583</v>
       </c>
       <c r="B129" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13411,10 +13411,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>544718</v>
+        <v>544708</v>
       </c>
       <c r="R129" t="n">
-        <v>6963053</v>
+        <v>6963086</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13451,7 +13451,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>3 stycken</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13478,32 +13478,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128087370</v>
+        <v>128087584</v>
       </c>
       <c r="B130" t="n">
-        <v>98469</v>
+        <v>98387</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13513,10 +13513,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>544751</v>
+        <v>544718</v>
       </c>
       <c r="R130" t="n">
-        <v>6963146</v>
+        <v>6963053</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13553,7 +13553,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>30 ex</t>
+          <t>3 stycken</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13580,10 +13580,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128087371</v>
+        <v>128087370</v>
       </c>
       <c r="B131" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13615,10 +13615,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>544559</v>
+        <v>544751</v>
       </c>
       <c r="R131" t="n">
-        <v>6963215</v>
+        <v>6963146</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13655,7 +13655,7 @@
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>100 ex</t>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13682,32 +13682,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128087574</v>
+        <v>128087371</v>
       </c>
       <c r="B132" t="n">
-        <v>92673</v>
+        <v>98470</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1968</v>
+        <v>220787</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13717,10 +13717,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>544552</v>
+        <v>544559</v>
       </c>
       <c r="R132" t="n">
-        <v>6963231</v>
+        <v>6963215</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13757,7 +13757,7 @@
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>Misstänker grantaggsvamp 1 exemplar</t>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -13784,32 +13784,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128087543</v>
+        <v>128078645</v>
       </c>
       <c r="B133" t="n">
-        <v>98469</v>
+        <v>80132</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13819,10 +13819,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>544674</v>
+        <v>544360</v>
       </c>
       <c r="R133" t="n">
-        <v>6963243</v>
+        <v>6963094</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13855,11 +13855,6 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -13886,10 +13881,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128087381</v>
+        <v>128087344</v>
       </c>
       <c r="B134" t="n">
-        <v>98386</v>
+        <v>80161</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13897,21 +13892,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>219790</v>
+        <v>6462</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13921,10 +13916,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>544531</v>
+        <v>544581</v>
       </c>
       <c r="R134" t="n">
-        <v>6963190</v>
+        <v>6963278</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13983,32 +13978,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128087530</v>
+        <v>128087534</v>
       </c>
       <c r="B135" t="n">
-        <v>98503</v>
+        <v>80132</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>219874</v>
+        <v>6458</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14018,10 +14013,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>544737</v>
+        <v>544326</v>
       </c>
       <c r="R135" t="n">
-        <v>6963047</v>
+        <v>6963248</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14080,32 +14075,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128087328</v>
+        <v>128087345</v>
       </c>
       <c r="B136" t="n">
-        <v>57672</v>
+        <v>80161</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14115,10 +14110,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>544736</v>
+        <v>544391</v>
       </c>
       <c r="R136" t="n">
-        <v>6963153</v>
+        <v>6963205</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14151,11 +14146,6 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14182,7 +14172,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128078645</v>
+        <v>128087540</v>
       </c>
       <c r="B137" t="n">
         <v>80132</v>
@@ -14217,10 +14207,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>544360</v>
+        <v>544282</v>
       </c>
       <c r="R137" t="n">
-        <v>6963094</v>
+        <v>6963082</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14279,32 +14269,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128087344</v>
+        <v>128087328</v>
       </c>
       <c r="B138" t="n">
-        <v>80161</v>
+        <v>57672</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14314,10 +14304,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>544581</v>
+        <v>544736</v>
       </c>
       <c r="R138" t="n">
-        <v>6963278</v>
+        <v>6963153</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14350,6 +14340,11 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14376,32 +14371,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128087534</v>
+        <v>128087530</v>
       </c>
       <c r="B139" t="n">
-        <v>80132</v>
+        <v>98504</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6458</v>
+        <v>219874</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14411,10 +14406,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>544326</v>
+        <v>544737</v>
       </c>
       <c r="R139" t="n">
-        <v>6963248</v>
+        <v>6963047</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14473,10 +14468,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128087345</v>
+        <v>128087381</v>
       </c>
       <c r="B140" t="n">
-        <v>80161</v>
+        <v>98387</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14484,21 +14479,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6462</v>
+        <v>219790</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14508,10 +14503,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>544391</v>
+        <v>544531</v>
       </c>
       <c r="R140" t="n">
-        <v>6963205</v>
+        <v>6963190</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14570,32 +14565,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128087540</v>
+        <v>128087557</v>
       </c>
       <c r="B141" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14605,10 +14600,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>544282</v>
+        <v>544552</v>
       </c>
       <c r="R141" t="n">
-        <v>6963082</v>
+        <v>6963231</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14641,6 +14636,11 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14667,10 +14667,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128087557</v>
+        <v>128087543</v>
       </c>
       <c r="B142" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14702,10 +14702,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>544552</v>
+        <v>544674</v>
       </c>
       <c r="R142" t="n">
-        <v>6963231</v>
+        <v>6963243</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14742,7 +14742,7 @@
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>30 stycken</t>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -14769,10 +14769,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128078685</v>
+        <v>128087368</v>
       </c>
       <c r="B143" t="n">
-        <v>56248</v>
+        <v>80132</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14780,39 +14780,34 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>206004</v>
+        <v>6458</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>544307</v>
+        <v>544314</v>
       </c>
       <c r="R143" t="n">
-        <v>6963069</v>
+        <v>6963248</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14874,7 +14869,7 @@
         <v>128078529</v>
       </c>
       <c r="B144" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14972,10 +14967,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128087368</v>
+        <v>128078685</v>
       </c>
       <c r="B145" t="n">
-        <v>80132</v>
+        <v>56248</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14983,34 +14978,39 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>544314</v>
+        <v>544307</v>
       </c>
       <c r="R145" t="n">
-        <v>6963248</v>
+        <v>6963069</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15174,7 +15174,7 @@
         <v>128094046</v>
       </c>
       <c r="B147" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15276,7 +15276,7 @@
         <v>128094050</v>
       </c>
       <c r="B148" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15472,32 +15472,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128094032</v>
+        <v>128094042</v>
       </c>
       <c r="B150" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15507,10 +15507,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>544279</v>
+        <v>544528</v>
       </c>
       <c r="R150" t="n">
-        <v>6963296</v>
+        <v>6963294</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15547,7 +15547,7 @@
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>75 ex</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15574,32 +15574,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128094042</v>
+        <v>128094032</v>
       </c>
       <c r="B151" t="n">
-        <v>98469</v>
+        <v>57672</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15609,10 +15609,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>544528</v>
+        <v>544279</v>
       </c>
       <c r="R151" t="n">
-        <v>6963294</v>
+        <v>6963296</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15649,7 +15649,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>75 ex</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15781,7 +15781,7 @@
         <v>128094044</v>
       </c>
       <c r="B153" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15883,7 +15883,7 @@
         <v>128094040</v>
       </c>
       <c r="B154" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15985,7 +15985,7 @@
         <v>128094043</v>
       </c>
       <c r="B155" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16084,10 +16084,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128094041</v>
+        <v>128094048</v>
       </c>
       <c r="B156" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16119,10 +16119,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>544411</v>
+        <v>544610</v>
       </c>
       <c r="R156" t="n">
-        <v>6963326</v>
+        <v>6963173</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16159,7 +16159,7 @@
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>34 ex</t>
+          <t>24 ex</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16186,10 +16186,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128094048</v>
+        <v>128094041</v>
       </c>
       <c r="B157" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16221,10 +16221,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>544610</v>
+        <v>544411</v>
       </c>
       <c r="R157" t="n">
-        <v>6963173</v>
+        <v>6963326</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16261,7 +16261,7 @@
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>24 ex</t>
+          <t>34 ex</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16291,7 +16291,7 @@
         <v>128094049</v>
       </c>
       <c r="B158" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>128094053</v>
       </c>
       <c r="B159" t="n">
-        <v>105507</v>
+        <v>105508</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16487,32 +16487,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128094052</v>
+        <v>128094047</v>
       </c>
       <c r="B160" t="n">
-        <v>56855</v>
+        <v>98470</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16522,10 +16522,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>544577</v>
+        <v>544641</v>
       </c>
       <c r="R160" t="n">
-        <v>6963169</v>
+        <v>6963158</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16562,7 +16562,7 @@
       </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>Individ noterad genom sång</t>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -16589,10 +16589,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128094047</v>
+        <v>128094051</v>
       </c>
       <c r="B161" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16624,10 +16624,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>544641</v>
+        <v>544310</v>
       </c>
       <c r="R161" t="n">
-        <v>6963158</v>
+        <v>6963314</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16664,7 +16664,7 @@
       </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>11 ex</t>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -16691,10 +16691,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128094051</v>
+        <v>128094045</v>
       </c>
       <c r="B162" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16726,10 +16726,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>544310</v>
+        <v>544760</v>
       </c>
       <c r="R162" t="n">
-        <v>6963314</v>
+        <v>6963251</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16766,7 +16766,7 @@
       </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>80 ex</t>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -16793,32 +16793,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128094045</v>
+        <v>128094052</v>
       </c>
       <c r="B163" t="n">
-        <v>98469</v>
+        <v>56855</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -16828,10 +16828,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>544760</v>
+        <v>544577</v>
       </c>
       <c r="R163" t="n">
-        <v>6963251</v>
+        <v>6963169</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -16868,7 +16868,7 @@
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>35 ex</t>
+          <t>Individ noterad genom sång</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -16898,7 +16898,7 @@
         <v>128094054</v>
       </c>
       <c r="B164" t="n">
-        <v>105507</v>
+        <v>105508</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17301,7 +17301,7 @@
         <v>128094055</v>
       </c>
       <c r="B168" t="n">
-        <v>105507</v>
+        <v>105508</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>

--- a/artfynd/A 32240-2025 artfynd.xlsx
+++ b/artfynd/A 32240-2025 artfynd.xlsx
@@ -1485,10 +1485,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128087516</v>
+        <v>128087526</v>
       </c>
       <c r="B10" t="n">
-        <v>57672</v>
+        <v>92634</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1496,21 +1496,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544388</v>
+        <v>544728</v>
       </c>
       <c r="R10" t="n">
-        <v>6963226</v>
+        <v>6963223</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall Äldre spår</t>
+          <t>10 exemplar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1587,10 +1587,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128087526</v>
+        <v>128087516</v>
       </c>
       <c r="B11" t="n">
-        <v>92634</v>
+        <v>57672</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1598,21 +1598,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4361</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544728</v>
+        <v>544388</v>
       </c>
       <c r="R11" t="n">
-        <v>6963223</v>
+        <v>6963226</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>10 exemplar</t>
+          <t>Ringhack av tretåig hackspett på Tall Äldre spår</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1786,10 +1786,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128081639</v>
+        <v>128087323</v>
       </c>
       <c r="B13" t="n">
-        <v>80133</v>
+        <v>57672</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1797,21 +1797,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544323</v>
+        <v>544646</v>
       </c>
       <c r="R13" t="n">
-        <v>6963268</v>
+        <v>6963095</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1857,6 +1857,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1883,32 +1888,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128087347</v>
+        <v>128087324</v>
       </c>
       <c r="B14" t="n">
-        <v>80161</v>
+        <v>57672</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1918,10 +1923,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544745</v>
+        <v>544792</v>
       </c>
       <c r="R14" t="n">
-        <v>6963195</v>
+        <v>6963047</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1954,6 +1959,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1980,10 +1990,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128087323</v>
+        <v>128081639</v>
       </c>
       <c r="B15" t="n">
-        <v>57672</v>
+        <v>80133</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1991,21 +2001,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2015,10 +2025,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544646</v>
+        <v>544323</v>
       </c>
       <c r="R15" t="n">
-        <v>6963095</v>
+        <v>6963268</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2051,11 +2061,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2082,32 +2087,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128087324</v>
+        <v>128087347</v>
       </c>
       <c r="B16" t="n">
-        <v>57672</v>
+        <v>80161</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2117,10 +2122,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544792</v>
+        <v>544745</v>
       </c>
       <c r="R16" t="n">
-        <v>6963047</v>
+        <v>6963195</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2153,11 +2158,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2388,10 +2388,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128087359</v>
+        <v>128087581</v>
       </c>
       <c r="B19" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2399,21 +2399,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2423,10 +2423,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544741</v>
+        <v>544192</v>
       </c>
       <c r="R19" t="n">
-        <v>6963165</v>
+        <v>6963197</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2485,10 +2485,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128087354</v>
+        <v>128087362</v>
       </c>
       <c r="B20" t="n">
-        <v>80133</v>
+        <v>80132</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2496,21 +2496,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544820</v>
+        <v>544799</v>
       </c>
       <c r="R20" t="n">
-        <v>6963278</v>
+        <v>6963263</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2582,32 +2582,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128087581</v>
+        <v>128087349</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>80161</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544192</v>
+        <v>544475</v>
       </c>
       <c r="R21" t="n">
-        <v>6963197</v>
+        <v>6963205</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2679,10 +2679,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128087362</v>
+        <v>128087354</v>
       </c>
       <c r="B22" t="n">
-        <v>80132</v>
+        <v>80133</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2690,21 +2690,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2714,10 +2714,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544799</v>
+        <v>544820</v>
       </c>
       <c r="R22" t="n">
-        <v>6963263</v>
+        <v>6963278</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2776,32 +2776,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128087349</v>
+        <v>128087569</v>
       </c>
       <c r="B23" t="n">
-        <v>80161</v>
+        <v>98470</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2811,10 +2811,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544475</v>
+        <v>544296</v>
       </c>
       <c r="R23" t="n">
-        <v>6963205</v>
+        <v>6963084</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2847,6 +2847,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>100stycken</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2873,7 +2878,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128087569</v>
+        <v>128087554</v>
       </c>
       <c r="B24" t="n">
         <v>98470</v>
@@ -2908,10 +2913,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544296</v>
+        <v>544659</v>
       </c>
       <c r="R24" t="n">
-        <v>6963084</v>
+        <v>6963253</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2948,7 +2953,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>100stycken</t>
+          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2975,32 +2980,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128087554</v>
+        <v>128087359</v>
       </c>
       <c r="B25" t="n">
-        <v>98470</v>
+        <v>78788</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3010,10 +3015,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544659</v>
+        <v>544741</v>
       </c>
       <c r="R25" t="n">
-        <v>6963253</v>
+        <v>6963165</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3046,11 +3051,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3077,32 +3077,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128087562</v>
+        <v>128087331</v>
       </c>
       <c r="B26" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3112,10 +3112,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>544367</v>
+        <v>544763</v>
       </c>
       <c r="R26" t="n">
-        <v>6963253</v>
+        <v>6963244</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>7. Kan möjlitvis finnas fler runt omkring.</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3179,49 +3179,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128078161</v>
+        <v>128087333</v>
       </c>
       <c r="B27" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544362</v>
+        <v>544355</v>
       </c>
       <c r="R27" t="n">
-        <v>6963061</v>
+        <v>6963212</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3254,6 +3250,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3280,49 +3281,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128078740</v>
+        <v>128087532</v>
       </c>
       <c r="B28" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544307</v>
+        <v>544491</v>
       </c>
       <c r="R28" t="n">
-        <v>6963089</v>
+        <v>6963099</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3381,7 +3378,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128087563</v>
+        <v>128087562</v>
       </c>
       <c r="B29" t="n">
         <v>98470</v>
@@ -3416,10 +3413,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544322</v>
+        <v>544367</v>
       </c>
       <c r="R29" t="n">
-        <v>6963250</v>
+        <v>6963253</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3456,7 +3453,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>12 stycken</t>
+          <t>7. Kan möjlitvis finnas fler runt omkring.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3483,45 +3480,49 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128087331</v>
+        <v>128078161</v>
       </c>
       <c r="B30" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>544763</v>
+        <v>544362</v>
       </c>
       <c r="R30" t="n">
-        <v>6963244</v>
+        <v>6963061</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3554,11 +3555,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3585,45 +3581,49 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128087333</v>
+        <v>128078740</v>
       </c>
       <c r="B31" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>544355</v>
+        <v>544307</v>
       </c>
       <c r="R31" t="n">
-        <v>6963212</v>
+        <v>6963089</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3656,11 +3656,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3687,32 +3682,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128087532</v>
+        <v>128087563</v>
       </c>
       <c r="B32" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3722,10 +3717,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544491</v>
+        <v>544322</v>
       </c>
       <c r="R32" t="n">
-        <v>6963099</v>
+        <v>6963250</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3758,6 +3753,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>12 stycken</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3886,10 +3886,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128087336</v>
+        <v>128079621</v>
       </c>
       <c r="B34" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3897,21 +3897,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3921,10 +3921,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>544398</v>
+        <v>544274</v>
       </c>
       <c r="R34" t="n">
-        <v>6963202</v>
+        <v>6963119</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3957,11 +3957,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3988,7 +3983,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128079621</v>
+        <v>128087533</v>
       </c>
       <c r="B35" t="n">
         <v>80132</v>
@@ -4023,10 +4018,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>544274</v>
+        <v>544473</v>
       </c>
       <c r="R35" t="n">
-        <v>6963119</v>
+        <v>6963102</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4085,32 +4080,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128087533</v>
+        <v>128087351</v>
       </c>
       <c r="B36" t="n">
-        <v>80132</v>
+        <v>80161</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4120,10 +4115,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>544473</v>
+        <v>544299</v>
       </c>
       <c r="R36" t="n">
-        <v>6963102</v>
+        <v>6963312</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4182,32 +4177,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128087351</v>
+        <v>128087365</v>
       </c>
       <c r="B37" t="n">
-        <v>80161</v>
+        <v>80132</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4217,10 +4212,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>544299</v>
+        <v>544469</v>
       </c>
       <c r="R37" t="n">
-        <v>6963312</v>
+        <v>6963145</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4279,10 +4274,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128087365</v>
+        <v>128087336</v>
       </c>
       <c r="B38" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4290,21 +4285,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4314,10 +4309,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>544469</v>
+        <v>544398</v>
       </c>
       <c r="R38" t="n">
-        <v>6963145</v>
+        <v>6963202</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4350,6 +4345,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4876,10 +4876,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128087360</v>
+        <v>128087340</v>
       </c>
       <c r="B44" t="n">
-        <v>80132</v>
+        <v>57832</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4887,21 +4887,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4911,10 +4911,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>544615</v>
+        <v>544485</v>
       </c>
       <c r="R44" t="n">
-        <v>6963093</v>
+        <v>6963237</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5371,10 +5371,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128087340</v>
+        <v>128087360</v>
       </c>
       <c r="B49" t="n">
-        <v>57832</v>
+        <v>80132</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5382,21 +5382,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>544485</v>
+        <v>544615</v>
       </c>
       <c r="R49" t="n">
-        <v>6963237</v>
+        <v>6963093</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5759,32 +5759,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128087553</v>
+        <v>128087339</v>
       </c>
       <c r="B53" t="n">
-        <v>98470</v>
+        <v>57832</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5794,10 +5794,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>544677</v>
+        <v>544850</v>
       </c>
       <c r="R53" t="n">
-        <v>6963260</v>
+        <v>6963099</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Mer än 70 stycken. Flera blommar</t>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5861,32 +5861,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128087555</v>
+        <v>128079839</v>
       </c>
       <c r="B54" t="n">
-        <v>98470</v>
+        <v>105508</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>544623</v>
+        <v>544288</v>
       </c>
       <c r="R54" t="n">
-        <v>6963241</v>
+        <v>6963182</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5932,11 +5932,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>60 stycken</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5963,32 +5958,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128079839</v>
+        <v>128087553</v>
       </c>
       <c r="B55" t="n">
-        <v>105508</v>
+        <v>98470</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5998,10 +5993,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>544288</v>
+        <v>544677</v>
       </c>
       <c r="R55" t="n">
-        <v>6963182</v>
+        <v>6963260</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6034,6 +6029,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Mer än 70 stycken. Flera blommar</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6060,32 +6060,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128087339</v>
+        <v>128087555</v>
       </c>
       <c r="B56" t="n">
-        <v>57832</v>
+        <v>98470</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>544850</v>
+        <v>544623</v>
       </c>
       <c r="R56" t="n">
-        <v>6963099</v>
+        <v>6963241</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Lockläte/övriga läten</t>
+          <t>60 stycken</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6565,32 +6565,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128087386</v>
+        <v>128087566</v>
       </c>
       <c r="B61" t="n">
-        <v>92636</v>
+        <v>98470</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4362</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6600,10 +6600,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>544822</v>
+        <v>544261</v>
       </c>
       <c r="R61" t="n">
-        <v>6963295</v>
+        <v>6963170</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6636,6 +6636,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>4. Stycken. Finns möjligtvis fler i blåbärsriset.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6662,32 +6667,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128078603</v>
+        <v>128087377</v>
       </c>
       <c r="B62" t="n">
-        <v>80161</v>
+        <v>98470</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6697,10 +6702,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>544360</v>
+        <v>544403</v>
       </c>
       <c r="R62" t="n">
-        <v>6963094</v>
+        <v>6963221</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6733,6 +6738,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6759,32 +6769,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128087523</v>
+        <v>128087378</v>
       </c>
       <c r="B63" t="n">
-        <v>80161</v>
+        <v>98470</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6794,10 +6804,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>544253</v>
+        <v>544218</v>
       </c>
       <c r="R63" t="n">
-        <v>6963139</v>
+        <v>6963229</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6830,6 +6840,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6856,32 +6871,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128087579</v>
+        <v>128087375</v>
       </c>
       <c r="B64" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6891,10 +6906,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>544204</v>
+        <v>544478</v>
       </c>
       <c r="R64" t="n">
-        <v>6963238</v>
+        <v>6963117</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6931,7 +6946,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Riklig förekomst av garnlav</t>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6958,10 +6973,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128087329</v>
+        <v>128087386</v>
       </c>
       <c r="B65" t="n">
-        <v>57672</v>
+        <v>92636</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6969,21 +6984,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>4362</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6993,10 +7008,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>544757</v>
+        <v>544822</v>
       </c>
       <c r="R65" t="n">
-        <v>6963172</v>
+        <v>6963295</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7029,11 +7044,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7060,32 +7070,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128087566</v>
+        <v>128078603</v>
       </c>
       <c r="B66" t="n">
-        <v>98470</v>
+        <v>80161</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7095,10 +7105,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>544261</v>
+        <v>544360</v>
       </c>
       <c r="R66" t="n">
-        <v>6963170</v>
+        <v>6963094</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7131,11 +7141,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>4. Stycken. Finns möjligtvis fler i blåbärsriset.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7162,32 +7167,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128087377</v>
+        <v>128087523</v>
       </c>
       <c r="B67" t="n">
-        <v>98470</v>
+        <v>80161</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7197,10 +7202,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>544403</v>
+        <v>544253</v>
       </c>
       <c r="R67" t="n">
-        <v>6963221</v>
+        <v>6963139</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7233,11 +7238,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>20 ex</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7264,32 +7264,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128087378</v>
+        <v>128087579</v>
       </c>
       <c r="B68" t="n">
-        <v>98470</v>
+        <v>79029</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7299,10 +7299,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>544218</v>
+        <v>544204</v>
       </c>
       <c r="R68" t="n">
-        <v>6963229</v>
+        <v>6963238</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7339,7 +7339,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>80 ex</t>
+          <t>Riklig förekomst av garnlav</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7366,32 +7366,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128087375</v>
+        <v>128087525</v>
       </c>
       <c r="B69" t="n">
-        <v>98470</v>
+        <v>56248</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>206004</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7401,10 +7401,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>544478</v>
+        <v>544385</v>
       </c>
       <c r="R69" t="n">
-        <v>6963117</v>
+        <v>6963074</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7437,11 +7437,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>35 ex</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7468,10 +7463,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128087525</v>
+        <v>128087329</v>
       </c>
       <c r="B70" t="n">
-        <v>56248</v>
+        <v>57672</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7479,21 +7474,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7503,10 +7498,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>544385</v>
+        <v>544757</v>
       </c>
       <c r="R70" t="n">
-        <v>6963074</v>
+        <v>6963172</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7539,6 +7534,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8182,45 +8182,49 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128087536</v>
+        <v>128079875</v>
       </c>
       <c r="B77" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>544215</v>
+        <v>544308</v>
       </c>
       <c r="R77" t="n">
-        <v>6963245</v>
+        <v>6963175</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8279,32 +8283,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128087343</v>
+        <v>128087542</v>
       </c>
       <c r="B78" t="n">
-        <v>80161</v>
+        <v>98470</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8314,10 +8318,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>544757</v>
+        <v>544752</v>
       </c>
       <c r="R78" t="n">
-        <v>6963156</v>
+        <v>6963192</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8350,6 +8354,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8376,45 +8385,49 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128087346</v>
+        <v>128080338</v>
       </c>
       <c r="B79" t="n">
-        <v>80161</v>
+        <v>98470</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>544422</v>
+        <v>544314</v>
       </c>
       <c r="R79" t="n">
-        <v>6963240</v>
+        <v>6963248</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8473,7 +8486,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128079875</v>
+        <v>128087547</v>
       </c>
       <c r="B80" t="n">
         <v>98470</v>
@@ -8501,21 +8514,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>544308</v>
+        <v>544380</v>
       </c>
       <c r="R80" t="n">
-        <v>6963175</v>
+        <v>6963236</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8548,6 +8557,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>33 stycken</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8574,32 +8588,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128087542</v>
+        <v>128087380</v>
       </c>
       <c r="B81" t="n">
-        <v>98470</v>
+        <v>105508</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8609,10 +8623,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>544752</v>
+        <v>544468</v>
       </c>
       <c r="R81" t="n">
-        <v>6963192</v>
+        <v>6963173</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8645,11 +8659,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8676,7 +8685,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128080338</v>
+        <v>128087560</v>
       </c>
       <c r="B82" t="n">
         <v>98470</v>
@@ -8704,21 +8713,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>544314</v>
+        <v>544383</v>
       </c>
       <c r="R82" t="n">
-        <v>6963248</v>
+        <v>6963236</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8751,6 +8756,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8777,32 +8787,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128087547</v>
+        <v>128087570</v>
       </c>
       <c r="B83" t="n">
-        <v>98470</v>
+        <v>56855</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8812,10 +8822,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>544380</v>
+        <v>544287</v>
       </c>
       <c r="R83" t="n">
-        <v>6963236</v>
+        <v>6963082</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8852,7 +8862,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>33 stycken</t>
+          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8879,32 +8889,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128087560</v>
+        <v>128087575</v>
       </c>
       <c r="B84" t="n">
-        <v>98470</v>
+        <v>92674</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>1968</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8914,10 +8924,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>544383</v>
+        <v>544532</v>
       </c>
       <c r="R84" t="n">
-        <v>6963236</v>
+        <v>6963250</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8954,7 +8964,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>40 stycken</t>
+          <t>Igen stor köttig svamp misstänker grantaggsvamp 2 ex</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8981,7 +8991,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128087575</v>
+        <v>128078492</v>
       </c>
       <c r="B85" t="n">
         <v>92674</v>
@@ -9016,10 +9026,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>544532</v>
+        <v>544362</v>
       </c>
       <c r="R85" t="n">
-        <v>6963250</v>
+        <v>6963073</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9052,11 +9062,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Igen stor köttig svamp misstänker grantaggsvamp 2 ex</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9083,10 +9088,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128078492</v>
+        <v>128087536</v>
       </c>
       <c r="B86" t="n">
-        <v>92674</v>
+        <v>80132</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9094,21 +9099,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1968</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9118,10 +9123,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>544362</v>
+        <v>544215</v>
       </c>
       <c r="R86" t="n">
-        <v>6963073</v>
+        <v>6963245</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9180,32 +9185,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128087570</v>
+        <v>128087343</v>
       </c>
       <c r="B87" t="n">
-        <v>56855</v>
+        <v>80161</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>102612</v>
+        <v>6462</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9215,10 +9220,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>544287</v>
+        <v>544757</v>
       </c>
       <c r="R87" t="n">
-        <v>6963082</v>
+        <v>6963156</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9251,11 +9256,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9282,32 +9282,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128087330</v>
+        <v>128087346</v>
       </c>
       <c r="B88" t="n">
-        <v>57672</v>
+        <v>80161</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9317,10 +9317,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>544750</v>
+        <v>544422</v>
       </c>
       <c r="R88" t="n">
-        <v>6963177</v>
+        <v>6963240</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9353,11 +9353,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9384,7 +9379,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128087335</v>
+        <v>128087330</v>
       </c>
       <c r="B89" t="n">
         <v>57672</v>
@@ -9419,10 +9414,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>544366</v>
+        <v>544750</v>
       </c>
       <c r="R89" t="n">
-        <v>6963181</v>
+        <v>6963177</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9486,32 +9481,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128087380</v>
+        <v>128087335</v>
       </c>
       <c r="B90" t="n">
-        <v>105508</v>
+        <v>57672</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221144</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9521,10 +9516,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>544468</v>
+        <v>544366</v>
       </c>
       <c r="R90" t="n">
-        <v>6963173</v>
+        <v>6963181</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9557,6 +9552,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9583,32 +9583,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128087539</v>
+        <v>128087376</v>
       </c>
       <c r="B91" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9618,10 +9618,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>544254</v>
+        <v>544503</v>
       </c>
       <c r="R91" t="n">
-        <v>6963139</v>
+        <v>6963182</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9654,6 +9654,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>60 ex</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9680,32 +9685,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128087341</v>
+        <v>128087379</v>
       </c>
       <c r="B92" t="n">
-        <v>80161</v>
+        <v>98470</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9715,10 +9720,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>544615</v>
+        <v>544263</v>
       </c>
       <c r="R92" t="n">
-        <v>6963101</v>
+        <v>6963254</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9751,6 +9756,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9879,32 +9889,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128087376</v>
+        <v>128087539</v>
       </c>
       <c r="B94" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9914,10 +9924,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>544503</v>
+        <v>544254</v>
       </c>
       <c r="R94" t="n">
-        <v>6963182</v>
+        <v>6963139</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9950,11 +9960,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>60 ex</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9981,32 +9986,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128087379</v>
+        <v>128087341</v>
       </c>
       <c r="B95" t="n">
-        <v>98470</v>
+        <v>80161</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10016,10 +10021,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>544263</v>
+        <v>544615</v>
       </c>
       <c r="R95" t="n">
-        <v>6963254</v>
+        <v>6963101</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10052,11 +10057,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>15 ex</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10083,32 +10083,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128087545</v>
+        <v>128087355</v>
       </c>
       <c r="B96" t="n">
-        <v>98470</v>
+        <v>97353</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10118,10 +10118,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>544633</v>
+        <v>544500</v>
       </c>
       <c r="R96" t="n">
-        <v>6963244</v>
+        <v>6963168</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10154,11 +10154,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10185,32 +10180,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128087567</v>
+        <v>128087522</v>
       </c>
       <c r="B97" t="n">
-        <v>98470</v>
+        <v>57832</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10220,10 +10215,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>544274</v>
+        <v>544494</v>
       </c>
       <c r="R97" t="n">
-        <v>6963090</v>
+        <v>6963243</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10256,11 +10251,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>110</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10287,7 +10277,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128087556</v>
+        <v>128087545</v>
       </c>
       <c r="B98" t="n">
         <v>98470</v>
@@ -10322,10 +10312,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>544594</v>
+        <v>544633</v>
       </c>
       <c r="R98" t="n">
-        <v>6963215</v>
+        <v>6963244</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10362,7 +10352,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>6 stycken. Kan finnas mer i omgivningen</t>
+          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10389,7 +10379,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128087373</v>
+        <v>128087567</v>
       </c>
       <c r="B99" t="n">
         <v>98470</v>
@@ -10424,10 +10414,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>544469</v>
+        <v>544274</v>
       </c>
       <c r="R99" t="n">
-        <v>6963122</v>
+        <v>6963090</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10464,7 +10454,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>60 ex</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10491,7 +10481,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128087559</v>
+        <v>128087556</v>
       </c>
       <c r="B100" t="n">
         <v>98470</v>
@@ -10526,10 +10516,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>544396</v>
+        <v>544594</v>
       </c>
       <c r="R100" t="n">
-        <v>6963233</v>
+        <v>6963215</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10566,7 +10556,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>18 stycken</t>
+          <t>6 stycken. Kan finnas mer i omgivningen</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10593,32 +10583,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128087355</v>
+        <v>128087373</v>
       </c>
       <c r="B101" t="n">
-        <v>97353</v>
+        <v>98470</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10628,10 +10618,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>544500</v>
+        <v>544469</v>
       </c>
       <c r="R101" t="n">
-        <v>6963168</v>
+        <v>6963122</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10664,6 +10654,11 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>60 ex</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10690,10 +10685,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128087383</v>
+        <v>128078864</v>
       </c>
       <c r="B102" t="n">
-        <v>80167</v>
+        <v>105508</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10701,21 +10696,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6463</v>
+        <v>221144</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10725,10 +10720,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>544566</v>
+        <v>544307</v>
       </c>
       <c r="R102" t="n">
-        <v>6963076</v>
+        <v>6963089</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10787,32 +10782,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128087384</v>
+        <v>128087559</v>
       </c>
       <c r="B103" t="n">
-        <v>80167</v>
+        <v>98470</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10822,10 +10817,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>544584</v>
+        <v>544396</v>
       </c>
       <c r="R103" t="n">
-        <v>6963261</v>
+        <v>6963233</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10858,6 +10853,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10884,10 +10884,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128087363</v>
+        <v>128087576</v>
       </c>
       <c r="B104" t="n">
-        <v>80132</v>
+        <v>92674</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10895,21 +10895,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>1968</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10919,10 +10919,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>544818</v>
+        <v>544529</v>
       </c>
       <c r="R104" t="n">
-        <v>6963278</v>
+        <v>6963245</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10955,6 +10955,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Misstänkt grantaggsvamp men med mörk tydlig ring i mitten.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10981,7 +10986,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128087576</v>
+        <v>128087572</v>
       </c>
       <c r="B105" t="n">
         <v>92674</v>
@@ -11016,7 +11021,7 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>544529</v>
+        <v>544632</v>
       </c>
       <c r="R105" t="n">
         <v>6963245</v>
@@ -11056,7 +11061,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Misstänkt grantaggsvamp men med mörk tydlig ring i mitten.</t>
+          <t>1 ex</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11083,32 +11088,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128087572</v>
+        <v>128087383</v>
       </c>
       <c r="B106" t="n">
-        <v>92674</v>
+        <v>80167</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1968</v>
+        <v>6463</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11118,10 +11123,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>544632</v>
+        <v>544566</v>
       </c>
       <c r="R106" t="n">
-        <v>6963245</v>
+        <v>6963076</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11154,11 +11159,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>1 ex</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11185,32 +11185,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128087522</v>
+        <v>128087384</v>
       </c>
       <c r="B107" t="n">
-        <v>57832</v>
+        <v>80167</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>103021</v>
+        <v>6463</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11220,10 +11220,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>544494</v>
+        <v>544584</v>
       </c>
       <c r="R107" t="n">
-        <v>6963243</v>
+        <v>6963261</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11282,32 +11282,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128078864</v>
+        <v>128087363</v>
       </c>
       <c r="B108" t="n">
-        <v>105508</v>
+        <v>80132</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>221144</v>
+        <v>6458</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11317,10 +11317,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>544307</v>
+        <v>544818</v>
       </c>
       <c r="R108" t="n">
-        <v>6963089</v>
+        <v>6963278</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11476,10 +11476,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128087531</v>
+        <v>128087586</v>
       </c>
       <c r="B110" t="n">
-        <v>98504</v>
+        <v>92642</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11487,21 +11487,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>219874</v>
+        <v>4364</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11511,10 +11511,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>544755</v>
+        <v>544281</v>
       </c>
       <c r="R110" t="n">
-        <v>6963130</v>
+        <v>6963257</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11551,7 +11551,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>2 stycken</t>
+          <t>2 nya exemplar 8 äldre ex</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11675,10 +11675,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128087586</v>
+        <v>128087531</v>
       </c>
       <c r="B112" t="n">
-        <v>92642</v>
+        <v>98504</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11686,21 +11686,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>4364</v>
+        <v>219874</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11710,10 +11710,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>544281</v>
+        <v>544755</v>
       </c>
       <c r="R112" t="n">
-        <v>6963257</v>
+        <v>6963130</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11750,7 +11750,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>2 nya exemplar 8 äldre ex</t>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12776,45 +12776,49 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128087582</v>
+        <v>128079571</v>
       </c>
       <c r="B123" t="n">
-        <v>98387</v>
+        <v>98470</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>544489</v>
+        <v>544274</v>
       </c>
       <c r="R123" t="n">
-        <v>6963098</v>
+        <v>6963119</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12873,7 +12877,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128079571</v>
+        <v>128078138</v>
       </c>
       <c r="B124" t="n">
         <v>98470</v>
@@ -12903,7 +12907,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -12912,10 +12916,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>544274</v>
+        <v>544374</v>
       </c>
       <c r="R124" t="n">
-        <v>6963119</v>
+        <v>6963056</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12974,49 +12978,45 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128078138</v>
+        <v>128087582</v>
       </c>
       <c r="B125" t="n">
-        <v>98470</v>
+        <v>98387</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>544374</v>
+        <v>544489</v>
       </c>
       <c r="R125" t="n">
-        <v>6963056</v>
+        <v>6963098</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13075,32 +13075,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128087574</v>
+        <v>128087370</v>
       </c>
       <c r="B126" t="n">
-        <v>92674</v>
+        <v>98470</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1968</v>
+        <v>220787</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13110,10 +13110,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>544552</v>
+        <v>544751</v>
       </c>
       <c r="R126" t="n">
-        <v>6963231</v>
+        <v>6963146</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13150,7 +13150,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>Misstänker grantaggsvamp 1 exemplar</t>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13177,32 +13177,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128079484</v>
+        <v>128087371</v>
       </c>
       <c r="B127" t="n">
-        <v>80168</v>
+        <v>98470</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13212,10 +13212,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>544289</v>
+        <v>544559</v>
       </c>
       <c r="R127" t="n">
-        <v>6963113</v>
+        <v>6963215</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13248,6 +13248,11 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13274,32 +13279,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128087334</v>
+        <v>128087583</v>
       </c>
       <c r="B128" t="n">
-        <v>57672</v>
+        <v>98387</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13309,10 +13314,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>544348</v>
+        <v>544708</v>
       </c>
       <c r="R128" t="n">
-        <v>6963187</v>
+        <v>6963086</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13349,7 +13354,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13376,7 +13381,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128087583</v>
+        <v>128087584</v>
       </c>
       <c r="B129" t="n">
         <v>98387</v>
@@ -13411,10 +13416,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>544708</v>
+        <v>544718</v>
       </c>
       <c r="R129" t="n">
-        <v>6963086</v>
+        <v>6963053</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13451,7 +13456,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3 stycken</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13478,32 +13483,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128087584</v>
+        <v>128087574</v>
       </c>
       <c r="B130" t="n">
-        <v>98387</v>
+        <v>92674</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>219790</v>
+        <v>1968</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13513,10 +13518,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>544718</v>
+        <v>544552</v>
       </c>
       <c r="R130" t="n">
-        <v>6963053</v>
+        <v>6963231</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13553,7 +13558,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>3 stycken</t>
+          <t>Misstänker grantaggsvamp 1 exemplar</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13580,32 +13585,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128087370</v>
+        <v>128079484</v>
       </c>
       <c r="B131" t="n">
-        <v>98470</v>
+        <v>80168</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13615,10 +13620,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>544751</v>
+        <v>544289</v>
       </c>
       <c r="R131" t="n">
-        <v>6963146</v>
+        <v>6963113</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13651,11 +13656,6 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>30 ex</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13682,32 +13682,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128087371</v>
+        <v>128087334</v>
       </c>
       <c r="B132" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13717,10 +13717,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>544559</v>
+        <v>544348</v>
       </c>
       <c r="R132" t="n">
-        <v>6963215</v>
+        <v>6963187</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13757,7 +13757,7 @@
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>100 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14371,32 +14371,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128087530</v>
+        <v>128087557</v>
       </c>
       <c r="B139" t="n">
-        <v>98504</v>
+        <v>98470</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14406,10 +14406,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>544737</v>
+        <v>544552</v>
       </c>
       <c r="R139" t="n">
-        <v>6963047</v>
+        <v>6963231</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14442,6 +14442,11 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14468,32 +14473,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128087381</v>
+        <v>128087543</v>
       </c>
       <c r="B140" t="n">
-        <v>98387</v>
+        <v>98470</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14503,10 +14508,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>544531</v>
+        <v>544674</v>
       </c>
       <c r="R140" t="n">
-        <v>6963190</v>
+        <v>6963243</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14539,6 +14544,11 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14565,32 +14575,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128087557</v>
+        <v>128087530</v>
       </c>
       <c r="B141" t="n">
-        <v>98470</v>
+        <v>98504</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14600,10 +14610,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>544552</v>
+        <v>544737</v>
       </c>
       <c r="R141" t="n">
-        <v>6963231</v>
+        <v>6963047</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14636,11 +14646,6 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14667,32 +14672,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128087543</v>
+        <v>128087381</v>
       </c>
       <c r="B142" t="n">
-        <v>98470</v>
+        <v>98387</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14702,10 +14707,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>544674</v>
+        <v>544531</v>
       </c>
       <c r="R142" t="n">
-        <v>6963243</v>
+        <v>6963190</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14738,11 +14743,6 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -14769,10 +14769,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128087368</v>
+        <v>128078685</v>
       </c>
       <c r="B143" t="n">
-        <v>80132</v>
+        <v>56248</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14780,34 +14780,39 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>544314</v>
+        <v>544307</v>
       </c>
       <c r="R143" t="n">
-        <v>6963248</v>
+        <v>6963069</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14967,10 +14972,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128078685</v>
+        <v>128087368</v>
       </c>
       <c r="B145" t="n">
-        <v>56248</v>
+        <v>80132</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14978,39 +14983,34 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>206004</v>
+        <v>6458</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>544307</v>
+        <v>544314</v>
       </c>
       <c r="R145" t="n">
-        <v>6963069</v>
+        <v>6963248</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15069,32 +15069,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128094035</v>
+        <v>128094046</v>
       </c>
       <c r="B146" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15104,10 +15104,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>544736</v>
+        <v>544754</v>
       </c>
       <c r="R146" t="n">
-        <v>6963232</v>
+        <v>6963261</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15144,7 +15144,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15171,32 +15171,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128094046</v>
+        <v>128094035</v>
       </c>
       <c r="B147" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15206,10 +15206,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>544754</v>
+        <v>544736</v>
       </c>
       <c r="R147" t="n">
-        <v>6963261</v>
+        <v>6963232</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15246,7 +15246,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>25 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15472,32 +15472,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128094042</v>
+        <v>128094032</v>
       </c>
       <c r="B150" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15507,10 +15507,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>544528</v>
+        <v>544279</v>
       </c>
       <c r="R150" t="n">
-        <v>6963294</v>
+        <v>6963296</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15547,7 +15547,7 @@
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>75 ex</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15574,32 +15574,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128094032</v>
+        <v>128094042</v>
       </c>
       <c r="B151" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15609,10 +15609,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>544279</v>
+        <v>544528</v>
       </c>
       <c r="R151" t="n">
-        <v>6963296</v>
+        <v>6963294</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15649,7 +15649,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>75 ex</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15676,32 +15676,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128094038</v>
+        <v>128094044</v>
       </c>
       <c r="B152" t="n">
-        <v>57669</v>
+        <v>98470</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15711,10 +15711,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>544469</v>
+        <v>544703</v>
       </c>
       <c r="R152" t="n">
-        <v>6963307</v>
+        <v>6963330</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15751,7 +15751,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Förbiflygande</t>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -15778,32 +15778,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128094044</v>
+        <v>128094038</v>
       </c>
       <c r="B153" t="n">
-        <v>98470</v>
+        <v>57669</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -15813,10 +15813,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>544703</v>
+        <v>544469</v>
       </c>
       <c r="R153" t="n">
-        <v>6963330</v>
+        <v>6963307</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15853,7 +15853,7 @@
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>100 ex</t>
+          <t>Förbiflygande</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16487,32 +16487,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128094047</v>
+        <v>128094052</v>
       </c>
       <c r="B160" t="n">
-        <v>98470</v>
+        <v>56855</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16522,10 +16522,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>544641</v>
+        <v>544577</v>
       </c>
       <c r="R160" t="n">
-        <v>6963158</v>
+        <v>6963169</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16562,7 +16562,7 @@
       </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>11 ex</t>
+          <t>Individ noterad genom sång</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -16589,7 +16589,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128094051</v>
+        <v>128094047</v>
       </c>
       <c r="B161" t="n">
         <v>98470</v>
@@ -16624,10 +16624,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>544310</v>
+        <v>544641</v>
       </c>
       <c r="R161" t="n">
-        <v>6963314</v>
+        <v>6963158</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16664,7 +16664,7 @@
       </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>80 ex</t>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -16691,7 +16691,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128094045</v>
+        <v>128094051</v>
       </c>
       <c r="B162" t="n">
         <v>98470</v>
@@ -16726,10 +16726,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>544760</v>
+        <v>544310</v>
       </c>
       <c r="R162" t="n">
-        <v>6963251</v>
+        <v>6963314</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16766,7 +16766,7 @@
       </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>35 ex</t>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -16793,32 +16793,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128094052</v>
+        <v>128094045</v>
       </c>
       <c r="B163" t="n">
-        <v>56855</v>
+        <v>98470</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -16828,10 +16828,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>544577</v>
+        <v>544760</v>
       </c>
       <c r="R163" t="n">
-        <v>6963169</v>
+        <v>6963251</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -16868,7 +16868,7 @@
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>Individ noterad genom sång</t>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD163" t="b">

--- a/artfynd/A 32240-2025 artfynd.xlsx
+++ b/artfynd/A 32240-2025 artfynd.xlsx
@@ -2184,32 +2184,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128087520</v>
+        <v>128087550</v>
       </c>
       <c r="B17" t="n">
-        <v>57832</v>
+        <v>98470</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544771</v>
+        <v>544490</v>
       </c>
       <c r="R17" t="n">
-        <v>6963083</v>
+        <v>6963099</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2 stycken.  Övriga läten</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2286,32 +2286,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128087550</v>
+        <v>128087520</v>
       </c>
       <c r="B18" t="n">
-        <v>98470</v>
+        <v>57832</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544490</v>
+        <v>544771</v>
       </c>
       <c r="R18" t="n">
-        <v>6963099</v>
+        <v>6963083</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2 stycken.  Övriga läten</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -5468,32 +5468,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128087342</v>
+        <v>128087339</v>
       </c>
       <c r="B50" t="n">
-        <v>80161</v>
+        <v>57832</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5503,10 +5503,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>544848</v>
+        <v>544850</v>
       </c>
       <c r="R50" t="n">
-        <v>6963086</v>
+        <v>6963099</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5539,6 +5539,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5565,32 +5570,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128087367</v>
+        <v>128087342</v>
       </c>
       <c r="B51" t="n">
-        <v>80132</v>
+        <v>80161</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5600,10 +5605,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>544298</v>
+        <v>544848</v>
       </c>
       <c r="R51" t="n">
-        <v>6963312</v>
+        <v>6963086</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5662,7 +5667,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128087364</v>
+        <v>128087367</v>
       </c>
       <c r="B52" t="n">
         <v>80132</v>
@@ -5697,10 +5702,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>544774</v>
+        <v>544298</v>
       </c>
       <c r="R52" t="n">
-        <v>6963282</v>
+        <v>6963312</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5759,10 +5764,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128087339</v>
+        <v>128087364</v>
       </c>
       <c r="B53" t="n">
-        <v>57832</v>
+        <v>80132</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5770,21 +5775,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5794,10 +5799,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>544850</v>
+        <v>544774</v>
       </c>
       <c r="R53" t="n">
-        <v>6963099</v>
+        <v>6963282</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5830,11 +5835,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6162,10 +6162,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128087356</v>
+        <v>128087585</v>
       </c>
       <c r="B57" t="n">
-        <v>80160</v>
+        <v>92642</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6173,21 +6173,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6461</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6197,10 +6197,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>544772</v>
+        <v>544536</v>
       </c>
       <c r="R57" t="n">
-        <v>6963323</v>
+        <v>6963255</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6233,6 +6233,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>8 äldre ex9 färska fruktkroppar</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6259,45 +6264,50 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128087357</v>
+        <v>128080012</v>
       </c>
       <c r="B58" t="n">
-        <v>80160</v>
+        <v>57672</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>544466</v>
+        <v>544324</v>
       </c>
       <c r="R58" t="n">
-        <v>6963277</v>
+        <v>6963220</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6330,6 +6340,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6356,10 +6371,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128087585</v>
+        <v>128087356</v>
       </c>
       <c r="B59" t="n">
-        <v>92642</v>
+        <v>80160</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6367,21 +6382,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>6461</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6391,10 +6406,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>544536</v>
+        <v>544772</v>
       </c>
       <c r="R59" t="n">
-        <v>6963255</v>
+        <v>6963323</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6427,11 +6442,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>8 äldre ex9 färska fruktkroppar</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6458,50 +6468,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128080012</v>
+        <v>128087357</v>
       </c>
       <c r="B60" t="n">
-        <v>57672</v>
+        <v>80160</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>544324</v>
+        <v>544466</v>
       </c>
       <c r="R60" t="n">
-        <v>6963220</v>
+        <v>6963277</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6534,11 +6539,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8182,49 +8182,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128079875</v>
+        <v>128087330</v>
       </c>
       <c r="B77" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>544308</v>
+        <v>544750</v>
       </c>
       <c r="R77" t="n">
-        <v>6963175</v>
+        <v>6963177</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8257,6 +8253,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8283,32 +8284,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128087542</v>
+        <v>128087335</v>
       </c>
       <c r="B78" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8318,10 +8319,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>544752</v>
+        <v>544366</v>
       </c>
       <c r="R78" t="n">
-        <v>6963192</v>
+        <v>6963181</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8358,7 +8359,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>40 stycken</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8385,49 +8386,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128080338</v>
+        <v>128087575</v>
       </c>
       <c r="B79" t="n">
-        <v>98470</v>
+        <v>92674</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>1968</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>544314</v>
+        <v>544532</v>
       </c>
       <c r="R79" t="n">
-        <v>6963248</v>
+        <v>6963250</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8460,6 +8457,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Igen stor köttig svamp misstänker grantaggsvamp 2 ex</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8486,32 +8488,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128087547</v>
+        <v>128078492</v>
       </c>
       <c r="B80" t="n">
-        <v>98470</v>
+        <v>92674</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>1968</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8521,10 +8523,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>544380</v>
+        <v>544362</v>
       </c>
       <c r="R80" t="n">
-        <v>6963236</v>
+        <v>6963073</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8557,11 +8559,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>33 stycken</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8588,32 +8585,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128087380</v>
+        <v>128087536</v>
       </c>
       <c r="B81" t="n">
-        <v>105508</v>
+        <v>80132</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221144</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8623,10 +8620,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>544468</v>
+        <v>544215</v>
       </c>
       <c r="R81" t="n">
-        <v>6963173</v>
+        <v>6963245</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8685,32 +8682,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128087560</v>
+        <v>128087343</v>
       </c>
       <c r="B82" t="n">
-        <v>98470</v>
+        <v>80161</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8720,10 +8717,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>544383</v>
+        <v>544757</v>
       </c>
       <c r="R82" t="n">
-        <v>6963236</v>
+        <v>6963156</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8756,11 +8753,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8787,32 +8779,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128087570</v>
+        <v>128087346</v>
       </c>
       <c r="B83" t="n">
-        <v>56855</v>
+        <v>80161</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>102612</v>
+        <v>6462</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8822,10 +8814,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>544287</v>
+        <v>544422</v>
       </c>
       <c r="R83" t="n">
-        <v>6963082</v>
+        <v>6963240</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8858,11 +8850,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8889,10 +8876,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128087575</v>
+        <v>128087570</v>
       </c>
       <c r="B84" t="n">
-        <v>92674</v>
+        <v>56855</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8900,21 +8887,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1968</v>
+        <v>102612</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8924,10 +8911,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>544532</v>
+        <v>544287</v>
       </c>
       <c r="R84" t="n">
-        <v>6963250</v>
+        <v>6963082</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8964,7 +8951,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Igen stor köttig svamp misstänker grantaggsvamp 2 ex</t>
+          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8991,45 +8978,49 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128078492</v>
+        <v>128079875</v>
       </c>
       <c r="B85" t="n">
-        <v>92674</v>
+        <v>98470</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1968</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>544362</v>
+        <v>544308</v>
       </c>
       <c r="R85" t="n">
-        <v>6963073</v>
+        <v>6963175</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9088,32 +9079,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128087536</v>
+        <v>128087542</v>
       </c>
       <c r="B86" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9123,10 +9114,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>544215</v>
+        <v>544752</v>
       </c>
       <c r="R86" t="n">
-        <v>6963245</v>
+        <v>6963192</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9159,6 +9150,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9185,45 +9181,49 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128087343</v>
+        <v>128080338</v>
       </c>
       <c r="B87" t="n">
-        <v>80161</v>
+        <v>98470</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>544757</v>
+        <v>544314</v>
       </c>
       <c r="R87" t="n">
-        <v>6963156</v>
+        <v>6963248</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9282,32 +9282,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128087346</v>
+        <v>128087547</v>
       </c>
       <c r="B88" t="n">
-        <v>80161</v>
+        <v>98470</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9317,10 +9317,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>544422</v>
+        <v>544380</v>
       </c>
       <c r="R88" t="n">
-        <v>6963240</v>
+        <v>6963236</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9353,6 +9353,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>33 stycken</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9379,32 +9384,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128087330</v>
+        <v>128087380</v>
       </c>
       <c r="B89" t="n">
-        <v>57672</v>
+        <v>105508</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9414,10 +9419,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>544750</v>
+        <v>544468</v>
       </c>
       <c r="R89" t="n">
-        <v>6963177</v>
+        <v>6963173</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9450,11 +9455,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9481,32 +9481,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128087335</v>
+        <v>128087560</v>
       </c>
       <c r="B90" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9516,10 +9516,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>544366</v>
+        <v>544383</v>
       </c>
       <c r="R90" t="n">
-        <v>6963181</v>
+        <v>6963236</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9556,7 +9556,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10083,10 +10083,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128087355</v>
+        <v>128087383</v>
       </c>
       <c r="B96" t="n">
-        <v>97353</v>
+        <v>80167</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10094,21 +10094,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>221941</v>
+        <v>6463</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10118,10 +10118,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>544500</v>
+        <v>544566</v>
       </c>
       <c r="R96" t="n">
-        <v>6963168</v>
+        <v>6963076</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10180,32 +10180,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128087522</v>
+        <v>128087384</v>
       </c>
       <c r="B97" t="n">
-        <v>57832</v>
+        <v>80167</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103021</v>
+        <v>6463</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10215,10 +10215,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>544494</v>
+        <v>544584</v>
       </c>
       <c r="R97" t="n">
-        <v>6963243</v>
+        <v>6963261</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10277,32 +10277,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128087545</v>
+        <v>128087363</v>
       </c>
       <c r="B98" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10312,10 +10312,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>544633</v>
+        <v>544818</v>
       </c>
       <c r="R98" t="n">
-        <v>6963244</v>
+        <v>6963278</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10348,11 +10348,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10379,32 +10374,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128087567</v>
+        <v>128087576</v>
       </c>
       <c r="B99" t="n">
-        <v>98470</v>
+        <v>92674</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>1968</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10414,10 +10409,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>544274</v>
+        <v>544529</v>
       </c>
       <c r="R99" t="n">
-        <v>6963090</v>
+        <v>6963245</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10454,7 +10449,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>Misstänkt grantaggsvamp men med mörk tydlig ring i mitten.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10481,32 +10476,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128087556</v>
+        <v>128087572</v>
       </c>
       <c r="B100" t="n">
-        <v>98470</v>
+        <v>92674</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>1968</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10516,10 +10511,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>544594</v>
+        <v>544632</v>
       </c>
       <c r="R100" t="n">
-        <v>6963215</v>
+        <v>6963245</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10556,7 +10551,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>6 stycken. Kan finnas mer i omgivningen</t>
+          <t>1 ex</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10583,32 +10578,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128087373</v>
+        <v>128087522</v>
       </c>
       <c r="B101" t="n">
-        <v>98470</v>
+        <v>57832</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10618,10 +10613,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>544469</v>
+        <v>544494</v>
       </c>
       <c r="R101" t="n">
-        <v>6963122</v>
+        <v>6963243</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10654,11 +10649,6 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>60 ex</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10685,32 +10675,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128078864</v>
+        <v>128087545</v>
       </c>
       <c r="B102" t="n">
-        <v>105508</v>
+        <v>98470</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10720,10 +10710,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>544307</v>
+        <v>544633</v>
       </c>
       <c r="R102" t="n">
-        <v>6963089</v>
+        <v>6963244</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10756,6 +10746,11 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10782,7 +10777,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128087559</v>
+        <v>128087567</v>
       </c>
       <c r="B103" t="n">
         <v>98470</v>
@@ -10817,10 +10812,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>544396</v>
+        <v>544274</v>
       </c>
       <c r="R103" t="n">
-        <v>6963233</v>
+        <v>6963090</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10857,7 +10852,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>18 stycken</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10884,32 +10879,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128087576</v>
+        <v>128087556</v>
       </c>
       <c r="B104" t="n">
-        <v>92674</v>
+        <v>98470</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1968</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10919,10 +10914,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>544529</v>
+        <v>544594</v>
       </c>
       <c r="R104" t="n">
-        <v>6963245</v>
+        <v>6963215</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10959,7 +10954,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Misstänkt grantaggsvamp men med mörk tydlig ring i mitten.</t>
+          <t>6 stycken. Kan finnas mer i omgivningen</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10986,32 +10981,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128087572</v>
+        <v>128087373</v>
       </c>
       <c r="B105" t="n">
-        <v>92674</v>
+        <v>98470</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1968</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11021,10 +11016,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>544632</v>
+        <v>544469</v>
       </c>
       <c r="R105" t="n">
-        <v>6963245</v>
+        <v>6963122</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11061,7 +11056,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>1 ex</t>
+          <t>60 ex</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11088,10 +11083,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128087383</v>
+        <v>128078864</v>
       </c>
       <c r="B106" t="n">
-        <v>80167</v>
+        <v>105508</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11099,21 +11094,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6463</v>
+        <v>221144</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11123,10 +11118,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>544566</v>
+        <v>544307</v>
       </c>
       <c r="R106" t="n">
-        <v>6963076</v>
+        <v>6963089</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11185,32 +11180,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128087384</v>
+        <v>128087559</v>
       </c>
       <c r="B107" t="n">
-        <v>80167</v>
+        <v>98470</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11220,10 +11215,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>544584</v>
+        <v>544396</v>
       </c>
       <c r="R107" t="n">
-        <v>6963261</v>
+        <v>6963233</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11256,6 +11251,11 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11282,32 +11282,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128087363</v>
+        <v>128087355</v>
       </c>
       <c r="B108" t="n">
-        <v>80132</v>
+        <v>97353</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6458</v>
+        <v>221941</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11317,10 +11317,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>544818</v>
+        <v>544500</v>
       </c>
       <c r="R108" t="n">
-        <v>6963278</v>
+        <v>6963168</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12184,45 +12184,49 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128087571</v>
+        <v>128079571</v>
       </c>
       <c r="B117" t="n">
-        <v>92674</v>
+        <v>98470</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1968</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>544679</v>
+        <v>544274</v>
       </c>
       <c r="R117" t="n">
-        <v>6963259</v>
+        <v>6963119</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12255,11 +12259,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Misstänker grantaggsvamp. 14 exemplar</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12286,45 +12285,49 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128087573</v>
+        <v>128078138</v>
       </c>
       <c r="B118" t="n">
-        <v>92674</v>
+        <v>98470</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1968</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>544684</v>
+        <v>544374</v>
       </c>
       <c r="R118" t="n">
-        <v>6963253</v>
+        <v>6963056</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12357,11 +12360,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Mörkt exemplar med vit yttre ring.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12388,32 +12386,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128079848</v>
+        <v>128087571</v>
       </c>
       <c r="B119" t="n">
-        <v>79053</v>
+        <v>92674</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6434</v>
+        <v>1968</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12423,10 +12421,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>544288</v>
+        <v>544679</v>
       </c>
       <c r="R119" t="n">
-        <v>6963182</v>
+        <v>6963259</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12459,6 +12457,11 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Misstänker grantaggsvamp. 14 exemplar</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12485,10 +12488,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128087538</v>
+        <v>128087573</v>
       </c>
       <c r="B120" t="n">
-        <v>80132</v>
+        <v>92674</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12496,21 +12499,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6458</v>
+        <v>1968</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12520,10 +12523,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>544262</v>
+        <v>544684</v>
       </c>
       <c r="R120" t="n">
-        <v>6963163</v>
+        <v>6963253</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12556,6 +12559,11 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Mörkt exemplar med vit yttre ring.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12582,32 +12590,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128087535</v>
+        <v>128079848</v>
       </c>
       <c r="B121" t="n">
-        <v>80132</v>
+        <v>79053</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6458</v>
+        <v>6434</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12617,10 +12625,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>544312</v>
+        <v>544288</v>
       </c>
       <c r="R121" t="n">
-        <v>6963244</v>
+        <v>6963182</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12679,10 +12687,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128078823</v>
+        <v>128087538</v>
       </c>
       <c r="B122" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12690,21 +12698,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12714,10 +12722,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>544307</v>
+        <v>544262</v>
       </c>
       <c r="R122" t="n">
-        <v>6963089</v>
+        <v>6963163</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12776,49 +12784,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128079571</v>
+        <v>128087535</v>
       </c>
       <c r="B123" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>544274</v>
+        <v>544312</v>
       </c>
       <c r="R123" t="n">
-        <v>6963119</v>
+        <v>6963244</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12877,49 +12881,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128078138</v>
+        <v>128078823</v>
       </c>
       <c r="B124" t="n">
-        <v>98470</v>
+        <v>79029</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>544374</v>
+        <v>544307</v>
       </c>
       <c r="R124" t="n">
-        <v>6963056</v>
+        <v>6963089</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13784,32 +13784,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128078645</v>
+        <v>128087557</v>
       </c>
       <c r="B133" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13819,10 +13819,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>544360</v>
+        <v>544552</v>
       </c>
       <c r="R133" t="n">
-        <v>6963094</v>
+        <v>6963231</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13855,6 +13855,11 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -13881,32 +13886,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128087344</v>
+        <v>128087543</v>
       </c>
       <c r="B134" t="n">
-        <v>80161</v>
+        <v>98470</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13916,10 +13921,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>544581</v>
+        <v>544674</v>
       </c>
       <c r="R134" t="n">
-        <v>6963278</v>
+        <v>6963243</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13952,6 +13957,11 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -13978,32 +13988,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128087534</v>
+        <v>128087530</v>
       </c>
       <c r="B135" t="n">
-        <v>80132</v>
+        <v>98504</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6458</v>
+        <v>219874</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14013,10 +14023,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>544326</v>
+        <v>544737</v>
       </c>
       <c r="R135" t="n">
-        <v>6963248</v>
+        <v>6963047</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14075,10 +14085,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128087345</v>
+        <v>128087381</v>
       </c>
       <c r="B136" t="n">
-        <v>80161</v>
+        <v>98387</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14086,21 +14096,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6462</v>
+        <v>219790</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14110,10 +14120,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>544391</v>
+        <v>544531</v>
       </c>
       <c r="R136" t="n">
-        <v>6963205</v>
+        <v>6963190</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14172,7 +14182,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128087540</v>
+        <v>128078645</v>
       </c>
       <c r="B137" t="n">
         <v>80132</v>
@@ -14207,10 +14217,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>544282</v>
+        <v>544360</v>
       </c>
       <c r="R137" t="n">
-        <v>6963082</v>
+        <v>6963094</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14269,32 +14279,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128087328</v>
+        <v>128087344</v>
       </c>
       <c r="B138" t="n">
-        <v>57672</v>
+        <v>80161</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14304,10 +14314,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>544736</v>
+        <v>544581</v>
       </c>
       <c r="R138" t="n">
-        <v>6963153</v>
+        <v>6963278</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14340,11 +14350,6 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14371,32 +14376,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128087557</v>
+        <v>128087534</v>
       </c>
       <c r="B139" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14406,10 +14411,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>544552</v>
+        <v>544326</v>
       </c>
       <c r="R139" t="n">
-        <v>6963231</v>
+        <v>6963248</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14442,11 +14447,6 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14473,32 +14473,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128087543</v>
+        <v>128087345</v>
       </c>
       <c r="B140" t="n">
-        <v>98470</v>
+        <v>80161</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14508,10 +14508,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>544674</v>
+        <v>544391</v>
       </c>
       <c r="R140" t="n">
-        <v>6963243</v>
+        <v>6963205</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14544,11 +14544,6 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14575,32 +14570,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128087530</v>
+        <v>128087540</v>
       </c>
       <c r="B141" t="n">
-        <v>98504</v>
+        <v>80132</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>219874</v>
+        <v>6458</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14610,10 +14605,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>544737</v>
+        <v>544282</v>
       </c>
       <c r="R141" t="n">
-        <v>6963047</v>
+        <v>6963082</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14672,32 +14667,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128087381</v>
+        <v>128087328</v>
       </c>
       <c r="B142" t="n">
-        <v>98387</v>
+        <v>57672</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14707,10 +14702,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>544531</v>
+        <v>544736</v>
       </c>
       <c r="R142" t="n">
-        <v>6963190</v>
+        <v>6963153</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14743,6 +14738,11 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15069,32 +15069,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128094046</v>
+        <v>128094035</v>
       </c>
       <c r="B146" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15104,10 +15104,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>544754</v>
+        <v>544736</v>
       </c>
       <c r="R146" t="n">
-        <v>6963261</v>
+        <v>6963232</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15144,7 +15144,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>25 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15171,32 +15171,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128094035</v>
+        <v>128094046</v>
       </c>
       <c r="B147" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15206,10 +15206,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>544736</v>
+        <v>544754</v>
       </c>
       <c r="R147" t="n">
-        <v>6963232</v>
+        <v>6963261</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15246,7 +15246,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15472,32 +15472,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128094032</v>
+        <v>128094042</v>
       </c>
       <c r="B150" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15507,10 +15507,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>544279</v>
+        <v>544528</v>
       </c>
       <c r="R150" t="n">
-        <v>6963296</v>
+        <v>6963294</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15547,7 +15547,7 @@
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>75 ex</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15574,32 +15574,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128094042</v>
+        <v>128094032</v>
       </c>
       <c r="B151" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15609,10 +15609,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>544528</v>
+        <v>544279</v>
       </c>
       <c r="R151" t="n">
-        <v>6963294</v>
+        <v>6963296</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15649,7 +15649,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>75 ex</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD151" t="b">

--- a/artfynd/A 32240-2025 artfynd.xlsx
+++ b/artfynd/A 32240-2025 artfynd.xlsx
@@ -3077,32 +3077,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128087331</v>
+        <v>128087382</v>
       </c>
       <c r="B26" t="n">
-        <v>57672</v>
+        <v>92642</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3112,10 +3112,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>544763</v>
+        <v>544198</v>
       </c>
       <c r="R26" t="n">
-        <v>6963244</v>
+        <v>6963225</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3179,10 +3179,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128087333</v>
+        <v>128087532</v>
       </c>
       <c r="B27" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3190,21 +3190,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3214,10 +3214,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544355</v>
+        <v>544491</v>
       </c>
       <c r="R27" t="n">
-        <v>6963212</v>
+        <v>6963099</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3250,11 +3250,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3281,10 +3276,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128087532</v>
+        <v>128087331</v>
       </c>
       <c r="B28" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3292,21 +3287,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3316,10 +3311,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544491</v>
+        <v>544763</v>
       </c>
       <c r="R28" t="n">
-        <v>6963099</v>
+        <v>6963244</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3352,6 +3347,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3378,32 +3378,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128087562</v>
+        <v>128087333</v>
       </c>
       <c r="B29" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3413,10 +3413,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544367</v>
+        <v>544355</v>
       </c>
       <c r="R29" t="n">
-        <v>6963253</v>
+        <v>6963212</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>7. Kan möjlitvis finnas fler runt omkring.</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3480,7 +3480,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128078161</v>
+        <v>128087562</v>
       </c>
       <c r="B30" t="n">
         <v>98470</v>
@@ -3508,21 +3508,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>544362</v>
+        <v>544367</v>
       </c>
       <c r="R30" t="n">
-        <v>6963061</v>
+        <v>6963253</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3555,6 +3551,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>7. Kan möjlitvis finnas fler runt omkring.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3581,7 +3582,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128078740</v>
+        <v>128078161</v>
       </c>
       <c r="B31" t="n">
         <v>98470</v>
@@ -3611,7 +3612,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3620,10 +3621,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>544307</v>
+        <v>544362</v>
       </c>
       <c r="R31" t="n">
-        <v>6963089</v>
+        <v>6963061</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3682,7 +3683,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128087563</v>
+        <v>128078740</v>
       </c>
       <c r="B32" t="n">
         <v>98470</v>
@@ -3710,17 +3711,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544322</v>
+        <v>544307</v>
       </c>
       <c r="R32" t="n">
-        <v>6963250</v>
+        <v>6963089</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3753,11 +3758,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>12 stycken</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3784,32 +3784,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128087382</v>
+        <v>128087563</v>
       </c>
       <c r="B33" t="n">
-        <v>92642</v>
+        <v>98470</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>544198</v>
+        <v>544322</v>
       </c>
       <c r="R33" t="n">
-        <v>6963225</v>
+        <v>6963250</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3859,7 +3859,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>5 ex</t>
+          <t>12 stycken</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4876,10 +4876,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128087340</v>
+        <v>128087361</v>
       </c>
       <c r="B44" t="n">
-        <v>57832</v>
+        <v>80132</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4887,21 +4887,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4911,10 +4911,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>544485</v>
+        <v>544865</v>
       </c>
       <c r="R44" t="n">
-        <v>6963237</v>
+        <v>6963092</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4973,32 +4973,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128087552</v>
+        <v>128087360</v>
       </c>
       <c r="B45" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5008,10 +5008,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>544687</v>
+        <v>544615</v>
       </c>
       <c r="R45" t="n">
-        <v>6963255</v>
+        <v>6963093</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5044,11 +5044,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>70</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5075,32 +5070,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128087548</v>
+        <v>128079768</v>
       </c>
       <c r="B46" t="n">
-        <v>98470</v>
+        <v>97353</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5110,10 +5105,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>544213</v>
+        <v>544287</v>
       </c>
       <c r="R46" t="n">
-        <v>6963197</v>
+        <v>6963168</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5146,11 +5141,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>100stycken.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5177,32 +5167,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128079768</v>
+        <v>128087340</v>
       </c>
       <c r="B47" t="n">
-        <v>97353</v>
+        <v>57832</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5212,10 +5202,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>544287</v>
+        <v>544485</v>
       </c>
       <c r="R47" t="n">
-        <v>6963168</v>
+        <v>6963237</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5274,32 +5264,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128087361</v>
+        <v>128087552</v>
       </c>
       <c r="B48" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5309,10 +5299,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>544865</v>
+        <v>544687</v>
       </c>
       <c r="R48" t="n">
-        <v>6963092</v>
+        <v>6963255</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5345,6 +5335,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>70</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5371,32 +5366,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128087360</v>
+        <v>128087548</v>
       </c>
       <c r="B49" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5406,10 +5401,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>544615</v>
+        <v>544213</v>
       </c>
       <c r="R49" t="n">
-        <v>6963093</v>
+        <v>6963197</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5442,6 +5437,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>100stycken.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5468,32 +5468,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128087339</v>
+        <v>128087342</v>
       </c>
       <c r="B50" t="n">
-        <v>57832</v>
+        <v>80161</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5503,10 +5503,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>544850</v>
+        <v>544848</v>
       </c>
       <c r="R50" t="n">
-        <v>6963099</v>
+        <v>6963086</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5539,11 +5539,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5570,32 +5565,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128087342</v>
+        <v>128087367</v>
       </c>
       <c r="B51" t="n">
-        <v>80161</v>
+        <v>80132</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5605,10 +5600,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>544848</v>
+        <v>544298</v>
       </c>
       <c r="R51" t="n">
-        <v>6963086</v>
+        <v>6963312</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5667,7 +5662,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128087367</v>
+        <v>128087364</v>
       </c>
       <c r="B52" t="n">
         <v>80132</v>
@@ -5702,10 +5697,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>544298</v>
+        <v>544774</v>
       </c>
       <c r="R52" t="n">
-        <v>6963312</v>
+        <v>6963282</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5764,10 +5759,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128087364</v>
+        <v>128087339</v>
       </c>
       <c r="B53" t="n">
-        <v>80132</v>
+        <v>57832</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5775,21 +5770,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5799,10 +5794,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>544774</v>
+        <v>544850</v>
       </c>
       <c r="R53" t="n">
-        <v>6963282</v>
+        <v>6963099</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5835,6 +5830,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 32240-2025 artfynd.xlsx
+++ b/artfynd/A 32240-2025 artfynd.xlsx
@@ -1786,10 +1786,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128087323</v>
+        <v>128087520</v>
       </c>
       <c r="B13" t="n">
-        <v>57672</v>
+        <v>57832</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1797,21 +1797,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544646</v>
+        <v>544771</v>
       </c>
       <c r="R13" t="n">
-        <v>6963095</v>
+        <v>6963083</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>2 stycken.  Övriga läten</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1888,7 +1888,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128087324</v>
+        <v>128087323</v>
       </c>
       <c r="B14" t="n">
         <v>57672</v>
@@ -1923,10 +1923,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544792</v>
+        <v>544646</v>
       </c>
       <c r="R14" t="n">
-        <v>6963047</v>
+        <v>6963095</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1990,10 +1990,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128081639</v>
+        <v>128087324</v>
       </c>
       <c r="B15" t="n">
-        <v>80133</v>
+        <v>57672</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2001,21 +2001,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2025,10 +2025,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544323</v>
+        <v>544792</v>
       </c>
       <c r="R15" t="n">
-        <v>6963268</v>
+        <v>6963047</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2061,6 +2061,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2087,32 +2092,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128087347</v>
+        <v>128081639</v>
       </c>
       <c r="B16" t="n">
-        <v>80161</v>
+        <v>80133</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2122,10 +2127,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544745</v>
+        <v>544323</v>
       </c>
       <c r="R16" t="n">
-        <v>6963195</v>
+        <v>6963268</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2184,32 +2189,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128087550</v>
+        <v>128087347</v>
       </c>
       <c r="B17" t="n">
-        <v>98470</v>
+        <v>80161</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2219,10 +2224,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544490</v>
+        <v>544745</v>
       </c>
       <c r="R17" t="n">
-        <v>6963099</v>
+        <v>6963195</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2255,11 +2260,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2286,32 +2286,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128087520</v>
+        <v>128087550</v>
       </c>
       <c r="B18" t="n">
-        <v>57832</v>
+        <v>98470</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544771</v>
+        <v>544490</v>
       </c>
       <c r="R18" t="n">
-        <v>6963083</v>
+        <v>6963099</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2 stycken.  Övriga läten</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -5468,32 +5468,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128087342</v>
+        <v>128087339</v>
       </c>
       <c r="B50" t="n">
-        <v>80161</v>
+        <v>57832</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5503,10 +5503,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>544848</v>
+        <v>544850</v>
       </c>
       <c r="R50" t="n">
-        <v>6963086</v>
+        <v>6963099</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5539,6 +5539,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5565,32 +5570,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128087367</v>
+        <v>128087342</v>
       </c>
       <c r="B51" t="n">
-        <v>80132</v>
+        <v>80161</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5600,10 +5605,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>544298</v>
+        <v>544848</v>
       </c>
       <c r="R51" t="n">
-        <v>6963312</v>
+        <v>6963086</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5662,7 +5667,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128087364</v>
+        <v>128087367</v>
       </c>
       <c r="B52" t="n">
         <v>80132</v>
@@ -5697,10 +5702,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>544774</v>
+        <v>544298</v>
       </c>
       <c r="R52" t="n">
-        <v>6963282</v>
+        <v>6963312</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5759,10 +5764,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128087339</v>
+        <v>128087364</v>
       </c>
       <c r="B53" t="n">
-        <v>57832</v>
+        <v>80132</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5770,21 +5775,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5794,10 +5799,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>544850</v>
+        <v>544774</v>
       </c>
       <c r="R53" t="n">
-        <v>6963099</v>
+        <v>6963282</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5830,11 +5835,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6565,32 +6565,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128087566</v>
+        <v>128087386</v>
       </c>
       <c r="B61" t="n">
-        <v>98470</v>
+        <v>92636</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>4362</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6600,10 +6600,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>544261</v>
+        <v>544822</v>
       </c>
       <c r="R61" t="n">
-        <v>6963170</v>
+        <v>6963295</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6636,11 +6636,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>4. Stycken. Finns möjligtvis fler i blåbärsriset.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6667,32 +6662,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128087377</v>
+        <v>128078603</v>
       </c>
       <c r="B62" t="n">
-        <v>98470</v>
+        <v>80161</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6702,10 +6697,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>544403</v>
+        <v>544360</v>
       </c>
       <c r="R62" t="n">
-        <v>6963221</v>
+        <v>6963094</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6738,11 +6733,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>20 ex</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6769,32 +6759,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128087378</v>
+        <v>128087523</v>
       </c>
       <c r="B63" t="n">
-        <v>98470</v>
+        <v>80161</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6804,10 +6794,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>544218</v>
+        <v>544253</v>
       </c>
       <c r="R63" t="n">
-        <v>6963229</v>
+        <v>6963139</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6840,11 +6830,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>80 ex</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6871,32 +6856,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128087375</v>
+        <v>128087579</v>
       </c>
       <c r="B64" t="n">
-        <v>98470</v>
+        <v>79029</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6906,10 +6891,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>544478</v>
+        <v>544204</v>
       </c>
       <c r="R64" t="n">
-        <v>6963117</v>
+        <v>6963238</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6946,7 +6931,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>35 ex</t>
+          <t>Riklig förekomst av garnlav</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6973,10 +6958,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128087386</v>
+        <v>128087329</v>
       </c>
       <c r="B65" t="n">
-        <v>92636</v>
+        <v>57672</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6984,21 +6969,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4362</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7008,10 +6993,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>544822</v>
+        <v>544757</v>
       </c>
       <c r="R65" t="n">
-        <v>6963295</v>
+        <v>6963172</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7044,6 +7029,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7070,32 +7060,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128078603</v>
+        <v>128087566</v>
       </c>
       <c r="B66" t="n">
-        <v>80161</v>
+        <v>98470</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7105,10 +7095,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>544360</v>
+        <v>544261</v>
       </c>
       <c r="R66" t="n">
-        <v>6963094</v>
+        <v>6963170</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7141,6 +7131,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>4. Stycken. Finns möjligtvis fler i blåbärsriset.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7167,32 +7162,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128087523</v>
+        <v>128087377</v>
       </c>
       <c r="B67" t="n">
-        <v>80161</v>
+        <v>98470</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7202,10 +7197,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>544253</v>
+        <v>544403</v>
       </c>
       <c r="R67" t="n">
-        <v>6963139</v>
+        <v>6963221</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7238,6 +7233,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7264,32 +7264,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128087579</v>
+        <v>128087378</v>
       </c>
       <c r="B68" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7299,10 +7299,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>544204</v>
+        <v>544218</v>
       </c>
       <c r="R68" t="n">
-        <v>6963238</v>
+        <v>6963229</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7339,7 +7339,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Riklig förekomst av garnlav</t>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7366,32 +7366,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128087525</v>
+        <v>128087375</v>
       </c>
       <c r="B69" t="n">
-        <v>56248</v>
+        <v>98470</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>206004</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7401,10 +7401,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>544385</v>
+        <v>544478</v>
       </c>
       <c r="R69" t="n">
-        <v>6963074</v>
+        <v>6963117</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7437,6 +7437,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7463,10 +7468,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128087329</v>
+        <v>128087525</v>
       </c>
       <c r="B70" t="n">
-        <v>57672</v>
+        <v>56248</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7474,21 +7479,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7498,10 +7503,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>544757</v>
+        <v>544385</v>
       </c>
       <c r="R70" t="n">
-        <v>6963172</v>
+        <v>6963074</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7534,11 +7539,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -10083,10 +10083,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128087383</v>
+        <v>128087355</v>
       </c>
       <c r="B96" t="n">
-        <v>80167</v>
+        <v>97353</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10094,21 +10094,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6463</v>
+        <v>221941</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10118,10 +10118,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>544566</v>
+        <v>544500</v>
       </c>
       <c r="R96" t="n">
-        <v>6963076</v>
+        <v>6963168</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10180,32 +10180,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128087384</v>
+        <v>128087522</v>
       </c>
       <c r="B97" t="n">
-        <v>80167</v>
+        <v>57832</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6463</v>
+        <v>103021</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10215,10 +10215,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>544584</v>
+        <v>544494</v>
       </c>
       <c r="R97" t="n">
-        <v>6963261</v>
+        <v>6963243</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10277,32 +10277,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128087363</v>
+        <v>128087545</v>
       </c>
       <c r="B98" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10312,10 +10312,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>544818</v>
+        <v>544633</v>
       </c>
       <c r="R98" t="n">
-        <v>6963278</v>
+        <v>6963244</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10348,6 +10348,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10374,32 +10379,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128087576</v>
+        <v>128087567</v>
       </c>
       <c r="B99" t="n">
-        <v>92674</v>
+        <v>98470</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1968</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10409,10 +10414,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>544529</v>
+        <v>544274</v>
       </c>
       <c r="R99" t="n">
-        <v>6963245</v>
+        <v>6963090</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10449,7 +10454,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Misstänkt grantaggsvamp men med mörk tydlig ring i mitten.</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10476,32 +10481,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128087572</v>
+        <v>128087556</v>
       </c>
       <c r="B100" t="n">
-        <v>92674</v>
+        <v>98470</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1968</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10511,10 +10516,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>544632</v>
+        <v>544594</v>
       </c>
       <c r="R100" t="n">
-        <v>6963245</v>
+        <v>6963215</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10551,7 +10556,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>1 ex</t>
+          <t>6 stycken. Kan finnas mer i omgivningen</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10578,32 +10583,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128087522</v>
+        <v>128087373</v>
       </c>
       <c r="B101" t="n">
-        <v>57832</v>
+        <v>98470</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10613,10 +10618,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>544494</v>
+        <v>544469</v>
       </c>
       <c r="R101" t="n">
-        <v>6963243</v>
+        <v>6963122</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10649,6 +10654,11 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>60 ex</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10675,32 +10685,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128087545</v>
+        <v>128078864</v>
       </c>
       <c r="B102" t="n">
-        <v>98470</v>
+        <v>105508</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10710,10 +10720,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>544633</v>
+        <v>544307</v>
       </c>
       <c r="R102" t="n">
-        <v>6963244</v>
+        <v>6963089</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10746,11 +10756,6 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10777,7 +10782,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128087567</v>
+        <v>128087559</v>
       </c>
       <c r="B103" t="n">
         <v>98470</v>
@@ -10812,10 +10817,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>544274</v>
+        <v>544396</v>
       </c>
       <c r="R103" t="n">
-        <v>6963090</v>
+        <v>6963233</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10852,7 +10857,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10879,32 +10884,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128087556</v>
+        <v>128087576</v>
       </c>
       <c r="B104" t="n">
-        <v>98470</v>
+        <v>92674</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>1968</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10914,10 +10919,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>544594</v>
+        <v>544529</v>
       </c>
       <c r="R104" t="n">
-        <v>6963215</v>
+        <v>6963245</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10954,7 +10959,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>6 stycken. Kan finnas mer i omgivningen</t>
+          <t>Misstänkt grantaggsvamp men med mörk tydlig ring i mitten.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10981,32 +10986,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128087373</v>
+        <v>128087572</v>
       </c>
       <c r="B105" t="n">
-        <v>98470</v>
+        <v>92674</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>1968</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11016,10 +11021,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>544469</v>
+        <v>544632</v>
       </c>
       <c r="R105" t="n">
-        <v>6963122</v>
+        <v>6963245</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11056,7 +11061,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>60 ex</t>
+          <t>1 ex</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11083,10 +11088,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128078864</v>
+        <v>128087383</v>
       </c>
       <c r="B106" t="n">
-        <v>105508</v>
+        <v>80167</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11094,21 +11099,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>221144</v>
+        <v>6463</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11118,10 +11123,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>544307</v>
+        <v>544566</v>
       </c>
       <c r="R106" t="n">
-        <v>6963089</v>
+        <v>6963076</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11180,32 +11185,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128087559</v>
+        <v>128087384</v>
       </c>
       <c r="B107" t="n">
-        <v>98470</v>
+        <v>80167</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11215,10 +11220,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>544396</v>
+        <v>544584</v>
       </c>
       <c r="R107" t="n">
-        <v>6963233</v>
+        <v>6963261</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11251,11 +11256,6 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11282,32 +11282,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128087355</v>
+        <v>128087363</v>
       </c>
       <c r="B108" t="n">
-        <v>97353</v>
+        <v>80132</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>221941</v>
+        <v>6458</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11317,10 +11317,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>544500</v>
+        <v>544818</v>
       </c>
       <c r="R108" t="n">
-        <v>6963168</v>
+        <v>6963278</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -15069,32 +15069,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128094035</v>
+        <v>128094046</v>
       </c>
       <c r="B146" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15104,10 +15104,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>544736</v>
+        <v>544754</v>
       </c>
       <c r="R146" t="n">
-        <v>6963232</v>
+        <v>6963261</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15144,7 +15144,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15171,32 +15171,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128094046</v>
+        <v>128094035</v>
       </c>
       <c r="B147" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15206,10 +15206,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>544754</v>
+        <v>544736</v>
       </c>
       <c r="R147" t="n">
-        <v>6963261</v>
+        <v>6963232</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15246,7 +15246,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>25 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15472,32 +15472,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128094042</v>
+        <v>128094032</v>
       </c>
       <c r="B150" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15507,10 +15507,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>544528</v>
+        <v>544279</v>
       </c>
       <c r="R150" t="n">
-        <v>6963294</v>
+        <v>6963296</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15547,7 +15547,7 @@
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>75 ex</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15574,32 +15574,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128094032</v>
+        <v>128094042</v>
       </c>
       <c r="B151" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15609,10 +15609,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>544279</v>
+        <v>544528</v>
       </c>
       <c r="R151" t="n">
-        <v>6963296</v>
+        <v>6963294</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15649,7 +15649,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>75 ex</t>
         </is>
       </c>
       <c r="AD151" t="b">

--- a/artfynd/A 32240-2025 artfynd.xlsx
+++ b/artfynd/A 32240-2025 artfynd.xlsx
@@ -2388,10 +2388,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128087581</v>
+        <v>128087354</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>80133</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2399,21 +2399,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2423,10 +2423,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544192</v>
+        <v>544820</v>
       </c>
       <c r="R19" t="n">
-        <v>6963197</v>
+        <v>6963278</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2485,10 +2485,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128087362</v>
+        <v>128087581</v>
       </c>
       <c r="B20" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2496,21 +2496,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544799</v>
+        <v>544192</v>
       </c>
       <c r="R20" t="n">
-        <v>6963263</v>
+        <v>6963197</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2582,32 +2582,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128087349</v>
+        <v>128087362</v>
       </c>
       <c r="B21" t="n">
-        <v>80161</v>
+        <v>80132</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544475</v>
+        <v>544799</v>
       </c>
       <c r="R21" t="n">
-        <v>6963205</v>
+        <v>6963263</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2679,32 +2679,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128087354</v>
+        <v>128087349</v>
       </c>
       <c r="B22" t="n">
-        <v>80133</v>
+        <v>80161</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2714,10 +2714,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544820</v>
+        <v>544475</v>
       </c>
       <c r="R22" t="n">
-        <v>6963278</v>
+        <v>6963205</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2776,32 +2776,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128087569</v>
+        <v>128087359</v>
       </c>
       <c r="B23" t="n">
-        <v>98470</v>
+        <v>78788</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2811,10 +2811,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544296</v>
+        <v>544741</v>
       </c>
       <c r="R23" t="n">
-        <v>6963084</v>
+        <v>6963165</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2847,11 +2847,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>100stycken</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2878,7 +2873,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128087554</v>
+        <v>128087569</v>
       </c>
       <c r="B24" t="n">
         <v>98470</v>
@@ -2913,10 +2908,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544659</v>
+        <v>544296</v>
       </c>
       <c r="R24" t="n">
-        <v>6963253</v>
+        <v>6963084</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2953,7 +2948,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>50 stycken</t>
+          <t>100stycken</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2980,32 +2975,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128087359</v>
+        <v>128087554</v>
       </c>
       <c r="B25" t="n">
-        <v>78788</v>
+        <v>98470</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3015,10 +3010,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544741</v>
+        <v>544659</v>
       </c>
       <c r="R25" t="n">
-        <v>6963165</v>
+        <v>6963253</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3051,6 +3046,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3077,32 +3077,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128087382</v>
+        <v>128087331</v>
       </c>
       <c r="B26" t="n">
-        <v>92642</v>
+        <v>57672</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3112,10 +3112,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>544198</v>
+        <v>544763</v>
       </c>
       <c r="R26" t="n">
-        <v>6963225</v>
+        <v>6963244</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>5 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3179,10 +3179,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128087532</v>
+        <v>128087333</v>
       </c>
       <c r="B27" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3190,21 +3190,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3214,10 +3214,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544491</v>
+        <v>544355</v>
       </c>
       <c r="R27" t="n">
-        <v>6963099</v>
+        <v>6963212</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3250,6 +3250,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3276,10 +3281,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128087331</v>
+        <v>128087532</v>
       </c>
       <c r="B28" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3287,21 +3292,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3311,10 +3316,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544763</v>
+        <v>544491</v>
       </c>
       <c r="R28" t="n">
-        <v>6963244</v>
+        <v>6963099</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3347,11 +3352,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3378,32 +3378,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128087333</v>
+        <v>128087562</v>
       </c>
       <c r="B29" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3413,10 +3413,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544355</v>
+        <v>544367</v>
       </c>
       <c r="R29" t="n">
-        <v>6963212</v>
+        <v>6963253</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>7. Kan möjlitvis finnas fler runt omkring.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3480,7 +3480,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128087562</v>
+        <v>128078161</v>
       </c>
       <c r="B30" t="n">
         <v>98470</v>
@@ -3508,17 +3508,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>544367</v>
+        <v>544362</v>
       </c>
       <c r="R30" t="n">
-        <v>6963253</v>
+        <v>6963061</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3551,11 +3555,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>7. Kan möjlitvis finnas fler runt omkring.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3582,7 +3581,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128078161</v>
+        <v>128078740</v>
       </c>
       <c r="B31" t="n">
         <v>98470</v>
@@ -3612,7 +3611,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3621,10 +3620,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>544362</v>
+        <v>544307</v>
       </c>
       <c r="R31" t="n">
-        <v>6963061</v>
+        <v>6963089</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3683,7 +3682,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128078740</v>
+        <v>128087563</v>
       </c>
       <c r="B32" t="n">
         <v>98470</v>
@@ -3711,21 +3710,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544307</v>
+        <v>544322</v>
       </c>
       <c r="R32" t="n">
-        <v>6963089</v>
+        <v>6963250</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3758,6 +3753,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>12 stycken</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3784,32 +3784,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128087563</v>
+        <v>128087382</v>
       </c>
       <c r="B33" t="n">
-        <v>98470</v>
+        <v>92642</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>544322</v>
+        <v>544198</v>
       </c>
       <c r="R33" t="n">
-        <v>6963250</v>
+        <v>6963225</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3859,7 +3859,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>12 stycken</t>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -6565,32 +6565,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128087386</v>
+        <v>128087566</v>
       </c>
       <c r="B61" t="n">
-        <v>92636</v>
+        <v>98470</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4362</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6600,10 +6600,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>544822</v>
+        <v>544261</v>
       </c>
       <c r="R61" t="n">
-        <v>6963295</v>
+        <v>6963170</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6636,6 +6636,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>4. Stycken. Finns möjligtvis fler i blåbärsriset.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6662,32 +6667,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128078603</v>
+        <v>128087377</v>
       </c>
       <c r="B62" t="n">
-        <v>80161</v>
+        <v>98470</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6697,10 +6702,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>544360</v>
+        <v>544403</v>
       </c>
       <c r="R62" t="n">
-        <v>6963094</v>
+        <v>6963221</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6733,6 +6738,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6759,32 +6769,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128087523</v>
+        <v>128087378</v>
       </c>
       <c r="B63" t="n">
-        <v>80161</v>
+        <v>98470</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6794,10 +6804,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>544253</v>
+        <v>544218</v>
       </c>
       <c r="R63" t="n">
-        <v>6963139</v>
+        <v>6963229</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6830,6 +6840,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6856,32 +6871,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128087579</v>
+        <v>128087375</v>
       </c>
       <c r="B64" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6891,10 +6906,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>544204</v>
+        <v>544478</v>
       </c>
       <c r="R64" t="n">
-        <v>6963238</v>
+        <v>6963117</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6931,7 +6946,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Riklig förekomst av garnlav</t>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6958,10 +6973,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128087329</v>
+        <v>128087386</v>
       </c>
       <c r="B65" t="n">
-        <v>57672</v>
+        <v>92636</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6969,21 +6984,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>4362</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6993,10 +7008,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>544757</v>
+        <v>544822</v>
       </c>
       <c r="R65" t="n">
-        <v>6963172</v>
+        <v>6963295</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7029,11 +7044,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7060,32 +7070,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128087566</v>
+        <v>128078603</v>
       </c>
       <c r="B66" t="n">
-        <v>98470</v>
+        <v>80161</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7095,10 +7105,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>544261</v>
+        <v>544360</v>
       </c>
       <c r="R66" t="n">
-        <v>6963170</v>
+        <v>6963094</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7131,11 +7141,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>4. Stycken. Finns möjligtvis fler i blåbärsriset.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7162,32 +7167,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128087377</v>
+        <v>128087523</v>
       </c>
       <c r="B67" t="n">
-        <v>98470</v>
+        <v>80161</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7197,10 +7202,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>544403</v>
+        <v>544253</v>
       </c>
       <c r="R67" t="n">
-        <v>6963221</v>
+        <v>6963139</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7233,11 +7238,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>20 ex</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7264,32 +7264,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128087378</v>
+        <v>128087579</v>
       </c>
       <c r="B68" t="n">
-        <v>98470</v>
+        <v>79029</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7299,10 +7299,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>544218</v>
+        <v>544204</v>
       </c>
       <c r="R68" t="n">
-        <v>6963229</v>
+        <v>6963238</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7339,7 +7339,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>80 ex</t>
+          <t>Riklig förekomst av garnlav</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7366,32 +7366,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128087375</v>
+        <v>128087525</v>
       </c>
       <c r="B69" t="n">
-        <v>98470</v>
+        <v>56248</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>206004</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7401,10 +7401,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>544478</v>
+        <v>544385</v>
       </c>
       <c r="R69" t="n">
-        <v>6963117</v>
+        <v>6963074</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7437,11 +7437,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>35 ex</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7468,10 +7463,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128087525</v>
+        <v>128087329</v>
       </c>
       <c r="B70" t="n">
-        <v>56248</v>
+        <v>57672</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7479,21 +7474,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7503,10 +7498,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>544385</v>
+        <v>544757</v>
       </c>
       <c r="R70" t="n">
-        <v>6963074</v>
+        <v>6963172</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7539,6 +7534,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -10083,10 +10083,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128087355</v>
+        <v>128087383</v>
       </c>
       <c r="B96" t="n">
-        <v>97353</v>
+        <v>80167</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10094,21 +10094,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>221941</v>
+        <v>6463</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10118,10 +10118,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>544500</v>
+        <v>544566</v>
       </c>
       <c r="R96" t="n">
-        <v>6963168</v>
+        <v>6963076</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10180,32 +10180,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128087522</v>
+        <v>128087384</v>
       </c>
       <c r="B97" t="n">
-        <v>57832</v>
+        <v>80167</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103021</v>
+        <v>6463</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10215,10 +10215,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>544494</v>
+        <v>544584</v>
       </c>
       <c r="R97" t="n">
-        <v>6963243</v>
+        <v>6963261</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10277,32 +10277,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128087545</v>
+        <v>128087363</v>
       </c>
       <c r="B98" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10312,10 +10312,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>544633</v>
+        <v>544818</v>
       </c>
       <c r="R98" t="n">
-        <v>6963244</v>
+        <v>6963278</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10348,11 +10348,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10379,32 +10374,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128087567</v>
+        <v>128087576</v>
       </c>
       <c r="B99" t="n">
-        <v>98470</v>
+        <v>92674</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>1968</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10414,10 +10409,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>544274</v>
+        <v>544529</v>
       </c>
       <c r="R99" t="n">
-        <v>6963090</v>
+        <v>6963245</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10454,7 +10449,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>Misstänkt grantaggsvamp men med mörk tydlig ring i mitten.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10481,32 +10476,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128087556</v>
+        <v>128087572</v>
       </c>
       <c r="B100" t="n">
-        <v>98470</v>
+        <v>92674</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>1968</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10516,10 +10511,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>544594</v>
+        <v>544632</v>
       </c>
       <c r="R100" t="n">
-        <v>6963215</v>
+        <v>6963245</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10556,7 +10551,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>6 stycken. Kan finnas mer i omgivningen</t>
+          <t>1 ex</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10583,32 +10578,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128087373</v>
+        <v>128087522</v>
       </c>
       <c r="B101" t="n">
-        <v>98470</v>
+        <v>57832</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10618,10 +10613,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>544469</v>
+        <v>544494</v>
       </c>
       <c r="R101" t="n">
-        <v>6963122</v>
+        <v>6963243</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10654,11 +10649,6 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>60 ex</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10685,32 +10675,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128078864</v>
+        <v>128087545</v>
       </c>
       <c r="B102" t="n">
-        <v>105508</v>
+        <v>98470</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10720,10 +10710,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>544307</v>
+        <v>544633</v>
       </c>
       <c r="R102" t="n">
-        <v>6963089</v>
+        <v>6963244</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10756,6 +10746,11 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10782,7 +10777,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128087559</v>
+        <v>128087567</v>
       </c>
       <c r="B103" t="n">
         <v>98470</v>
@@ -10817,10 +10812,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>544396</v>
+        <v>544274</v>
       </c>
       <c r="R103" t="n">
-        <v>6963233</v>
+        <v>6963090</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10857,7 +10852,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>18 stycken</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10884,32 +10879,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128087576</v>
+        <v>128087556</v>
       </c>
       <c r="B104" t="n">
-        <v>92674</v>
+        <v>98470</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1968</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10919,10 +10914,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>544529</v>
+        <v>544594</v>
       </c>
       <c r="R104" t="n">
-        <v>6963245</v>
+        <v>6963215</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10959,7 +10954,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Misstänkt grantaggsvamp men med mörk tydlig ring i mitten.</t>
+          <t>6 stycken. Kan finnas mer i omgivningen</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10986,32 +10981,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128087572</v>
+        <v>128087373</v>
       </c>
       <c r="B105" t="n">
-        <v>92674</v>
+        <v>98470</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1968</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11021,10 +11016,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>544632</v>
+        <v>544469</v>
       </c>
       <c r="R105" t="n">
-        <v>6963245</v>
+        <v>6963122</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11061,7 +11056,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>1 ex</t>
+          <t>60 ex</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11088,10 +11083,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128087383</v>
+        <v>128078864</v>
       </c>
       <c r="B106" t="n">
-        <v>80167</v>
+        <v>105508</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11099,21 +11094,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6463</v>
+        <v>221144</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11123,10 +11118,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>544566</v>
+        <v>544307</v>
       </c>
       <c r="R106" t="n">
-        <v>6963076</v>
+        <v>6963089</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11185,32 +11180,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128087384</v>
+        <v>128087559</v>
       </c>
       <c r="B107" t="n">
-        <v>80167</v>
+        <v>98470</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11220,10 +11215,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>544584</v>
+        <v>544396</v>
       </c>
       <c r="R107" t="n">
-        <v>6963261</v>
+        <v>6963233</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11256,6 +11251,11 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11282,32 +11282,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128087363</v>
+        <v>128087355</v>
       </c>
       <c r="B108" t="n">
-        <v>80132</v>
+        <v>97353</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6458</v>
+        <v>221941</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11317,10 +11317,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>544818</v>
+        <v>544500</v>
       </c>
       <c r="R108" t="n">
-        <v>6963278</v>
+        <v>6963168</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11379,45 +11379,49 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128087577</v>
+        <v>128079656</v>
       </c>
       <c r="B109" t="n">
-        <v>92674</v>
+        <v>98470</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1968</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>544494</v>
+        <v>544277</v>
       </c>
       <c r="R109" t="n">
-        <v>6963243</v>
+        <v>6963150</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11476,32 +11480,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128087586</v>
+        <v>128087565</v>
       </c>
       <c r="B110" t="n">
-        <v>92642</v>
+        <v>98470</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11511,10 +11515,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>544281</v>
+        <v>544249</v>
       </c>
       <c r="R110" t="n">
-        <v>6963257</v>
+        <v>6963223</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11551,7 +11555,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>2 nya exemplar 8 äldre ex</t>
+          <t>10. Kan möjlitvis finns mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11578,32 +11582,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128087578</v>
+        <v>128087372</v>
       </c>
       <c r="B111" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11613,10 +11617,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>544246</v>
+        <v>544472</v>
       </c>
       <c r="R111" t="n">
-        <v>6963257</v>
+        <v>6963201</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11649,6 +11653,11 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11675,32 +11684,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128087531</v>
+        <v>128087551</v>
       </c>
       <c r="B112" t="n">
-        <v>98504</v>
+        <v>98470</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11710,10 +11719,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>544755</v>
+        <v>544694</v>
       </c>
       <c r="R112" t="n">
-        <v>6963130</v>
+        <v>6963258</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11750,7 +11759,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>2 stycken</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11777,49 +11786,45 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128079656</v>
+        <v>128087531</v>
       </c>
       <c r="B113" t="n">
-        <v>98470</v>
+        <v>98504</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>544277</v>
+        <v>544755</v>
       </c>
       <c r="R113" t="n">
-        <v>6963150</v>
+        <v>6963130</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11852,6 +11857,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11878,32 +11888,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128087565</v>
+        <v>128087577</v>
       </c>
       <c r="B114" t="n">
-        <v>98470</v>
+        <v>92674</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220787</v>
+        <v>1968</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11913,10 +11923,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>544249</v>
+        <v>544494</v>
       </c>
       <c r="R114" t="n">
-        <v>6963223</v>
+        <v>6963243</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11949,11 +11959,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>10. Kan möjlitvis finns mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11980,32 +11985,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128087372</v>
+        <v>128087586</v>
       </c>
       <c r="B115" t="n">
-        <v>98470</v>
+        <v>92642</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12015,10 +12020,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>544472</v>
+        <v>544281</v>
       </c>
       <c r="R115" t="n">
-        <v>6963201</v>
+        <v>6963257</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12055,7 +12060,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>8 ex</t>
+          <t>2 nya exemplar 8 äldre ex</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12082,32 +12087,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128087551</v>
+        <v>128087578</v>
       </c>
       <c r="B116" t="n">
-        <v>98470</v>
+        <v>79029</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12117,10 +12122,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>544694</v>
+        <v>544246</v>
       </c>
       <c r="R116" t="n">
-        <v>6963258</v>
+        <v>6963257</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12153,11 +12158,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -15472,32 +15472,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128094032</v>
+        <v>128094042</v>
       </c>
       <c r="B150" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15507,10 +15507,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>544279</v>
+        <v>544528</v>
       </c>
       <c r="R150" t="n">
-        <v>6963296</v>
+        <v>6963294</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15547,7 +15547,7 @@
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>75 ex</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15574,32 +15574,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128094042</v>
+        <v>128094032</v>
       </c>
       <c r="B151" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15609,10 +15609,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>544528</v>
+        <v>544279</v>
       </c>
       <c r="R151" t="n">
-        <v>6963294</v>
+        <v>6963296</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15649,7 +15649,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>75 ex</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD151" t="b">

--- a/artfynd/A 32240-2025 artfynd.xlsx
+++ b/artfynd/A 32240-2025 artfynd.xlsx
@@ -1786,10 +1786,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128087520</v>
+        <v>128087323</v>
       </c>
       <c r="B13" t="n">
-        <v>57832</v>
+        <v>57672</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1797,21 +1797,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544771</v>
+        <v>544646</v>
       </c>
       <c r="R13" t="n">
-        <v>6963083</v>
+        <v>6963095</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2 stycken.  Övriga läten</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1888,7 +1888,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128087323</v>
+        <v>128087324</v>
       </c>
       <c r="B14" t="n">
         <v>57672</v>
@@ -1923,10 +1923,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544646</v>
+        <v>544792</v>
       </c>
       <c r="R14" t="n">
-        <v>6963095</v>
+        <v>6963047</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1990,10 +1990,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128087324</v>
+        <v>128081639</v>
       </c>
       <c r="B15" t="n">
-        <v>57672</v>
+        <v>80133</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2001,21 +2001,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2025,10 +2025,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544792</v>
+        <v>544323</v>
       </c>
       <c r="R15" t="n">
-        <v>6963047</v>
+        <v>6963268</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2061,11 +2061,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2092,32 +2087,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128081639</v>
+        <v>128087347</v>
       </c>
       <c r="B16" t="n">
-        <v>80133</v>
+        <v>80161</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2127,10 +2122,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544323</v>
+        <v>544745</v>
       </c>
       <c r="R16" t="n">
-        <v>6963268</v>
+        <v>6963195</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2189,32 +2184,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128087347</v>
+        <v>128087520</v>
       </c>
       <c r="B17" t="n">
-        <v>80161</v>
+        <v>57832</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2224,10 +2219,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544745</v>
+        <v>544771</v>
       </c>
       <c r="R17" t="n">
-        <v>6963195</v>
+        <v>6963083</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2260,6 +2255,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2 stycken.  Övriga läten</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2388,10 +2388,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128087354</v>
+        <v>128087581</v>
       </c>
       <c r="B19" t="n">
-        <v>80133</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2399,21 +2399,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2423,10 +2423,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544820</v>
+        <v>544192</v>
       </c>
       <c r="R19" t="n">
-        <v>6963278</v>
+        <v>6963197</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2485,10 +2485,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128087581</v>
+        <v>128087362</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2496,21 +2496,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544192</v>
+        <v>544799</v>
       </c>
       <c r="R20" t="n">
-        <v>6963197</v>
+        <v>6963263</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2582,32 +2582,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128087362</v>
+        <v>128087349</v>
       </c>
       <c r="B21" t="n">
-        <v>80132</v>
+        <v>80161</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544799</v>
+        <v>544475</v>
       </c>
       <c r="R21" t="n">
-        <v>6963263</v>
+        <v>6963205</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2679,32 +2679,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128087349</v>
+        <v>128087354</v>
       </c>
       <c r="B22" t="n">
-        <v>80161</v>
+        <v>80133</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2714,10 +2714,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544475</v>
+        <v>544820</v>
       </c>
       <c r="R22" t="n">
-        <v>6963205</v>
+        <v>6963278</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2776,32 +2776,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128087359</v>
+        <v>128087569</v>
       </c>
       <c r="B23" t="n">
-        <v>78788</v>
+        <v>98470</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2811,10 +2811,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544741</v>
+        <v>544296</v>
       </c>
       <c r="R23" t="n">
-        <v>6963165</v>
+        <v>6963084</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2847,6 +2847,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>100stycken</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2873,7 +2878,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128087569</v>
+        <v>128087554</v>
       </c>
       <c r="B24" t="n">
         <v>98470</v>
@@ -2908,10 +2913,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544296</v>
+        <v>544659</v>
       </c>
       <c r="R24" t="n">
-        <v>6963084</v>
+        <v>6963253</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2948,7 +2953,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>100stycken</t>
+          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2975,32 +2980,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128087554</v>
+        <v>128087359</v>
       </c>
       <c r="B25" t="n">
-        <v>98470</v>
+        <v>78788</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3010,10 +3015,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544659</v>
+        <v>544741</v>
       </c>
       <c r="R25" t="n">
-        <v>6963253</v>
+        <v>6963165</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3046,11 +3051,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3077,32 +3077,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128087331</v>
+        <v>128087382</v>
       </c>
       <c r="B26" t="n">
-        <v>57672</v>
+        <v>92642</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3112,10 +3112,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>544763</v>
+        <v>544198</v>
       </c>
       <c r="R26" t="n">
-        <v>6963244</v>
+        <v>6963225</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3179,10 +3179,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128087333</v>
+        <v>128087532</v>
       </c>
       <c r="B27" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3190,21 +3190,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3214,10 +3214,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544355</v>
+        <v>544491</v>
       </c>
       <c r="R27" t="n">
-        <v>6963212</v>
+        <v>6963099</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3250,11 +3250,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3281,10 +3276,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128087532</v>
+        <v>128087331</v>
       </c>
       <c r="B28" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3292,21 +3287,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3316,10 +3311,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544491</v>
+        <v>544763</v>
       </c>
       <c r="R28" t="n">
-        <v>6963099</v>
+        <v>6963244</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3352,6 +3347,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3378,32 +3378,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128087562</v>
+        <v>128087333</v>
       </c>
       <c r="B29" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3413,10 +3413,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544367</v>
+        <v>544355</v>
       </c>
       <c r="R29" t="n">
-        <v>6963253</v>
+        <v>6963212</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>7. Kan möjlitvis finnas fler runt omkring.</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3480,7 +3480,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128078161</v>
+        <v>128087562</v>
       </c>
       <c r="B30" t="n">
         <v>98470</v>
@@ -3508,21 +3508,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>544362</v>
+        <v>544367</v>
       </c>
       <c r="R30" t="n">
-        <v>6963061</v>
+        <v>6963253</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3555,6 +3551,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>7. Kan möjlitvis finnas fler runt omkring.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3581,7 +3582,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128078740</v>
+        <v>128078161</v>
       </c>
       <c r="B31" t="n">
         <v>98470</v>
@@ -3611,7 +3612,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3620,10 +3621,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>544307</v>
+        <v>544362</v>
       </c>
       <c r="R31" t="n">
-        <v>6963089</v>
+        <v>6963061</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3682,7 +3683,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128087563</v>
+        <v>128078740</v>
       </c>
       <c r="B32" t="n">
         <v>98470</v>
@@ -3710,17 +3711,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544322</v>
+        <v>544307</v>
       </c>
       <c r="R32" t="n">
-        <v>6963250</v>
+        <v>6963089</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3753,11 +3758,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>12 stycken</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3784,32 +3784,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128087382</v>
+        <v>128087563</v>
       </c>
       <c r="B33" t="n">
-        <v>92642</v>
+        <v>98470</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>544198</v>
+        <v>544322</v>
       </c>
       <c r="R33" t="n">
-        <v>6963225</v>
+        <v>6963250</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3859,7 +3859,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>5 ex</t>
+          <t>12 stycken</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -6565,32 +6565,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128087566</v>
+        <v>128087386</v>
       </c>
       <c r="B61" t="n">
-        <v>98470</v>
+        <v>92636</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>4362</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6600,10 +6600,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>544261</v>
+        <v>544822</v>
       </c>
       <c r="R61" t="n">
-        <v>6963170</v>
+        <v>6963295</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6636,11 +6636,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>4. Stycken. Finns möjligtvis fler i blåbärsriset.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6667,32 +6662,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128087377</v>
+        <v>128078603</v>
       </c>
       <c r="B62" t="n">
-        <v>98470</v>
+        <v>80161</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6702,10 +6697,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>544403</v>
+        <v>544360</v>
       </c>
       <c r="R62" t="n">
-        <v>6963221</v>
+        <v>6963094</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6738,11 +6733,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>20 ex</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6769,32 +6759,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128087378</v>
+        <v>128087523</v>
       </c>
       <c r="B63" t="n">
-        <v>98470</v>
+        <v>80161</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6804,10 +6794,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>544218</v>
+        <v>544253</v>
       </c>
       <c r="R63" t="n">
-        <v>6963229</v>
+        <v>6963139</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6840,11 +6830,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>80 ex</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6871,32 +6856,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128087375</v>
+        <v>128087579</v>
       </c>
       <c r="B64" t="n">
-        <v>98470</v>
+        <v>79029</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6906,10 +6891,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>544478</v>
+        <v>544204</v>
       </c>
       <c r="R64" t="n">
-        <v>6963117</v>
+        <v>6963238</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6946,7 +6931,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>35 ex</t>
+          <t>Riklig förekomst av garnlav</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6973,10 +6958,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128087386</v>
+        <v>128087329</v>
       </c>
       <c r="B65" t="n">
-        <v>92636</v>
+        <v>57672</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6984,21 +6969,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4362</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7008,10 +6993,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>544822</v>
+        <v>544757</v>
       </c>
       <c r="R65" t="n">
-        <v>6963295</v>
+        <v>6963172</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7044,6 +7029,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7070,32 +7060,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128078603</v>
+        <v>128087566</v>
       </c>
       <c r="B66" t="n">
-        <v>80161</v>
+        <v>98470</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7105,10 +7095,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>544360</v>
+        <v>544261</v>
       </c>
       <c r="R66" t="n">
-        <v>6963094</v>
+        <v>6963170</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7141,6 +7131,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>4. Stycken. Finns möjligtvis fler i blåbärsriset.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7167,32 +7162,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128087523</v>
+        <v>128087377</v>
       </c>
       <c r="B67" t="n">
-        <v>80161</v>
+        <v>98470</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7202,10 +7197,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>544253</v>
+        <v>544403</v>
       </c>
       <c r="R67" t="n">
-        <v>6963139</v>
+        <v>6963221</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7238,6 +7233,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7264,32 +7264,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128087579</v>
+        <v>128087378</v>
       </c>
       <c r="B68" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7299,10 +7299,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>544204</v>
+        <v>544218</v>
       </c>
       <c r="R68" t="n">
-        <v>6963238</v>
+        <v>6963229</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7339,7 +7339,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Riklig förekomst av garnlav</t>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7366,32 +7366,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128087525</v>
+        <v>128087375</v>
       </c>
       <c r="B69" t="n">
-        <v>56248</v>
+        <v>98470</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>206004</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7401,10 +7401,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>544385</v>
+        <v>544478</v>
       </c>
       <c r="R69" t="n">
-        <v>6963074</v>
+        <v>6963117</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7437,6 +7437,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7463,10 +7468,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128087329</v>
+        <v>128087525</v>
       </c>
       <c r="B70" t="n">
-        <v>57672</v>
+        <v>56248</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7474,21 +7479,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7498,10 +7503,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>544757</v>
+        <v>544385</v>
       </c>
       <c r="R70" t="n">
-        <v>6963172</v>
+        <v>6963074</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7534,11 +7539,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -11379,49 +11379,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128079656</v>
+        <v>128087577</v>
       </c>
       <c r="B109" t="n">
-        <v>98470</v>
+        <v>92674</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>1968</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>544277</v>
+        <v>544494</v>
       </c>
       <c r="R109" t="n">
-        <v>6963150</v>
+        <v>6963243</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11480,32 +11476,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128087565</v>
+        <v>128087586</v>
       </c>
       <c r="B110" t="n">
-        <v>98470</v>
+        <v>92642</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11515,10 +11511,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>544249</v>
+        <v>544281</v>
       </c>
       <c r="R110" t="n">
-        <v>6963223</v>
+        <v>6963257</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11555,7 +11551,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>10. Kan möjlitvis finns mer i blåbärsriset</t>
+          <t>2 nya exemplar 8 äldre ex</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11582,32 +11578,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128087372</v>
+        <v>128087578</v>
       </c>
       <c r="B111" t="n">
-        <v>98470</v>
+        <v>79029</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11617,10 +11613,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>544472</v>
+        <v>544246</v>
       </c>
       <c r="R111" t="n">
-        <v>6963201</v>
+        <v>6963257</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11653,11 +11649,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>8 ex</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11684,32 +11675,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128087551</v>
+        <v>128087531</v>
       </c>
       <c r="B112" t="n">
-        <v>98470</v>
+        <v>98504</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11719,10 +11710,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>544694</v>
+        <v>544755</v>
       </c>
       <c r="R112" t="n">
-        <v>6963258</v>
+        <v>6963130</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11759,7 +11750,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11786,45 +11777,49 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128087531</v>
+        <v>128079656</v>
       </c>
       <c r="B113" t="n">
-        <v>98504</v>
+        <v>98470</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>544755</v>
+        <v>544277</v>
       </c>
       <c r="R113" t="n">
-        <v>6963130</v>
+        <v>6963150</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11857,11 +11852,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11888,32 +11878,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128087577</v>
+        <v>128087565</v>
       </c>
       <c r="B114" t="n">
-        <v>92674</v>
+        <v>98470</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1968</v>
+        <v>220787</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11923,10 +11913,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>544494</v>
+        <v>544249</v>
       </c>
       <c r="R114" t="n">
-        <v>6963243</v>
+        <v>6963223</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11959,6 +11949,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>10. Kan möjlitvis finns mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11985,32 +11980,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128087586</v>
+        <v>128087372</v>
       </c>
       <c r="B115" t="n">
-        <v>92642</v>
+        <v>98470</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12020,10 +12015,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>544281</v>
+        <v>544472</v>
       </c>
       <c r="R115" t="n">
-        <v>6963257</v>
+        <v>6963201</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12060,7 +12055,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>2 nya exemplar 8 äldre ex</t>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12087,32 +12082,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128087578</v>
+        <v>128087551</v>
       </c>
       <c r="B116" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12122,10 +12117,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>544246</v>
+        <v>544694</v>
       </c>
       <c r="R116" t="n">
-        <v>6963257</v>
+        <v>6963258</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12158,6 +12153,11 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="AD116" t="b">

--- a/artfynd/A 32240-2025 artfynd.xlsx
+++ b/artfynd/A 32240-2025 artfynd.xlsx
@@ -1786,10 +1786,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128087323</v>
+        <v>128087520</v>
       </c>
       <c r="B13" t="n">
-        <v>57672</v>
+        <v>57832</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1797,21 +1797,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544646</v>
+        <v>544771</v>
       </c>
       <c r="R13" t="n">
-        <v>6963095</v>
+        <v>6963083</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>2 stycken.  Övriga läten</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1888,7 +1888,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128087324</v>
+        <v>128087323</v>
       </c>
       <c r="B14" t="n">
         <v>57672</v>
@@ -1923,10 +1923,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544792</v>
+        <v>544646</v>
       </c>
       <c r="R14" t="n">
-        <v>6963047</v>
+        <v>6963095</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1990,10 +1990,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128081639</v>
+        <v>128087324</v>
       </c>
       <c r="B15" t="n">
-        <v>80133</v>
+        <v>57672</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2001,21 +2001,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2025,10 +2025,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544323</v>
+        <v>544792</v>
       </c>
       <c r="R15" t="n">
-        <v>6963268</v>
+        <v>6963047</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2061,6 +2061,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2087,32 +2092,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128087347</v>
+        <v>128081639</v>
       </c>
       <c r="B16" t="n">
-        <v>80161</v>
+        <v>80133</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2122,10 +2127,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544745</v>
+        <v>544323</v>
       </c>
       <c r="R16" t="n">
-        <v>6963195</v>
+        <v>6963268</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2184,32 +2189,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128087520</v>
+        <v>128087347</v>
       </c>
       <c r="B17" t="n">
-        <v>57832</v>
+        <v>80161</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2219,10 +2224,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544771</v>
+        <v>544745</v>
       </c>
       <c r="R17" t="n">
-        <v>6963083</v>
+        <v>6963195</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2255,11 +2260,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>2 stycken.  Övriga läten</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2388,10 +2388,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128087581</v>
+        <v>128087354</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>80133</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2399,21 +2399,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2423,10 +2423,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544192</v>
+        <v>544820</v>
       </c>
       <c r="R19" t="n">
-        <v>6963197</v>
+        <v>6963278</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2485,10 +2485,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128087362</v>
+        <v>128087581</v>
       </c>
       <c r="B20" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2496,21 +2496,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544799</v>
+        <v>544192</v>
       </c>
       <c r="R20" t="n">
-        <v>6963263</v>
+        <v>6963197</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2582,32 +2582,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128087349</v>
+        <v>128087362</v>
       </c>
       <c r="B21" t="n">
-        <v>80161</v>
+        <v>80132</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544475</v>
+        <v>544799</v>
       </c>
       <c r="R21" t="n">
-        <v>6963205</v>
+        <v>6963263</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2679,32 +2679,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128087354</v>
+        <v>128087349</v>
       </c>
       <c r="B22" t="n">
-        <v>80133</v>
+        <v>80161</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2714,10 +2714,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544820</v>
+        <v>544475</v>
       </c>
       <c r="R22" t="n">
-        <v>6963278</v>
+        <v>6963205</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2776,32 +2776,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128087569</v>
+        <v>128087359</v>
       </c>
       <c r="B23" t="n">
-        <v>98470</v>
+        <v>78788</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2811,10 +2811,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544296</v>
+        <v>544741</v>
       </c>
       <c r="R23" t="n">
-        <v>6963084</v>
+        <v>6963165</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2847,11 +2847,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>100stycken</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2878,7 +2873,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128087554</v>
+        <v>128087569</v>
       </c>
       <c r="B24" t="n">
         <v>98470</v>
@@ -2913,10 +2908,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544659</v>
+        <v>544296</v>
       </c>
       <c r="R24" t="n">
-        <v>6963253</v>
+        <v>6963084</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2953,7 +2948,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>50 stycken</t>
+          <t>100stycken</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2980,32 +2975,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128087359</v>
+        <v>128087554</v>
       </c>
       <c r="B25" t="n">
-        <v>78788</v>
+        <v>98470</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3015,10 +3010,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544741</v>
+        <v>544659</v>
       </c>
       <c r="R25" t="n">
-        <v>6963165</v>
+        <v>6963253</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3051,6 +3046,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4876,10 +4876,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128087361</v>
+        <v>128087340</v>
       </c>
       <c r="B44" t="n">
-        <v>80132</v>
+        <v>57832</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4887,21 +4887,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4911,10 +4911,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>544865</v>
+        <v>544485</v>
       </c>
       <c r="R44" t="n">
-        <v>6963092</v>
+        <v>6963237</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4973,32 +4973,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128087360</v>
+        <v>128087552</v>
       </c>
       <c r="B45" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5008,10 +5008,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>544615</v>
+        <v>544687</v>
       </c>
       <c r="R45" t="n">
-        <v>6963093</v>
+        <v>6963255</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5044,6 +5044,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>70</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5070,32 +5075,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128079768</v>
+        <v>128087548</v>
       </c>
       <c r="B46" t="n">
-        <v>97353</v>
+        <v>98470</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5105,10 +5110,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>544287</v>
+        <v>544213</v>
       </c>
       <c r="R46" t="n">
-        <v>6963168</v>
+        <v>6963197</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5141,6 +5146,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>100stycken.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5167,32 +5177,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128087340</v>
+        <v>128079768</v>
       </c>
       <c r="B47" t="n">
-        <v>57832</v>
+        <v>97353</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>221941</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5202,10 +5212,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>544485</v>
+        <v>544287</v>
       </c>
       <c r="R47" t="n">
-        <v>6963237</v>
+        <v>6963168</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5264,32 +5274,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128087552</v>
+        <v>128087361</v>
       </c>
       <c r="B48" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5299,10 +5309,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>544687</v>
+        <v>544865</v>
       </c>
       <c r="R48" t="n">
-        <v>6963255</v>
+        <v>6963092</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5335,11 +5345,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>70</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5366,32 +5371,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128087548</v>
+        <v>128087360</v>
       </c>
       <c r="B49" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5401,10 +5406,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>544213</v>
+        <v>544615</v>
       </c>
       <c r="R49" t="n">
-        <v>6963197</v>
+        <v>6963093</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5437,11 +5442,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>100stycken.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5468,32 +5468,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128087339</v>
+        <v>128087342</v>
       </c>
       <c r="B50" t="n">
-        <v>57832</v>
+        <v>80161</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5503,10 +5503,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>544850</v>
+        <v>544848</v>
       </c>
       <c r="R50" t="n">
-        <v>6963099</v>
+        <v>6963086</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5539,11 +5539,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5570,32 +5565,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128087342</v>
+        <v>128087367</v>
       </c>
       <c r="B51" t="n">
-        <v>80161</v>
+        <v>80132</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5605,10 +5600,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>544848</v>
+        <v>544298</v>
       </c>
       <c r="R51" t="n">
-        <v>6963086</v>
+        <v>6963312</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5667,7 +5662,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128087367</v>
+        <v>128087364</v>
       </c>
       <c r="B52" t="n">
         <v>80132</v>
@@ -5702,10 +5697,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>544298</v>
+        <v>544774</v>
       </c>
       <c r="R52" t="n">
-        <v>6963312</v>
+        <v>6963282</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5764,10 +5759,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128087364</v>
+        <v>128087339</v>
       </c>
       <c r="B53" t="n">
-        <v>80132</v>
+        <v>57832</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5775,21 +5770,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5799,10 +5794,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>544774</v>
+        <v>544850</v>
       </c>
       <c r="R53" t="n">
-        <v>6963282</v>
+        <v>6963099</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5835,6 +5830,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6162,10 +6162,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128087585</v>
+        <v>128087356</v>
       </c>
       <c r="B57" t="n">
-        <v>92642</v>
+        <v>80160</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6173,21 +6173,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>6461</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6197,10 +6197,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>544536</v>
+        <v>544772</v>
       </c>
       <c r="R57" t="n">
-        <v>6963255</v>
+        <v>6963323</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6233,11 +6233,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>8 äldre ex9 färska fruktkroppar</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6264,50 +6259,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128080012</v>
+        <v>128087357</v>
       </c>
       <c r="B58" t="n">
-        <v>57672</v>
+        <v>80160</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>544324</v>
+        <v>544466</v>
       </c>
       <c r="R58" t="n">
-        <v>6963220</v>
+        <v>6963277</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6340,11 +6330,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6371,10 +6356,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128087356</v>
+        <v>128087585</v>
       </c>
       <c r="B59" t="n">
-        <v>80160</v>
+        <v>92642</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6382,21 +6367,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6461</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6406,10 +6391,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>544772</v>
+        <v>544536</v>
       </c>
       <c r="R59" t="n">
-        <v>6963323</v>
+        <v>6963255</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6442,6 +6427,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>8 äldre ex9 färska fruktkroppar</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6468,45 +6458,50 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128087357</v>
+        <v>128080012</v>
       </c>
       <c r="B60" t="n">
-        <v>80160</v>
+        <v>57672</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>544466</v>
+        <v>544324</v>
       </c>
       <c r="R60" t="n">
-        <v>6963277</v>
+        <v>6963220</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6539,6 +6534,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8182,45 +8182,49 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128087330</v>
+        <v>128079875</v>
       </c>
       <c r="B77" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>544750</v>
+        <v>544308</v>
       </c>
       <c r="R77" t="n">
-        <v>6963177</v>
+        <v>6963175</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8253,11 +8257,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8284,32 +8283,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128087335</v>
+        <v>128087542</v>
       </c>
       <c r="B78" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8319,10 +8318,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>544366</v>
+        <v>544752</v>
       </c>
       <c r="R78" t="n">
-        <v>6963181</v>
+        <v>6963192</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8359,7 +8358,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8386,45 +8385,49 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128087575</v>
+        <v>128080338</v>
       </c>
       <c r="B79" t="n">
-        <v>92674</v>
+        <v>98470</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1968</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>544532</v>
+        <v>544314</v>
       </c>
       <c r="R79" t="n">
-        <v>6963250</v>
+        <v>6963248</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8457,11 +8460,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Igen stor köttig svamp misstänker grantaggsvamp 2 ex</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8488,32 +8486,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128078492</v>
+        <v>128087547</v>
       </c>
       <c r="B80" t="n">
-        <v>92674</v>
+        <v>98470</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1968</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8523,10 +8521,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>544362</v>
+        <v>544380</v>
       </c>
       <c r="R80" t="n">
-        <v>6963073</v>
+        <v>6963236</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8559,6 +8557,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>33 stycken</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8585,32 +8588,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128087536</v>
+        <v>128087380</v>
       </c>
       <c r="B81" t="n">
-        <v>80132</v>
+        <v>105508</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>221144</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8620,10 +8623,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>544215</v>
+        <v>544468</v>
       </c>
       <c r="R81" t="n">
-        <v>6963245</v>
+        <v>6963173</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8682,32 +8685,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128087343</v>
+        <v>128087560</v>
       </c>
       <c r="B82" t="n">
-        <v>80161</v>
+        <v>98470</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8717,10 +8720,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>544757</v>
+        <v>544383</v>
       </c>
       <c r="R82" t="n">
-        <v>6963156</v>
+        <v>6963236</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8753,6 +8756,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8779,32 +8787,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128087346</v>
+        <v>128087570</v>
       </c>
       <c r="B83" t="n">
-        <v>80161</v>
+        <v>56855</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6462</v>
+        <v>102612</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8814,10 +8822,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>544422</v>
+        <v>544287</v>
       </c>
       <c r="R83" t="n">
-        <v>6963240</v>
+        <v>6963082</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8850,6 +8858,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8876,10 +8889,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128087570</v>
+        <v>128087575</v>
       </c>
       <c r="B84" t="n">
-        <v>56855</v>
+        <v>92674</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8887,21 +8900,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>102612</v>
+        <v>1968</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8911,10 +8924,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>544287</v>
+        <v>544532</v>
       </c>
       <c r="R84" t="n">
-        <v>6963082</v>
+        <v>6963250</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8951,7 +8964,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Fjäder</t>
+          <t>Igen stor köttig svamp misstänker grantaggsvamp 2 ex</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8978,49 +8991,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128079875</v>
+        <v>128078492</v>
       </c>
       <c r="B85" t="n">
-        <v>98470</v>
+        <v>92674</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>1968</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>544308</v>
+        <v>544362</v>
       </c>
       <c r="R85" t="n">
-        <v>6963175</v>
+        <v>6963073</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9079,32 +9088,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128087542</v>
+        <v>128087536</v>
       </c>
       <c r="B86" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9114,10 +9123,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>544752</v>
+        <v>544215</v>
       </c>
       <c r="R86" t="n">
-        <v>6963192</v>
+        <v>6963245</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9150,11 +9159,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9181,49 +9185,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128080338</v>
+        <v>128087343</v>
       </c>
       <c r="B87" t="n">
-        <v>98470</v>
+        <v>80161</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>544314</v>
+        <v>544757</v>
       </c>
       <c r="R87" t="n">
-        <v>6963248</v>
+        <v>6963156</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9282,32 +9282,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128087547</v>
+        <v>128087346</v>
       </c>
       <c r="B88" t="n">
-        <v>98470</v>
+        <v>80161</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9317,10 +9317,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>544380</v>
+        <v>544422</v>
       </c>
       <c r="R88" t="n">
-        <v>6963236</v>
+        <v>6963240</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9353,11 +9353,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>33 stycken</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9384,32 +9379,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128087380</v>
+        <v>128087330</v>
       </c>
       <c r="B89" t="n">
-        <v>105508</v>
+        <v>57672</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221144</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9419,10 +9414,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>544468</v>
+        <v>544750</v>
       </c>
       <c r="R89" t="n">
-        <v>6963173</v>
+        <v>6963177</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9455,6 +9450,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9481,32 +9481,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128087560</v>
+        <v>128087335</v>
       </c>
       <c r="B90" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9516,10 +9516,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>544383</v>
+        <v>544366</v>
       </c>
       <c r="R90" t="n">
-        <v>6963236</v>
+        <v>6963181</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9556,7 +9556,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>40 stycken</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10083,10 +10083,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128087383</v>
+        <v>128087355</v>
       </c>
       <c r="B96" t="n">
-        <v>80167</v>
+        <v>97353</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10094,21 +10094,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6463</v>
+        <v>221941</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10118,10 +10118,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>544566</v>
+        <v>544500</v>
       </c>
       <c r="R96" t="n">
-        <v>6963076</v>
+        <v>6963168</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10180,32 +10180,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128087384</v>
+        <v>128087522</v>
       </c>
       <c r="B97" t="n">
-        <v>80167</v>
+        <v>57832</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6463</v>
+        <v>103021</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10215,10 +10215,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>544584</v>
+        <v>544494</v>
       </c>
       <c r="R97" t="n">
-        <v>6963261</v>
+        <v>6963243</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10277,32 +10277,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128087363</v>
+        <v>128087545</v>
       </c>
       <c r="B98" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10312,10 +10312,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>544818</v>
+        <v>544633</v>
       </c>
       <c r="R98" t="n">
-        <v>6963278</v>
+        <v>6963244</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10348,6 +10348,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10374,32 +10379,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128087576</v>
+        <v>128087567</v>
       </c>
       <c r="B99" t="n">
-        <v>92674</v>
+        <v>98470</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1968</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10409,10 +10414,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>544529</v>
+        <v>544274</v>
       </c>
       <c r="R99" t="n">
-        <v>6963245</v>
+        <v>6963090</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10449,7 +10454,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Misstänkt grantaggsvamp men med mörk tydlig ring i mitten.</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10476,32 +10481,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128087572</v>
+        <v>128087556</v>
       </c>
       <c r="B100" t="n">
-        <v>92674</v>
+        <v>98470</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1968</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10511,10 +10516,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>544632</v>
+        <v>544594</v>
       </c>
       <c r="R100" t="n">
-        <v>6963245</v>
+        <v>6963215</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10551,7 +10556,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>1 ex</t>
+          <t>6 stycken. Kan finnas mer i omgivningen</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10578,32 +10583,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128087522</v>
+        <v>128087373</v>
       </c>
       <c r="B101" t="n">
-        <v>57832</v>
+        <v>98470</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10613,10 +10618,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>544494</v>
+        <v>544469</v>
       </c>
       <c r="R101" t="n">
-        <v>6963243</v>
+        <v>6963122</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10649,6 +10654,11 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>60 ex</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10675,32 +10685,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128087545</v>
+        <v>128078864</v>
       </c>
       <c r="B102" t="n">
-        <v>98470</v>
+        <v>105508</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10710,10 +10720,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>544633</v>
+        <v>544307</v>
       </c>
       <c r="R102" t="n">
-        <v>6963244</v>
+        <v>6963089</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10746,11 +10756,6 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10777,7 +10782,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128087567</v>
+        <v>128087559</v>
       </c>
       <c r="B103" t="n">
         <v>98470</v>
@@ -10812,10 +10817,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>544274</v>
+        <v>544396</v>
       </c>
       <c r="R103" t="n">
-        <v>6963090</v>
+        <v>6963233</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10852,7 +10857,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10879,32 +10884,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128087556</v>
+        <v>128087576</v>
       </c>
       <c r="B104" t="n">
-        <v>98470</v>
+        <v>92674</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>1968</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10914,10 +10919,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>544594</v>
+        <v>544529</v>
       </c>
       <c r="R104" t="n">
-        <v>6963215</v>
+        <v>6963245</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10954,7 +10959,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>6 stycken. Kan finnas mer i omgivningen</t>
+          <t>Misstänkt grantaggsvamp men med mörk tydlig ring i mitten.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10981,32 +10986,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128087373</v>
+        <v>128087572</v>
       </c>
       <c r="B105" t="n">
-        <v>98470</v>
+        <v>92674</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>1968</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11016,10 +11021,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>544469</v>
+        <v>544632</v>
       </c>
       <c r="R105" t="n">
-        <v>6963122</v>
+        <v>6963245</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11056,7 +11061,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>60 ex</t>
+          <t>1 ex</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11083,10 +11088,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128078864</v>
+        <v>128087383</v>
       </c>
       <c r="B106" t="n">
-        <v>105508</v>
+        <v>80167</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11094,21 +11099,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>221144</v>
+        <v>6463</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11118,10 +11123,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>544307</v>
+        <v>544566</v>
       </c>
       <c r="R106" t="n">
-        <v>6963089</v>
+        <v>6963076</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11180,32 +11185,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128087559</v>
+        <v>128087384</v>
       </c>
       <c r="B107" t="n">
-        <v>98470</v>
+        <v>80167</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11215,10 +11220,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>544396</v>
+        <v>544584</v>
       </c>
       <c r="R107" t="n">
-        <v>6963233</v>
+        <v>6963261</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11251,11 +11256,6 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11282,32 +11282,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128087355</v>
+        <v>128087363</v>
       </c>
       <c r="B108" t="n">
-        <v>97353</v>
+        <v>80132</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>221941</v>
+        <v>6458</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11317,10 +11317,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>544500</v>
+        <v>544818</v>
       </c>
       <c r="R108" t="n">
-        <v>6963168</v>
+        <v>6963278</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12184,49 +12184,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128079571</v>
+        <v>128087571</v>
       </c>
       <c r="B117" t="n">
-        <v>98470</v>
+        <v>92674</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>1968</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>544274</v>
+        <v>544679</v>
       </c>
       <c r="R117" t="n">
-        <v>6963119</v>
+        <v>6963259</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12259,6 +12255,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Misstänker grantaggsvamp. 14 exemplar</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12285,49 +12286,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128078138</v>
+        <v>128087573</v>
       </c>
       <c r="B118" t="n">
-        <v>98470</v>
+        <v>92674</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>1968</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>544374</v>
+        <v>544684</v>
       </c>
       <c r="R118" t="n">
-        <v>6963056</v>
+        <v>6963253</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12360,6 +12357,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Mörkt exemplar med vit yttre ring.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12386,32 +12388,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128087571</v>
+        <v>128079848</v>
       </c>
       <c r="B119" t="n">
-        <v>92674</v>
+        <v>79053</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1968</v>
+        <v>6434</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12421,10 +12423,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>544679</v>
+        <v>544288</v>
       </c>
       <c r="R119" t="n">
-        <v>6963259</v>
+        <v>6963182</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12457,11 +12459,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Misstänker grantaggsvamp. 14 exemplar</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12488,10 +12485,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128087573</v>
+        <v>128087538</v>
       </c>
       <c r="B120" t="n">
-        <v>92674</v>
+        <v>80132</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12499,21 +12496,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1968</v>
+        <v>6458</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12523,10 +12520,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>544684</v>
+        <v>544262</v>
       </c>
       <c r="R120" t="n">
-        <v>6963253</v>
+        <v>6963163</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12559,11 +12556,6 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Mörkt exemplar med vit yttre ring.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12590,32 +12582,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128079848</v>
+        <v>128087535</v>
       </c>
       <c r="B121" t="n">
-        <v>79053</v>
+        <v>80132</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6434</v>
+        <v>6458</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12625,10 +12617,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>544288</v>
+        <v>544312</v>
       </c>
       <c r="R121" t="n">
-        <v>6963182</v>
+        <v>6963244</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12687,10 +12679,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128087538</v>
+        <v>128078823</v>
       </c>
       <c r="B122" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12698,21 +12690,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12722,10 +12714,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>544262</v>
+        <v>544307</v>
       </c>
       <c r="R122" t="n">
-        <v>6963163</v>
+        <v>6963089</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12784,45 +12776,49 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128087535</v>
+        <v>128079571</v>
       </c>
       <c r="B123" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>544312</v>
+        <v>544274</v>
       </c>
       <c r="R123" t="n">
-        <v>6963244</v>
+        <v>6963119</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12881,45 +12877,49 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128078823</v>
+        <v>128078138</v>
       </c>
       <c r="B124" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>544307</v>
+        <v>544374</v>
       </c>
       <c r="R124" t="n">
-        <v>6963089</v>
+        <v>6963056</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13075,32 +13075,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128087370</v>
+        <v>128079484</v>
       </c>
       <c r="B126" t="n">
-        <v>98470</v>
+        <v>80168</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13110,10 +13110,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>544751</v>
+        <v>544289</v>
       </c>
       <c r="R126" t="n">
-        <v>6963146</v>
+        <v>6963113</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13146,11 +13146,6 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>30 ex</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13177,32 +13172,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128087371</v>
+        <v>128087334</v>
       </c>
       <c r="B127" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13212,10 +13207,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>544559</v>
+        <v>544348</v>
       </c>
       <c r="R127" t="n">
-        <v>6963215</v>
+        <v>6963187</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13252,7 +13247,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>100 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13279,32 +13274,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128087583</v>
+        <v>128087574</v>
       </c>
       <c r="B128" t="n">
-        <v>98387</v>
+        <v>92674</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>219790</v>
+        <v>1968</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13314,10 +13309,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>544708</v>
+        <v>544552</v>
       </c>
       <c r="R128" t="n">
-        <v>6963086</v>
+        <v>6963231</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13354,7 +13349,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Misstänker grantaggsvamp 1 exemplar</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13381,7 +13376,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128087584</v>
+        <v>128087583</v>
       </c>
       <c r="B129" t="n">
         <v>98387</v>
@@ -13416,10 +13411,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>544718</v>
+        <v>544708</v>
       </c>
       <c r="R129" t="n">
-        <v>6963053</v>
+        <v>6963086</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13456,7 +13451,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>3 stycken</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13483,32 +13478,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128087574</v>
+        <v>128087584</v>
       </c>
       <c r="B130" t="n">
-        <v>92674</v>
+        <v>98387</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1968</v>
+        <v>219790</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13518,10 +13513,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>544552</v>
+        <v>544718</v>
       </c>
       <c r="R130" t="n">
-        <v>6963231</v>
+        <v>6963053</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13558,7 +13553,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Misstänker grantaggsvamp 1 exemplar</t>
+          <t>3 stycken</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13585,32 +13580,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128079484</v>
+        <v>128087370</v>
       </c>
       <c r="B131" t="n">
-        <v>80168</v>
+        <v>98470</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13620,10 +13615,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>544289</v>
+        <v>544751</v>
       </c>
       <c r="R131" t="n">
-        <v>6963113</v>
+        <v>6963146</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13656,6 +13651,11 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13682,32 +13682,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128087334</v>
+        <v>128087371</v>
       </c>
       <c r="B132" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13717,10 +13717,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>544348</v>
+        <v>544559</v>
       </c>
       <c r="R132" t="n">
-        <v>6963187</v>
+        <v>6963215</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13757,7 +13757,7 @@
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -13784,32 +13784,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128087557</v>
+        <v>128078645</v>
       </c>
       <c r="B133" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13819,10 +13819,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>544552</v>
+        <v>544360</v>
       </c>
       <c r="R133" t="n">
-        <v>6963231</v>
+        <v>6963094</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13855,11 +13855,6 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -13886,32 +13881,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128087543</v>
+        <v>128087344</v>
       </c>
       <c r="B134" t="n">
-        <v>98470</v>
+        <v>80161</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13921,10 +13916,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>544674</v>
+        <v>544581</v>
       </c>
       <c r="R134" t="n">
-        <v>6963243</v>
+        <v>6963278</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13957,11 +13952,6 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -13988,32 +13978,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128087530</v>
+        <v>128087534</v>
       </c>
       <c r="B135" t="n">
-        <v>98504</v>
+        <v>80132</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>219874</v>
+        <v>6458</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14023,10 +14013,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>544737</v>
+        <v>544326</v>
       </c>
       <c r="R135" t="n">
-        <v>6963047</v>
+        <v>6963248</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14085,10 +14075,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128087381</v>
+        <v>128087345</v>
       </c>
       <c r="B136" t="n">
-        <v>98387</v>
+        <v>80161</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14096,21 +14086,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>219790</v>
+        <v>6462</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14120,10 +14110,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>544531</v>
+        <v>544391</v>
       </c>
       <c r="R136" t="n">
-        <v>6963190</v>
+        <v>6963205</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14182,7 +14172,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128078645</v>
+        <v>128087540</v>
       </c>
       <c r="B137" t="n">
         <v>80132</v>
@@ -14217,10 +14207,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>544360</v>
+        <v>544282</v>
       </c>
       <c r="R137" t="n">
-        <v>6963094</v>
+        <v>6963082</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14279,32 +14269,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128087344</v>
+        <v>128087328</v>
       </c>
       <c r="B138" t="n">
-        <v>80161</v>
+        <v>57672</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14314,10 +14304,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>544581</v>
+        <v>544736</v>
       </c>
       <c r="R138" t="n">
-        <v>6963278</v>
+        <v>6963153</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14350,6 +14340,11 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14376,32 +14371,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128087534</v>
+        <v>128087557</v>
       </c>
       <c r="B139" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14411,10 +14406,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>544326</v>
+        <v>544552</v>
       </c>
       <c r="R139" t="n">
-        <v>6963248</v>
+        <v>6963231</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14447,6 +14442,11 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14473,32 +14473,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128087345</v>
+        <v>128087543</v>
       </c>
       <c r="B140" t="n">
-        <v>80161</v>
+        <v>98470</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14508,10 +14508,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>544391</v>
+        <v>544674</v>
       </c>
       <c r="R140" t="n">
-        <v>6963205</v>
+        <v>6963243</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14544,6 +14544,11 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14570,32 +14575,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128087540</v>
+        <v>128087530</v>
       </c>
       <c r="B141" t="n">
-        <v>80132</v>
+        <v>98504</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6458</v>
+        <v>219874</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14605,10 +14610,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>544282</v>
+        <v>544737</v>
       </c>
       <c r="R141" t="n">
-        <v>6963082</v>
+        <v>6963047</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14667,32 +14672,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128087328</v>
+        <v>128087381</v>
       </c>
       <c r="B142" t="n">
-        <v>57672</v>
+        <v>98387</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14702,10 +14707,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>544736</v>
+        <v>544531</v>
       </c>
       <c r="R142" t="n">
-        <v>6963153</v>
+        <v>6963190</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14738,11 +14743,6 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15069,32 +15069,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128094046</v>
+        <v>128094035</v>
       </c>
       <c r="B146" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15104,10 +15104,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>544754</v>
+        <v>544736</v>
       </c>
       <c r="R146" t="n">
-        <v>6963261</v>
+        <v>6963232</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15144,7 +15144,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>25 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15171,32 +15171,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128094035</v>
+        <v>128094046</v>
       </c>
       <c r="B147" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15206,10 +15206,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>544736</v>
+        <v>544754</v>
       </c>
       <c r="R147" t="n">
-        <v>6963232</v>
+        <v>6963261</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15246,7 +15246,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15472,32 +15472,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128094042</v>
+        <v>128094032</v>
       </c>
       <c r="B150" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15507,10 +15507,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>544528</v>
+        <v>544279</v>
       </c>
       <c r="R150" t="n">
-        <v>6963294</v>
+        <v>6963296</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15547,7 +15547,7 @@
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>75 ex</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15574,32 +15574,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128094032</v>
+        <v>128094042</v>
       </c>
       <c r="B151" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15609,10 +15609,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>544279</v>
+        <v>544528</v>
       </c>
       <c r="R151" t="n">
-        <v>6963296</v>
+        <v>6963294</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15649,7 +15649,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>75 ex</t>
         </is>
       </c>
       <c r="AD151" t="b">

--- a/artfynd/A 32240-2025 artfynd.xlsx
+++ b/artfynd/A 32240-2025 artfynd.xlsx
@@ -995,32 +995,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128087541</v>
+        <v>128087558</v>
       </c>
       <c r="B5" t="n">
-        <v>78787</v>
+        <v>98478</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544267</v>
+        <v>544428</v>
       </c>
       <c r="R5" t="n">
-        <v>6963196</v>
+        <v>6963233</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,6 +1066,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1092,32 +1097,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128087528</v>
+        <v>128087541</v>
       </c>
       <c r="B6" t="n">
-        <v>80160</v>
+        <v>78790</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1127,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544198</v>
+        <v>544267</v>
       </c>
       <c r="R6" t="n">
-        <v>6963228</v>
+        <v>6963196</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,7 +1197,7 @@
         <v>128087358</v>
       </c>
       <c r="B7" t="n">
-        <v>80160</v>
+        <v>80163</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,7 +1294,7 @@
         <v>128087524</v>
       </c>
       <c r="B8" t="n">
-        <v>80161</v>
+        <v>80164</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1383,32 +1388,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128087558</v>
+        <v>128087528</v>
       </c>
       <c r="B9" t="n">
-        <v>98470</v>
+        <v>80163</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1418,10 +1423,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544428</v>
+        <v>544198</v>
       </c>
       <c r="R9" t="n">
-        <v>6963233</v>
+        <v>6963228</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1454,11 +1459,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1485,32 +1485,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128087526</v>
+        <v>128078559</v>
       </c>
       <c r="B10" t="n">
-        <v>92634</v>
+        <v>97355</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4361</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544728</v>
+        <v>544359</v>
       </c>
       <c r="R10" t="n">
-        <v>6963223</v>
+        <v>6963083</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,11 +1556,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>10 exemplar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1587,10 +1582,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128087516</v>
+        <v>128087526</v>
       </c>
       <c r="B11" t="n">
-        <v>57672</v>
+        <v>92642</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1598,21 +1593,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1622,10 +1617,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544388</v>
+        <v>544728</v>
       </c>
       <c r="R11" t="n">
-        <v>6963226</v>
+        <v>6963223</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1662,7 +1657,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall Äldre spår</t>
+          <t>10 exemplar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1689,32 +1684,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128078559</v>
+        <v>128087516</v>
       </c>
       <c r="B12" t="n">
-        <v>97347</v>
+        <v>57673</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1724,10 +1719,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544359</v>
+        <v>544388</v>
       </c>
       <c r="R12" t="n">
-        <v>6963083</v>
+        <v>6963226</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1760,6 +1755,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall Äldre spår</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1789,7 +1789,7 @@
         <v>128087520</v>
       </c>
       <c r="B13" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         <v>128087323</v>
       </c>
       <c r="B14" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>128087324</v>
       </c>
       <c r="B15" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2092,32 +2092,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128081639</v>
+        <v>128087550</v>
       </c>
       <c r="B16" t="n">
-        <v>80133</v>
+        <v>98478</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544323</v>
+        <v>544490</v>
       </c>
       <c r="R16" t="n">
-        <v>6963268</v>
+        <v>6963099</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2163,6 +2163,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2189,32 +2194,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128087347</v>
+        <v>128081639</v>
       </c>
       <c r="B17" t="n">
-        <v>80161</v>
+        <v>80136</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2224,10 +2229,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544745</v>
+        <v>544323</v>
       </c>
       <c r="R17" t="n">
-        <v>6963195</v>
+        <v>6963268</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2286,32 +2291,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128087550</v>
+        <v>128087347</v>
       </c>
       <c r="B18" t="n">
-        <v>98470</v>
+        <v>80164</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2321,10 +2326,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544490</v>
+        <v>544745</v>
       </c>
       <c r="R18" t="n">
-        <v>6963099</v>
+        <v>6963195</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2357,11 +2362,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2391,7 +2391,7 @@
         <v>128087354</v>
       </c>
       <c r="B19" t="n">
-        <v>80133</v>
+        <v>80136</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>128087581</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2582,32 +2582,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128087362</v>
+        <v>128087349</v>
       </c>
       <c r="B21" t="n">
-        <v>80132</v>
+        <v>80164</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544799</v>
+        <v>544475</v>
       </c>
       <c r="R21" t="n">
-        <v>6963263</v>
+        <v>6963205</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2679,32 +2679,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128087349</v>
+        <v>128087362</v>
       </c>
       <c r="B22" t="n">
-        <v>80161</v>
+        <v>80135</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2714,10 +2714,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544475</v>
+        <v>544799</v>
       </c>
       <c r="R22" t="n">
-        <v>6963205</v>
+        <v>6963263</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2776,32 +2776,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128087359</v>
+        <v>128087569</v>
       </c>
       <c r="B23" t="n">
-        <v>78788</v>
+        <v>98478</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2811,10 +2811,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544741</v>
+        <v>544296</v>
       </c>
       <c r="R23" t="n">
-        <v>6963165</v>
+        <v>6963084</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2847,6 +2847,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>100stycken</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2873,10 +2878,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128087569</v>
+        <v>128087554</v>
       </c>
       <c r="B24" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2908,10 +2913,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544296</v>
+        <v>544659</v>
       </c>
       <c r="R24" t="n">
-        <v>6963084</v>
+        <v>6963253</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2948,7 +2953,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>100stycken</t>
+          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2975,32 +2980,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128087554</v>
+        <v>128087359</v>
       </c>
       <c r="B25" t="n">
-        <v>98470</v>
+        <v>78791</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3010,10 +3015,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544659</v>
+        <v>544741</v>
       </c>
       <c r="R25" t="n">
-        <v>6963253</v>
+        <v>6963165</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3046,11 +3051,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3077,45 +3077,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128087382</v>
+        <v>128078740</v>
       </c>
       <c r="B26" t="n">
-        <v>92642</v>
+        <v>98478</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>544198</v>
+        <v>544307</v>
       </c>
       <c r="R26" t="n">
-        <v>6963225</v>
+        <v>6963089</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3148,11 +3152,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>5 ex</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3179,32 +3178,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128087532</v>
+        <v>128087563</v>
       </c>
       <c r="B27" t="n">
-        <v>80132</v>
+        <v>98478</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3214,10 +3213,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544491</v>
+        <v>544322</v>
       </c>
       <c r="R27" t="n">
-        <v>6963099</v>
+        <v>6963250</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3250,6 +3249,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>12 stycken</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3276,32 +3280,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128087331</v>
+        <v>128087562</v>
       </c>
       <c r="B28" t="n">
-        <v>57672</v>
+        <v>98478</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3311,10 +3315,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544763</v>
+        <v>544367</v>
       </c>
       <c r="R28" t="n">
-        <v>6963244</v>
+        <v>6963253</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3351,7 +3355,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>7. Kan möjlitvis finnas fler runt omkring.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3378,45 +3382,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128087333</v>
+        <v>128078161</v>
       </c>
       <c r="B29" t="n">
-        <v>57672</v>
+        <v>98478</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544355</v>
+        <v>544362</v>
       </c>
       <c r="R29" t="n">
-        <v>6963212</v>
+        <v>6963061</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3449,11 +3457,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3480,32 +3483,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128087562</v>
+        <v>128087331</v>
       </c>
       <c r="B30" t="n">
-        <v>98470</v>
+        <v>57673</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3515,10 +3518,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>544367</v>
+        <v>544763</v>
       </c>
       <c r="R30" t="n">
-        <v>6963253</v>
+        <v>6963244</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3555,7 +3558,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>7. Kan möjlitvis finnas fler runt omkring.</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3582,49 +3585,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128078161</v>
+        <v>128087333</v>
       </c>
       <c r="B31" t="n">
-        <v>98470</v>
+        <v>57673</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>544362</v>
+        <v>544355</v>
       </c>
       <c r="R31" t="n">
-        <v>6963061</v>
+        <v>6963212</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3657,6 +3656,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3683,49 +3687,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128078740</v>
+        <v>128087532</v>
       </c>
       <c r="B32" t="n">
-        <v>98470</v>
+        <v>80135</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544307</v>
+        <v>544491</v>
       </c>
       <c r="R32" t="n">
-        <v>6963089</v>
+        <v>6963099</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3784,32 +3784,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128087563</v>
+        <v>128087382</v>
       </c>
       <c r="B33" t="n">
-        <v>98470</v>
+        <v>92650</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>544322</v>
+        <v>544198</v>
       </c>
       <c r="R33" t="n">
-        <v>6963250</v>
+        <v>6963225</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3859,7 +3859,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>12 stycken</t>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3886,10 +3886,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128079621</v>
+        <v>128087336</v>
       </c>
       <c r="B34" t="n">
-        <v>80132</v>
+        <v>57673</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3897,21 +3897,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3921,10 +3921,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>544274</v>
+        <v>544398</v>
       </c>
       <c r="R34" t="n">
-        <v>6963119</v>
+        <v>6963202</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3957,6 +3957,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3983,32 +3988,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128087533</v>
+        <v>128087351</v>
       </c>
       <c r="B35" t="n">
-        <v>80132</v>
+        <v>80164</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4018,10 +4023,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>544473</v>
+        <v>544299</v>
       </c>
       <c r="R35" t="n">
-        <v>6963102</v>
+        <v>6963312</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4080,32 +4085,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128087351</v>
+        <v>128087365</v>
       </c>
       <c r="B36" t="n">
-        <v>80161</v>
+        <v>80135</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4115,10 +4120,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>544299</v>
+        <v>544469</v>
       </c>
       <c r="R36" t="n">
-        <v>6963312</v>
+        <v>6963145</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4177,10 +4182,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128087365</v>
+        <v>128079621</v>
       </c>
       <c r="B37" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4212,10 +4217,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>544469</v>
+        <v>544274</v>
       </c>
       <c r="R37" t="n">
-        <v>6963145</v>
+        <v>6963119</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4274,10 +4279,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128087336</v>
+        <v>128087533</v>
       </c>
       <c r="B38" t="n">
-        <v>57672</v>
+        <v>80135</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4285,21 +4290,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4309,10 +4314,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>544398</v>
+        <v>544473</v>
       </c>
       <c r="R38" t="n">
-        <v>6963202</v>
+        <v>6963102</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4345,11 +4350,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4379,7 +4379,7 @@
         <v>128087588</v>
       </c>
       <c r="B39" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>128087527</v>
       </c>
       <c r="B40" t="n">
-        <v>80160</v>
+        <v>80163</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>128087369</v>
       </c>
       <c r="B41" t="n">
-        <v>80168</v>
+        <v>80171</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>128087332</v>
       </c>
       <c r="B42" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4777,7 +4777,7 @@
         <v>128087517</v>
       </c>
       <c r="B43" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         <v>128087340</v>
       </c>
       <c r="B44" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4973,32 +4973,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128087552</v>
+        <v>128079768</v>
       </c>
       <c r="B45" t="n">
-        <v>98470</v>
+        <v>97361</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5008,10 +5008,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>544687</v>
+        <v>544287</v>
       </c>
       <c r="R45" t="n">
-        <v>6963255</v>
+        <v>6963168</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5044,11 +5044,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>70</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5075,10 +5070,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128087548</v>
+        <v>128087552</v>
       </c>
       <c r="B46" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5110,10 +5105,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>544213</v>
+        <v>544687</v>
       </c>
       <c r="R46" t="n">
-        <v>6963197</v>
+        <v>6963255</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5150,7 +5145,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>100stycken.</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5177,32 +5172,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128079768</v>
+        <v>128087548</v>
       </c>
       <c r="B47" t="n">
-        <v>97353</v>
+        <v>98478</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5212,10 +5207,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>544287</v>
+        <v>544213</v>
       </c>
       <c r="R47" t="n">
-        <v>6963168</v>
+        <v>6963197</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5248,6 +5243,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>100stycken.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5277,7 +5277,7 @@
         <v>128087361</v>
       </c>
       <c r="B48" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>128087360</v>
       </c>
       <c r="B49" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5468,32 +5468,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128087342</v>
+        <v>128087553</v>
       </c>
       <c r="B50" t="n">
-        <v>80161</v>
+        <v>98478</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5503,10 +5503,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>544848</v>
+        <v>544677</v>
       </c>
       <c r="R50" t="n">
-        <v>6963086</v>
+        <v>6963260</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5539,6 +5539,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Mer än 70 stycken. Flera blommar</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5565,32 +5570,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128087367</v>
+        <v>128087555</v>
       </c>
       <c r="B51" t="n">
-        <v>80132</v>
+        <v>98478</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5600,10 +5605,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>544298</v>
+        <v>544623</v>
       </c>
       <c r="R51" t="n">
-        <v>6963312</v>
+        <v>6963241</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5636,6 +5641,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>60 stycken</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5662,32 +5672,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128087364</v>
+        <v>128079839</v>
       </c>
       <c r="B52" t="n">
-        <v>80132</v>
+        <v>105516</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>221144</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5697,10 +5707,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>544774</v>
+        <v>544288</v>
       </c>
       <c r="R52" t="n">
-        <v>6963282</v>
+        <v>6963182</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5759,10 +5769,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128087339</v>
+        <v>128087364</v>
       </c>
       <c r="B53" t="n">
-        <v>57832</v>
+        <v>80135</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5770,21 +5780,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5794,10 +5804,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>544850</v>
+        <v>544774</v>
       </c>
       <c r="R53" t="n">
-        <v>6963099</v>
+        <v>6963282</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5830,11 +5840,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5861,10 +5866,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128079839</v>
+        <v>128087342</v>
       </c>
       <c r="B54" t="n">
-        <v>105508</v>
+        <v>80164</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5872,21 +5877,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221144</v>
+        <v>6462</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5896,10 +5901,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>544288</v>
+        <v>544848</v>
       </c>
       <c r="R54" t="n">
-        <v>6963182</v>
+        <v>6963086</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5958,32 +5963,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128087553</v>
+        <v>128087367</v>
       </c>
       <c r="B55" t="n">
-        <v>98470</v>
+        <v>80135</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5993,10 +5998,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>544677</v>
+        <v>544298</v>
       </c>
       <c r="R55" t="n">
-        <v>6963260</v>
+        <v>6963312</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6029,11 +6034,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Mer än 70 stycken. Flera blommar</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6060,32 +6060,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128087555</v>
+        <v>128087339</v>
       </c>
       <c r="B56" t="n">
-        <v>98470</v>
+        <v>57833</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>544623</v>
+        <v>544850</v>
       </c>
       <c r="R56" t="n">
-        <v>6963241</v>
+        <v>6963099</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>60 stycken</t>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6162,10 +6162,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128087356</v>
+        <v>128087585</v>
       </c>
       <c r="B57" t="n">
-        <v>80160</v>
+        <v>92650</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6173,21 +6173,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6461</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6197,10 +6197,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>544772</v>
+        <v>544536</v>
       </c>
       <c r="R57" t="n">
-        <v>6963323</v>
+        <v>6963255</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6233,6 +6233,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>8 äldre ex9 färska fruktkroppar</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6262,7 +6267,7 @@
         <v>128087357</v>
       </c>
       <c r="B58" t="n">
-        <v>80160</v>
+        <v>80163</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6356,10 +6361,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128087585</v>
+        <v>128087356</v>
       </c>
       <c r="B59" t="n">
-        <v>92642</v>
+        <v>80163</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6367,21 +6372,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>6461</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6391,10 +6396,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>544536</v>
+        <v>544772</v>
       </c>
       <c r="R59" t="n">
-        <v>6963255</v>
+        <v>6963323</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6427,11 +6432,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>8 äldre ex9 färska fruktkroppar</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6461,7 +6461,7 @@
         <v>128080012</v>
       </c>
       <c r="B60" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6565,10 +6565,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128087386</v>
+        <v>128087525</v>
       </c>
       <c r="B61" t="n">
-        <v>92636</v>
+        <v>56248</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6576,21 +6576,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4362</v>
+        <v>206004</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6600,10 +6600,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>544822</v>
+        <v>544385</v>
       </c>
       <c r="R61" t="n">
-        <v>6963295</v>
+        <v>6963074</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6662,32 +6662,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128078603</v>
+        <v>128087375</v>
       </c>
       <c r="B62" t="n">
-        <v>80161</v>
+        <v>98478</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6697,10 +6697,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>544360</v>
+        <v>544478</v>
       </c>
       <c r="R62" t="n">
-        <v>6963094</v>
+        <v>6963117</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6733,6 +6733,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6759,32 +6764,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128087523</v>
+        <v>128087566</v>
       </c>
       <c r="B63" t="n">
-        <v>80161</v>
+        <v>98478</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6794,10 +6799,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>544253</v>
+        <v>544261</v>
       </c>
       <c r="R63" t="n">
-        <v>6963139</v>
+        <v>6963170</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6830,6 +6835,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>4. Stycken. Finns möjligtvis fler i blåbärsriset.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6856,32 +6866,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128087579</v>
+        <v>128087378</v>
       </c>
       <c r="B64" t="n">
-        <v>79029</v>
+        <v>98478</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6891,10 +6901,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>544204</v>
+        <v>544218</v>
       </c>
       <c r="R64" t="n">
-        <v>6963238</v>
+        <v>6963229</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6931,7 +6941,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Riklig förekomst av garnlav</t>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6958,32 +6968,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128087329</v>
+        <v>128087377</v>
       </c>
       <c r="B65" t="n">
-        <v>57672</v>
+        <v>98478</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6993,10 +7003,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>544757</v>
+        <v>544403</v>
       </c>
       <c r="R65" t="n">
-        <v>6963172</v>
+        <v>6963221</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7033,7 +7043,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7060,32 +7070,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128087566</v>
+        <v>128087386</v>
       </c>
       <c r="B66" t="n">
-        <v>98470</v>
+        <v>92644</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>4362</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7095,10 +7105,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>544261</v>
+        <v>544822</v>
       </c>
       <c r="R66" t="n">
-        <v>6963170</v>
+        <v>6963295</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7131,11 +7141,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>4. Stycken. Finns möjligtvis fler i blåbärsriset.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7162,32 +7167,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128087377</v>
+        <v>128087579</v>
       </c>
       <c r="B67" t="n">
-        <v>98470</v>
+        <v>79032</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7197,10 +7202,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>544403</v>
+        <v>544204</v>
       </c>
       <c r="R67" t="n">
-        <v>6963221</v>
+        <v>6963238</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7237,7 +7242,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>20 ex</t>
+          <t>Riklig förekomst av garnlav</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7264,32 +7269,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128087378</v>
+        <v>128087523</v>
       </c>
       <c r="B68" t="n">
-        <v>98470</v>
+        <v>80164</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7299,10 +7304,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>544218</v>
+        <v>544253</v>
       </c>
       <c r="R68" t="n">
-        <v>6963229</v>
+        <v>6963139</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7335,11 +7340,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>80 ex</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7366,32 +7366,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128087375</v>
+        <v>128078603</v>
       </c>
       <c r="B69" t="n">
-        <v>98470</v>
+        <v>80164</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7401,10 +7401,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>544478</v>
+        <v>544360</v>
       </c>
       <c r="R69" t="n">
-        <v>6963117</v>
+        <v>6963094</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7437,11 +7437,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>35 ex</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7468,10 +7463,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128087525</v>
+        <v>128087329</v>
       </c>
       <c r="B70" t="n">
-        <v>56248</v>
+        <v>57673</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7479,21 +7474,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7503,10 +7498,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>544385</v>
+        <v>544757</v>
       </c>
       <c r="R70" t="n">
-        <v>6963074</v>
+        <v>6963172</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7539,6 +7534,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7565,10 +7565,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128087366</v>
+        <v>128087337</v>
       </c>
       <c r="B71" t="n">
-        <v>80132</v>
+        <v>57673</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7576,21 +7576,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7600,10 +7600,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>544407</v>
+        <v>544197</v>
       </c>
       <c r="R71" t="n">
-        <v>6963184</v>
+        <v>6963237</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7636,6 +7636,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7662,10 +7667,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128087537</v>
+        <v>128080035</v>
       </c>
       <c r="B72" t="n">
-        <v>80132</v>
+        <v>57673</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7673,34 +7678,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>544205</v>
+        <v>544340</v>
       </c>
       <c r="R72" t="n">
-        <v>6963241</v>
+        <v>6963223</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7733,6 +7743,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7759,10 +7774,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128087337</v>
+        <v>128080054</v>
       </c>
       <c r="B73" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7788,16 +7803,21 @@
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>544197</v>
+        <v>544301</v>
       </c>
       <c r="R73" t="n">
-        <v>6963237</v>
+        <v>6963231</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7834,7 +7854,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7861,10 +7881,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128080035</v>
+        <v>128080149</v>
       </c>
       <c r="B74" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7901,10 +7921,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>544340</v>
+        <v>544295</v>
       </c>
       <c r="R74" t="n">
-        <v>6963223</v>
+        <v>6963226</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7968,10 +7988,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128080054</v>
+        <v>128087537</v>
       </c>
       <c r="B75" t="n">
-        <v>57672</v>
+        <v>80135</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7979,39 +7999,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>544301</v>
+        <v>544205</v>
       </c>
       <c r="R75" t="n">
-        <v>6963231</v>
+        <v>6963241</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8044,11 +8059,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8075,10 +8085,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128080149</v>
+        <v>128087366</v>
       </c>
       <c r="B76" t="n">
-        <v>57672</v>
+        <v>80135</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8086,39 +8096,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>544295</v>
+        <v>544407</v>
       </c>
       <c r="R76" t="n">
-        <v>6963226</v>
+        <v>6963184</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8151,11 +8156,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8182,49 +8182,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128079875</v>
+        <v>128087575</v>
       </c>
       <c r="B77" t="n">
-        <v>98470</v>
+        <v>92682</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>1968</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>544308</v>
+        <v>544532</v>
       </c>
       <c r="R77" t="n">
-        <v>6963175</v>
+        <v>6963250</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8257,6 +8253,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Igen stor köttig svamp misstänker grantaggsvamp 2 ex</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8283,32 +8284,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128087542</v>
+        <v>128078492</v>
       </c>
       <c r="B78" t="n">
-        <v>98470</v>
+        <v>92682</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>1968</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8318,10 +8319,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>544752</v>
+        <v>544362</v>
       </c>
       <c r="R78" t="n">
-        <v>6963192</v>
+        <v>6963073</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8354,11 +8355,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8385,49 +8381,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128080338</v>
+        <v>128087343</v>
       </c>
       <c r="B79" t="n">
-        <v>98470</v>
+        <v>80164</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>544314</v>
+        <v>544757</v>
       </c>
       <c r="R79" t="n">
-        <v>6963248</v>
+        <v>6963156</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8486,32 +8478,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128087547</v>
+        <v>128087536</v>
       </c>
       <c r="B80" t="n">
-        <v>98470</v>
+        <v>80135</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8521,10 +8513,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>544380</v>
+        <v>544215</v>
       </c>
       <c r="R80" t="n">
-        <v>6963236</v>
+        <v>6963245</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8557,11 +8549,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>33 stycken</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8588,10 +8575,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128087380</v>
+        <v>128087346</v>
       </c>
       <c r="B81" t="n">
-        <v>105508</v>
+        <v>80164</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8599,21 +8586,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221144</v>
+        <v>6462</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8623,10 +8610,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>544468</v>
+        <v>544422</v>
       </c>
       <c r="R81" t="n">
-        <v>6963173</v>
+        <v>6963240</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8685,32 +8672,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128087560</v>
+        <v>128087570</v>
       </c>
       <c r="B82" t="n">
-        <v>98470</v>
+        <v>56855</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8720,10 +8707,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>544383</v>
+        <v>544287</v>
       </c>
       <c r="R82" t="n">
-        <v>6963236</v>
+        <v>6963082</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8760,7 +8747,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>40 stycken</t>
+          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8787,10 +8774,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128087570</v>
+        <v>128087330</v>
       </c>
       <c r="B83" t="n">
-        <v>56855</v>
+        <v>57673</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8798,16 +8785,16 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -8822,10 +8809,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>544287</v>
+        <v>544750</v>
       </c>
       <c r="R83" t="n">
-        <v>6963082</v>
+        <v>6963177</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8862,7 +8849,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Fjäder</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8889,10 +8876,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128087575</v>
+        <v>128087335</v>
       </c>
       <c r="B84" t="n">
-        <v>92674</v>
+        <v>57673</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8900,21 +8887,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1968</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8924,10 +8911,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>544532</v>
+        <v>544366</v>
       </c>
       <c r="R84" t="n">
-        <v>6963250</v>
+        <v>6963181</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8964,7 +8951,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Igen stor köttig svamp misstänker grantaggsvamp 2 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8991,32 +8978,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128078492</v>
+        <v>128087547</v>
       </c>
       <c r="B85" t="n">
-        <v>92674</v>
+        <v>98478</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1968</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9026,10 +9013,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>544362</v>
+        <v>544380</v>
       </c>
       <c r="R85" t="n">
-        <v>6963073</v>
+        <v>6963236</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9062,6 +9049,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>33 stycken</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9088,32 +9080,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128087536</v>
+        <v>128087560</v>
       </c>
       <c r="B86" t="n">
-        <v>80132</v>
+        <v>98478</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9123,10 +9115,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>544215</v>
+        <v>544383</v>
       </c>
       <c r="R86" t="n">
-        <v>6963245</v>
+        <v>6963236</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9159,6 +9151,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9185,32 +9182,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128087343</v>
+        <v>128087542</v>
       </c>
       <c r="B87" t="n">
-        <v>80161</v>
+        <v>98478</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9220,10 +9217,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>544757</v>
+        <v>544752</v>
       </c>
       <c r="R87" t="n">
-        <v>6963156</v>
+        <v>6963192</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9256,6 +9253,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9282,45 +9284,49 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128087346</v>
+        <v>128079875</v>
       </c>
       <c r="B88" t="n">
-        <v>80161</v>
+        <v>98478</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>544422</v>
+        <v>544308</v>
       </c>
       <c r="R88" t="n">
-        <v>6963240</v>
+        <v>6963175</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9379,32 +9385,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128087330</v>
+        <v>128087380</v>
       </c>
       <c r="B89" t="n">
-        <v>57672</v>
+        <v>105516</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9414,10 +9420,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>544750</v>
+        <v>544468</v>
       </c>
       <c r="R89" t="n">
-        <v>6963177</v>
+        <v>6963173</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9450,11 +9456,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9481,45 +9482,49 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128087335</v>
+        <v>128080338</v>
       </c>
       <c r="B90" t="n">
-        <v>57672</v>
+        <v>98478</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>544366</v>
+        <v>544314</v>
       </c>
       <c r="R90" t="n">
-        <v>6963181</v>
+        <v>6963248</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9552,11 +9557,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9583,32 +9583,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128087376</v>
+        <v>128087587</v>
       </c>
       <c r="B91" t="n">
-        <v>98470</v>
+        <v>92650</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9618,10 +9618,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>544503</v>
+        <v>544245</v>
       </c>
       <c r="R91" t="n">
-        <v>6963182</v>
+        <v>6963255</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9658,7 +9658,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>60 ex</t>
+          <t>4stycken</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9685,32 +9685,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128087379</v>
+        <v>128087539</v>
       </c>
       <c r="B92" t="n">
-        <v>98470</v>
+        <v>80135</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9720,10 +9720,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>544263</v>
+        <v>544254</v>
       </c>
       <c r="R92" t="n">
-        <v>6963254</v>
+        <v>6963139</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9756,11 +9756,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>15 ex</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9787,10 +9782,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128087587</v>
+        <v>128087341</v>
       </c>
       <c r="B93" t="n">
-        <v>92642</v>
+        <v>80164</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9798,21 +9793,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9822,10 +9817,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>544245</v>
+        <v>544615</v>
       </c>
       <c r="R93" t="n">
-        <v>6963255</v>
+        <v>6963101</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9858,11 +9853,6 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>4stycken</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9889,32 +9879,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128087539</v>
+        <v>128087379</v>
       </c>
       <c r="B94" t="n">
-        <v>80132</v>
+        <v>98478</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9924,10 +9914,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>544254</v>
+        <v>544263</v>
       </c>
       <c r="R94" t="n">
-        <v>6963139</v>
+        <v>6963254</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9960,6 +9950,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9986,32 +9981,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128087341</v>
+        <v>128087376</v>
       </c>
       <c r="B95" t="n">
-        <v>80161</v>
+        <v>98478</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10021,10 +10016,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>544615</v>
+        <v>544503</v>
       </c>
       <c r="R95" t="n">
-        <v>6963101</v>
+        <v>6963182</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10057,6 +10052,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>60 ex</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10083,32 +10083,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128087355</v>
+        <v>128087576</v>
       </c>
       <c r="B96" t="n">
-        <v>97353</v>
+        <v>92682</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>221941</v>
+        <v>1968</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10118,10 +10118,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>544500</v>
+        <v>544529</v>
       </c>
       <c r="R96" t="n">
-        <v>6963168</v>
+        <v>6963245</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10154,6 +10154,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Misstänkt grantaggsvamp men med mörk tydlig ring i mitten.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10180,10 +10185,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128087522</v>
+        <v>128087572</v>
       </c>
       <c r="B97" t="n">
-        <v>57832</v>
+        <v>92682</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10191,21 +10196,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103021</v>
+        <v>1968</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10215,10 +10220,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>544494</v>
+        <v>544632</v>
       </c>
       <c r="R97" t="n">
-        <v>6963243</v>
+        <v>6963245</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10251,6 +10256,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>1 ex</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10277,32 +10287,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128087545</v>
+        <v>128087384</v>
       </c>
       <c r="B98" t="n">
-        <v>98470</v>
+        <v>80170</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10312,10 +10322,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>544633</v>
+        <v>544584</v>
       </c>
       <c r="R98" t="n">
-        <v>6963244</v>
+        <v>6963261</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10348,11 +10358,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10379,32 +10384,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128087567</v>
+        <v>128087383</v>
       </c>
       <c r="B99" t="n">
-        <v>98470</v>
+        <v>80170</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10414,10 +10419,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>544274</v>
+        <v>544566</v>
       </c>
       <c r="R99" t="n">
-        <v>6963090</v>
+        <v>6963076</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10450,11 +10455,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>110</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10481,32 +10481,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128087556</v>
+        <v>128087363</v>
       </c>
       <c r="B100" t="n">
-        <v>98470</v>
+        <v>80135</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10516,10 +10516,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>544594</v>
+        <v>544818</v>
       </c>
       <c r="R100" t="n">
-        <v>6963215</v>
+        <v>6963278</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10552,11 +10552,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>6 stycken. Kan finnas mer i omgivningen</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10583,32 +10578,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128087373</v>
+        <v>128087522</v>
       </c>
       <c r="B101" t="n">
-        <v>98470</v>
+        <v>57833</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10618,10 +10613,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>544469</v>
+        <v>544494</v>
       </c>
       <c r="R101" t="n">
-        <v>6963122</v>
+        <v>6963243</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10654,11 +10649,6 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>60 ex</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10685,10 +10675,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128078864</v>
+        <v>128087355</v>
       </c>
       <c r="B102" t="n">
-        <v>105508</v>
+        <v>97361</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10696,21 +10686,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>221144</v>
+        <v>221941</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10720,10 +10710,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>544307</v>
+        <v>544500</v>
       </c>
       <c r="R102" t="n">
-        <v>6963089</v>
+        <v>6963168</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10782,32 +10772,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128087559</v>
+        <v>128078864</v>
       </c>
       <c r="B103" t="n">
-        <v>98470</v>
+        <v>105516</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10817,10 +10807,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>544396</v>
+        <v>544307</v>
       </c>
       <c r="R103" t="n">
-        <v>6963233</v>
+        <v>6963089</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10853,11 +10843,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10884,32 +10869,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128087576</v>
+        <v>128087556</v>
       </c>
       <c r="B104" t="n">
-        <v>92674</v>
+        <v>98478</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1968</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10919,10 +10904,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>544529</v>
+        <v>544594</v>
       </c>
       <c r="R104" t="n">
-        <v>6963245</v>
+        <v>6963215</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10959,7 +10944,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Misstänkt grantaggsvamp men med mörk tydlig ring i mitten.</t>
+          <t>6 stycken. Kan finnas mer i omgivningen</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10986,32 +10971,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128087572</v>
+        <v>128087567</v>
       </c>
       <c r="B105" t="n">
-        <v>92674</v>
+        <v>98478</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1968</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11021,10 +11006,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>544632</v>
+        <v>544274</v>
       </c>
       <c r="R105" t="n">
-        <v>6963245</v>
+        <v>6963090</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11061,7 +11046,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>1 ex</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11088,32 +11073,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128087383</v>
+        <v>128087545</v>
       </c>
       <c r="B106" t="n">
-        <v>80167</v>
+        <v>98478</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11123,10 +11108,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>544566</v>
+        <v>544633</v>
       </c>
       <c r="R106" t="n">
-        <v>6963076</v>
+        <v>6963244</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11159,6 +11144,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11185,32 +11175,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128087384</v>
+        <v>128087559</v>
       </c>
       <c r="B107" t="n">
-        <v>80167</v>
+        <v>98478</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11220,10 +11210,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>544584</v>
+        <v>544396</v>
       </c>
       <c r="R107" t="n">
-        <v>6963261</v>
+        <v>6963233</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11256,6 +11246,11 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11282,32 +11277,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128087363</v>
+        <v>128087373</v>
       </c>
       <c r="B108" t="n">
-        <v>80132</v>
+        <v>98478</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11317,10 +11312,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>544818</v>
+        <v>544469</v>
       </c>
       <c r="R108" t="n">
-        <v>6963278</v>
+        <v>6963122</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11353,6 +11348,11 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>60 ex</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11379,32 +11379,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128087577</v>
+        <v>128087586</v>
       </c>
       <c r="B109" t="n">
-        <v>92674</v>
+        <v>92650</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1968</v>
+        <v>4364</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11414,10 +11414,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>544494</v>
+        <v>544281</v>
       </c>
       <c r="R109" t="n">
-        <v>6963243</v>
+        <v>6963257</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11450,6 +11450,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>2 nya exemplar 8 äldre ex</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11476,32 +11481,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128087586</v>
+        <v>128087577</v>
       </c>
       <c r="B110" t="n">
-        <v>92642</v>
+        <v>92682</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>4364</v>
+        <v>1968</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11511,10 +11516,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>544281</v>
+        <v>544494</v>
       </c>
       <c r="R110" t="n">
-        <v>6963257</v>
+        <v>6963243</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11547,11 +11552,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>2 nya exemplar 8 äldre ex</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11578,45 +11578,49 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128087578</v>
+        <v>128079656</v>
       </c>
       <c r="B111" t="n">
-        <v>79029</v>
+        <v>98478</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>544246</v>
+        <v>544277</v>
       </c>
       <c r="R111" t="n">
-        <v>6963257</v>
+        <v>6963150</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11675,32 +11679,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128087531</v>
+        <v>128087551</v>
       </c>
       <c r="B112" t="n">
-        <v>98504</v>
+        <v>98478</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11710,10 +11714,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>544755</v>
+        <v>544694</v>
       </c>
       <c r="R112" t="n">
-        <v>6963130</v>
+        <v>6963258</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11750,7 +11754,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>2 stycken</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11777,10 +11781,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128079656</v>
+        <v>128087565</v>
       </c>
       <c r="B113" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11805,21 +11809,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>544277</v>
+        <v>544249</v>
       </c>
       <c r="R113" t="n">
-        <v>6963150</v>
+        <v>6963223</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11852,6 +11852,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>10. Kan möjlitvis finns mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11878,32 +11883,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128087565</v>
+        <v>128087531</v>
       </c>
       <c r="B114" t="n">
-        <v>98470</v>
+        <v>98512</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11913,10 +11918,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>544249</v>
+        <v>544755</v>
       </c>
       <c r="R114" t="n">
-        <v>6963223</v>
+        <v>6963130</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11953,7 +11958,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>10. Kan möjlitvis finns mer i blåbärsriset</t>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11983,7 +11988,7 @@
         <v>128087372</v>
       </c>
       <c r="B115" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12082,32 +12087,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128087551</v>
+        <v>128087578</v>
       </c>
       <c r="B116" t="n">
-        <v>98470</v>
+        <v>79032</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12117,10 +12122,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>544694</v>
+        <v>544246</v>
       </c>
       <c r="R116" t="n">
-        <v>6963258</v>
+        <v>6963257</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12153,11 +12158,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12184,32 +12184,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128087571</v>
+        <v>128079848</v>
       </c>
       <c r="B117" t="n">
-        <v>92674</v>
+        <v>79056</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1968</v>
+        <v>6434</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12219,10 +12219,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>544679</v>
+        <v>544288</v>
       </c>
       <c r="R117" t="n">
-        <v>6963259</v>
+        <v>6963182</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12255,11 +12255,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Misstänker grantaggsvamp. 14 exemplar</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12286,10 +12281,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128087573</v>
+        <v>128078823</v>
       </c>
       <c r="B118" t="n">
-        <v>92674</v>
+        <v>79032</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12297,21 +12292,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1968</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12321,10 +12316,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>544684</v>
+        <v>544307</v>
       </c>
       <c r="R118" t="n">
-        <v>6963253</v>
+        <v>6963089</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12357,11 +12352,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Mörkt exemplar med vit yttre ring.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12388,32 +12378,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128079848</v>
+        <v>128087571</v>
       </c>
       <c r="B119" t="n">
-        <v>79053</v>
+        <v>92682</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6434</v>
+        <v>1968</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12423,10 +12413,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>544288</v>
+        <v>544679</v>
       </c>
       <c r="R119" t="n">
-        <v>6963182</v>
+        <v>6963259</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12459,6 +12449,11 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Misstänker grantaggsvamp. 14 exemplar</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12485,10 +12480,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128087538</v>
+        <v>128087573</v>
       </c>
       <c r="B120" t="n">
-        <v>80132</v>
+        <v>92682</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12496,21 +12491,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6458</v>
+        <v>1968</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12520,10 +12515,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>544262</v>
+        <v>544684</v>
       </c>
       <c r="R120" t="n">
-        <v>6963163</v>
+        <v>6963253</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12556,6 +12551,11 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Mörkt exemplar med vit yttre ring.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12585,7 +12585,7 @@
         <v>128087535</v>
       </c>
       <c r="B121" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12679,10 +12679,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128078823</v>
+        <v>128087538</v>
       </c>
       <c r="B122" t="n">
-        <v>79029</v>
+        <v>80135</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12690,21 +12690,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12714,10 +12714,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>544307</v>
+        <v>544262</v>
       </c>
       <c r="R122" t="n">
-        <v>6963089</v>
+        <v>6963163</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12776,49 +12776,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128079571</v>
+        <v>128087582</v>
       </c>
       <c r="B123" t="n">
-        <v>98470</v>
+        <v>98395</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>544274</v>
+        <v>544489</v>
       </c>
       <c r="R123" t="n">
-        <v>6963119</v>
+        <v>6963098</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12877,10 +12873,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128078138</v>
+        <v>128079571</v>
       </c>
       <c r="B124" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12907,7 +12903,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>400</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -12916,10 +12912,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>544374</v>
+        <v>544274</v>
       </c>
       <c r="R124" t="n">
-        <v>6963056</v>
+        <v>6963119</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12978,45 +12974,49 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128087582</v>
+        <v>128078138</v>
       </c>
       <c r="B125" t="n">
-        <v>98387</v>
+        <v>98478</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>544489</v>
+        <v>544374</v>
       </c>
       <c r="R125" t="n">
-        <v>6963098</v>
+        <v>6963056</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13078,7 +13078,7 @@
         <v>128079484</v>
       </c>
       <c r="B126" t="n">
-        <v>80168</v>
+        <v>80171</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>128087334</v>
       </c>
       <c r="B127" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13277,7 +13277,7 @@
         <v>128087574</v>
       </c>
       <c r="B128" t="n">
-        <v>92674</v>
+        <v>92682</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13379,7 +13379,7 @@
         <v>128087583</v>
       </c>
       <c r="B129" t="n">
-        <v>98387</v>
+        <v>98395</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13481,7 +13481,7 @@
         <v>128087584</v>
       </c>
       <c r="B130" t="n">
-        <v>98387</v>
+        <v>98395</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>128087370</v>
       </c>
       <c r="B131" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13685,7 +13685,7 @@
         <v>128087371</v>
       </c>
       <c r="B132" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13784,32 +13784,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128078645</v>
+        <v>128087344</v>
       </c>
       <c r="B133" t="n">
-        <v>80132</v>
+        <v>80164</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13819,10 +13819,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>544360</v>
+        <v>544581</v>
       </c>
       <c r="R133" t="n">
-        <v>6963094</v>
+        <v>6963278</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13881,32 +13881,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128087344</v>
+        <v>128078645</v>
       </c>
       <c r="B134" t="n">
-        <v>80161</v>
+        <v>80135</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13916,10 +13916,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>544581</v>
+        <v>544360</v>
       </c>
       <c r="R134" t="n">
-        <v>6963278</v>
+        <v>6963094</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13978,10 +13978,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128087534</v>
+        <v>128087540</v>
       </c>
       <c r="B135" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14013,10 +14013,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>544326</v>
+        <v>544282</v>
       </c>
       <c r="R135" t="n">
-        <v>6963248</v>
+        <v>6963082</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14078,7 +14078,7 @@
         <v>128087345</v>
       </c>
       <c r="B136" t="n">
-        <v>80161</v>
+        <v>80164</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14172,10 +14172,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128087540</v>
+        <v>128087534</v>
       </c>
       <c r="B137" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14207,10 +14207,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>544282</v>
+        <v>544326</v>
       </c>
       <c r="R137" t="n">
-        <v>6963082</v>
+        <v>6963248</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14272,7 +14272,7 @@
         <v>128087328</v>
       </c>
       <c r="B138" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14371,32 +14371,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128087557</v>
+        <v>128087530</v>
       </c>
       <c r="B139" t="n">
-        <v>98470</v>
+        <v>98512</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14406,10 +14406,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>544552</v>
+        <v>544737</v>
       </c>
       <c r="R139" t="n">
-        <v>6963231</v>
+        <v>6963047</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14442,11 +14442,6 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14473,32 +14468,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128087543</v>
+        <v>128087381</v>
       </c>
       <c r="B140" t="n">
-        <v>98470</v>
+        <v>98395</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14508,10 +14503,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>544674</v>
+        <v>544531</v>
       </c>
       <c r="R140" t="n">
-        <v>6963243</v>
+        <v>6963190</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14544,11 +14539,6 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14575,32 +14565,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128087530</v>
+        <v>128087543</v>
       </c>
       <c r="B141" t="n">
-        <v>98504</v>
+        <v>98478</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14610,10 +14600,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>544737</v>
+        <v>544674</v>
       </c>
       <c r="R141" t="n">
-        <v>6963047</v>
+        <v>6963243</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14646,6 +14636,11 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14672,32 +14667,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128087381</v>
+        <v>128087557</v>
       </c>
       <c r="B142" t="n">
-        <v>98387</v>
+        <v>98478</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14707,10 +14702,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>544531</v>
+        <v>544552</v>
       </c>
       <c r="R142" t="n">
-        <v>6963190</v>
+        <v>6963231</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14743,6 +14738,11 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -14871,49 +14871,45 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128078529</v>
+        <v>128087368</v>
       </c>
       <c r="B144" t="n">
-        <v>98470</v>
+        <v>80135</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>544351</v>
+        <v>544314</v>
       </c>
       <c r="R144" t="n">
-        <v>6963065</v>
+        <v>6963248</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14972,45 +14968,49 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128087368</v>
+        <v>128078529</v>
       </c>
       <c r="B145" t="n">
-        <v>80132</v>
+        <v>98478</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>544314</v>
+        <v>544351</v>
       </c>
       <c r="R145" t="n">
-        <v>6963248</v>
+        <v>6963065</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15069,32 +15069,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128094035</v>
+        <v>128094046</v>
       </c>
       <c r="B146" t="n">
-        <v>57672</v>
+        <v>98478</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15104,10 +15104,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>544736</v>
+        <v>544754</v>
       </c>
       <c r="R146" t="n">
-        <v>6963232</v>
+        <v>6963261</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15144,7 +15144,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15171,32 +15171,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128094046</v>
+        <v>128094035</v>
       </c>
       <c r="B147" t="n">
-        <v>98470</v>
+        <v>57673</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15206,10 +15206,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>544754</v>
+        <v>544736</v>
       </c>
       <c r="R147" t="n">
-        <v>6963261</v>
+        <v>6963232</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15246,7 +15246,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>25 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15276,7 +15276,7 @@
         <v>128094050</v>
       </c>
       <c r="B148" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15378,7 +15378,7 @@
         <v>128094039</v>
       </c>
       <c r="B149" t="n">
-        <v>80133</v>
+        <v>80136</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15475,7 +15475,7 @@
         <v>128094032</v>
       </c>
       <c r="B150" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15577,7 +15577,7 @@
         <v>128094042</v>
       </c>
       <c r="B151" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>128094044</v>
       </c>
       <c r="B152" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>128094038</v>
       </c>
       <c r="B153" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15880,10 +15880,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128094040</v>
+        <v>128094043</v>
       </c>
       <c r="B154" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15915,10 +15915,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>544323</v>
+        <v>544546</v>
       </c>
       <c r="R154" t="n">
-        <v>6963323</v>
+        <v>6963293</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>7 ex</t>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -15982,10 +15982,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128094043</v>
+        <v>128094040</v>
       </c>
       <c r="B155" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16017,10 +16017,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>544546</v>
+        <v>544323</v>
       </c>
       <c r="R155" t="n">
-        <v>6963293</v>
+        <v>6963323</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16057,7 +16057,7 @@
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>25 ex</t>
+          <t>7 ex</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16087,7 +16087,7 @@
         <v>128094048</v>
       </c>
       <c r="B156" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>128094041</v>
       </c>
       <c r="B157" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16291,7 +16291,7 @@
         <v>128094049</v>
       </c>
       <c r="B158" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>128094053</v>
       </c>
       <c r="B159" t="n">
-        <v>105508</v>
+        <v>105516</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>128094047</v>
       </c>
       <c r="B161" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16691,32 +16691,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128094051</v>
+        <v>128094054</v>
       </c>
       <c r="B162" t="n">
-        <v>98470</v>
+        <v>105516</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16726,10 +16726,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>544310</v>
+        <v>544321</v>
       </c>
       <c r="R162" t="n">
-        <v>6963314</v>
+        <v>6963319</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16762,11 +16762,6 @@
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>80 ex</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -16793,10 +16788,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128094045</v>
+        <v>128094051</v>
       </c>
       <c r="B163" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16828,10 +16823,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>544760</v>
+        <v>544310</v>
       </c>
       <c r="R163" t="n">
-        <v>6963251</v>
+        <v>6963314</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -16868,7 +16863,7 @@
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>35 ex</t>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -16895,32 +16890,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128094054</v>
+        <v>128094045</v>
       </c>
       <c r="B164" t="n">
-        <v>105508</v>
+        <v>98478</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -16930,10 +16925,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>544321</v>
+        <v>544760</v>
       </c>
       <c r="R164" t="n">
-        <v>6963319</v>
+        <v>6963251</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -16966,6 +16961,11 @@
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -16992,10 +16992,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128094033</v>
+        <v>128094036</v>
       </c>
       <c r="B165" t="n">
-        <v>57672</v>
+        <v>57833</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17003,21 +17003,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17027,10 +17027,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>544475</v>
+        <v>544566</v>
       </c>
       <c r="R165" t="n">
-        <v>6963299</v>
+        <v>6963163</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17067,7 +17067,7 @@
       </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Lockläte övriga läten</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17094,10 +17094,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128094036</v>
+        <v>128094033</v>
       </c>
       <c r="B166" t="n">
-        <v>57832</v>
+        <v>57673</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17105,21 +17105,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17129,10 +17129,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>544566</v>
+        <v>544475</v>
       </c>
       <c r="R166" t="n">
-        <v>6963163</v>
+        <v>6963299</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17169,7 +17169,7 @@
       </c>
       <c r="AC166" t="inlineStr">
         <is>
-          <t>Lockläte övriga läten</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17199,7 +17199,7 @@
         <v>128094034</v>
       </c>
       <c r="B167" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17301,7 +17301,7 @@
         <v>128094055</v>
       </c>
       <c r="B168" t="n">
-        <v>105508</v>
+        <v>105516</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>

--- a/artfynd/A 32240-2025 artfynd.xlsx
+++ b/artfynd/A 32240-2025 artfynd.xlsx
@@ -995,32 +995,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128087558</v>
+        <v>128087541</v>
       </c>
       <c r="B5" t="n">
-        <v>98478</v>
+        <v>78790</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544428</v>
+        <v>544267</v>
       </c>
       <c r="R5" t="n">
-        <v>6963233</v>
+        <v>6963196</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,11 +1066,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,32 +1092,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128087541</v>
+        <v>128087358</v>
       </c>
       <c r="B6" t="n">
-        <v>78790</v>
+        <v>80163</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6461</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544267</v>
+        <v>544278</v>
       </c>
       <c r="R6" t="n">
-        <v>6963196</v>
+        <v>6963265</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128087358</v>
+        <v>128087524</v>
       </c>
       <c r="B7" t="n">
-        <v>80163</v>
+        <v>80164</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1205,21 +1200,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1229,10 +1224,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544278</v>
+        <v>544281</v>
       </c>
       <c r="R7" t="n">
-        <v>6963265</v>
+        <v>6963082</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,10 +1286,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128087524</v>
+        <v>128087528</v>
       </c>
       <c r="B8" t="n">
-        <v>80164</v>
+        <v>80163</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,21 +1297,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1326,10 +1321,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544281</v>
+        <v>544198</v>
       </c>
       <c r="R8" t="n">
-        <v>6963082</v>
+        <v>6963228</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,32 +1383,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128087528</v>
+        <v>128087558</v>
       </c>
       <c r="B9" t="n">
-        <v>80163</v>
+        <v>98478</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1423,10 +1418,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544198</v>
+        <v>544428</v>
       </c>
       <c r="R9" t="n">
-        <v>6963228</v>
+        <v>6963233</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,6 +1454,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1786,32 +1786,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128087520</v>
+        <v>128087347</v>
       </c>
       <c r="B13" t="n">
-        <v>57833</v>
+        <v>80164</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544771</v>
+        <v>544745</v>
       </c>
       <c r="R13" t="n">
-        <v>6963083</v>
+        <v>6963195</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1857,11 +1857,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>2 stycken.  Övriga läten</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2092,32 +2087,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128087550</v>
+        <v>128087520</v>
       </c>
       <c r="B16" t="n">
-        <v>98478</v>
+        <v>57833</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2127,10 +2122,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544490</v>
+        <v>544771</v>
       </c>
       <c r="R16" t="n">
-        <v>6963099</v>
+        <v>6963083</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2167,7 +2162,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2 stycken.  Övriga läten</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2194,32 +2189,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128081639</v>
+        <v>128087550</v>
       </c>
       <c r="B17" t="n">
-        <v>80136</v>
+        <v>98478</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2229,10 +2224,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544323</v>
+        <v>544490</v>
       </c>
       <c r="R17" t="n">
-        <v>6963268</v>
+        <v>6963099</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2265,6 +2260,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2291,32 +2291,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128087347</v>
+        <v>128081639</v>
       </c>
       <c r="B18" t="n">
-        <v>80164</v>
+        <v>80136</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2326,10 +2326,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544745</v>
+        <v>544323</v>
       </c>
       <c r="R18" t="n">
-        <v>6963195</v>
+        <v>6963268</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3687,32 +3687,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128087532</v>
+        <v>128087382</v>
       </c>
       <c r="B32" t="n">
-        <v>80135</v>
+        <v>92650</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3722,10 +3722,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544491</v>
+        <v>544198</v>
       </c>
       <c r="R32" t="n">
-        <v>6963099</v>
+        <v>6963225</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3758,6 +3758,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3784,32 +3789,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128087382</v>
+        <v>128087532</v>
       </c>
       <c r="B33" t="n">
-        <v>92650</v>
+        <v>80135</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3819,10 +3824,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>544198</v>
+        <v>544491</v>
       </c>
       <c r="R33" t="n">
-        <v>6963225</v>
+        <v>6963099</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3855,11 +3860,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>5 ex</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4876,32 +4876,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128087340</v>
+        <v>128079768</v>
       </c>
       <c r="B44" t="n">
-        <v>57833</v>
+        <v>97361</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>221941</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4911,10 +4911,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>544485</v>
+        <v>544287</v>
       </c>
       <c r="R44" t="n">
-        <v>6963237</v>
+        <v>6963168</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4973,32 +4973,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128079768</v>
+        <v>128087552</v>
       </c>
       <c r="B45" t="n">
-        <v>97361</v>
+        <v>98478</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5008,10 +5008,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>544287</v>
+        <v>544687</v>
       </c>
       <c r="R45" t="n">
-        <v>6963168</v>
+        <v>6963255</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5044,6 +5044,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>70</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5070,7 +5075,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128087552</v>
+        <v>128087548</v>
       </c>
       <c r="B46" t="n">
         <v>98478</v>
@@ -5105,10 +5110,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>544687</v>
+        <v>544213</v>
       </c>
       <c r="R46" t="n">
-        <v>6963255</v>
+        <v>6963197</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5145,7 +5150,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>100stycken.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5172,32 +5177,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128087548</v>
+        <v>128087361</v>
       </c>
       <c r="B47" t="n">
-        <v>98478</v>
+        <v>80135</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5207,10 +5212,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>544213</v>
+        <v>544865</v>
       </c>
       <c r="R47" t="n">
-        <v>6963197</v>
+        <v>6963092</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5243,11 +5248,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>100stycken.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5274,7 +5274,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128087361</v>
+        <v>128087360</v>
       </c>
       <c r="B48" t="n">
         <v>80135</v>
@@ -5309,10 +5309,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>544865</v>
+        <v>544615</v>
       </c>
       <c r="R48" t="n">
-        <v>6963092</v>
+        <v>6963093</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5371,10 +5371,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128087360</v>
+        <v>128087340</v>
       </c>
       <c r="B49" t="n">
-        <v>80135</v>
+        <v>57833</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5382,21 +5382,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>544615</v>
+        <v>544485</v>
       </c>
       <c r="R49" t="n">
-        <v>6963093</v>
+        <v>6963237</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -7565,10 +7565,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128087337</v>
+        <v>128087537</v>
       </c>
       <c r="B71" t="n">
-        <v>57673</v>
+        <v>80135</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7576,21 +7576,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7600,10 +7600,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>544197</v>
+        <v>544205</v>
       </c>
       <c r="R71" t="n">
-        <v>6963237</v>
+        <v>6963241</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7636,11 +7636,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7667,10 +7662,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128080035</v>
+        <v>128087366</v>
       </c>
       <c r="B72" t="n">
-        <v>57673</v>
+        <v>80135</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7678,39 +7673,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>544340</v>
+        <v>544407</v>
       </c>
       <c r="R72" t="n">
-        <v>6963223</v>
+        <v>6963184</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7743,11 +7733,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7774,7 +7759,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128080054</v>
+        <v>128087337</v>
       </c>
       <c r="B73" t="n">
         <v>57673</v>
@@ -7803,21 +7788,16 @@
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>544301</v>
+        <v>544197</v>
       </c>
       <c r="R73" t="n">
-        <v>6963231</v>
+        <v>6963237</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7854,7 +7834,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7881,7 +7861,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128080149</v>
+        <v>128080035</v>
       </c>
       <c r="B74" t="n">
         <v>57673</v>
@@ -7921,10 +7901,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>544295</v>
+        <v>544340</v>
       </c>
       <c r="R74" t="n">
-        <v>6963226</v>
+        <v>6963223</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7988,10 +7968,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128087537</v>
+        <v>128080054</v>
       </c>
       <c r="B75" t="n">
-        <v>80135</v>
+        <v>57673</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7999,34 +7979,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>544205</v>
+        <v>544301</v>
       </c>
       <c r="R75" t="n">
-        <v>6963241</v>
+        <v>6963231</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8059,6 +8044,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8085,10 +8075,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128087366</v>
+        <v>128080149</v>
       </c>
       <c r="B76" t="n">
-        <v>80135</v>
+        <v>57673</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8096,34 +8086,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>544407</v>
+        <v>544295</v>
       </c>
       <c r="R76" t="n">
-        <v>6963184</v>
+        <v>6963226</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8156,6 +8151,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -11379,45 +11379,49 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128087586</v>
+        <v>128079656</v>
       </c>
       <c r="B109" t="n">
-        <v>92650</v>
+        <v>98478</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>544281</v>
+        <v>544277</v>
       </c>
       <c r="R109" t="n">
-        <v>6963257</v>
+        <v>6963150</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11450,11 +11454,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>2 nya exemplar 8 äldre ex</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11481,32 +11480,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128087577</v>
+        <v>128087551</v>
       </c>
       <c r="B110" t="n">
-        <v>92682</v>
+        <v>98478</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1968</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11516,10 +11515,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>544494</v>
+        <v>544694</v>
       </c>
       <c r="R110" t="n">
-        <v>6963243</v>
+        <v>6963258</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11552,6 +11551,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11578,7 +11582,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128079656</v>
+        <v>128087565</v>
       </c>
       <c r="B111" t="n">
         <v>98478</v>
@@ -11606,21 +11610,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>544277</v>
+        <v>544249</v>
       </c>
       <c r="R111" t="n">
-        <v>6963150</v>
+        <v>6963223</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11653,6 +11653,11 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>10. Kan möjlitvis finns mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11679,7 +11684,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128087551</v>
+        <v>128087372</v>
       </c>
       <c r="B112" t="n">
         <v>98478</v>
@@ -11714,10 +11719,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>544694</v>
+        <v>544472</v>
       </c>
       <c r="R112" t="n">
-        <v>6963258</v>
+        <v>6963201</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11754,7 +11759,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11781,32 +11786,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128087565</v>
+        <v>128087577</v>
       </c>
       <c r="B113" t="n">
-        <v>98478</v>
+        <v>92682</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>220787</v>
+        <v>1968</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11816,10 +11821,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>544249</v>
+        <v>544494</v>
       </c>
       <c r="R113" t="n">
-        <v>6963223</v>
+        <v>6963243</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11852,11 +11857,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>10. Kan möjlitvis finns mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11883,10 +11883,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128087531</v>
+        <v>128087586</v>
       </c>
       <c r="B114" t="n">
-        <v>98512</v>
+        <v>92650</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11894,21 +11894,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>219874</v>
+        <v>4364</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11918,10 +11918,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>544755</v>
+        <v>544281</v>
       </c>
       <c r="R114" t="n">
-        <v>6963130</v>
+        <v>6963257</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11958,7 +11958,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>2 stycken</t>
+          <t>2 nya exemplar 8 äldre ex</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11985,32 +11985,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128087372</v>
+        <v>128087578</v>
       </c>
       <c r="B115" t="n">
-        <v>98478</v>
+        <v>79032</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12020,10 +12020,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>544472</v>
+        <v>544246</v>
       </c>
       <c r="R115" t="n">
-        <v>6963201</v>
+        <v>6963257</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12056,11 +12056,6 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>8 ex</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12087,32 +12082,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128087578</v>
+        <v>128087531</v>
       </c>
       <c r="B116" t="n">
-        <v>79032</v>
+        <v>98512</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>219874</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12122,10 +12117,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>544246</v>
+        <v>544755</v>
       </c>
       <c r="R116" t="n">
-        <v>6963257</v>
+        <v>6963130</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12158,6 +12153,11 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12184,32 +12184,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128079848</v>
+        <v>128087571</v>
       </c>
       <c r="B117" t="n">
-        <v>79056</v>
+        <v>92682</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6434</v>
+        <v>1968</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12219,10 +12219,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>544288</v>
+        <v>544679</v>
       </c>
       <c r="R117" t="n">
-        <v>6963182</v>
+        <v>6963259</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12255,6 +12255,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Misstänker grantaggsvamp. 14 exemplar</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12281,10 +12286,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128078823</v>
+        <v>128087573</v>
       </c>
       <c r="B118" t="n">
-        <v>79032</v>
+        <v>92682</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12292,21 +12297,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>1968</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12316,10 +12321,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>544307</v>
+        <v>544684</v>
       </c>
       <c r="R118" t="n">
-        <v>6963089</v>
+        <v>6963253</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12352,6 +12357,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Mörkt exemplar med vit yttre ring.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12378,32 +12388,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128087571</v>
+        <v>128079848</v>
       </c>
       <c r="B119" t="n">
-        <v>92682</v>
+        <v>79056</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1968</v>
+        <v>6434</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12413,10 +12423,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>544679</v>
+        <v>544288</v>
       </c>
       <c r="R119" t="n">
-        <v>6963259</v>
+        <v>6963182</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12449,11 +12459,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Misstänker grantaggsvamp. 14 exemplar</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12480,10 +12485,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128087573</v>
+        <v>128078823</v>
       </c>
       <c r="B120" t="n">
-        <v>92682</v>
+        <v>79032</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12491,21 +12496,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1968</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12515,10 +12520,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>544684</v>
+        <v>544307</v>
       </c>
       <c r="R120" t="n">
-        <v>6963253</v>
+        <v>6963089</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12551,11 +12556,6 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Mörkt exemplar med vit yttre ring.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12582,45 +12582,49 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128087535</v>
+        <v>128079571</v>
       </c>
       <c r="B121" t="n">
-        <v>80135</v>
+        <v>98478</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>544312</v>
+        <v>544274</v>
       </c>
       <c r="R121" t="n">
-        <v>6963244</v>
+        <v>6963119</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12679,45 +12683,49 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128087538</v>
+        <v>128078138</v>
       </c>
       <c r="B122" t="n">
-        <v>80135</v>
+        <v>98478</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>544262</v>
+        <v>544374</v>
       </c>
       <c r="R122" t="n">
-        <v>6963163</v>
+        <v>6963056</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12873,49 +12881,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128079571</v>
+        <v>128087535</v>
       </c>
       <c r="B124" t="n">
-        <v>98478</v>
+        <v>80135</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>544274</v>
+        <v>544312</v>
       </c>
       <c r="R124" t="n">
-        <v>6963119</v>
+        <v>6963244</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12974,49 +12978,45 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128078138</v>
+        <v>128087538</v>
       </c>
       <c r="B125" t="n">
-        <v>98478</v>
+        <v>80135</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>544374</v>
+        <v>544262</v>
       </c>
       <c r="R125" t="n">
-        <v>6963056</v>
+        <v>6963163</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14769,10 +14769,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128078685</v>
+        <v>128087368</v>
       </c>
       <c r="B143" t="n">
-        <v>56248</v>
+        <v>80135</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14780,39 +14780,34 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>206004</v>
+        <v>6458</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>544307</v>
+        <v>544314</v>
       </c>
       <c r="R143" t="n">
-        <v>6963069</v>
+        <v>6963248</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14871,45 +14866,49 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128087368</v>
+        <v>128078529</v>
       </c>
       <c r="B144" t="n">
-        <v>80135</v>
+        <v>98478</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>544314</v>
+        <v>544351</v>
       </c>
       <c r="R144" t="n">
-        <v>6963248</v>
+        <v>6963065</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14968,37 +14967,38 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128078529</v>
+        <v>128078685</v>
       </c>
       <c r="B145" t="n">
-        <v>98478</v>
+        <v>56248</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>220787</v>
+        <v>206004</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -15007,10 +15007,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>544351</v>
+        <v>544307</v>
       </c>
       <c r="R145" t="n">
-        <v>6963065</v>
+        <v>6963069</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15069,32 +15069,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128094046</v>
+        <v>128094035</v>
       </c>
       <c r="B146" t="n">
-        <v>98478</v>
+        <v>57673</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15104,10 +15104,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>544754</v>
+        <v>544736</v>
       </c>
       <c r="R146" t="n">
-        <v>6963261</v>
+        <v>6963232</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15144,7 +15144,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>25 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15171,32 +15171,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128094035</v>
+        <v>128094046</v>
       </c>
       <c r="B147" t="n">
-        <v>57673</v>
+        <v>98478</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15206,10 +15206,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>544736</v>
+        <v>544754</v>
       </c>
       <c r="R147" t="n">
-        <v>6963232</v>
+        <v>6963261</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15246,7 +15246,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD147" t="b">

--- a/artfynd/A 32240-2025 artfynd.xlsx
+++ b/artfynd/A 32240-2025 artfynd.xlsx
@@ -995,32 +995,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128087541</v>
+        <v>128087558</v>
       </c>
       <c r="B5" t="n">
-        <v>78790</v>
+        <v>98571</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544267</v>
+        <v>544428</v>
       </c>
       <c r="R5" t="n">
-        <v>6963196</v>
+        <v>6963233</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,6 +1066,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1092,32 +1097,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128087358</v>
+        <v>128087541</v>
       </c>
       <c r="B6" t="n">
-        <v>80163</v>
+        <v>78840</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1127,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544278</v>
+        <v>544267</v>
       </c>
       <c r="R6" t="n">
-        <v>6963265</v>
+        <v>6963196</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128087524</v>
+        <v>128087528</v>
       </c>
       <c r="B7" t="n">
-        <v>80164</v>
+        <v>80216</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1200,21 +1205,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1224,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544281</v>
+        <v>544198</v>
       </c>
       <c r="R7" t="n">
-        <v>6963082</v>
+        <v>6963228</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128087528</v>
+        <v>128087358</v>
       </c>
       <c r="B8" t="n">
-        <v>80163</v>
+        <v>80216</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1321,10 +1326,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544198</v>
+        <v>544278</v>
       </c>
       <c r="R8" t="n">
-        <v>6963228</v>
+        <v>6963265</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,32 +1388,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128087558</v>
+        <v>128087524</v>
       </c>
       <c r="B9" t="n">
-        <v>98478</v>
+        <v>80217</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1418,10 +1423,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544428</v>
+        <v>544281</v>
       </c>
       <c r="R9" t="n">
-        <v>6963233</v>
+        <v>6963082</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1454,11 +1459,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1488,7 +1488,7 @@
         <v>128078559</v>
       </c>
       <c r="B10" t="n">
-        <v>97355</v>
+        <v>97448</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>128087526</v>
       </c>
       <c r="B11" t="n">
-        <v>92642</v>
+        <v>92734</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>128087516</v>
       </c>
       <c r="B12" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1786,32 +1786,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128087347</v>
+        <v>128081639</v>
       </c>
       <c r="B13" t="n">
-        <v>80164</v>
+        <v>80189</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544745</v>
+        <v>544323</v>
       </c>
       <c r="R13" t="n">
-        <v>6963195</v>
+        <v>6963268</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1883,10 +1883,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128087323</v>
+        <v>128087324</v>
       </c>
       <c r="B14" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544646</v>
+        <v>544792</v>
       </c>
       <c r="R14" t="n">
-        <v>6963095</v>
+        <v>6963047</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1985,10 +1985,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128087324</v>
+        <v>128087323</v>
       </c>
       <c r="B15" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544792</v>
+        <v>544646</v>
       </c>
       <c r="R15" t="n">
-        <v>6963047</v>
+        <v>6963095</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2087,32 +2087,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128087520</v>
+        <v>128087347</v>
       </c>
       <c r="B16" t="n">
-        <v>57833</v>
+        <v>80217</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2122,10 +2122,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544771</v>
+        <v>544745</v>
       </c>
       <c r="R16" t="n">
-        <v>6963083</v>
+        <v>6963195</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2158,11 +2158,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>2 stycken.  Övriga läten</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2189,32 +2184,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128087550</v>
+        <v>128087520</v>
       </c>
       <c r="B17" t="n">
-        <v>98478</v>
+        <v>57845</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2224,10 +2219,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544490</v>
+        <v>544771</v>
       </c>
       <c r="R17" t="n">
-        <v>6963099</v>
+        <v>6963083</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2264,7 +2259,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2 stycken.  Övriga läten</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2291,32 +2286,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128081639</v>
+        <v>128087550</v>
       </c>
       <c r="B18" t="n">
-        <v>80136</v>
+        <v>98571</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2326,10 +2321,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544323</v>
+        <v>544490</v>
       </c>
       <c r="R18" t="n">
-        <v>6963268</v>
+        <v>6963099</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2362,6 +2357,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2388,10 +2388,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128087354</v>
+        <v>128087581</v>
       </c>
       <c r="B19" t="n">
-        <v>80136</v>
+        <v>79083</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2399,21 +2399,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2423,10 +2423,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544820</v>
+        <v>544192</v>
       </c>
       <c r="R19" t="n">
-        <v>6963278</v>
+        <v>6963197</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2485,10 +2485,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128087581</v>
+        <v>128087362</v>
       </c>
       <c r="B20" t="n">
-        <v>79032</v>
+        <v>80188</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2496,21 +2496,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544192</v>
+        <v>544799</v>
       </c>
       <c r="R20" t="n">
-        <v>6963197</v>
+        <v>6963263</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2585,7 +2585,7 @@
         <v>128087349</v>
       </c>
       <c r="B21" t="n">
-        <v>80164</v>
+        <v>80217</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2679,32 +2679,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128087362</v>
+        <v>128087569</v>
       </c>
       <c r="B22" t="n">
-        <v>80135</v>
+        <v>98571</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2714,10 +2714,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544799</v>
+        <v>544296</v>
       </c>
       <c r="R22" t="n">
-        <v>6963263</v>
+        <v>6963084</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2750,6 +2750,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>100stycken</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2776,10 +2781,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128087569</v>
+        <v>128087554</v>
       </c>
       <c r="B23" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2811,10 +2816,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544296</v>
+        <v>544659</v>
       </c>
       <c r="R23" t="n">
-        <v>6963084</v>
+        <v>6963253</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2851,7 +2856,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>100stycken</t>
+          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2878,32 +2883,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128087554</v>
+        <v>128087359</v>
       </c>
       <c r="B24" t="n">
-        <v>98478</v>
+        <v>78841</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2913,10 +2918,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544659</v>
+        <v>544741</v>
       </c>
       <c r="R24" t="n">
-        <v>6963253</v>
+        <v>6963165</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2949,11 +2954,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2980,10 +2980,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128087359</v>
+        <v>128087354</v>
       </c>
       <c r="B25" t="n">
-        <v>78791</v>
+        <v>80189</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2991,21 +2991,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544741</v>
+        <v>544820</v>
       </c>
       <c r="R25" t="n">
-        <v>6963165</v>
+        <v>6963278</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3077,49 +3077,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128078740</v>
+        <v>128087532</v>
       </c>
       <c r="B26" t="n">
-        <v>98478</v>
+        <v>80188</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>544307</v>
+        <v>544491</v>
       </c>
       <c r="R26" t="n">
-        <v>6963089</v>
+        <v>6963099</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3178,32 +3174,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128087563</v>
+        <v>128087382</v>
       </c>
       <c r="B27" t="n">
-        <v>98478</v>
+        <v>92742</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3213,10 +3209,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544322</v>
+        <v>544198</v>
       </c>
       <c r="R27" t="n">
-        <v>6963250</v>
+        <v>6963225</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3253,7 +3249,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>12 stycken</t>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3280,32 +3276,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128087562</v>
+        <v>128087333</v>
       </c>
       <c r="B28" t="n">
-        <v>98478</v>
+        <v>57685</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3315,10 +3311,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544367</v>
+        <v>544355</v>
       </c>
       <c r="R28" t="n">
-        <v>6963253</v>
+        <v>6963212</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3355,7 +3351,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>7. Kan möjlitvis finnas fler runt omkring.</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3382,49 +3378,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128078161</v>
+        <v>128087331</v>
       </c>
       <c r="B29" t="n">
-        <v>98478</v>
+        <v>57685</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544362</v>
+        <v>544763</v>
       </c>
       <c r="R29" t="n">
-        <v>6963061</v>
+        <v>6963244</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3457,6 +3449,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3483,32 +3480,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128087331</v>
+        <v>128087562</v>
       </c>
       <c r="B30" t="n">
-        <v>57673</v>
+        <v>98571</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3518,10 +3515,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>544763</v>
+        <v>544367</v>
       </c>
       <c r="R30" t="n">
-        <v>6963244</v>
+        <v>6963253</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3558,7 +3555,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>7. Kan möjlitvis finnas fler runt omkring.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3585,45 +3582,49 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128087333</v>
+        <v>128078161</v>
       </c>
       <c r="B31" t="n">
-        <v>57673</v>
+        <v>98571</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>544355</v>
+        <v>544362</v>
       </c>
       <c r="R31" t="n">
-        <v>6963212</v>
+        <v>6963061</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3656,11 +3657,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3687,45 +3683,49 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128087382</v>
+        <v>128078740</v>
       </c>
       <c r="B32" t="n">
-        <v>92650</v>
+        <v>98571</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544198</v>
+        <v>544307</v>
       </c>
       <c r="R32" t="n">
-        <v>6963225</v>
+        <v>6963089</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3758,11 +3758,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>5 ex</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3789,32 +3784,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128087532</v>
+        <v>128087563</v>
       </c>
       <c r="B33" t="n">
-        <v>80135</v>
+        <v>98571</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3824,10 +3819,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>544491</v>
+        <v>544322</v>
       </c>
       <c r="R33" t="n">
-        <v>6963099</v>
+        <v>6963250</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3860,6 +3855,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>12 stycken</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3886,10 +3886,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128087336</v>
+        <v>128079621</v>
       </c>
       <c r="B34" t="n">
-        <v>57673</v>
+        <v>80188</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3897,21 +3897,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3921,10 +3921,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>544398</v>
+        <v>544274</v>
       </c>
       <c r="R34" t="n">
-        <v>6963202</v>
+        <v>6963119</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3957,11 +3957,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3988,32 +3983,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128087351</v>
+        <v>128087533</v>
       </c>
       <c r="B35" t="n">
-        <v>80164</v>
+        <v>80188</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4023,10 +4018,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>544299</v>
+        <v>544473</v>
       </c>
       <c r="R35" t="n">
-        <v>6963312</v>
+        <v>6963102</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4085,32 +4080,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128087365</v>
+        <v>128087351</v>
       </c>
       <c r="B36" t="n">
-        <v>80135</v>
+        <v>80217</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4120,10 +4115,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>544469</v>
+        <v>544299</v>
       </c>
       <c r="R36" t="n">
-        <v>6963145</v>
+        <v>6963312</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4182,10 +4177,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128079621</v>
+        <v>128087365</v>
       </c>
       <c r="B37" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4217,10 +4212,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>544274</v>
+        <v>544469</v>
       </c>
       <c r="R37" t="n">
-        <v>6963119</v>
+        <v>6963145</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4279,10 +4274,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128087533</v>
+        <v>128087336</v>
       </c>
       <c r="B38" t="n">
-        <v>80135</v>
+        <v>57685</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4290,21 +4285,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4314,10 +4309,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>544473</v>
+        <v>544398</v>
       </c>
       <c r="R38" t="n">
-        <v>6963102</v>
+        <v>6963202</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4350,6 +4345,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4376,10 +4376,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128087588</v>
+        <v>128087527</v>
       </c>
       <c r="B39" t="n">
-        <v>92650</v>
+        <v>80216</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4387,21 +4387,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>6461</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>544183</v>
+        <v>544246</v>
       </c>
       <c r="R39" t="n">
-        <v>6963214</v>
+        <v>6963259</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4447,11 +4447,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>9 ex äldre exemplar</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4478,10 +4473,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128087527</v>
+        <v>128087369</v>
       </c>
       <c r="B40" t="n">
-        <v>80163</v>
+        <v>80224</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4489,21 +4484,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6461</v>
+        <v>6464</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4513,10 +4508,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>544246</v>
+        <v>544721</v>
       </c>
       <c r="R40" t="n">
-        <v>6963259</v>
+        <v>6963277</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4575,10 +4570,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128087369</v>
+        <v>128087588</v>
       </c>
       <c r="B41" t="n">
-        <v>80171</v>
+        <v>92742</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4586,21 +4581,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4610,10 +4605,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>544721</v>
+        <v>544183</v>
       </c>
       <c r="R41" t="n">
-        <v>6963277</v>
+        <v>6963214</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4646,6 +4641,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>9 ex äldre exemplar</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4675,7 +4675,7 @@
         <v>128087332</v>
       </c>
       <c r="B42" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4777,7 +4777,7 @@
         <v>128087517</v>
       </c>
       <c r="B43" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         <v>128079768</v>
       </c>
       <c r="B44" t="n">
-        <v>97361</v>
+        <v>97454</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4973,32 +4973,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128087552</v>
+        <v>128087340</v>
       </c>
       <c r="B45" t="n">
-        <v>98478</v>
+        <v>57845</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5008,10 +5008,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>544687</v>
+        <v>544485</v>
       </c>
       <c r="R45" t="n">
-        <v>6963255</v>
+        <v>6963237</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5044,11 +5044,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>70</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5075,10 +5070,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128087548</v>
+        <v>128087552</v>
       </c>
       <c r="B46" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5110,10 +5105,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>544213</v>
+        <v>544687</v>
       </c>
       <c r="R46" t="n">
-        <v>6963197</v>
+        <v>6963255</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5150,7 +5145,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>100stycken.</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5177,32 +5172,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128087361</v>
+        <v>128087548</v>
       </c>
       <c r="B47" t="n">
-        <v>80135</v>
+        <v>98571</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5212,10 +5207,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>544865</v>
+        <v>544213</v>
       </c>
       <c r="R47" t="n">
-        <v>6963092</v>
+        <v>6963197</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5248,6 +5243,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>100stycken.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5274,10 +5274,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128087360</v>
+        <v>128087361</v>
       </c>
       <c r="B48" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5309,10 +5309,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>544615</v>
+        <v>544865</v>
       </c>
       <c r="R48" t="n">
-        <v>6963093</v>
+        <v>6963092</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5371,10 +5371,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128087340</v>
+        <v>128087360</v>
       </c>
       <c r="B49" t="n">
-        <v>57833</v>
+        <v>80188</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5382,21 +5382,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>544485</v>
+        <v>544615</v>
       </c>
       <c r="R49" t="n">
-        <v>6963237</v>
+        <v>6963093</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5468,32 +5468,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128087553</v>
+        <v>128087342</v>
       </c>
       <c r="B50" t="n">
-        <v>98478</v>
+        <v>80217</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5503,10 +5503,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>544677</v>
+        <v>544848</v>
       </c>
       <c r="R50" t="n">
-        <v>6963260</v>
+        <v>6963086</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5539,11 +5539,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Mer än 70 stycken. Flera blommar</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5570,32 +5565,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128087555</v>
+        <v>128087367</v>
       </c>
       <c r="B51" t="n">
-        <v>98478</v>
+        <v>80188</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5605,10 +5600,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>544623</v>
+        <v>544298</v>
       </c>
       <c r="R51" t="n">
-        <v>6963241</v>
+        <v>6963312</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5641,11 +5636,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>60 stycken</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5672,32 +5662,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128079839</v>
+        <v>128087364</v>
       </c>
       <c r="B52" t="n">
-        <v>105516</v>
+        <v>80188</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221144</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5707,10 +5697,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>544288</v>
+        <v>544774</v>
       </c>
       <c r="R52" t="n">
-        <v>6963182</v>
+        <v>6963282</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5769,10 +5759,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128087364</v>
+        <v>128087339</v>
       </c>
       <c r="B53" t="n">
-        <v>80135</v>
+        <v>57845</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5780,21 +5770,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5804,10 +5794,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>544774</v>
+        <v>544850</v>
       </c>
       <c r="R53" t="n">
-        <v>6963282</v>
+        <v>6963099</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5840,6 +5830,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5866,10 +5861,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128087342</v>
+        <v>128079839</v>
       </c>
       <c r="B54" t="n">
-        <v>80164</v>
+        <v>105609</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5877,21 +5872,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6462</v>
+        <v>221144</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5901,10 +5896,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>544848</v>
+        <v>544288</v>
       </c>
       <c r="R54" t="n">
-        <v>6963086</v>
+        <v>6963182</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5963,32 +5958,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128087367</v>
+        <v>128087553</v>
       </c>
       <c r="B55" t="n">
-        <v>80135</v>
+        <v>98571</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5998,10 +5993,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>544298</v>
+        <v>544677</v>
       </c>
       <c r="R55" t="n">
-        <v>6963312</v>
+        <v>6963260</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6034,6 +6029,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Mer än 70 stycken. Flera blommar</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6060,32 +6060,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128087339</v>
+        <v>128087555</v>
       </c>
       <c r="B56" t="n">
-        <v>57833</v>
+        <v>98571</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>544850</v>
+        <v>544623</v>
       </c>
       <c r="R56" t="n">
-        <v>6963099</v>
+        <v>6963241</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Lockläte/övriga läten</t>
+          <t>60 stycken</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6162,45 +6162,50 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128087585</v>
+        <v>128080012</v>
       </c>
       <c r="B57" t="n">
-        <v>92650</v>
+        <v>57685</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>544536</v>
+        <v>544324</v>
       </c>
       <c r="R57" t="n">
-        <v>6963255</v>
+        <v>6963220</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6237,7 +6242,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>8 äldre ex9 färska fruktkroppar</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6264,10 +6269,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128087357</v>
+        <v>128087585</v>
       </c>
       <c r="B58" t="n">
-        <v>80163</v>
+        <v>92742</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6275,21 +6280,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6461</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6299,10 +6304,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>544466</v>
+        <v>544536</v>
       </c>
       <c r="R58" t="n">
-        <v>6963277</v>
+        <v>6963255</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6335,6 +6340,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>8 äldre ex9 färska fruktkroppar</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6364,7 +6374,7 @@
         <v>128087356</v>
       </c>
       <c r="B59" t="n">
-        <v>80163</v>
+        <v>80216</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6458,50 +6468,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128080012</v>
+        <v>128087357</v>
       </c>
       <c r="B60" t="n">
-        <v>57673</v>
+        <v>80216</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>544324</v>
+        <v>544466</v>
       </c>
       <c r="R60" t="n">
-        <v>6963220</v>
+        <v>6963277</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6534,11 +6539,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6565,32 +6565,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128087525</v>
+        <v>128078603</v>
       </c>
       <c r="B61" t="n">
-        <v>56248</v>
+        <v>80217</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>206004</v>
+        <v>6462</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6600,10 +6600,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>544385</v>
+        <v>544360</v>
       </c>
       <c r="R61" t="n">
-        <v>6963074</v>
+        <v>6963094</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6662,32 +6662,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128087375</v>
+        <v>128087523</v>
       </c>
       <c r="B62" t="n">
-        <v>98478</v>
+        <v>80217</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6697,10 +6697,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>544478</v>
+        <v>544253</v>
       </c>
       <c r="R62" t="n">
-        <v>6963117</v>
+        <v>6963139</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6733,11 +6733,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>35 ex</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6764,32 +6759,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128087566</v>
+        <v>128087579</v>
       </c>
       <c r="B63" t="n">
-        <v>98478</v>
+        <v>79083</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6799,10 +6794,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>544261</v>
+        <v>544204</v>
       </c>
       <c r="R63" t="n">
-        <v>6963170</v>
+        <v>6963238</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6839,7 +6834,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>4. Stycken. Finns möjligtvis fler i blåbärsriset.</t>
+          <t>Riklig förekomst av garnlav</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6866,32 +6861,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128087378</v>
+        <v>128087386</v>
       </c>
       <c r="B64" t="n">
-        <v>98478</v>
+        <v>92736</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>4362</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6901,10 +6896,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>544218</v>
+        <v>544822</v>
       </c>
       <c r="R64" t="n">
-        <v>6963229</v>
+        <v>6963295</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6937,11 +6932,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>80 ex</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6968,32 +6958,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128087377</v>
+        <v>128087329</v>
       </c>
       <c r="B65" t="n">
-        <v>98478</v>
+        <v>57685</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7003,10 +6993,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>544403</v>
+        <v>544757</v>
       </c>
       <c r="R65" t="n">
-        <v>6963221</v>
+        <v>6963172</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7043,7 +7033,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>20 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7070,10 +7060,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128087386</v>
+        <v>128087525</v>
       </c>
       <c r="B66" t="n">
-        <v>92644</v>
+        <v>56260</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7081,21 +7071,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4362</v>
+        <v>206004</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7105,10 +7095,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>544822</v>
+        <v>544385</v>
       </c>
       <c r="R66" t="n">
-        <v>6963295</v>
+        <v>6963074</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7167,32 +7157,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128087579</v>
+        <v>128087566</v>
       </c>
       <c r="B67" t="n">
-        <v>79032</v>
+        <v>98571</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7202,10 +7192,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>544204</v>
+        <v>544261</v>
       </c>
       <c r="R67" t="n">
-        <v>6963238</v>
+        <v>6963170</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7242,7 +7232,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Riklig förekomst av garnlav</t>
+          <t>4. Stycken. Finns möjligtvis fler i blåbärsriset.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7269,32 +7259,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128087523</v>
+        <v>128087377</v>
       </c>
       <c r="B68" t="n">
-        <v>80164</v>
+        <v>98571</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7304,10 +7294,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>544253</v>
+        <v>544403</v>
       </c>
       <c r="R68" t="n">
-        <v>6963139</v>
+        <v>6963221</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7340,6 +7330,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7366,32 +7361,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128078603</v>
+        <v>128087378</v>
       </c>
       <c r="B69" t="n">
-        <v>80164</v>
+        <v>98571</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7401,10 +7396,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>544360</v>
+        <v>544218</v>
       </c>
       <c r="R69" t="n">
-        <v>6963094</v>
+        <v>6963229</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7437,6 +7432,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7463,32 +7463,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128087329</v>
+        <v>128087375</v>
       </c>
       <c r="B70" t="n">
-        <v>57673</v>
+        <v>98571</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7498,10 +7498,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>544757</v>
+        <v>544478</v>
       </c>
       <c r="R70" t="n">
-        <v>6963172</v>
+        <v>6963117</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7565,10 +7565,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128087537</v>
+        <v>128087366</v>
       </c>
       <c r="B71" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7600,10 +7600,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>544205</v>
+        <v>544407</v>
       </c>
       <c r="R71" t="n">
-        <v>6963241</v>
+        <v>6963184</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7662,10 +7662,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128087366</v>
+        <v>128087537</v>
       </c>
       <c r="B72" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7697,10 +7697,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>544407</v>
+        <v>544205</v>
       </c>
       <c r="R72" t="n">
-        <v>6963184</v>
+        <v>6963241</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7759,10 +7759,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128087337</v>
+        <v>128080054</v>
       </c>
       <c r="B73" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7788,16 +7788,21 @@
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>544197</v>
+        <v>544301</v>
       </c>
       <c r="R73" t="n">
-        <v>6963237</v>
+        <v>6963231</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7834,7 +7839,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7864,7 +7869,7 @@
         <v>128080035</v>
       </c>
       <c r="B74" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7968,10 +7973,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128080054</v>
+        <v>128080149</v>
       </c>
       <c r="B75" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8008,10 +8013,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>544301</v>
+        <v>544295</v>
       </c>
       <c r="R75" t="n">
-        <v>6963231</v>
+        <v>6963226</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8075,10 +8080,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128080149</v>
+        <v>128087337</v>
       </c>
       <c r="B76" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8104,21 +8109,16 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>544295</v>
+        <v>544197</v>
       </c>
       <c r="R76" t="n">
-        <v>6963226</v>
+        <v>6963237</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8155,7 +8155,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8185,7 +8185,7 @@
         <v>128087575</v>
       </c>
       <c r="B77" t="n">
-        <v>92682</v>
+        <v>92774</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8287,7 +8287,7 @@
         <v>128078492</v>
       </c>
       <c r="B78" t="n">
-        <v>92682</v>
+        <v>92774</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8381,45 +8381,49 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128087343</v>
+        <v>128079875</v>
       </c>
       <c r="B79" t="n">
-        <v>80164</v>
+        <v>98571</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>544757</v>
+        <v>544308</v>
       </c>
       <c r="R79" t="n">
-        <v>6963156</v>
+        <v>6963175</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8478,32 +8482,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128087536</v>
+        <v>128087542</v>
       </c>
       <c r="B80" t="n">
-        <v>80135</v>
+        <v>98571</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8513,10 +8517,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>544215</v>
+        <v>544752</v>
       </c>
       <c r="R80" t="n">
-        <v>6963245</v>
+        <v>6963192</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8549,6 +8553,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8575,45 +8584,49 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128087346</v>
+        <v>128080338</v>
       </c>
       <c r="B81" t="n">
-        <v>80164</v>
+        <v>98571</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>544422</v>
+        <v>544314</v>
       </c>
       <c r="R81" t="n">
-        <v>6963240</v>
+        <v>6963248</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8672,32 +8685,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128087570</v>
+        <v>128087547</v>
       </c>
       <c r="B82" t="n">
-        <v>56855</v>
+        <v>98571</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8707,10 +8720,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>544287</v>
+        <v>544380</v>
       </c>
       <c r="R82" t="n">
-        <v>6963082</v>
+        <v>6963236</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8747,7 +8760,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Fjäder</t>
+          <t>33 stycken</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8774,32 +8787,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128087330</v>
+        <v>128087380</v>
       </c>
       <c r="B83" t="n">
-        <v>57673</v>
+        <v>105609</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8809,10 +8822,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>544750</v>
+        <v>544468</v>
       </c>
       <c r="R83" t="n">
-        <v>6963177</v>
+        <v>6963173</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8845,11 +8858,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8876,32 +8884,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128087335</v>
+        <v>128087560</v>
       </c>
       <c r="B84" t="n">
-        <v>57673</v>
+        <v>98571</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8911,10 +8919,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>544366</v>
+        <v>544383</v>
       </c>
       <c r="R84" t="n">
-        <v>6963181</v>
+        <v>6963236</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8951,7 +8959,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8978,32 +8986,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128087547</v>
+        <v>128087536</v>
       </c>
       <c r="B85" t="n">
-        <v>98478</v>
+        <v>80188</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9013,10 +9021,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>544380</v>
+        <v>544215</v>
       </c>
       <c r="R85" t="n">
-        <v>6963236</v>
+        <v>6963245</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9049,11 +9057,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>33 stycken</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9080,32 +9083,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128087560</v>
+        <v>128087343</v>
       </c>
       <c r="B86" t="n">
-        <v>98478</v>
+        <v>80217</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9115,10 +9118,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>544383</v>
+        <v>544757</v>
       </c>
       <c r="R86" t="n">
-        <v>6963236</v>
+        <v>6963156</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9151,11 +9154,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9182,32 +9180,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128087542</v>
+        <v>128087346</v>
       </c>
       <c r="B87" t="n">
-        <v>98478</v>
+        <v>80217</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9217,10 +9215,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>544752</v>
+        <v>544422</v>
       </c>
       <c r="R87" t="n">
-        <v>6963192</v>
+        <v>6963240</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9253,11 +9251,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9284,49 +9277,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128079875</v>
+        <v>128087335</v>
       </c>
       <c r="B88" t="n">
-        <v>98478</v>
+        <v>57685</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>544308</v>
+        <v>544366</v>
       </c>
       <c r="R88" t="n">
-        <v>6963175</v>
+        <v>6963181</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9359,6 +9348,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9385,32 +9379,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128087380</v>
+        <v>128087330</v>
       </c>
       <c r="B89" t="n">
-        <v>105516</v>
+        <v>57685</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221144</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9420,10 +9414,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>544468</v>
+        <v>544750</v>
       </c>
       <c r="R89" t="n">
-        <v>6963173</v>
+        <v>6963177</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9456,6 +9450,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9482,49 +9481,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128080338</v>
+        <v>128087570</v>
       </c>
       <c r="B90" t="n">
-        <v>98478</v>
+        <v>56867</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>544314</v>
+        <v>544287</v>
       </c>
       <c r="R90" t="n">
-        <v>6963248</v>
+        <v>6963082</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9557,6 +9552,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9586,7 +9586,7 @@
         <v>128087587</v>
       </c>
       <c r="B91" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>128087539</v>
       </c>
       <c r="B92" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         <v>128087341</v>
       </c>
       <c r="B93" t="n">
-        <v>80164</v>
+        <v>80217</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9879,10 +9879,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128087379</v>
+        <v>128087376</v>
       </c>
       <c r="B94" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9914,10 +9914,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>544263</v>
+        <v>544503</v>
       </c>
       <c r="R94" t="n">
-        <v>6963254</v>
+        <v>6963182</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9954,7 +9954,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>15 ex</t>
+          <t>60 ex</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9981,10 +9981,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128087376</v>
+        <v>128087379</v>
       </c>
       <c r="B95" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10016,10 +10016,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>544503</v>
+        <v>544263</v>
       </c>
       <c r="R95" t="n">
-        <v>6963182</v>
+        <v>6963254</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10056,7 +10056,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>60 ex</t>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10083,10 +10083,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128087576</v>
+        <v>128087522</v>
       </c>
       <c r="B96" t="n">
-        <v>92682</v>
+        <v>57845</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10094,21 +10094,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1968</v>
+        <v>103021</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10118,10 +10118,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>544529</v>
+        <v>544494</v>
       </c>
       <c r="R96" t="n">
-        <v>6963245</v>
+        <v>6963243</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10154,11 +10154,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Misstänkt grantaggsvamp men med mörk tydlig ring i mitten.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10185,32 +10180,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128087572</v>
+        <v>128087545</v>
       </c>
       <c r="B97" t="n">
-        <v>92682</v>
+        <v>98571</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1968</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10220,10 +10215,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>544632</v>
+        <v>544633</v>
       </c>
       <c r="R97" t="n">
-        <v>6963245</v>
+        <v>6963244</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10260,7 +10255,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>1 ex</t>
+          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10287,32 +10282,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128087384</v>
+        <v>128087567</v>
       </c>
       <c r="B98" t="n">
-        <v>80170</v>
+        <v>98571</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10322,10 +10317,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>544584</v>
+        <v>544274</v>
       </c>
       <c r="R98" t="n">
-        <v>6963261</v>
+        <v>6963090</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10358,6 +10353,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>110</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10384,32 +10384,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128087383</v>
+        <v>128087556</v>
       </c>
       <c r="B99" t="n">
-        <v>80170</v>
+        <v>98571</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10419,10 +10419,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>544566</v>
+        <v>544594</v>
       </c>
       <c r="R99" t="n">
-        <v>6963076</v>
+        <v>6963215</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10455,6 +10455,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>6 stycken. Kan finnas mer i omgivningen</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10481,32 +10486,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128087363</v>
+        <v>128087373</v>
       </c>
       <c r="B100" t="n">
-        <v>80135</v>
+        <v>98571</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10516,10 +10521,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>544818</v>
+        <v>544469</v>
       </c>
       <c r="R100" t="n">
-        <v>6963278</v>
+        <v>6963122</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10552,6 +10557,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>60 ex</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10578,32 +10588,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128087522</v>
+        <v>128078864</v>
       </c>
       <c r="B101" t="n">
-        <v>57833</v>
+        <v>105609</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10613,10 +10623,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>544494</v>
+        <v>544307</v>
       </c>
       <c r="R101" t="n">
-        <v>6963243</v>
+        <v>6963089</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10675,32 +10685,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128087355</v>
+        <v>128087559</v>
       </c>
       <c r="B102" t="n">
-        <v>97361</v>
+        <v>98571</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10710,10 +10720,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>544500</v>
+        <v>544396</v>
       </c>
       <c r="R102" t="n">
-        <v>6963168</v>
+        <v>6963233</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10746,6 +10756,11 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10772,10 +10787,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128078864</v>
+        <v>128087355</v>
       </c>
       <c r="B103" t="n">
-        <v>105516</v>
+        <v>97454</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10783,21 +10798,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>221144</v>
+        <v>221941</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10807,10 +10822,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>544307</v>
+        <v>544500</v>
       </c>
       <c r="R103" t="n">
-        <v>6963089</v>
+        <v>6963168</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10869,32 +10884,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128087556</v>
+        <v>128087576</v>
       </c>
       <c r="B104" t="n">
-        <v>98478</v>
+        <v>92774</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>1968</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10904,10 +10919,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>544594</v>
+        <v>544529</v>
       </c>
       <c r="R104" t="n">
-        <v>6963215</v>
+        <v>6963245</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10944,7 +10959,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>6 stycken. Kan finnas mer i omgivningen</t>
+          <t>Misstänkt grantaggsvamp men med mörk tydlig ring i mitten.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10971,32 +10986,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128087567</v>
+        <v>128087572</v>
       </c>
       <c r="B105" t="n">
-        <v>98478</v>
+        <v>92774</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>1968</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11006,10 +11021,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>544274</v>
+        <v>544632</v>
       </c>
       <c r="R105" t="n">
-        <v>6963090</v>
+        <v>6963245</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11046,7 +11061,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>1 ex</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11073,32 +11088,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128087545</v>
+        <v>128087384</v>
       </c>
       <c r="B106" t="n">
-        <v>98478</v>
+        <v>80223</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11108,10 +11123,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>544633</v>
+        <v>544584</v>
       </c>
       <c r="R106" t="n">
-        <v>6963244</v>
+        <v>6963261</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11144,11 +11159,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11175,32 +11185,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128087559</v>
+        <v>128087383</v>
       </c>
       <c r="B107" t="n">
-        <v>98478</v>
+        <v>80223</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11210,10 +11220,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>544396</v>
+        <v>544566</v>
       </c>
       <c r="R107" t="n">
-        <v>6963233</v>
+        <v>6963076</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11246,11 +11256,6 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11277,32 +11282,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128087373</v>
+        <v>128087363</v>
       </c>
       <c r="B108" t="n">
-        <v>98478</v>
+        <v>80188</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11312,10 +11317,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>544469</v>
+        <v>544818</v>
       </c>
       <c r="R108" t="n">
-        <v>6963122</v>
+        <v>6963278</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11348,11 +11353,6 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>60 ex</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11379,49 +11379,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128079656</v>
+        <v>128087586</v>
       </c>
       <c r="B109" t="n">
-        <v>98478</v>
+        <v>92742</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>544277</v>
+        <v>544281</v>
       </c>
       <c r="R109" t="n">
-        <v>6963150</v>
+        <v>6963257</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11454,6 +11450,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>2 nya exemplar 8 äldre ex</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11480,32 +11481,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128087551</v>
+        <v>128087577</v>
       </c>
       <c r="B110" t="n">
-        <v>98478</v>
+        <v>92774</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>1968</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11515,10 +11516,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>544694</v>
+        <v>544494</v>
       </c>
       <c r="R110" t="n">
-        <v>6963258</v>
+        <v>6963243</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11551,11 +11552,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11582,32 +11578,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128087565</v>
+        <v>128087578</v>
       </c>
       <c r="B111" t="n">
-        <v>98478</v>
+        <v>79083</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11617,10 +11613,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>544249</v>
+        <v>544246</v>
       </c>
       <c r="R111" t="n">
-        <v>6963223</v>
+        <v>6963257</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11653,11 +11649,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>10. Kan möjlitvis finns mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11684,32 +11675,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128087372</v>
+        <v>128087531</v>
       </c>
       <c r="B112" t="n">
-        <v>98478</v>
+        <v>98605</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11719,10 +11710,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>544472</v>
+        <v>544755</v>
       </c>
       <c r="R112" t="n">
-        <v>6963201</v>
+        <v>6963130</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11759,7 +11750,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>8 ex</t>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11786,45 +11777,49 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128087577</v>
+        <v>128079656</v>
       </c>
       <c r="B113" t="n">
-        <v>92682</v>
+        <v>98571</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1968</v>
+        <v>220787</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>544494</v>
+        <v>544277</v>
       </c>
       <c r="R113" t="n">
-        <v>6963243</v>
+        <v>6963150</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11883,32 +11878,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128087586</v>
+        <v>128087565</v>
       </c>
       <c r="B114" t="n">
-        <v>92650</v>
+        <v>98571</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11918,10 +11913,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>544281</v>
+        <v>544249</v>
       </c>
       <c r="R114" t="n">
-        <v>6963257</v>
+        <v>6963223</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11958,7 +11953,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>2 nya exemplar 8 äldre ex</t>
+          <t>10. Kan möjlitvis finns mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11985,32 +11980,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128087578</v>
+        <v>128087372</v>
       </c>
       <c r="B115" t="n">
-        <v>79032</v>
+        <v>98571</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12020,10 +12015,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>544246</v>
+        <v>544472</v>
       </c>
       <c r="R115" t="n">
-        <v>6963257</v>
+        <v>6963201</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12056,6 +12051,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12082,32 +12082,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128087531</v>
+        <v>128087551</v>
       </c>
       <c r="B116" t="n">
-        <v>98512</v>
+        <v>98571</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12117,10 +12117,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>544755</v>
+        <v>544694</v>
       </c>
       <c r="R116" t="n">
-        <v>6963130</v>
+        <v>6963258</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12157,7 +12157,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>2 stycken</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12187,7 +12187,7 @@
         <v>128087571</v>
       </c>
       <c r="B117" t="n">
-        <v>92682</v>
+        <v>92774</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>128087573</v>
       </c>
       <c r="B118" t="n">
-        <v>92682</v>
+        <v>92774</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
         <v>128079848</v>
       </c>
       <c r="B119" t="n">
-        <v>79056</v>
+        <v>79107</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12485,10 +12485,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128078823</v>
+        <v>128087538</v>
       </c>
       <c r="B120" t="n">
-        <v>79032</v>
+        <v>80188</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12496,21 +12496,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12520,10 +12520,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>544307</v>
+        <v>544262</v>
       </c>
       <c r="R120" t="n">
-        <v>6963089</v>
+        <v>6963163</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12582,49 +12582,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128079571</v>
+        <v>128087535</v>
       </c>
       <c r="B121" t="n">
-        <v>98478</v>
+        <v>80188</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>544274</v>
+        <v>544312</v>
       </c>
       <c r="R121" t="n">
-        <v>6963119</v>
+        <v>6963244</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12683,49 +12679,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128078138</v>
+        <v>128078823</v>
       </c>
       <c r="B122" t="n">
-        <v>98478</v>
+        <v>79083</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>544374</v>
+        <v>544307</v>
       </c>
       <c r="R122" t="n">
-        <v>6963056</v>
+        <v>6963089</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12787,7 +12779,7 @@
         <v>128087582</v>
       </c>
       <c r="B123" t="n">
-        <v>98395</v>
+        <v>98488</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12881,45 +12873,49 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128087535</v>
+        <v>128079571</v>
       </c>
       <c r="B124" t="n">
-        <v>80135</v>
+        <v>98571</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>544312</v>
+        <v>544274</v>
       </c>
       <c r="R124" t="n">
-        <v>6963244</v>
+        <v>6963119</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12978,45 +12974,49 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128087538</v>
+        <v>128078138</v>
       </c>
       <c r="B125" t="n">
-        <v>80135</v>
+        <v>98571</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>544262</v>
+        <v>544374</v>
       </c>
       <c r="R125" t="n">
-        <v>6963163</v>
+        <v>6963056</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13078,7 +13078,7 @@
         <v>128079484</v>
       </c>
       <c r="B126" t="n">
-        <v>80171</v>
+        <v>80224</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>128087334</v>
       </c>
       <c r="B127" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13277,7 +13277,7 @@
         <v>128087574</v>
       </c>
       <c r="B128" t="n">
-        <v>92682</v>
+        <v>92774</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13376,10 +13376,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128087583</v>
+        <v>128087584</v>
       </c>
       <c r="B129" t="n">
-        <v>98395</v>
+        <v>98488</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13411,10 +13411,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>544708</v>
+        <v>544718</v>
       </c>
       <c r="R129" t="n">
-        <v>6963086</v>
+        <v>6963053</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13451,7 +13451,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3 stycken</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13478,10 +13478,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128087584</v>
+        <v>128087583</v>
       </c>
       <c r="B130" t="n">
-        <v>98395</v>
+        <v>98488</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13513,10 +13513,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>544718</v>
+        <v>544708</v>
       </c>
       <c r="R130" t="n">
-        <v>6963053</v>
+        <v>6963086</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13553,7 +13553,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>3 stycken</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13583,7 +13583,7 @@
         <v>128087370</v>
       </c>
       <c r="B131" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13685,7 +13685,7 @@
         <v>128087371</v>
       </c>
       <c r="B132" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13784,32 +13784,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128087344</v>
+        <v>128087328</v>
       </c>
       <c r="B133" t="n">
-        <v>80164</v>
+        <v>57685</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13819,10 +13819,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>544581</v>
+        <v>544736</v>
       </c>
       <c r="R133" t="n">
-        <v>6963278</v>
+        <v>6963153</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13855,6 +13855,11 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -13881,32 +13886,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128078645</v>
+        <v>128087381</v>
       </c>
       <c r="B134" t="n">
-        <v>80135</v>
+        <v>98488</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13916,10 +13921,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>544360</v>
+        <v>544531</v>
       </c>
       <c r="R134" t="n">
-        <v>6963094</v>
+        <v>6963190</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13978,32 +13983,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128087540</v>
+        <v>128087530</v>
       </c>
       <c r="B135" t="n">
-        <v>80135</v>
+        <v>98605</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6458</v>
+        <v>219874</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14013,10 +14018,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>544282</v>
+        <v>544737</v>
       </c>
       <c r="R135" t="n">
-        <v>6963082</v>
+        <v>6963047</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14075,32 +14080,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128087345</v>
+        <v>128087557</v>
       </c>
       <c r="B136" t="n">
-        <v>80164</v>
+        <v>98571</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14110,10 +14115,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>544391</v>
+        <v>544552</v>
       </c>
       <c r="R136" t="n">
-        <v>6963205</v>
+        <v>6963231</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14146,6 +14151,11 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14172,32 +14182,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128087534</v>
+        <v>128087543</v>
       </c>
       <c r="B137" t="n">
-        <v>80135</v>
+        <v>98571</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14207,10 +14217,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>544326</v>
+        <v>544674</v>
       </c>
       <c r="R137" t="n">
-        <v>6963248</v>
+        <v>6963243</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14243,6 +14253,11 @@
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14269,10 +14284,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128087328</v>
+        <v>128078645</v>
       </c>
       <c r="B138" t="n">
-        <v>57673</v>
+        <v>80188</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14280,21 +14295,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14304,10 +14319,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>544736</v>
+        <v>544360</v>
       </c>
       <c r="R138" t="n">
-        <v>6963153</v>
+        <v>6963094</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14340,11 +14355,6 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14371,10 +14381,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128087530</v>
+        <v>128087344</v>
       </c>
       <c r="B139" t="n">
-        <v>98512</v>
+        <v>80217</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14382,21 +14392,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>219874</v>
+        <v>6462</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14406,10 +14416,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>544737</v>
+        <v>544581</v>
       </c>
       <c r="R139" t="n">
-        <v>6963047</v>
+        <v>6963278</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14468,32 +14478,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128087381</v>
+        <v>128087534</v>
       </c>
       <c r="B140" t="n">
-        <v>98395</v>
+        <v>80188</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14503,10 +14513,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>544531</v>
+        <v>544326</v>
       </c>
       <c r="R140" t="n">
-        <v>6963190</v>
+        <v>6963248</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14565,32 +14575,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128087543</v>
+        <v>128087345</v>
       </c>
       <c r="B141" t="n">
-        <v>98478</v>
+        <v>80217</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14600,10 +14610,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>544674</v>
+        <v>544391</v>
       </c>
       <c r="R141" t="n">
-        <v>6963243</v>
+        <v>6963205</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14636,11 +14646,6 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14667,32 +14672,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128087557</v>
+        <v>128087540</v>
       </c>
       <c r="B142" t="n">
-        <v>98478</v>
+        <v>80188</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14702,10 +14707,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>544552</v>
+        <v>544282</v>
       </c>
       <c r="R142" t="n">
-        <v>6963231</v>
+        <v>6963082</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14738,11 +14743,6 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -14769,45 +14769,49 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128087368</v>
+        <v>128078529</v>
       </c>
       <c r="B143" t="n">
-        <v>80135</v>
+        <v>98571</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>544314</v>
+        <v>544351</v>
       </c>
       <c r="R143" t="n">
-        <v>6963248</v>
+        <v>6963065</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14866,49 +14870,45 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128078529</v>
+        <v>128087368</v>
       </c>
       <c r="B144" t="n">
-        <v>98478</v>
+        <v>80188</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>544351</v>
+        <v>544314</v>
       </c>
       <c r="R144" t="n">
-        <v>6963065</v>
+        <v>6963248</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14970,7 +14970,7 @@
         <v>128078685</v>
       </c>
       <c r="B145" t="n">
-        <v>56248</v>
+        <v>56260</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
         <v>128094035</v>
       </c>
       <c r="B146" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>128094046</v>
       </c>
       <c r="B147" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15276,7 +15276,7 @@
         <v>128094050</v>
       </c>
       <c r="B148" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15378,7 +15378,7 @@
         <v>128094039</v>
       </c>
       <c r="B149" t="n">
-        <v>80136</v>
+        <v>80189</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15475,7 +15475,7 @@
         <v>128094032</v>
       </c>
       <c r="B150" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15577,7 +15577,7 @@
         <v>128094042</v>
       </c>
       <c r="B151" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15676,32 +15676,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128094044</v>
+        <v>128094038</v>
       </c>
       <c r="B152" t="n">
-        <v>98478</v>
+        <v>57682</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15711,10 +15711,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>544703</v>
+        <v>544469</v>
       </c>
       <c r="R152" t="n">
-        <v>6963330</v>
+        <v>6963307</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15751,7 +15751,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>100 ex</t>
+          <t>Förbiflygande</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -15778,32 +15778,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128094038</v>
+        <v>128094044</v>
       </c>
       <c r="B153" t="n">
-        <v>57670</v>
+        <v>98571</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -15813,10 +15813,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>544469</v>
+        <v>544703</v>
       </c>
       <c r="R153" t="n">
-        <v>6963307</v>
+        <v>6963330</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15853,7 +15853,7 @@
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>Förbiflygande</t>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -15880,10 +15880,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128094043</v>
+        <v>128094040</v>
       </c>
       <c r="B154" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15915,10 +15915,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>544546</v>
+        <v>544323</v>
       </c>
       <c r="R154" t="n">
-        <v>6963293</v>
+        <v>6963323</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>25 ex</t>
+          <t>7 ex</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -15982,10 +15982,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128094040</v>
+        <v>128094043</v>
       </c>
       <c r="B155" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16017,10 +16017,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>544323</v>
+        <v>544546</v>
       </c>
       <c r="R155" t="n">
-        <v>6963323</v>
+        <v>6963293</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16057,7 +16057,7 @@
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>7 ex</t>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16087,7 +16087,7 @@
         <v>128094048</v>
       </c>
       <c r="B156" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>128094041</v>
       </c>
       <c r="B157" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16291,7 +16291,7 @@
         <v>128094049</v>
       </c>
       <c r="B158" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>128094053</v>
       </c>
       <c r="B159" t="n">
-        <v>105516</v>
+        <v>105609</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16487,32 +16487,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128094052</v>
+        <v>128094047</v>
       </c>
       <c r="B160" t="n">
-        <v>56855</v>
+        <v>98571</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16522,10 +16522,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>544577</v>
+        <v>544641</v>
       </c>
       <c r="R160" t="n">
-        <v>6963169</v>
+        <v>6963158</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16562,7 +16562,7 @@
       </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>Individ noterad genom sång</t>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -16589,10 +16589,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128094047</v>
+        <v>128094051</v>
       </c>
       <c r="B161" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16624,10 +16624,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>544641</v>
+        <v>544310</v>
       </c>
       <c r="R161" t="n">
-        <v>6963158</v>
+        <v>6963314</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16664,7 +16664,7 @@
       </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>11 ex</t>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -16691,32 +16691,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128094054</v>
+        <v>128094045</v>
       </c>
       <c r="B162" t="n">
-        <v>105516</v>
+        <v>98571</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16726,10 +16726,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>544321</v>
+        <v>544760</v>
       </c>
       <c r="R162" t="n">
-        <v>6963319</v>
+        <v>6963251</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16762,6 +16762,11 @@
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -16788,32 +16793,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128094051</v>
+        <v>128094054</v>
       </c>
       <c r="B163" t="n">
-        <v>98478</v>
+        <v>105609</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -16823,10 +16828,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>544310</v>
+        <v>544321</v>
       </c>
       <c r="R163" t="n">
-        <v>6963314</v>
+        <v>6963319</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -16859,11 +16864,6 @@
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>80 ex</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -16890,32 +16890,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128094045</v>
+        <v>128094052</v>
       </c>
       <c r="B164" t="n">
-        <v>98478</v>
+        <v>56867</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -16925,10 +16925,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>544760</v>
+        <v>544577</v>
       </c>
       <c r="R164" t="n">
-        <v>6963251</v>
+        <v>6963169</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -16965,7 +16965,7 @@
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>35 ex</t>
+          <t>Individ noterad genom sång</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -16992,10 +16992,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128094036</v>
+        <v>128094033</v>
       </c>
       <c r="B165" t="n">
-        <v>57833</v>
+        <v>57685</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17003,21 +17003,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17027,10 +17027,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>544566</v>
+        <v>544475</v>
       </c>
       <c r="R165" t="n">
-        <v>6963163</v>
+        <v>6963299</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17067,7 +17067,7 @@
       </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>Lockläte övriga läten</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17094,10 +17094,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128094033</v>
+        <v>128094036</v>
       </c>
       <c r="B166" t="n">
-        <v>57673</v>
+        <v>57845</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17105,21 +17105,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17129,10 +17129,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>544475</v>
+        <v>544566</v>
       </c>
       <c r="R166" t="n">
-        <v>6963299</v>
+        <v>6963163</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17169,7 +17169,7 @@
       </c>
       <c r="AC166" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Lockläte övriga läten</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17199,7 +17199,7 @@
         <v>128094034</v>
       </c>
       <c r="B167" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17301,7 +17301,7 @@
         <v>128094055</v>
       </c>
       <c r="B168" t="n">
-        <v>105516</v>
+        <v>105609</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>

--- a/artfynd/A 32240-2025 artfynd.xlsx
+++ b/artfynd/A 32240-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY168"/>
+  <dimension ref="A1:AY169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -995,32 +995,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128087558</v>
+        <v>128087541</v>
       </c>
       <c r="B5" t="n">
-        <v>98571</v>
+        <v>78840</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544428</v>
+        <v>544267</v>
       </c>
       <c r="R5" t="n">
-        <v>6963233</v>
+        <v>6963196</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,11 +1066,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,32 +1092,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128087541</v>
+        <v>128087528</v>
       </c>
       <c r="B6" t="n">
-        <v>78840</v>
+        <v>80216</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6461</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544267</v>
+        <v>544198</v>
       </c>
       <c r="R6" t="n">
-        <v>6963196</v>
+        <v>6963228</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1189,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128087528</v>
+        <v>128087358</v>
       </c>
       <c r="B7" t="n">
         <v>80216</v>
@@ -1229,10 +1224,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544198</v>
+        <v>544278</v>
       </c>
       <c r="R7" t="n">
-        <v>6963228</v>
+        <v>6963265</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,10 +1286,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128087358</v>
+        <v>128087524</v>
       </c>
       <c r="B8" t="n">
-        <v>80216</v>
+        <v>80217</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,21 +1297,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1326,10 +1321,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544278</v>
+        <v>544281</v>
       </c>
       <c r="R8" t="n">
-        <v>6963265</v>
+        <v>6963082</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,32 +1383,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128087524</v>
+        <v>128087558</v>
       </c>
       <c r="B9" t="n">
-        <v>80217</v>
+        <v>98571</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1423,10 +1418,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544281</v>
+        <v>544428</v>
       </c>
       <c r="R9" t="n">
-        <v>6963082</v>
+        <v>6963233</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,6 +1454,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1485,32 +1485,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128078559</v>
+        <v>128087516</v>
       </c>
       <c r="B10" t="n">
-        <v>97448</v>
+        <v>57685</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544359</v>
+        <v>544388</v>
       </c>
       <c r="R10" t="n">
-        <v>6963083</v>
+        <v>6963226</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,6 +1556,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall Äldre spår</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1684,32 +1689,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128087516</v>
+        <v>128078559</v>
       </c>
       <c r="B12" t="n">
-        <v>57685</v>
+        <v>97448</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1719,10 +1724,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544388</v>
+        <v>544359</v>
       </c>
       <c r="R12" t="n">
-        <v>6963226</v>
+        <v>6963083</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1755,11 +1760,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall Äldre spår</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1786,32 +1786,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128081639</v>
+        <v>128087347</v>
       </c>
       <c r="B13" t="n">
-        <v>80189</v>
+        <v>80217</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544323</v>
+        <v>544745</v>
       </c>
       <c r="R13" t="n">
-        <v>6963268</v>
+        <v>6963195</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1883,10 +1883,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128087324</v>
+        <v>128087520</v>
       </c>
       <c r="B14" t="n">
-        <v>57685</v>
+        <v>57845</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1894,21 +1894,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544792</v>
+        <v>544771</v>
       </c>
       <c r="R14" t="n">
-        <v>6963047</v>
+        <v>6963083</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>2 stycken.  Övriga läten</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1985,32 +1985,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128087323</v>
+        <v>128087550</v>
       </c>
       <c r="B15" t="n">
-        <v>57685</v>
+        <v>98571</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544646</v>
+        <v>544490</v>
       </c>
       <c r="R15" t="n">
-        <v>6963095</v>
+        <v>6963099</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2087,32 +2087,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128087347</v>
+        <v>128081639</v>
       </c>
       <c r="B16" t="n">
-        <v>80217</v>
+        <v>80189</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2122,10 +2122,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544745</v>
+        <v>544323</v>
       </c>
       <c r="R16" t="n">
-        <v>6963195</v>
+        <v>6963268</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2184,10 +2184,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128087520</v>
+        <v>128087323</v>
       </c>
       <c r="B17" t="n">
-        <v>57845</v>
+        <v>57685</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2195,21 +2195,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544771</v>
+        <v>544646</v>
       </c>
       <c r="R17" t="n">
-        <v>6963083</v>
+        <v>6963095</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2 stycken.  Övriga läten</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2286,32 +2286,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128087550</v>
+        <v>128087324</v>
       </c>
       <c r="B18" t="n">
-        <v>98571</v>
+        <v>57685</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544490</v>
+        <v>544792</v>
       </c>
       <c r="R18" t="n">
-        <v>6963099</v>
+        <v>6963047</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2388,10 +2388,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128087581</v>
+        <v>128087359</v>
       </c>
       <c r="B19" t="n">
-        <v>79083</v>
+        <v>78841</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2399,21 +2399,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2423,10 +2423,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544192</v>
+        <v>544741</v>
       </c>
       <c r="R19" t="n">
-        <v>6963197</v>
+        <v>6963165</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2485,10 +2485,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128087362</v>
+        <v>128087354</v>
       </c>
       <c r="B20" t="n">
-        <v>80188</v>
+        <v>80189</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2496,21 +2496,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544799</v>
+        <v>544820</v>
       </c>
       <c r="R20" t="n">
-        <v>6963263</v>
+        <v>6963278</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2582,32 +2582,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128087349</v>
+        <v>128087581</v>
       </c>
       <c r="B21" t="n">
-        <v>80217</v>
+        <v>79083</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544475</v>
+        <v>544192</v>
       </c>
       <c r="R21" t="n">
-        <v>6963205</v>
+        <v>6963197</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2679,32 +2679,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128087569</v>
+        <v>128087362</v>
       </c>
       <c r="B22" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2714,10 +2714,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544296</v>
+        <v>544799</v>
       </c>
       <c r="R22" t="n">
-        <v>6963084</v>
+        <v>6963263</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2750,11 +2750,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>100stycken</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2781,32 +2776,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128087554</v>
+        <v>128087349</v>
       </c>
       <c r="B23" t="n">
-        <v>98571</v>
+        <v>80217</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2816,10 +2811,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544659</v>
+        <v>544475</v>
       </c>
       <c r="R23" t="n">
-        <v>6963253</v>
+        <v>6963205</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2852,11 +2847,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2883,32 +2873,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128087359</v>
+        <v>128087569</v>
       </c>
       <c r="B24" t="n">
-        <v>78841</v>
+        <v>98571</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2918,10 +2908,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544741</v>
+        <v>544296</v>
       </c>
       <c r="R24" t="n">
-        <v>6963165</v>
+        <v>6963084</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2954,6 +2944,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>100stycken</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2980,32 +2975,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128087354</v>
+        <v>128087554</v>
       </c>
       <c r="B25" t="n">
-        <v>80189</v>
+        <v>98571</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3015,10 +3010,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544820</v>
+        <v>544659</v>
       </c>
       <c r="R25" t="n">
-        <v>6963278</v>
+        <v>6963253</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3051,6 +3046,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3077,32 +3077,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128087532</v>
+        <v>128087382</v>
       </c>
       <c r="B26" t="n">
-        <v>80188</v>
+        <v>92742</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3112,10 +3112,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>544491</v>
+        <v>544198</v>
       </c>
       <c r="R26" t="n">
-        <v>6963099</v>
+        <v>6963225</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3148,6 +3148,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3174,32 +3179,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128087382</v>
+        <v>128087562</v>
       </c>
       <c r="B27" t="n">
-        <v>92742</v>
+        <v>98571</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3209,10 +3214,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544198</v>
+        <v>544367</v>
       </c>
       <c r="R27" t="n">
-        <v>6963225</v>
+        <v>6963253</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3249,7 +3254,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>5 ex</t>
+          <t>7. Kan möjlitvis finnas fler runt omkring.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3276,45 +3281,49 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128087333</v>
+        <v>128078161</v>
       </c>
       <c r="B28" t="n">
-        <v>57685</v>
+        <v>98571</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544355</v>
+        <v>544362</v>
       </c>
       <c r="R28" t="n">
-        <v>6963212</v>
+        <v>6963061</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3347,11 +3356,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3378,45 +3382,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128087331</v>
+        <v>128078740</v>
       </c>
       <c r="B29" t="n">
-        <v>57685</v>
+        <v>98571</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544763</v>
+        <v>544307</v>
       </c>
       <c r="R29" t="n">
-        <v>6963244</v>
+        <v>6963089</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3449,11 +3457,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3480,7 +3483,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128087562</v>
+        <v>128087563</v>
       </c>
       <c r="B30" t="n">
         <v>98571</v>
@@ -3515,10 +3518,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>544367</v>
+        <v>544322</v>
       </c>
       <c r="R30" t="n">
-        <v>6963253</v>
+        <v>6963250</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3555,7 +3558,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>7. Kan möjlitvis finnas fler runt omkring.</t>
+          <t>12 stycken</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3582,49 +3585,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128078161</v>
+        <v>128087532</v>
       </c>
       <c r="B31" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>544362</v>
+        <v>544491</v>
       </c>
       <c r="R31" t="n">
-        <v>6963061</v>
+        <v>6963099</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3683,49 +3682,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128078740</v>
+        <v>128087331</v>
       </c>
       <c r="B32" t="n">
-        <v>98571</v>
+        <v>57685</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544307</v>
+        <v>544763</v>
       </c>
       <c r="R32" t="n">
-        <v>6963089</v>
+        <v>6963244</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3758,6 +3753,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3784,32 +3784,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128087563</v>
+        <v>128087333</v>
       </c>
       <c r="B33" t="n">
-        <v>98571</v>
+        <v>57685</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>544322</v>
+        <v>544355</v>
       </c>
       <c r="R33" t="n">
-        <v>6963250</v>
+        <v>6963212</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3859,7 +3859,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>12 stycken</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4376,10 +4376,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128087527</v>
+        <v>128087588</v>
       </c>
       <c r="B39" t="n">
-        <v>80216</v>
+        <v>92742</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4387,21 +4387,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6461</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>544246</v>
+        <v>544183</v>
       </c>
       <c r="R39" t="n">
-        <v>6963259</v>
+        <v>6963214</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4447,6 +4447,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>9 ex äldre exemplar</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4473,10 +4478,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128087369</v>
+        <v>128087527</v>
       </c>
       <c r="B40" t="n">
-        <v>80224</v>
+        <v>80216</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4484,21 +4489,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6464</v>
+        <v>6461</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4508,10 +4513,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>544721</v>
+        <v>544246</v>
       </c>
       <c r="R40" t="n">
-        <v>6963277</v>
+        <v>6963259</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4570,10 +4575,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128087588</v>
+        <v>128087369</v>
       </c>
       <c r="B41" t="n">
-        <v>92742</v>
+        <v>80224</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4581,21 +4586,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4605,10 +4610,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>544183</v>
+        <v>544721</v>
       </c>
       <c r="R41" t="n">
-        <v>6963214</v>
+        <v>6963277</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4641,11 +4646,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>9 ex äldre exemplar</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4876,32 +4876,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128079768</v>
+        <v>128087552</v>
       </c>
       <c r="B44" t="n">
-        <v>97454</v>
+        <v>98571</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4911,10 +4911,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>544287</v>
+        <v>544687</v>
       </c>
       <c r="R44" t="n">
-        <v>6963168</v>
+        <v>6963255</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4947,6 +4947,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>70</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4973,32 +4978,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128087340</v>
+        <v>128087548</v>
       </c>
       <c r="B45" t="n">
-        <v>57845</v>
+        <v>98571</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5008,10 +5013,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>544485</v>
+        <v>544213</v>
       </c>
       <c r="R45" t="n">
-        <v>6963237</v>
+        <v>6963197</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5044,6 +5049,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>100stycken.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5070,32 +5080,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128087552</v>
+        <v>128087361</v>
       </c>
       <c r="B46" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5105,10 +5115,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>544687</v>
+        <v>544865</v>
       </c>
       <c r="R46" t="n">
-        <v>6963255</v>
+        <v>6963092</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5141,11 +5151,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>70</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5172,32 +5177,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128087548</v>
+        <v>128087360</v>
       </c>
       <c r="B47" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5207,10 +5212,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>544213</v>
+        <v>544615</v>
       </c>
       <c r="R47" t="n">
-        <v>6963197</v>
+        <v>6963093</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5243,11 +5248,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>100stycken.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5274,10 +5274,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128087361</v>
+        <v>128087340</v>
       </c>
       <c r="B48" t="n">
-        <v>80188</v>
+        <v>57845</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5285,21 +5285,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5309,10 +5309,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>544865</v>
+        <v>544485</v>
       </c>
       <c r="R48" t="n">
-        <v>6963092</v>
+        <v>6963237</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5371,32 +5371,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128087360</v>
+        <v>128079768</v>
       </c>
       <c r="B49" t="n">
-        <v>80188</v>
+        <v>97454</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>221941</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>544615</v>
+        <v>544287</v>
       </c>
       <c r="R49" t="n">
-        <v>6963093</v>
+        <v>6963168</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6162,50 +6162,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128080012</v>
+        <v>128087585</v>
       </c>
       <c r="B57" t="n">
-        <v>57685</v>
+        <v>92742</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>544324</v>
+        <v>544536</v>
       </c>
       <c r="R57" t="n">
-        <v>6963220</v>
+        <v>6963255</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6242,7 +6237,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>8 äldre ex9 färska fruktkroppar</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6269,10 +6264,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128087585</v>
+        <v>128087356</v>
       </c>
       <c r="B58" t="n">
-        <v>92742</v>
+        <v>80216</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6280,21 +6275,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>6461</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6304,10 +6299,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>544536</v>
+        <v>544772</v>
       </c>
       <c r="R58" t="n">
-        <v>6963255</v>
+        <v>6963323</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6340,11 +6335,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>8 äldre ex9 färska fruktkroppar</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6371,7 +6361,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128087356</v>
+        <v>128087357</v>
       </c>
       <c r="B59" t="n">
         <v>80216</v>
@@ -6406,10 +6396,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>544772</v>
+        <v>544466</v>
       </c>
       <c r="R59" t="n">
-        <v>6963323</v>
+        <v>6963277</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6468,45 +6458,50 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128087357</v>
+        <v>128080012</v>
       </c>
       <c r="B60" t="n">
-        <v>80216</v>
+        <v>57685</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>544466</v>
+        <v>544324</v>
       </c>
       <c r="R60" t="n">
-        <v>6963277</v>
+        <v>6963220</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6539,6 +6534,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6565,32 +6565,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128078603</v>
+        <v>128087525</v>
       </c>
       <c r="B61" t="n">
-        <v>80217</v>
+        <v>56260</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6462</v>
+        <v>206004</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6600,10 +6600,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>544360</v>
+        <v>544385</v>
       </c>
       <c r="R61" t="n">
-        <v>6963094</v>
+        <v>6963074</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6662,32 +6662,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128087523</v>
+        <v>128087566</v>
       </c>
       <c r="B62" t="n">
-        <v>80217</v>
+        <v>98571</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6697,10 +6697,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>544253</v>
+        <v>544261</v>
       </c>
       <c r="R62" t="n">
-        <v>6963139</v>
+        <v>6963170</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6733,6 +6733,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>4. Stycken. Finns möjligtvis fler i blåbärsriset.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6759,32 +6764,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128087579</v>
+        <v>128087377</v>
       </c>
       <c r="B63" t="n">
-        <v>79083</v>
+        <v>98571</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6794,10 +6799,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>544204</v>
+        <v>544403</v>
       </c>
       <c r="R63" t="n">
-        <v>6963238</v>
+        <v>6963221</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6834,7 +6839,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Riklig förekomst av garnlav</t>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6861,32 +6866,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128087386</v>
+        <v>128087378</v>
       </c>
       <c r="B64" t="n">
-        <v>92736</v>
+        <v>98571</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4362</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6896,10 +6901,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>544822</v>
+        <v>544218</v>
       </c>
       <c r="R64" t="n">
-        <v>6963295</v>
+        <v>6963229</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6932,6 +6937,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6958,32 +6968,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128087329</v>
+        <v>128087375</v>
       </c>
       <c r="B65" t="n">
-        <v>57685</v>
+        <v>98571</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6993,10 +7003,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>544757</v>
+        <v>544478</v>
       </c>
       <c r="R65" t="n">
-        <v>6963172</v>
+        <v>6963117</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7033,7 +7043,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7060,10 +7070,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128087525</v>
+        <v>128087386</v>
       </c>
       <c r="B66" t="n">
-        <v>56260</v>
+        <v>92736</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7071,21 +7081,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>206004</v>
+        <v>4362</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7095,10 +7105,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>544385</v>
+        <v>544822</v>
       </c>
       <c r="R66" t="n">
-        <v>6963074</v>
+        <v>6963295</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7157,32 +7167,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128087566</v>
+        <v>128078603</v>
       </c>
       <c r="B67" t="n">
-        <v>98571</v>
+        <v>80217</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7192,10 +7202,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>544261</v>
+        <v>544360</v>
       </c>
       <c r="R67" t="n">
-        <v>6963170</v>
+        <v>6963094</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7228,11 +7238,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>4. Stycken. Finns möjligtvis fler i blåbärsriset.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7259,32 +7264,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128087377</v>
+        <v>128087523</v>
       </c>
       <c r="B68" t="n">
-        <v>98571</v>
+        <v>80217</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7294,10 +7299,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>544403</v>
+        <v>544253</v>
       </c>
       <c r="R68" t="n">
-        <v>6963221</v>
+        <v>6963139</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7330,11 +7335,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>20 ex</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7361,32 +7361,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128087378</v>
+        <v>128087579</v>
       </c>
       <c r="B69" t="n">
-        <v>98571</v>
+        <v>79083</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7396,10 +7396,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>544218</v>
+        <v>544204</v>
       </c>
       <c r="R69" t="n">
-        <v>6963229</v>
+        <v>6963238</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>80 ex</t>
+          <t>Riklig förekomst av garnlav</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7463,32 +7463,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128087375</v>
+        <v>128087329</v>
       </c>
       <c r="B70" t="n">
-        <v>98571</v>
+        <v>57685</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7498,10 +7498,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>544478</v>
+        <v>544757</v>
       </c>
       <c r="R70" t="n">
-        <v>6963117</v>
+        <v>6963172</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>35 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7565,10 +7565,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128087366</v>
+        <v>128087337</v>
       </c>
       <c r="B71" t="n">
-        <v>80188</v>
+        <v>57685</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7576,21 +7576,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7600,10 +7600,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>544407</v>
+        <v>544197</v>
       </c>
       <c r="R71" t="n">
-        <v>6963184</v>
+        <v>6963237</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7636,6 +7636,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7662,10 +7667,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128087537</v>
+        <v>128080035</v>
       </c>
       <c r="B72" t="n">
-        <v>80188</v>
+        <v>57685</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7673,34 +7678,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>544205</v>
+        <v>544340</v>
       </c>
       <c r="R72" t="n">
-        <v>6963241</v>
+        <v>6963223</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7733,6 +7743,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7866,7 +7881,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128080035</v>
+        <v>128080149</v>
       </c>
       <c r="B74" t="n">
         <v>57685</v>
@@ -7906,10 +7921,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>544340</v>
+        <v>544295</v>
       </c>
       <c r="R74" t="n">
-        <v>6963223</v>
+        <v>6963226</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7973,10 +7988,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128080149</v>
+        <v>128087366</v>
       </c>
       <c r="B75" t="n">
-        <v>57685</v>
+        <v>80188</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7984,39 +7999,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>544295</v>
+        <v>544407</v>
       </c>
       <c r="R75" t="n">
-        <v>6963226</v>
+        <v>6963184</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8049,11 +8059,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8080,10 +8085,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128087337</v>
+        <v>128087537</v>
       </c>
       <c r="B76" t="n">
-        <v>57685</v>
+        <v>80188</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8091,21 +8096,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8115,10 +8120,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>544197</v>
+        <v>544205</v>
       </c>
       <c r="R76" t="n">
-        <v>6963237</v>
+        <v>6963241</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8151,11 +8156,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8381,49 +8381,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128079875</v>
+        <v>128087570</v>
       </c>
       <c r="B79" t="n">
-        <v>98571</v>
+        <v>56867</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>544308</v>
+        <v>544287</v>
       </c>
       <c r="R79" t="n">
-        <v>6963175</v>
+        <v>6963082</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8456,6 +8452,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8482,7 +8483,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128087542</v>
+        <v>128079875</v>
       </c>
       <c r="B80" t="n">
         <v>98571</v>
@@ -8510,17 +8511,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>544752</v>
+        <v>544308</v>
       </c>
       <c r="R80" t="n">
-        <v>6963192</v>
+        <v>6963175</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8553,11 +8558,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8584,7 +8584,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128080338</v>
+        <v>128087542</v>
       </c>
       <c r="B81" t="n">
         <v>98571</v>
@@ -8612,21 +8612,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>544314</v>
+        <v>544752</v>
       </c>
       <c r="R81" t="n">
-        <v>6963248</v>
+        <v>6963192</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8659,6 +8655,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8685,7 +8686,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128087547</v>
+        <v>128080338</v>
       </c>
       <c r="B82" t="n">
         <v>98571</v>
@@ -8713,17 +8714,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>544380</v>
+        <v>544314</v>
       </c>
       <c r="R82" t="n">
-        <v>6963236</v>
+        <v>6963248</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8756,11 +8761,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>33 stycken</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8787,32 +8787,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128087380</v>
+        <v>128087547</v>
       </c>
       <c r="B83" t="n">
-        <v>105609</v>
+        <v>98571</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8822,10 +8822,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>544468</v>
+        <v>544380</v>
       </c>
       <c r="R83" t="n">
-        <v>6963173</v>
+        <v>6963236</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8858,6 +8858,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>33 stycken</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8884,32 +8889,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128087560</v>
+        <v>128087380</v>
       </c>
       <c r="B84" t="n">
-        <v>98571</v>
+        <v>105609</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8919,10 +8924,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>544383</v>
+        <v>544468</v>
       </c>
       <c r="R84" t="n">
-        <v>6963236</v>
+        <v>6963173</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8955,11 +8960,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8986,32 +8986,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128087536</v>
+        <v>128087560</v>
       </c>
       <c r="B85" t="n">
-        <v>80188</v>
+        <v>98571</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9021,10 +9021,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>544215</v>
+        <v>544383</v>
       </c>
       <c r="R85" t="n">
-        <v>6963245</v>
+        <v>6963236</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9057,6 +9057,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9083,32 +9088,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128087343</v>
+        <v>128087536</v>
       </c>
       <c r="B86" t="n">
-        <v>80217</v>
+        <v>80188</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9118,10 +9123,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>544757</v>
+        <v>544215</v>
       </c>
       <c r="R86" t="n">
-        <v>6963156</v>
+        <v>6963245</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9180,7 +9185,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128087346</v>
+        <v>128087343</v>
       </c>
       <c r="B87" t="n">
         <v>80217</v>
@@ -9215,10 +9220,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>544422</v>
+        <v>544757</v>
       </c>
       <c r="R87" t="n">
-        <v>6963240</v>
+        <v>6963156</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9277,32 +9282,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128087335</v>
+        <v>128087346</v>
       </c>
       <c r="B88" t="n">
-        <v>57685</v>
+        <v>80217</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9312,10 +9317,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>544366</v>
+        <v>544422</v>
       </c>
       <c r="R88" t="n">
-        <v>6963181</v>
+        <v>6963240</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9348,11 +9353,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9481,10 +9481,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128087570</v>
+        <v>128087335</v>
       </c>
       <c r="B90" t="n">
-        <v>56867</v>
+        <v>57685</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9492,16 +9492,16 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -9516,10 +9516,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>544287</v>
+        <v>544366</v>
       </c>
       <c r="R90" t="n">
-        <v>6963082</v>
+        <v>6963181</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9556,7 +9556,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Fjäder</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9583,32 +9583,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128087587</v>
+        <v>128087376</v>
       </c>
       <c r="B91" t="n">
-        <v>92742</v>
+        <v>98571</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9618,10 +9618,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>544245</v>
+        <v>544503</v>
       </c>
       <c r="R91" t="n">
-        <v>6963255</v>
+        <v>6963182</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9658,7 +9658,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>4stycken</t>
+          <t>60 ex</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9685,32 +9685,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128087539</v>
+        <v>128087379</v>
       </c>
       <c r="B92" t="n">
-        <v>80188</v>
+        <v>98571</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9720,10 +9720,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>544254</v>
+        <v>544263</v>
       </c>
       <c r="R92" t="n">
-        <v>6963139</v>
+        <v>6963254</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9756,6 +9756,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9782,10 +9787,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128087341</v>
+        <v>128087587</v>
       </c>
       <c r="B93" t="n">
-        <v>80217</v>
+        <v>92742</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9793,21 +9798,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9817,10 +9822,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>544615</v>
+        <v>544245</v>
       </c>
       <c r="R93" t="n">
-        <v>6963101</v>
+        <v>6963255</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9853,6 +9858,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>4stycken</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9879,32 +9889,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128087376</v>
+        <v>128087539</v>
       </c>
       <c r="B94" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9914,10 +9924,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>544503</v>
+        <v>544254</v>
       </c>
       <c r="R94" t="n">
-        <v>6963182</v>
+        <v>6963139</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9950,11 +9960,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>60 ex</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9981,32 +9986,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128087379</v>
+        <v>128087341</v>
       </c>
       <c r="B95" t="n">
-        <v>98571</v>
+        <v>80217</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10016,10 +10021,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>544263</v>
+        <v>544615</v>
       </c>
       <c r="R95" t="n">
-        <v>6963254</v>
+        <v>6963101</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10052,11 +10057,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>15 ex</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10083,10 +10083,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128087522</v>
+        <v>128087576</v>
       </c>
       <c r="B96" t="n">
-        <v>57845</v>
+        <v>92774</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10094,21 +10094,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>103021</v>
+        <v>1968</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10118,10 +10118,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>544494</v>
+        <v>544529</v>
       </c>
       <c r="R96" t="n">
-        <v>6963243</v>
+        <v>6963245</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10154,6 +10154,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Misstänkt grantaggsvamp men med mörk tydlig ring i mitten.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10180,32 +10185,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128087545</v>
+        <v>128087572</v>
       </c>
       <c r="B97" t="n">
-        <v>98571</v>
+        <v>92774</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>1968</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10215,10 +10220,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>544633</v>
+        <v>544632</v>
       </c>
       <c r="R97" t="n">
-        <v>6963244</v>
+        <v>6963245</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10255,7 +10260,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>30 stycken</t>
+          <t>1 ex</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10282,32 +10287,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128087567</v>
+        <v>128087383</v>
       </c>
       <c r="B98" t="n">
-        <v>98571</v>
+        <v>80223</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10317,10 +10322,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>544274</v>
+        <v>544566</v>
       </c>
       <c r="R98" t="n">
-        <v>6963090</v>
+        <v>6963076</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10353,11 +10358,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>110</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10384,32 +10384,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128087556</v>
+        <v>128087384</v>
       </c>
       <c r="B99" t="n">
-        <v>98571</v>
+        <v>80223</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10419,10 +10419,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>544594</v>
+        <v>544584</v>
       </c>
       <c r="R99" t="n">
-        <v>6963215</v>
+        <v>6963261</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10455,11 +10455,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>6 stycken. Kan finnas mer i omgivningen</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10486,32 +10481,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128087373</v>
+        <v>128087363</v>
       </c>
       <c r="B100" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10521,10 +10516,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>544469</v>
+        <v>544818</v>
       </c>
       <c r="R100" t="n">
-        <v>6963122</v>
+        <v>6963278</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10557,11 +10552,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>60 ex</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10588,32 +10578,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128078864</v>
+        <v>128087522</v>
       </c>
       <c r="B101" t="n">
-        <v>105609</v>
+        <v>57845</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10623,10 +10613,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>544307</v>
+        <v>544494</v>
       </c>
       <c r="R101" t="n">
-        <v>6963089</v>
+        <v>6963243</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10685,7 +10675,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128087559</v>
+        <v>128087545</v>
       </c>
       <c r="B102" t="n">
         <v>98571</v>
@@ -10720,10 +10710,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>544396</v>
+        <v>544633</v>
       </c>
       <c r="R102" t="n">
-        <v>6963233</v>
+        <v>6963244</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10760,7 +10750,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>18 stycken</t>
+          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10787,32 +10777,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128087355</v>
+        <v>128087567</v>
       </c>
       <c r="B103" t="n">
-        <v>97454</v>
+        <v>98571</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10822,10 +10812,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>544500</v>
+        <v>544274</v>
       </c>
       <c r="R103" t="n">
-        <v>6963168</v>
+        <v>6963090</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10858,6 +10848,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>110</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10884,32 +10879,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128087576</v>
+        <v>128087556</v>
       </c>
       <c r="B104" t="n">
-        <v>92774</v>
+        <v>98571</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1968</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10919,10 +10914,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>544529</v>
+        <v>544594</v>
       </c>
       <c r="R104" t="n">
-        <v>6963245</v>
+        <v>6963215</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10959,7 +10954,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Misstänkt grantaggsvamp men med mörk tydlig ring i mitten.</t>
+          <t>6 stycken. Kan finnas mer i omgivningen</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10986,32 +10981,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128087572</v>
+        <v>128087373</v>
       </c>
       <c r="B105" t="n">
-        <v>92774</v>
+        <v>98571</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1968</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11021,10 +11016,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>544632</v>
+        <v>544469</v>
       </c>
       <c r="R105" t="n">
-        <v>6963245</v>
+        <v>6963122</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11061,7 +11056,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>1 ex</t>
+          <t>60 ex</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11088,10 +11083,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128087384</v>
+        <v>128078864</v>
       </c>
       <c r="B106" t="n">
-        <v>80223</v>
+        <v>105609</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11099,21 +11094,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6463</v>
+        <v>221144</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11123,10 +11118,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>544584</v>
+        <v>544307</v>
       </c>
       <c r="R106" t="n">
-        <v>6963261</v>
+        <v>6963089</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11185,32 +11180,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128087383</v>
+        <v>128087559</v>
       </c>
       <c r="B107" t="n">
-        <v>80223</v>
+        <v>98571</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11220,10 +11215,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>544566</v>
+        <v>544396</v>
       </c>
       <c r="R107" t="n">
-        <v>6963076</v>
+        <v>6963233</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11256,6 +11251,11 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11282,32 +11282,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128087363</v>
+        <v>128087355</v>
       </c>
       <c r="B108" t="n">
-        <v>80188</v>
+        <v>97454</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6458</v>
+        <v>221941</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11317,10 +11317,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>544818</v>
+        <v>544500</v>
       </c>
       <c r="R108" t="n">
-        <v>6963278</v>
+        <v>6963168</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11675,45 +11675,49 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128087531</v>
+        <v>128079656</v>
       </c>
       <c r="B112" t="n">
-        <v>98605</v>
+        <v>98571</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>544755</v>
+        <v>544277</v>
       </c>
       <c r="R112" t="n">
-        <v>6963130</v>
+        <v>6963150</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11746,11 +11750,6 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11777,7 +11776,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128079656</v>
+        <v>128087565</v>
       </c>
       <c r="B113" t="n">
         <v>98571</v>
@@ -11805,21 +11804,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>544277</v>
+        <v>544249</v>
       </c>
       <c r="R113" t="n">
-        <v>6963150</v>
+        <v>6963223</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11852,6 +11847,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>10. Kan möjlitvis finns mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11878,7 +11878,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128087565</v>
+        <v>128087372</v>
       </c>
       <c r="B114" t="n">
         <v>98571</v>
@@ -11913,10 +11913,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>544249</v>
+        <v>544472</v>
       </c>
       <c r="R114" t="n">
-        <v>6963223</v>
+        <v>6963201</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11953,7 +11953,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>10. Kan möjlitvis finns mer i blåbärsriset</t>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11980,7 +11980,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128087372</v>
+        <v>128087551</v>
       </c>
       <c r="B115" t="n">
         <v>98571</v>
@@ -12015,10 +12015,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>544472</v>
+        <v>544694</v>
       </c>
       <c r="R115" t="n">
-        <v>6963201</v>
+        <v>6963258</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12055,7 +12055,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>8 ex</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12082,32 +12082,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128087551</v>
+        <v>128087531</v>
       </c>
       <c r="B116" t="n">
-        <v>98571</v>
+        <v>98605</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12117,10 +12117,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>544694</v>
+        <v>544755</v>
       </c>
       <c r="R116" t="n">
-        <v>6963258</v>
+        <v>6963130</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12157,7 +12157,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12184,10 +12184,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128087571</v>
+        <v>128087538</v>
       </c>
       <c r="B117" t="n">
-        <v>92774</v>
+        <v>80188</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12195,21 +12195,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1968</v>
+        <v>6458</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12219,10 +12219,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>544679</v>
+        <v>544262</v>
       </c>
       <c r="R117" t="n">
-        <v>6963259</v>
+        <v>6963163</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12255,11 +12255,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Misstänker grantaggsvamp. 14 exemplar</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12286,32 +12281,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128087573</v>
+        <v>128087582</v>
       </c>
       <c r="B118" t="n">
-        <v>92774</v>
+        <v>98488</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1968</v>
+        <v>219790</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12321,10 +12316,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>544684</v>
+        <v>544489</v>
       </c>
       <c r="R118" t="n">
-        <v>6963253</v>
+        <v>6963098</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12357,11 +12352,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Mörkt exemplar med vit yttre ring.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12388,32 +12378,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128079848</v>
+        <v>128087535</v>
       </c>
       <c r="B119" t="n">
-        <v>79107</v>
+        <v>80188</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6434</v>
+        <v>6458</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12423,10 +12413,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>544288</v>
+        <v>544312</v>
       </c>
       <c r="R119" t="n">
-        <v>6963182</v>
+        <v>6963244</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12485,10 +12475,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128087538</v>
+        <v>128078823</v>
       </c>
       <c r="B120" t="n">
-        <v>80188</v>
+        <v>79083</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12496,21 +12486,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12520,10 +12510,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>544262</v>
+        <v>544307</v>
       </c>
       <c r="R120" t="n">
-        <v>6963163</v>
+        <v>6963089</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12582,10 +12572,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128087535</v>
+        <v>128087571</v>
       </c>
       <c r="B121" t="n">
-        <v>80188</v>
+        <v>92774</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12593,21 +12583,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6458</v>
+        <v>1968</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12617,10 +12607,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>544312</v>
+        <v>544679</v>
       </c>
       <c r="R121" t="n">
-        <v>6963244</v>
+        <v>6963259</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12653,6 +12643,11 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Misstänker grantaggsvamp. 14 exemplar</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12679,10 +12674,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128078823</v>
+        <v>128087573</v>
       </c>
       <c r="B122" t="n">
-        <v>79083</v>
+        <v>92774</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12690,21 +12685,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>1968</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12714,10 +12709,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>544307</v>
+        <v>544684</v>
       </c>
       <c r="R122" t="n">
-        <v>6963089</v>
+        <v>6963253</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12750,6 +12745,11 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Mörkt exemplar med vit yttre ring.</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12776,10 +12776,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128087582</v>
+        <v>128079848</v>
       </c>
       <c r="B123" t="n">
-        <v>98488</v>
+        <v>79107</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12787,21 +12787,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>219790</v>
+        <v>6434</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12811,10 +12811,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>544489</v>
+        <v>544288</v>
       </c>
       <c r="R123" t="n">
-        <v>6963098</v>
+        <v>6963182</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13274,32 +13274,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128087574</v>
+        <v>128087584</v>
       </c>
       <c r="B128" t="n">
-        <v>92774</v>
+        <v>98488</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1968</v>
+        <v>219790</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13309,10 +13309,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>544552</v>
+        <v>544718</v>
       </c>
       <c r="R128" t="n">
-        <v>6963231</v>
+        <v>6963053</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13349,7 +13349,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>Misstänker grantaggsvamp 1 exemplar</t>
+          <t>3 stycken</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13376,7 +13376,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128087584</v>
+        <v>128087583</v>
       </c>
       <c r="B129" t="n">
         <v>98488</v>
@@ -13411,10 +13411,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>544718</v>
+        <v>544708</v>
       </c>
       <c r="R129" t="n">
-        <v>6963053</v>
+        <v>6963086</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13451,7 +13451,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>3 stycken</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13478,32 +13478,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128087583</v>
+        <v>128087574</v>
       </c>
       <c r="B130" t="n">
-        <v>98488</v>
+        <v>92774</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>219790</v>
+        <v>1968</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13513,10 +13513,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>544708</v>
+        <v>544552</v>
       </c>
       <c r="R130" t="n">
-        <v>6963086</v>
+        <v>6963231</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13553,7 +13553,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Misstänker grantaggsvamp 1 exemplar</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13784,10 +13784,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128087328</v>
+        <v>128078645</v>
       </c>
       <c r="B133" t="n">
-        <v>57685</v>
+        <v>80188</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13795,21 +13795,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13819,10 +13819,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>544736</v>
+        <v>544360</v>
       </c>
       <c r="R133" t="n">
-        <v>6963153</v>
+        <v>6963094</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13855,11 +13855,6 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -13886,10 +13881,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128087381</v>
+        <v>128087344</v>
       </c>
       <c r="B134" t="n">
-        <v>98488</v>
+        <v>80217</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13897,21 +13892,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>219790</v>
+        <v>6462</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13921,10 +13916,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>544531</v>
+        <v>544581</v>
       </c>
       <c r="R134" t="n">
-        <v>6963190</v>
+        <v>6963278</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13983,32 +13978,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128087530</v>
+        <v>128087534</v>
       </c>
       <c r="B135" t="n">
-        <v>98605</v>
+        <v>80188</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>219874</v>
+        <v>6458</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14018,10 +14013,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>544737</v>
+        <v>544326</v>
       </c>
       <c r="R135" t="n">
-        <v>6963047</v>
+        <v>6963248</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14080,32 +14075,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128087557</v>
+        <v>128087345</v>
       </c>
       <c r="B136" t="n">
-        <v>98571</v>
+        <v>80217</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14115,10 +14110,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>544552</v>
+        <v>544391</v>
       </c>
       <c r="R136" t="n">
-        <v>6963231</v>
+        <v>6963205</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14151,11 +14146,6 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14182,32 +14172,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128087543</v>
+        <v>128087540</v>
       </c>
       <c r="B137" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14217,10 +14207,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>544674</v>
+        <v>544282</v>
       </c>
       <c r="R137" t="n">
-        <v>6963243</v>
+        <v>6963082</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14253,11 +14243,6 @@
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14284,32 +14269,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128078645</v>
+        <v>128087557</v>
       </c>
       <c r="B138" t="n">
-        <v>80188</v>
+        <v>98571</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14319,10 +14304,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>544360</v>
+        <v>544552</v>
       </c>
       <c r="R138" t="n">
-        <v>6963094</v>
+        <v>6963231</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14355,6 +14340,11 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14381,32 +14371,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128087344</v>
+        <v>128087543</v>
       </c>
       <c r="B139" t="n">
-        <v>80217</v>
+        <v>98571</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14416,10 +14406,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>544581</v>
+        <v>544674</v>
       </c>
       <c r="R139" t="n">
-        <v>6963278</v>
+        <v>6963243</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14452,6 +14442,11 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14478,10 +14473,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128087534</v>
+        <v>128087328</v>
       </c>
       <c r="B140" t="n">
-        <v>80188</v>
+        <v>57685</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14489,21 +14484,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14513,10 +14508,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>544326</v>
+        <v>544736</v>
       </c>
       <c r="R140" t="n">
-        <v>6963248</v>
+        <v>6963153</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14549,6 +14544,11 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14575,10 +14575,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128087345</v>
+        <v>128087381</v>
       </c>
       <c r="B141" t="n">
-        <v>80217</v>
+        <v>98488</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14586,21 +14586,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6462</v>
+        <v>219790</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14610,10 +14610,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>544391</v>
+        <v>544531</v>
       </c>
       <c r="R141" t="n">
-        <v>6963205</v>
+        <v>6963190</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14672,32 +14672,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128087540</v>
+        <v>128087530</v>
       </c>
       <c r="B142" t="n">
-        <v>80188</v>
+        <v>98605</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6458</v>
+        <v>219874</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14707,10 +14707,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>544282</v>
+        <v>544737</v>
       </c>
       <c r="R142" t="n">
-        <v>6963082</v>
+        <v>6963047</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14769,49 +14769,45 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128078529</v>
+        <v>128087368</v>
       </c>
       <c r="B143" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>544351</v>
+        <v>544314</v>
       </c>
       <c r="R143" t="n">
-        <v>6963065</v>
+        <v>6963248</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14870,10 +14866,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128087368</v>
+        <v>128078685</v>
       </c>
       <c r="B144" t="n">
-        <v>80188</v>
+        <v>56260</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14881,34 +14877,39 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>544314</v>
+        <v>544307</v>
       </c>
       <c r="R144" t="n">
-        <v>6963248</v>
+        <v>6963069</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14967,38 +14968,37 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128078685</v>
+        <v>128078529</v>
       </c>
       <c r="B145" t="n">
-        <v>56260</v>
+        <v>98571</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>206004</v>
+        <v>220787</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -15007,10 +15007,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>544307</v>
+        <v>544351</v>
       </c>
       <c r="R145" t="n">
-        <v>6963069</v>
+        <v>6963065</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16487,32 +16487,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128094047</v>
+        <v>128094052</v>
       </c>
       <c r="B160" t="n">
-        <v>98571</v>
+        <v>56867</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16522,10 +16522,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>544641</v>
+        <v>544577</v>
       </c>
       <c r="R160" t="n">
-        <v>6963158</v>
+        <v>6963169</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16562,7 +16562,7 @@
       </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>11 ex</t>
+          <t>Individ noterad genom sång</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -16589,7 +16589,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128094051</v>
+        <v>128094047</v>
       </c>
       <c r="B161" t="n">
         <v>98571</v>
@@ -16624,10 +16624,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>544310</v>
+        <v>544641</v>
       </c>
       <c r="R161" t="n">
-        <v>6963314</v>
+        <v>6963158</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16664,7 +16664,7 @@
       </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>80 ex</t>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -16691,7 +16691,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128094045</v>
+        <v>128094051</v>
       </c>
       <c r="B162" t="n">
         <v>98571</v>
@@ -16726,10 +16726,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>544760</v>
+        <v>544310</v>
       </c>
       <c r="R162" t="n">
-        <v>6963251</v>
+        <v>6963314</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16766,7 +16766,7 @@
       </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>35 ex</t>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -16793,32 +16793,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128094054</v>
+        <v>128094045</v>
       </c>
       <c r="B163" t="n">
-        <v>105609</v>
+        <v>98571</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -16828,10 +16828,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>544321</v>
+        <v>544760</v>
       </c>
       <c r="R163" t="n">
-        <v>6963319</v>
+        <v>6963251</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -16864,6 +16864,11 @@
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -16890,32 +16895,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128094052</v>
+        <v>128094054</v>
       </c>
       <c r="B164" t="n">
-        <v>56867</v>
+        <v>105609</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>102612</v>
+        <v>221144</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -16925,10 +16930,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>544577</v>
+        <v>544321</v>
       </c>
       <c r="R164" t="n">
-        <v>6963169</v>
+        <v>6963319</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -16961,11 +16966,6 @@
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>Individ noterad genom sång</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17393,6 +17393,120 @@
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>128119261</v>
+      </c>
+      <c r="B169" t="n">
+        <v>56867</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr"/>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>Västermyrberget, Mörtsjön, Hällesjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q169" t="n">
+        <v>544592</v>
+      </c>
+      <c r="R169" t="n">
+        <v>6963140</v>
+      </c>
+      <c r="S169" t="n">
+        <v>10</v>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>Två järpeungar satt och tryckte bakom en låga och flög upp precis framför mig.</t>
+        </is>
+      </c>
+      <c r="AD169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT169" t="inlineStr"/>
+      <c r="AW169" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX169" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY169" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32240-2025 artfynd.xlsx
+++ b/artfynd/A 32240-2025 artfynd.xlsx
@@ -1485,10 +1485,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128087516</v>
+        <v>128087526</v>
       </c>
       <c r="B10" t="n">
-        <v>57685</v>
+        <v>92734</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1496,21 +1496,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544388</v>
+        <v>544728</v>
       </c>
       <c r="R10" t="n">
-        <v>6963226</v>
+        <v>6963223</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall Äldre spår</t>
+          <t>10 exemplar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1587,10 +1587,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128087526</v>
+        <v>128087516</v>
       </c>
       <c r="B11" t="n">
-        <v>92734</v>
+        <v>57685</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1598,21 +1598,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4361</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544728</v>
+        <v>544388</v>
       </c>
       <c r="R11" t="n">
-        <v>6963223</v>
+        <v>6963226</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>10 exemplar</t>
+          <t>Ringhack av tretåig hackspett på Tall Äldre spår</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1786,32 +1786,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128087347</v>
+        <v>128081639</v>
       </c>
       <c r="B13" t="n">
-        <v>80217</v>
+        <v>80189</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544745</v>
+        <v>544323</v>
       </c>
       <c r="R13" t="n">
-        <v>6963195</v>
+        <v>6963268</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1883,32 +1883,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128087520</v>
+        <v>128087347</v>
       </c>
       <c r="B14" t="n">
-        <v>57845</v>
+        <v>80217</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544771</v>
+        <v>544745</v>
       </c>
       <c r="R14" t="n">
-        <v>6963083</v>
+        <v>6963195</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1954,11 +1954,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>2 stycken.  Övriga läten</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1985,32 +1980,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128087550</v>
+        <v>128087323</v>
       </c>
       <c r="B15" t="n">
-        <v>98571</v>
+        <v>57685</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2020,10 +2015,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544490</v>
+        <v>544646</v>
       </c>
       <c r="R15" t="n">
-        <v>6963099</v>
+        <v>6963095</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2060,7 +2055,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2087,10 +2082,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128081639</v>
+        <v>128087324</v>
       </c>
       <c r="B16" t="n">
-        <v>80189</v>
+        <v>57685</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2098,21 +2093,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2122,10 +2117,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544323</v>
+        <v>544792</v>
       </c>
       <c r="R16" t="n">
-        <v>6963268</v>
+        <v>6963047</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2158,6 +2153,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2184,10 +2184,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128087323</v>
+        <v>128087520</v>
       </c>
       <c r="B17" t="n">
-        <v>57685</v>
+        <v>57845</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2195,21 +2195,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544646</v>
+        <v>544771</v>
       </c>
       <c r="R17" t="n">
-        <v>6963095</v>
+        <v>6963083</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>2 stycken.  Övriga läten</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2286,32 +2286,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128087324</v>
+        <v>128087550</v>
       </c>
       <c r="B18" t="n">
-        <v>57685</v>
+        <v>98571</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544792</v>
+        <v>544490</v>
       </c>
       <c r="R18" t="n">
-        <v>6963047</v>
+        <v>6963099</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2388,10 +2388,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128087359</v>
+        <v>128087354</v>
       </c>
       <c r="B19" t="n">
-        <v>78841</v>
+        <v>80189</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2399,21 +2399,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2423,10 +2423,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544741</v>
+        <v>544820</v>
       </c>
       <c r="R19" t="n">
-        <v>6963165</v>
+        <v>6963278</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2485,10 +2485,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128087354</v>
+        <v>128087581</v>
       </c>
       <c r="B20" t="n">
-        <v>80189</v>
+        <v>79083</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2496,21 +2496,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544820</v>
+        <v>544192</v>
       </c>
       <c r="R20" t="n">
-        <v>6963278</v>
+        <v>6963197</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2582,10 +2582,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128087581</v>
+        <v>128087362</v>
       </c>
       <c r="B21" t="n">
-        <v>79083</v>
+        <v>80188</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2593,21 +2593,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544192</v>
+        <v>544799</v>
       </c>
       <c r="R21" t="n">
-        <v>6963197</v>
+        <v>6963263</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2679,32 +2679,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128087362</v>
+        <v>128087349</v>
       </c>
       <c r="B22" t="n">
-        <v>80188</v>
+        <v>80217</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2714,10 +2714,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544799</v>
+        <v>544475</v>
       </c>
       <c r="R22" t="n">
-        <v>6963263</v>
+        <v>6963205</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2776,32 +2776,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128087349</v>
+        <v>128087359</v>
       </c>
       <c r="B23" t="n">
-        <v>80217</v>
+        <v>78841</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2811,10 +2811,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544475</v>
+        <v>544741</v>
       </c>
       <c r="R23" t="n">
-        <v>6963205</v>
+        <v>6963165</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3179,32 +3179,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128087562</v>
+        <v>128087532</v>
       </c>
       <c r="B27" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3214,10 +3214,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544367</v>
+        <v>544491</v>
       </c>
       <c r="R27" t="n">
-        <v>6963253</v>
+        <v>6963099</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3250,11 +3250,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>7. Kan möjlitvis finnas fler runt omkring.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3281,49 +3276,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128078161</v>
+        <v>128087331</v>
       </c>
       <c r="B28" t="n">
-        <v>98571</v>
+        <v>57685</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544362</v>
+        <v>544763</v>
       </c>
       <c r="R28" t="n">
-        <v>6963061</v>
+        <v>6963244</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3356,6 +3347,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3382,49 +3378,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128078740</v>
+        <v>128087333</v>
       </c>
       <c r="B29" t="n">
-        <v>98571</v>
+        <v>57685</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544307</v>
+        <v>544355</v>
       </c>
       <c r="R29" t="n">
-        <v>6963089</v>
+        <v>6963212</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3457,6 +3449,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3483,7 +3480,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128087563</v>
+        <v>128087562</v>
       </c>
       <c r="B30" t="n">
         <v>98571</v>
@@ -3518,10 +3515,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>544322</v>
+        <v>544367</v>
       </c>
       <c r="R30" t="n">
-        <v>6963250</v>
+        <v>6963253</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3558,7 +3555,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>12 stycken</t>
+          <t>7. Kan möjlitvis finnas fler runt omkring.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3585,45 +3582,49 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128087532</v>
+        <v>128078161</v>
       </c>
       <c r="B31" t="n">
-        <v>80188</v>
+        <v>98571</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>544491</v>
+        <v>544362</v>
       </c>
       <c r="R31" t="n">
-        <v>6963099</v>
+        <v>6963061</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3682,45 +3683,49 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128087331</v>
+        <v>128078740</v>
       </c>
       <c r="B32" t="n">
-        <v>57685</v>
+        <v>98571</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544763</v>
+        <v>544307</v>
       </c>
       <c r="R32" t="n">
-        <v>6963244</v>
+        <v>6963089</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3753,11 +3758,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3784,32 +3784,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128087333</v>
+        <v>128087563</v>
       </c>
       <c r="B33" t="n">
-        <v>57685</v>
+        <v>98571</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>544355</v>
+        <v>544322</v>
       </c>
       <c r="R33" t="n">
-        <v>6963212</v>
+        <v>6963250</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3859,7 +3859,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>12 stycken</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4876,32 +4876,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128087552</v>
+        <v>128087361</v>
       </c>
       <c r="B44" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4911,10 +4911,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>544687</v>
+        <v>544865</v>
       </c>
       <c r="R44" t="n">
-        <v>6963255</v>
+        <v>6963092</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4947,11 +4947,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>70</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4978,32 +4973,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128087548</v>
+        <v>128087360</v>
       </c>
       <c r="B45" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5013,10 +5008,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>544213</v>
+        <v>544615</v>
       </c>
       <c r="R45" t="n">
-        <v>6963197</v>
+        <v>6963093</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5049,11 +5044,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>100stycken.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5080,32 +5070,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128087361</v>
+        <v>128087552</v>
       </c>
       <c r="B46" t="n">
-        <v>80188</v>
+        <v>98571</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5115,10 +5105,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>544865</v>
+        <v>544687</v>
       </c>
       <c r="R46" t="n">
-        <v>6963092</v>
+        <v>6963255</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5151,6 +5141,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>70</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5177,32 +5172,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128087360</v>
+        <v>128087548</v>
       </c>
       <c r="B47" t="n">
-        <v>80188</v>
+        <v>98571</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5212,10 +5207,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>544615</v>
+        <v>544213</v>
       </c>
       <c r="R47" t="n">
-        <v>6963093</v>
+        <v>6963197</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5248,6 +5243,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>100stycken.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5274,32 +5274,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128087340</v>
+        <v>128079768</v>
       </c>
       <c r="B48" t="n">
-        <v>57845</v>
+        <v>97454</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>221941</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5309,10 +5309,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>544485</v>
+        <v>544287</v>
       </c>
       <c r="R48" t="n">
-        <v>6963237</v>
+        <v>6963168</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5371,32 +5371,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128079768</v>
+        <v>128087340</v>
       </c>
       <c r="B49" t="n">
-        <v>97454</v>
+        <v>57845</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>544287</v>
+        <v>544485</v>
       </c>
       <c r="R49" t="n">
-        <v>6963168</v>
+        <v>6963237</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6162,10 +6162,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128087585</v>
+        <v>128087356</v>
       </c>
       <c r="B57" t="n">
-        <v>92742</v>
+        <v>80216</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6173,21 +6173,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>6461</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6197,10 +6197,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>544536</v>
+        <v>544772</v>
       </c>
       <c r="R57" t="n">
-        <v>6963255</v>
+        <v>6963323</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6233,11 +6233,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>8 äldre ex9 färska fruktkroppar</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6264,7 +6259,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128087356</v>
+        <v>128087357</v>
       </c>
       <c r="B58" t="n">
         <v>80216</v>
@@ -6299,10 +6294,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>544772</v>
+        <v>544466</v>
       </c>
       <c r="R58" t="n">
-        <v>6963323</v>
+        <v>6963277</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6361,45 +6356,50 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128087357</v>
+        <v>128080012</v>
       </c>
       <c r="B59" t="n">
-        <v>80216</v>
+        <v>57685</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>544466</v>
+        <v>544324</v>
       </c>
       <c r="R59" t="n">
-        <v>6963277</v>
+        <v>6963220</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6432,6 +6432,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6458,50 +6463,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128080012</v>
+        <v>128087585</v>
       </c>
       <c r="B60" t="n">
-        <v>57685</v>
+        <v>92742</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>544324</v>
+        <v>544536</v>
       </c>
       <c r="R60" t="n">
-        <v>6963220</v>
+        <v>6963255</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>8 äldre ex9 färska fruktkroppar</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6565,10 +6565,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128087525</v>
+        <v>128087386</v>
       </c>
       <c r="B61" t="n">
-        <v>56260</v>
+        <v>92736</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6576,21 +6576,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>206004</v>
+        <v>4362</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6600,10 +6600,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>544385</v>
+        <v>544822</v>
       </c>
       <c r="R61" t="n">
-        <v>6963074</v>
+        <v>6963295</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6662,32 +6662,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128087566</v>
+        <v>128087579</v>
       </c>
       <c r="B62" t="n">
-        <v>98571</v>
+        <v>79083</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6697,10 +6697,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>544261</v>
+        <v>544204</v>
       </c>
       <c r="R62" t="n">
-        <v>6963170</v>
+        <v>6963238</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6737,7 +6737,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>4. Stycken. Finns möjligtvis fler i blåbärsriset.</t>
+          <t>Riklig förekomst av garnlav</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6764,32 +6764,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128087377</v>
+        <v>128078603</v>
       </c>
       <c r="B63" t="n">
-        <v>98571</v>
+        <v>80217</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>544403</v>
+        <v>544360</v>
       </c>
       <c r="R63" t="n">
-        <v>6963221</v>
+        <v>6963094</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6835,11 +6835,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>20 ex</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6866,32 +6861,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128087378</v>
+        <v>128087523</v>
       </c>
       <c r="B64" t="n">
-        <v>98571</v>
+        <v>80217</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6901,10 +6896,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>544218</v>
+        <v>544253</v>
       </c>
       <c r="R64" t="n">
-        <v>6963229</v>
+        <v>6963139</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6937,11 +6932,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>80 ex</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6968,32 +6958,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128087375</v>
+        <v>128087329</v>
       </c>
       <c r="B65" t="n">
-        <v>98571</v>
+        <v>57685</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7003,10 +6993,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>544478</v>
+        <v>544757</v>
       </c>
       <c r="R65" t="n">
-        <v>6963117</v>
+        <v>6963172</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7043,7 +7033,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>35 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7070,10 +7060,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128087386</v>
+        <v>128087525</v>
       </c>
       <c r="B66" t="n">
-        <v>92736</v>
+        <v>56260</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7081,21 +7071,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4362</v>
+        <v>206004</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7105,10 +7095,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>544822</v>
+        <v>544385</v>
       </c>
       <c r="R66" t="n">
-        <v>6963295</v>
+        <v>6963074</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7167,32 +7157,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128078603</v>
+        <v>128087566</v>
       </c>
       <c r="B67" t="n">
-        <v>80217</v>
+        <v>98571</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7202,10 +7192,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>544360</v>
+        <v>544261</v>
       </c>
       <c r="R67" t="n">
-        <v>6963094</v>
+        <v>6963170</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7238,6 +7228,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>4. Stycken. Finns möjligtvis fler i blåbärsriset.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7264,32 +7259,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128087523</v>
+        <v>128087377</v>
       </c>
       <c r="B68" t="n">
-        <v>80217</v>
+        <v>98571</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7299,10 +7294,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>544253</v>
+        <v>544403</v>
       </c>
       <c r="R68" t="n">
-        <v>6963139</v>
+        <v>6963221</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7335,6 +7330,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7361,32 +7361,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128087579</v>
+        <v>128087378</v>
       </c>
       <c r="B69" t="n">
-        <v>79083</v>
+        <v>98571</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7396,10 +7396,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>544204</v>
+        <v>544218</v>
       </c>
       <c r="R69" t="n">
-        <v>6963238</v>
+        <v>6963229</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Riklig förekomst av garnlav</t>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7463,32 +7463,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128087329</v>
+        <v>128087375</v>
       </c>
       <c r="B70" t="n">
-        <v>57685</v>
+        <v>98571</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7498,10 +7498,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>544757</v>
+        <v>544478</v>
       </c>
       <c r="R70" t="n">
-        <v>6963172</v>
+        <v>6963117</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7565,10 +7565,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128087337</v>
+        <v>128087366</v>
       </c>
       <c r="B71" t="n">
-        <v>57685</v>
+        <v>80188</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7576,21 +7576,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7600,10 +7600,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>544197</v>
+        <v>544407</v>
       </c>
       <c r="R71" t="n">
-        <v>6963237</v>
+        <v>6963184</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7636,11 +7636,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7667,10 +7662,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128080035</v>
+        <v>128087537</v>
       </c>
       <c r="B72" t="n">
-        <v>57685</v>
+        <v>80188</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7678,39 +7673,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>544340</v>
+        <v>544205</v>
       </c>
       <c r="R72" t="n">
-        <v>6963223</v>
+        <v>6963241</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7743,11 +7733,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7774,7 +7759,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128080054</v>
+        <v>128087337</v>
       </c>
       <c r="B73" t="n">
         <v>57685</v>
@@ -7803,21 +7788,16 @@
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>544301</v>
+        <v>544197</v>
       </c>
       <c r="R73" t="n">
-        <v>6963231</v>
+        <v>6963237</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7854,7 +7834,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7881,7 +7861,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128080149</v>
+        <v>128080035</v>
       </c>
       <c r="B74" t="n">
         <v>57685</v>
@@ -7921,10 +7901,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>544295</v>
+        <v>544340</v>
       </c>
       <c r="R74" t="n">
-        <v>6963226</v>
+        <v>6963223</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7988,10 +7968,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128087366</v>
+        <v>128080054</v>
       </c>
       <c r="B75" t="n">
-        <v>80188</v>
+        <v>57685</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7999,34 +7979,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>544407</v>
+        <v>544301</v>
       </c>
       <c r="R75" t="n">
-        <v>6963184</v>
+        <v>6963231</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8059,6 +8044,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8085,10 +8075,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128087537</v>
+        <v>128080149</v>
       </c>
       <c r="B76" t="n">
-        <v>80188</v>
+        <v>57685</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8096,34 +8086,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>544205</v>
+        <v>544295</v>
       </c>
       <c r="R76" t="n">
-        <v>6963241</v>
+        <v>6963226</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8156,6 +8151,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8182,10 +8182,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128087575</v>
+        <v>128087536</v>
       </c>
       <c r="B77" t="n">
-        <v>92774</v>
+        <v>80188</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8193,21 +8193,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1968</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8217,10 +8217,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>544532</v>
+        <v>544215</v>
       </c>
       <c r="R77" t="n">
-        <v>6963250</v>
+        <v>6963245</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8253,11 +8253,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Igen stor köttig svamp misstänker grantaggsvamp 2 ex</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8284,32 +8279,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128078492</v>
+        <v>128087343</v>
       </c>
       <c r="B78" t="n">
-        <v>92774</v>
+        <v>80217</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1968</v>
+        <v>6462</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8319,10 +8314,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>544362</v>
+        <v>544757</v>
       </c>
       <c r="R78" t="n">
-        <v>6963073</v>
+        <v>6963156</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8381,32 +8376,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128087570</v>
+        <v>128087346</v>
       </c>
       <c r="B79" t="n">
-        <v>56867</v>
+        <v>80217</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>102612</v>
+        <v>6462</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8416,10 +8411,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>544287</v>
+        <v>544422</v>
       </c>
       <c r="R79" t="n">
-        <v>6963082</v>
+        <v>6963240</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8452,11 +8447,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8483,49 +8473,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128079875</v>
+        <v>128087570</v>
       </c>
       <c r="B80" t="n">
-        <v>98571</v>
+        <v>56867</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>544308</v>
+        <v>544287</v>
       </c>
       <c r="R80" t="n">
-        <v>6963175</v>
+        <v>6963082</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8558,6 +8544,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8584,32 +8575,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128087542</v>
+        <v>128087330</v>
       </c>
       <c r="B81" t="n">
-        <v>98571</v>
+        <v>57685</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8619,10 +8610,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>544752</v>
+        <v>544750</v>
       </c>
       <c r="R81" t="n">
-        <v>6963192</v>
+        <v>6963177</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8659,7 +8650,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>40 stycken</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8686,49 +8677,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128080338</v>
+        <v>128087335</v>
       </c>
       <c r="B82" t="n">
-        <v>98571</v>
+        <v>57685</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>544314</v>
+        <v>544366</v>
       </c>
       <c r="R82" t="n">
-        <v>6963248</v>
+        <v>6963181</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8761,6 +8748,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8787,32 +8779,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128087547</v>
+        <v>128087575</v>
       </c>
       <c r="B83" t="n">
-        <v>98571</v>
+        <v>92774</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>1968</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8822,10 +8814,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>544380</v>
+        <v>544532</v>
       </c>
       <c r="R83" t="n">
-        <v>6963236</v>
+        <v>6963250</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8862,7 +8854,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>33 stycken</t>
+          <t>Igen stor köttig svamp misstänker grantaggsvamp 2 ex</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8889,32 +8881,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128087380</v>
+        <v>128078492</v>
       </c>
       <c r="B84" t="n">
-        <v>105609</v>
+        <v>92774</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221144</v>
+        <v>1968</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8924,10 +8916,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>544468</v>
+        <v>544362</v>
       </c>
       <c r="R84" t="n">
-        <v>6963173</v>
+        <v>6963073</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8986,32 +8978,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128087560</v>
+        <v>128087380</v>
       </c>
       <c r="B85" t="n">
-        <v>98571</v>
+        <v>105609</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9021,10 +9013,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>544383</v>
+        <v>544468</v>
       </c>
       <c r="R85" t="n">
-        <v>6963236</v>
+        <v>6963173</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9057,11 +9049,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9088,45 +9075,49 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128087536</v>
+        <v>128079875</v>
       </c>
       <c r="B86" t="n">
-        <v>80188</v>
+        <v>98571</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>544215</v>
+        <v>544308</v>
       </c>
       <c r="R86" t="n">
-        <v>6963245</v>
+        <v>6963175</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9185,32 +9176,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128087343</v>
+        <v>128087542</v>
       </c>
       <c r="B87" t="n">
-        <v>80217</v>
+        <v>98571</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9220,10 +9211,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>544757</v>
+        <v>544752</v>
       </c>
       <c r="R87" t="n">
-        <v>6963156</v>
+        <v>6963192</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9256,6 +9247,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9282,45 +9278,49 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128087346</v>
+        <v>128080338</v>
       </c>
       <c r="B88" t="n">
-        <v>80217</v>
+        <v>98571</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>544422</v>
+        <v>544314</v>
       </c>
       <c r="R88" t="n">
-        <v>6963240</v>
+        <v>6963248</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9379,32 +9379,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128087330</v>
+        <v>128087547</v>
       </c>
       <c r="B89" t="n">
-        <v>57685</v>
+        <v>98571</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9414,10 +9414,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>544750</v>
+        <v>544380</v>
       </c>
       <c r="R89" t="n">
-        <v>6963177</v>
+        <v>6963236</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9454,7 +9454,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>33 stycken</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9481,32 +9481,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128087335</v>
+        <v>128087560</v>
       </c>
       <c r="B90" t="n">
-        <v>57685</v>
+        <v>98571</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9516,10 +9516,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>544366</v>
+        <v>544383</v>
       </c>
       <c r="R90" t="n">
-        <v>6963181</v>
+        <v>6963236</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9556,7 +9556,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9787,32 +9787,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128087587</v>
+        <v>128087539</v>
       </c>
       <c r="B93" t="n">
-        <v>92742</v>
+        <v>80188</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9822,10 +9822,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>544245</v>
+        <v>544254</v>
       </c>
       <c r="R93" t="n">
-        <v>6963255</v>
+        <v>6963139</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9858,11 +9858,6 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>4stycken</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9889,32 +9884,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128087539</v>
+        <v>128087341</v>
       </c>
       <c r="B94" t="n">
-        <v>80188</v>
+        <v>80217</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9924,10 +9919,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>544254</v>
+        <v>544615</v>
       </c>
       <c r="R94" t="n">
-        <v>6963139</v>
+        <v>6963101</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9986,10 +9981,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128087341</v>
+        <v>128087587</v>
       </c>
       <c r="B95" t="n">
-        <v>80217</v>
+        <v>92742</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9997,21 +9992,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10021,10 +10016,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>544615</v>
+        <v>544245</v>
       </c>
       <c r="R95" t="n">
-        <v>6963101</v>
+        <v>6963255</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10057,6 +10052,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>4stycken</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10083,10 +10083,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128087576</v>
+        <v>128087522</v>
       </c>
       <c r="B96" t="n">
-        <v>92774</v>
+        <v>57845</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10094,21 +10094,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1968</v>
+        <v>103021</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10118,10 +10118,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>544529</v>
+        <v>544494</v>
       </c>
       <c r="R96" t="n">
-        <v>6963245</v>
+        <v>6963243</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10154,11 +10154,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Misstänkt grantaggsvamp men med mörk tydlig ring i mitten.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10185,7 +10180,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128087572</v>
+        <v>128087576</v>
       </c>
       <c r="B97" t="n">
         <v>92774</v>
@@ -10220,7 +10215,7 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>544632</v>
+        <v>544529</v>
       </c>
       <c r="R97" t="n">
         <v>6963245</v>
@@ -10260,7 +10255,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>1 ex</t>
+          <t>Misstänkt grantaggsvamp men med mörk tydlig ring i mitten.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10287,32 +10282,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128087383</v>
+        <v>128087572</v>
       </c>
       <c r="B98" t="n">
-        <v>80223</v>
+        <v>92774</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6463</v>
+        <v>1968</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10322,10 +10317,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>544566</v>
+        <v>544632</v>
       </c>
       <c r="R98" t="n">
-        <v>6963076</v>
+        <v>6963245</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10358,6 +10353,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>1 ex</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10384,7 +10384,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128087384</v>
+        <v>128087383</v>
       </c>
       <c r="B99" t="n">
         <v>80223</v>
@@ -10419,10 +10419,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>544584</v>
+        <v>544566</v>
       </c>
       <c r="R99" t="n">
-        <v>6963261</v>
+        <v>6963076</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10481,32 +10481,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128087363</v>
+        <v>128087384</v>
       </c>
       <c r="B100" t="n">
-        <v>80188</v>
+        <v>80223</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10516,10 +10516,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>544818</v>
+        <v>544584</v>
       </c>
       <c r="R100" t="n">
-        <v>6963278</v>
+        <v>6963261</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10578,10 +10578,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128087522</v>
+        <v>128087363</v>
       </c>
       <c r="B101" t="n">
-        <v>57845</v>
+        <v>80188</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10589,21 +10589,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10613,10 +10613,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>544494</v>
+        <v>544818</v>
       </c>
       <c r="R101" t="n">
-        <v>6963243</v>
+        <v>6963278</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10675,32 +10675,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128087545</v>
+        <v>128078864</v>
       </c>
       <c r="B102" t="n">
-        <v>98571</v>
+        <v>105609</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10710,10 +10710,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>544633</v>
+        <v>544307</v>
       </c>
       <c r="R102" t="n">
-        <v>6963244</v>
+        <v>6963089</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10746,11 +10746,6 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10777,7 +10772,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128087567</v>
+        <v>128087545</v>
       </c>
       <c r="B103" t="n">
         <v>98571</v>
@@ -10812,10 +10807,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>544274</v>
+        <v>544633</v>
       </c>
       <c r="R103" t="n">
-        <v>6963090</v>
+        <v>6963244</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10852,7 +10847,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10879,32 +10874,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128087556</v>
+        <v>128087355</v>
       </c>
       <c r="B104" t="n">
-        <v>98571</v>
+        <v>97454</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10914,10 +10909,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>544594</v>
+        <v>544500</v>
       </c>
       <c r="R104" t="n">
-        <v>6963215</v>
+        <v>6963168</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10950,11 +10945,6 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>6 stycken. Kan finnas mer i omgivningen</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10981,7 +10971,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128087373</v>
+        <v>128087567</v>
       </c>
       <c r="B105" t="n">
         <v>98571</v>
@@ -11016,10 +11006,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>544469</v>
+        <v>544274</v>
       </c>
       <c r="R105" t="n">
-        <v>6963122</v>
+        <v>6963090</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11056,7 +11046,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>60 ex</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11083,32 +11073,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128078864</v>
+        <v>128087556</v>
       </c>
       <c r="B106" t="n">
-        <v>105609</v>
+        <v>98571</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11118,10 +11108,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>544307</v>
+        <v>544594</v>
       </c>
       <c r="R106" t="n">
-        <v>6963089</v>
+        <v>6963215</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11154,6 +11144,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>6 stycken. Kan finnas mer i omgivningen</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11180,7 +11175,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128087559</v>
+        <v>128087373</v>
       </c>
       <c r="B107" t="n">
         <v>98571</v>
@@ -11215,10 +11210,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>544396</v>
+        <v>544469</v>
       </c>
       <c r="R107" t="n">
-        <v>6963233</v>
+        <v>6963122</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11255,7 +11250,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>18 stycken</t>
+          <t>60 ex</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11282,32 +11277,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128087355</v>
+        <v>128087559</v>
       </c>
       <c r="B108" t="n">
-        <v>97454</v>
+        <v>98571</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11317,10 +11312,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>544500</v>
+        <v>544396</v>
       </c>
       <c r="R108" t="n">
-        <v>6963168</v>
+        <v>6963233</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11353,6 +11348,11 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11379,32 +11379,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128087586</v>
+        <v>128087577</v>
       </c>
       <c r="B109" t="n">
-        <v>92742</v>
+        <v>92774</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4364</v>
+        <v>1968</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11414,10 +11414,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>544281</v>
+        <v>544494</v>
       </c>
       <c r="R109" t="n">
-        <v>6963257</v>
+        <v>6963243</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11450,11 +11450,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>2 nya exemplar 8 äldre ex</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11481,32 +11476,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128087577</v>
+        <v>128087586</v>
       </c>
       <c r="B110" t="n">
-        <v>92774</v>
+        <v>92742</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1968</v>
+        <v>4364</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11516,10 +11511,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>544494</v>
+        <v>544281</v>
       </c>
       <c r="R110" t="n">
-        <v>6963243</v>
+        <v>6963257</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11552,6 +11547,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>2 nya exemplar 8 äldre ex</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11878,7 +11878,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128087372</v>
+        <v>128087551</v>
       </c>
       <c r="B114" t="n">
         <v>98571</v>
@@ -11913,10 +11913,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>544472</v>
+        <v>544694</v>
       </c>
       <c r="R114" t="n">
-        <v>6963201</v>
+        <v>6963258</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11953,7 +11953,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>8 ex</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11980,32 +11980,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128087551</v>
+        <v>128087531</v>
       </c>
       <c r="B115" t="n">
-        <v>98571</v>
+        <v>98605</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12015,10 +12015,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>544694</v>
+        <v>544755</v>
       </c>
       <c r="R115" t="n">
-        <v>6963258</v>
+        <v>6963130</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12055,7 +12055,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12082,32 +12082,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128087531</v>
+        <v>128087372</v>
       </c>
       <c r="B116" t="n">
-        <v>98605</v>
+        <v>98571</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12117,10 +12117,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>544755</v>
+        <v>544472</v>
       </c>
       <c r="R116" t="n">
-        <v>6963130</v>
+        <v>6963201</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12157,7 +12157,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>2 stycken</t>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12184,10 +12184,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128087538</v>
+        <v>128087571</v>
       </c>
       <c r="B117" t="n">
-        <v>80188</v>
+        <v>92774</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12195,21 +12195,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6458</v>
+        <v>1968</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12219,10 +12219,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>544262</v>
+        <v>544679</v>
       </c>
       <c r="R117" t="n">
-        <v>6963163</v>
+        <v>6963259</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12255,6 +12255,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Misstänker grantaggsvamp. 14 exemplar</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12281,32 +12286,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128087582</v>
+        <v>128087573</v>
       </c>
       <c r="B118" t="n">
-        <v>98488</v>
+        <v>92774</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>219790</v>
+        <v>1968</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12316,10 +12321,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>544489</v>
+        <v>544684</v>
       </c>
       <c r="R118" t="n">
-        <v>6963098</v>
+        <v>6963253</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12352,6 +12357,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Mörkt exemplar med vit yttre ring.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12378,10 +12388,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128087535</v>
+        <v>128078823</v>
       </c>
       <c r="B119" t="n">
-        <v>80188</v>
+        <v>79083</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12389,21 +12399,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12413,10 +12423,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>544312</v>
+        <v>544307</v>
       </c>
       <c r="R119" t="n">
-        <v>6963244</v>
+        <v>6963089</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12475,32 +12485,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128078823</v>
+        <v>128079848</v>
       </c>
       <c r="B120" t="n">
-        <v>79083</v>
+        <v>79107</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12510,10 +12520,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>544307</v>
+        <v>544288</v>
       </c>
       <c r="R120" t="n">
-        <v>6963089</v>
+        <v>6963182</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12572,10 +12582,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128087571</v>
+        <v>128087538</v>
       </c>
       <c r="B121" t="n">
-        <v>92774</v>
+        <v>80188</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12583,21 +12593,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1968</v>
+        <v>6458</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12607,10 +12617,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>544679</v>
+        <v>544262</v>
       </c>
       <c r="R121" t="n">
-        <v>6963259</v>
+        <v>6963163</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12643,11 +12653,6 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Misstänker grantaggsvamp. 14 exemplar</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12674,10 +12679,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128087573</v>
+        <v>128087535</v>
       </c>
       <c r="B122" t="n">
-        <v>92774</v>
+        <v>80188</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12685,21 +12690,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1968</v>
+        <v>6458</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12709,10 +12714,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>544684</v>
+        <v>544312</v>
       </c>
       <c r="R122" t="n">
-        <v>6963253</v>
+        <v>6963244</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12745,11 +12750,6 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Mörkt exemplar med vit yttre ring.</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12776,10 +12776,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128079848</v>
+        <v>128087582</v>
       </c>
       <c r="B123" t="n">
-        <v>79107</v>
+        <v>98488</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12787,21 +12787,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6434</v>
+        <v>219790</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12811,10 +12811,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>544288</v>
+        <v>544489</v>
       </c>
       <c r="R123" t="n">
-        <v>6963182</v>
+        <v>6963098</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13075,32 +13075,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128079484</v>
+        <v>128087574</v>
       </c>
       <c r="B126" t="n">
-        <v>80224</v>
+        <v>92774</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6464</v>
+        <v>1968</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13110,10 +13110,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>544289</v>
+        <v>544552</v>
       </c>
       <c r="R126" t="n">
-        <v>6963113</v>
+        <v>6963231</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13146,6 +13146,11 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Misstänker grantaggsvamp 1 exemplar</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13274,10 +13279,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128087584</v>
+        <v>128079484</v>
       </c>
       <c r="B128" t="n">
-        <v>98488</v>
+        <v>80224</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13285,21 +13290,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>219790</v>
+        <v>6464</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13309,10 +13314,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>544718</v>
+        <v>544289</v>
       </c>
       <c r="R128" t="n">
-        <v>6963053</v>
+        <v>6963113</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13345,11 +13350,6 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>3 stycken</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13478,32 +13478,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128087574</v>
+        <v>128087584</v>
       </c>
       <c r="B130" t="n">
-        <v>92774</v>
+        <v>98488</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1968</v>
+        <v>219790</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13513,10 +13513,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>544552</v>
+        <v>544718</v>
       </c>
       <c r="R130" t="n">
-        <v>6963231</v>
+        <v>6963053</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13553,7 +13553,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Misstänker grantaggsvamp 1 exemplar</t>
+          <t>3 stycken</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13784,32 +13784,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128078645</v>
+        <v>128087557</v>
       </c>
       <c r="B133" t="n">
-        <v>80188</v>
+        <v>98571</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13819,10 +13819,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>544360</v>
+        <v>544552</v>
       </c>
       <c r="R133" t="n">
-        <v>6963094</v>
+        <v>6963231</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13855,6 +13855,11 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -13881,32 +13886,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128087344</v>
+        <v>128087543</v>
       </c>
       <c r="B134" t="n">
-        <v>80217</v>
+        <v>98571</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13916,10 +13921,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>544581</v>
+        <v>544674</v>
       </c>
       <c r="R134" t="n">
-        <v>6963278</v>
+        <v>6963243</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13952,6 +13957,11 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -13978,7 +13988,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128087534</v>
+        <v>128078645</v>
       </c>
       <c r="B135" t="n">
         <v>80188</v>
@@ -14013,10 +14023,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>544326</v>
+        <v>544360</v>
       </c>
       <c r="R135" t="n">
-        <v>6963248</v>
+        <v>6963094</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14075,7 +14085,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128087345</v>
+        <v>128087344</v>
       </c>
       <c r="B136" t="n">
         <v>80217</v>
@@ -14110,10 +14120,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>544391</v>
+        <v>544581</v>
       </c>
       <c r="R136" t="n">
-        <v>6963205</v>
+        <v>6963278</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14172,7 +14182,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128087540</v>
+        <v>128087534</v>
       </c>
       <c r="B137" t="n">
         <v>80188</v>
@@ -14207,10 +14217,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>544282</v>
+        <v>544326</v>
       </c>
       <c r="R137" t="n">
-        <v>6963082</v>
+        <v>6963248</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14269,32 +14279,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128087557</v>
+        <v>128087345</v>
       </c>
       <c r="B138" t="n">
-        <v>98571</v>
+        <v>80217</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14304,10 +14314,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>544552</v>
+        <v>544391</v>
       </c>
       <c r="R138" t="n">
-        <v>6963231</v>
+        <v>6963205</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14340,11 +14350,6 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14371,32 +14376,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128087543</v>
+        <v>128087540</v>
       </c>
       <c r="B139" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14406,10 +14411,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>544674</v>
+        <v>544282</v>
       </c>
       <c r="R139" t="n">
-        <v>6963243</v>
+        <v>6963082</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14442,11 +14447,6 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14575,10 +14575,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128087381</v>
+        <v>128087530</v>
       </c>
       <c r="B141" t="n">
-        <v>98488</v>
+        <v>98605</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14586,21 +14586,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>219790</v>
+        <v>219874</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14610,10 +14610,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>544531</v>
+        <v>544737</v>
       </c>
       <c r="R141" t="n">
-        <v>6963190</v>
+        <v>6963047</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14672,10 +14672,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128087530</v>
+        <v>128087381</v>
       </c>
       <c r="B142" t="n">
-        <v>98605</v>
+        <v>98488</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14683,21 +14683,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14707,10 +14707,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>544737</v>
+        <v>544531</v>
       </c>
       <c r="R142" t="n">
-        <v>6963047</v>
+        <v>6963190</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15069,32 +15069,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128094035</v>
+        <v>128094046</v>
       </c>
       <c r="B146" t="n">
-        <v>57685</v>
+        <v>98571</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15104,10 +15104,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>544736</v>
+        <v>544754</v>
       </c>
       <c r="R146" t="n">
-        <v>6963232</v>
+        <v>6963261</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15144,7 +15144,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15171,32 +15171,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128094046</v>
+        <v>128094035</v>
       </c>
       <c r="B147" t="n">
-        <v>98571</v>
+        <v>57685</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15206,10 +15206,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>544754</v>
+        <v>544736</v>
       </c>
       <c r="R147" t="n">
-        <v>6963261</v>
+        <v>6963232</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15246,7 +15246,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>25 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16589,32 +16589,32 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128094047</v>
+        <v>128094054</v>
       </c>
       <c r="B161" t="n">
-        <v>98571</v>
+        <v>105609</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16624,10 +16624,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>544641</v>
+        <v>544321</v>
       </c>
       <c r="R161" t="n">
-        <v>6963158</v>
+        <v>6963319</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16660,11 +16660,6 @@
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>11 ex</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -16895,32 +16890,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128094054</v>
+        <v>128094047</v>
       </c>
       <c r="B164" t="n">
-        <v>105609</v>
+        <v>98571</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -16930,10 +16925,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>544321</v>
+        <v>544641</v>
       </c>
       <c r="R164" t="n">
-        <v>6963319</v>
+        <v>6963158</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -16966,6 +16961,11 @@
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD164" t="b">

--- a/artfynd/A 32240-2025 artfynd.xlsx
+++ b/artfynd/A 32240-2025 artfynd.xlsx
@@ -4376,32 +4376,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128087588</v>
+        <v>128087332</v>
       </c>
       <c r="B39" t="n">
-        <v>92742</v>
+        <v>57685</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>544183</v>
+        <v>544431</v>
       </c>
       <c r="R39" t="n">
-        <v>6963214</v>
+        <v>6963190</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>9 ex äldre exemplar</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4478,32 +4478,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128087527</v>
+        <v>128087517</v>
       </c>
       <c r="B40" t="n">
-        <v>80216</v>
+        <v>57685</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4513,10 +4513,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>544246</v>
+        <v>544381</v>
       </c>
       <c r="R40" t="n">
-        <v>6963259</v>
+        <v>6963236</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4549,6 +4549,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall Äldre ringhack som återanvänds ( äldre och färska)</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4575,10 +4580,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128087369</v>
+        <v>128087588</v>
       </c>
       <c r="B41" t="n">
-        <v>80224</v>
+        <v>92742</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4586,21 +4591,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4610,10 +4615,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>544721</v>
+        <v>544183</v>
       </c>
       <c r="R41" t="n">
-        <v>6963277</v>
+        <v>6963214</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4646,6 +4651,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>9 ex äldre exemplar</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4672,32 +4682,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128087332</v>
+        <v>128087527</v>
       </c>
       <c r="B42" t="n">
-        <v>57685</v>
+        <v>80216</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4707,10 +4717,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>544431</v>
+        <v>544246</v>
       </c>
       <c r="R42" t="n">
-        <v>6963190</v>
+        <v>6963259</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4743,11 +4753,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4774,32 +4779,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128087517</v>
+        <v>128087369</v>
       </c>
       <c r="B43" t="n">
-        <v>57685</v>
+        <v>80224</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4809,10 +4814,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>544381</v>
+        <v>544721</v>
       </c>
       <c r="R43" t="n">
-        <v>6963236</v>
+        <v>6963277</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4845,11 +4850,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall Äldre ringhack som återanvänds ( äldre och färska)</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5468,10 +5468,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128087342</v>
+        <v>128079839</v>
       </c>
       <c r="B50" t="n">
-        <v>80217</v>
+        <v>105609</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5479,21 +5479,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6462</v>
+        <v>221144</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5503,10 +5503,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>544848</v>
+        <v>544288</v>
       </c>
       <c r="R50" t="n">
-        <v>6963086</v>
+        <v>6963182</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5565,32 +5565,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128087367</v>
+        <v>128087553</v>
       </c>
       <c r="B51" t="n">
-        <v>80188</v>
+        <v>98571</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5600,10 +5600,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>544298</v>
+        <v>544677</v>
       </c>
       <c r="R51" t="n">
-        <v>6963312</v>
+        <v>6963260</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5636,6 +5636,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Mer än 70 stycken. Flera blommar</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5662,32 +5667,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128087364</v>
+        <v>128087555</v>
       </c>
       <c r="B52" t="n">
-        <v>80188</v>
+        <v>98571</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5697,10 +5702,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>544774</v>
+        <v>544623</v>
       </c>
       <c r="R52" t="n">
-        <v>6963282</v>
+        <v>6963241</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5733,6 +5738,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>60 stycken</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5861,10 +5871,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128079839</v>
+        <v>128087342</v>
       </c>
       <c r="B54" t="n">
-        <v>105609</v>
+        <v>80217</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5872,21 +5882,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221144</v>
+        <v>6462</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5896,10 +5906,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>544288</v>
+        <v>544848</v>
       </c>
       <c r="R54" t="n">
-        <v>6963182</v>
+        <v>6963086</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5958,32 +5968,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128087553</v>
+        <v>128087367</v>
       </c>
       <c r="B55" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5993,10 +6003,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>544677</v>
+        <v>544298</v>
       </c>
       <c r="R55" t="n">
-        <v>6963260</v>
+        <v>6963312</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6029,11 +6039,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Mer än 70 stycken. Flera blommar</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6060,32 +6065,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128087555</v>
+        <v>128087364</v>
       </c>
       <c r="B56" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6095,10 +6100,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>544623</v>
+        <v>544774</v>
       </c>
       <c r="R56" t="n">
-        <v>6963241</v>
+        <v>6963282</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6131,11 +6136,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>60 stycken</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7565,10 +7565,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128087366</v>
+        <v>128087337</v>
       </c>
       <c r="B71" t="n">
-        <v>80188</v>
+        <v>57685</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7576,21 +7576,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7600,10 +7600,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>544407</v>
+        <v>544197</v>
       </c>
       <c r="R71" t="n">
-        <v>6963184</v>
+        <v>6963237</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7636,6 +7636,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7662,10 +7667,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128087537</v>
+        <v>128080035</v>
       </c>
       <c r="B72" t="n">
-        <v>80188</v>
+        <v>57685</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7673,34 +7678,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>544205</v>
+        <v>544340</v>
       </c>
       <c r="R72" t="n">
-        <v>6963241</v>
+        <v>6963223</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7733,6 +7743,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7759,7 +7774,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128087337</v>
+        <v>128080054</v>
       </c>
       <c r="B73" t="n">
         <v>57685</v>
@@ -7788,16 +7803,21 @@
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>544197</v>
+        <v>544301</v>
       </c>
       <c r="R73" t="n">
-        <v>6963237</v>
+        <v>6963231</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7834,7 +7854,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7861,7 +7881,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128080035</v>
+        <v>128080149</v>
       </c>
       <c r="B74" t="n">
         <v>57685</v>
@@ -7901,10 +7921,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>544340</v>
+        <v>544295</v>
       </c>
       <c r="R74" t="n">
-        <v>6963223</v>
+        <v>6963226</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7968,10 +7988,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128080054</v>
+        <v>128087366</v>
       </c>
       <c r="B75" t="n">
-        <v>57685</v>
+        <v>80188</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7979,39 +7999,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>544301</v>
+        <v>544407</v>
       </c>
       <c r="R75" t="n">
-        <v>6963231</v>
+        <v>6963184</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8044,11 +8059,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8075,10 +8085,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128080149</v>
+        <v>128087537</v>
       </c>
       <c r="B76" t="n">
-        <v>57685</v>
+        <v>80188</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8086,39 +8096,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>544295</v>
+        <v>544205</v>
       </c>
       <c r="R76" t="n">
-        <v>6963226</v>
+        <v>6963241</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8151,11 +8156,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8182,10 +8182,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128087536</v>
+        <v>128087575</v>
       </c>
       <c r="B77" t="n">
-        <v>80188</v>
+        <v>92774</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8193,21 +8193,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>1968</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8217,10 +8217,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>544215</v>
+        <v>544532</v>
       </c>
       <c r="R77" t="n">
-        <v>6963245</v>
+        <v>6963250</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8253,6 +8253,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Igen stor köttig svamp misstänker grantaggsvamp 2 ex</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8279,32 +8284,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128087343</v>
+        <v>128078492</v>
       </c>
       <c r="B78" t="n">
-        <v>80217</v>
+        <v>92774</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6462</v>
+        <v>1968</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8314,10 +8319,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>544757</v>
+        <v>544362</v>
       </c>
       <c r="R78" t="n">
-        <v>6963156</v>
+        <v>6963073</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8376,32 +8381,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128087346</v>
+        <v>128087536</v>
       </c>
       <c r="B79" t="n">
-        <v>80217</v>
+        <v>80188</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8411,10 +8416,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>544422</v>
+        <v>544215</v>
       </c>
       <c r="R79" t="n">
-        <v>6963240</v>
+        <v>6963245</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8473,32 +8478,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128087570</v>
+        <v>128087343</v>
       </c>
       <c r="B80" t="n">
-        <v>56867</v>
+        <v>80217</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>102612</v>
+        <v>6462</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8508,10 +8513,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>544287</v>
+        <v>544757</v>
       </c>
       <c r="R80" t="n">
-        <v>6963082</v>
+        <v>6963156</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8544,11 +8549,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8575,32 +8575,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128087330</v>
+        <v>128087346</v>
       </c>
       <c r="B81" t="n">
-        <v>57685</v>
+        <v>80217</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8610,10 +8610,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>544750</v>
+        <v>544422</v>
       </c>
       <c r="R81" t="n">
-        <v>6963177</v>
+        <v>6963240</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8646,11 +8646,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8677,32 +8672,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128087335</v>
+        <v>128087380</v>
       </c>
       <c r="B82" t="n">
-        <v>57685</v>
+        <v>105609</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8712,10 +8707,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>544366</v>
+        <v>544468</v>
       </c>
       <c r="R82" t="n">
-        <v>6963181</v>
+        <v>6963173</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8748,11 +8743,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8779,45 +8769,49 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128087575</v>
+        <v>128079875</v>
       </c>
       <c r="B83" t="n">
-        <v>92774</v>
+        <v>98571</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1968</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>544532</v>
+        <v>544308</v>
       </c>
       <c r="R83" t="n">
-        <v>6963250</v>
+        <v>6963175</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8850,11 +8844,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Igen stor köttig svamp misstänker grantaggsvamp 2 ex</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8881,32 +8870,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128078492</v>
+        <v>128087542</v>
       </c>
       <c r="B84" t="n">
-        <v>92774</v>
+        <v>98571</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1968</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8916,10 +8905,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>544362</v>
+        <v>544752</v>
       </c>
       <c r="R84" t="n">
-        <v>6963073</v>
+        <v>6963192</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8952,6 +8941,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8978,45 +8972,49 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128087380</v>
+        <v>128080338</v>
       </c>
       <c r="B85" t="n">
-        <v>105609</v>
+        <v>98571</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>544468</v>
+        <v>544314</v>
       </c>
       <c r="R85" t="n">
-        <v>6963173</v>
+        <v>6963248</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9075,7 +9073,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128079875</v>
+        <v>128087547</v>
       </c>
       <c r="B86" t="n">
         <v>98571</v>
@@ -9103,21 +9101,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>544308</v>
+        <v>544380</v>
       </c>
       <c r="R86" t="n">
-        <v>6963175</v>
+        <v>6963236</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9150,6 +9144,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>33 stycken</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9176,7 +9175,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128087542</v>
+        <v>128087560</v>
       </c>
       <c r="B87" t="n">
         <v>98571</v>
@@ -9211,10 +9210,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>544752</v>
+        <v>544383</v>
       </c>
       <c r="R87" t="n">
-        <v>6963192</v>
+        <v>6963236</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9278,49 +9277,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128080338</v>
+        <v>128087570</v>
       </c>
       <c r="B88" t="n">
-        <v>98571</v>
+        <v>56867</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>544314</v>
+        <v>544287</v>
       </c>
       <c r="R88" t="n">
-        <v>6963248</v>
+        <v>6963082</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9353,6 +9348,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9379,32 +9379,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128087547</v>
+        <v>128087330</v>
       </c>
       <c r="B89" t="n">
-        <v>98571</v>
+        <v>57685</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9414,10 +9414,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>544380</v>
+        <v>544750</v>
       </c>
       <c r="R89" t="n">
-        <v>6963236</v>
+        <v>6963177</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9454,7 +9454,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>33 stycken</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9481,32 +9481,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128087560</v>
+        <v>128087335</v>
       </c>
       <c r="B90" t="n">
-        <v>98571</v>
+        <v>57685</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9516,10 +9516,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>544383</v>
+        <v>544366</v>
       </c>
       <c r="R90" t="n">
-        <v>6963236</v>
+        <v>6963181</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9556,7 +9556,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>40 stycken</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11578,32 +11578,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128087578</v>
+        <v>128087531</v>
       </c>
       <c r="B111" t="n">
-        <v>79083</v>
+        <v>98605</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>219874</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11613,10 +11613,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>544246</v>
+        <v>544755</v>
       </c>
       <c r="R111" t="n">
-        <v>6963257</v>
+        <v>6963130</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11649,6 +11649,11 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11675,49 +11680,45 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128079656</v>
+        <v>128087578</v>
       </c>
       <c r="B112" t="n">
-        <v>98571</v>
+        <v>79083</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>544277</v>
+        <v>544246</v>
       </c>
       <c r="R112" t="n">
-        <v>6963150</v>
+        <v>6963257</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11776,7 +11777,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128087565</v>
+        <v>128079656</v>
       </c>
       <c r="B113" t="n">
         <v>98571</v>
@@ -11804,17 +11805,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Västermyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>544249</v>
+        <v>544277</v>
       </c>
       <c r="R113" t="n">
-        <v>6963223</v>
+        <v>6963150</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11847,11 +11852,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>10. Kan möjlitvis finns mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11878,7 +11878,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128087551</v>
+        <v>128087565</v>
       </c>
       <c r="B114" t="n">
         <v>98571</v>
@@ -11913,10 +11913,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>544694</v>
+        <v>544249</v>
       </c>
       <c r="R114" t="n">
-        <v>6963258</v>
+        <v>6963223</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11953,7 +11953,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10. Kan möjlitvis finns mer i blåbärsriset</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11980,32 +11980,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128087531</v>
+        <v>128087372</v>
       </c>
       <c r="B115" t="n">
-        <v>98605</v>
+        <v>98571</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12015,10 +12015,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>544755</v>
+        <v>544472</v>
       </c>
       <c r="R115" t="n">
-        <v>6963130</v>
+        <v>6963201</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12055,7 +12055,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>2 stycken</t>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12082,7 +12082,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128087372</v>
+        <v>128087551</v>
       </c>
       <c r="B116" t="n">
         <v>98571</v>
@@ -12117,10 +12117,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>544472</v>
+        <v>544694</v>
       </c>
       <c r="R116" t="n">
-        <v>6963201</v>
+        <v>6963258</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12157,7 +12157,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>8 ex</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13177,32 +13177,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128087334</v>
+        <v>128079484</v>
       </c>
       <c r="B127" t="n">
-        <v>57685</v>
+        <v>80224</v>
       </c>
       <c r="D127" t="inlineStr">
   